--- a/src/inventory/War.xlsx
+++ b/src/inventory/War.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="604">
   <si>
     <t>Code/SKU</t>
   </si>
@@ -833,10 +833,10 @@
     <t>৳550.00</t>
   </si>
   <si>
-    <t>৳3,850.00</t>
-  </si>
-  <si>
-    <t>৳5,880.00</t>
+    <t>৳3,300.00</t>
+  </si>
+  <si>
+    <t>৳5,040.00</t>
   </si>
   <si>
     <t>109-0104-001</t>
@@ -938,6 +938,9 @@
     <t>Drop Shoulder T-Shirt 05</t>
   </si>
   <si>
+    <t>৳1,580.00</t>
+  </si>
+  <si>
     <t>109-0102-074</t>
   </si>
   <si>
@@ -1034,9 +1037,6 @@
     <t>M</t>
   </si>
   <si>
-    <t>৳3,300.00</t>
-  </si>
-  <si>
     <t>৳4,740.00</t>
   </si>
   <si>
@@ -1145,7 +1145,7 @@
     <t>Men / T-SHIRT,Drop Shoulder</t>
   </si>
   <si>
-    <t>৳3,360.00</t>
+    <t>৳2,520.00</t>
   </si>
   <si>
     <t>৳840.00</t>
@@ -1163,9 +1163,6 @@
     <t>Deep Violet Drop Shoulder T-Shirt</t>
   </si>
   <si>
-    <t>৳1,580.00</t>
-  </si>
-  <si>
     <t>109-0501-001</t>
   </si>
   <si>
@@ -1217,6 +1214,18 @@
     <t>105-0301-001</t>
   </si>
   <si>
+    <t>102-0302-006</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 006</t>
+  </si>
+  <si>
+    <t>৳1,950.00</t>
+  </si>
+  <si>
+    <t>৳3,975.00</t>
+  </si>
+  <si>
     <t>103-0200-098</t>
   </si>
   <si>
@@ -1283,18 +1292,6 @@
     <t>৳1,299.00</t>
   </si>
   <si>
-    <t>102-0302-006</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 006</t>
-  </si>
-  <si>
-    <t>৳1,950.00</t>
-  </si>
-  <si>
-    <t>৳3,975.00</t>
-  </si>
-  <si>
     <t>102-0301-002</t>
   </si>
   <si>
@@ -1349,6 +1346,9 @@
     <t>Cuban Shirt 001</t>
   </si>
   <si>
+    <t>৳1,300.00</t>
+  </si>
+  <si>
     <t>109-0101-049</t>
   </si>
   <si>
@@ -1373,9 +1373,6 @@
     <t>৳1,770.00</t>
   </si>
   <si>
-    <t>৳1,300.00</t>
-  </si>
-  <si>
     <t>৳278.57</t>
   </si>
   <si>
@@ -1475,6 +1472,15 @@
     <t>Men / NEW IN,NEW,MEN,ACCESSORIES,WALLET,LONG</t>
   </si>
   <si>
+    <t>105-0101-372</t>
+  </si>
+  <si>
+    <t>Deep Harbor T-shirt</t>
+  </si>
+  <si>
+    <t>৳3,200.00</t>
+  </si>
+  <si>
     <t>৳1,325.00</t>
   </si>
   <si>
@@ -1496,6 +1502,12 @@
     <t>Cuban Shier 003</t>
   </si>
   <si>
+    <t>105-0101-376</t>
+  </si>
+  <si>
+    <t>City Slate T-shirt</t>
+  </si>
+  <si>
     <t>105-0101-380</t>
   </si>
   <si>
@@ -1520,15 +1532,6 @@
     <t>৳4,760.00</t>
   </si>
   <si>
-    <t>105-0101-372</t>
-  </si>
-  <si>
-    <t>Deep Harbor T-shirt</t>
-  </si>
-  <si>
-    <t>৳3,200.00</t>
-  </si>
-  <si>
     <t>105-0101-371</t>
   </si>
   <si>
@@ -1610,15 +1613,15 @@
     <t>Full Sleeve Mustard StripeT-shirt</t>
   </si>
   <si>
-    <t>105-0101-376</t>
-  </si>
-  <si>
-    <t>City Slate T-shirt</t>
-  </si>
-  <si>
     <t>৳6,360.00</t>
   </si>
   <si>
+    <t>105-0101-379</t>
+  </si>
+  <si>
+    <t>Essential White T-shirt</t>
+  </si>
+  <si>
     <t>102-0301-009</t>
   </si>
   <si>
@@ -1629,12 +1632,6 @@
   </si>
   <si>
     <t>Full Sleeve White Stripe T-shirt</t>
-  </si>
-  <si>
-    <t>105-0101-379</t>
-  </si>
-  <si>
-    <t>Essential White T-shirt</t>
   </si>
   <si>
     <t>৳525.00</t>
@@ -4684,7 +4681,7 @@
         <v>270</v>
       </c>
       <c r="F98">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G98" t="s">
         <v>271</v>
@@ -4964,27 +4961,27 @@
         <v>270</v>
       </c>
       <c r="F109">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G109" t="s">
         <v>271</v>
       </c>
       <c r="H109" t="s">
-        <v>285</v>
+        <v>199</v>
       </c>
       <c r="I109" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B110" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E110" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F110">
         <v>3.0</v>
@@ -4993,18 +4990,18 @@
         <v>226</v>
       </c>
       <c r="H110" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I110" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B111" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E111" t="s">
         <v>197</v>
@@ -5024,10 +5021,10 @@
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B112" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E112" t="s">
         <v>197</v>
@@ -5062,10 +5059,10 @@
         <v>1.0</v>
       </c>
       <c r="G113" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H113" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I113" t="s">
         <v>264</v>
@@ -5099,10 +5096,10 @@
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B115" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E115" t="s">
         <v>225</v>
@@ -5122,10 +5119,10 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B116" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E116" t="s">
         <v>225</v>
@@ -5140,7 +5137,7 @@
         <v>276</v>
       </c>
       <c r="I116" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -5160,10 +5157,10 @@
         <v>3.0</v>
       </c>
       <c r="G117" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H117" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I117" t="s">
         <v>179</v>
@@ -5171,10 +5168,10 @@
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B118" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E118" t="s">
         <v>225</v>
@@ -5194,10 +5191,10 @@
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B119" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E119" t="s">
         <v>197</v>
@@ -5206,13 +5203,13 @@
         <v>4.0</v>
       </c>
       <c r="G119" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H119" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I119" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -5223,7 +5220,7 @@
         <v>304</v>
       </c>
       <c r="C120" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E120" t="s">
         <v>298</v>
@@ -5243,13 +5240,13 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B121" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E121" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F121">
         <v>1.0</v>
@@ -5261,15 +5258,15 @@
         <v>226</v>
       </c>
       <c r="I121" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B122" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E122" t="s">
         <v>197</v>
@@ -5284,7 +5281,7 @@
         <v>72</v>
       </c>
       <c r="I122" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -5295,7 +5292,7 @@
         <v>283</v>
       </c>
       <c r="C123" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E123" t="s">
         <v>270</v>
@@ -5307,7 +5304,7 @@
         <v>271</v>
       </c>
       <c r="H123" t="s">
-        <v>339</v>
+        <v>272</v>
       </c>
       <c r="I123" t="s">
         <v>340</v>
@@ -5382,7 +5379,7 @@
         <v>72</v>
       </c>
       <c r="I126" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -5393,7 +5390,7 @@
         <v>352</v>
       </c>
       <c r="E127" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F127">
         <v>3.0</v>
@@ -5402,10 +5399,10 @@
         <v>226</v>
       </c>
       <c r="H127" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I127" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -5465,7 +5462,7 @@
         <v>283</v>
       </c>
       <c r="C130" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E130" t="s">
         <v>270</v>
@@ -5491,7 +5488,7 @@
         <v>306</v>
       </c>
       <c r="C131" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E131" t="s">
         <v>270</v>
@@ -5575,13 +5572,13 @@
         <v>375</v>
       </c>
       <c r="F134">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G134" t="s">
         <v>276</v>
       </c>
       <c r="H134" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="I134" t="s">
         <v>376</v>
@@ -5633,7 +5630,7 @@
         <v>227</v>
       </c>
       <c r="I136" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -5659,7 +5656,7 @@
         <v>277</v>
       </c>
       <c r="I137" t="s">
-        <v>382</v>
+        <v>307</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -5670,7 +5667,7 @@
         <v>296</v>
       </c>
       <c r="C138" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E138" t="s">
         <v>298</v>
@@ -5685,7 +5682,7 @@
         <v>277</v>
       </c>
       <c r="I138" t="s">
-        <v>382</v>
+        <v>307</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -5696,7 +5693,7 @@
         <v>381</v>
       </c>
       <c r="C139" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E139" t="s">
         <v>298</v>
@@ -5737,30 +5734,30 @@
         <v>277</v>
       </c>
       <c r="I140" t="s">
-        <v>382</v>
+        <v>307</v>
       </c>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" t="s">
+        <v>382</v>
+      </c>
+      <c r="B141" t="s">
         <v>383</v>
       </c>
-      <c r="B141" t="s">
+      <c r="E141" t="s">
         <v>384</v>
-      </c>
-      <c r="E141" t="s">
-        <v>385</v>
       </c>
       <c r="F141">
         <v>9.0</v>
       </c>
       <c r="G141" t="s">
+        <v>385</v>
+      </c>
+      <c r="H141" t="s">
         <v>386</v>
       </c>
-      <c r="H141" t="s">
+      <c r="I141" t="s">
         <v>387</v>
-      </c>
-      <c r="I141" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -5812,7 +5809,7 @@
         <v>72</v>
       </c>
       <c r="I143" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -5832,24 +5829,24 @@
         <v>4.0</v>
       </c>
       <c r="G144" t="s">
+        <v>389</v>
+      </c>
+      <c r="H144" t="s">
         <v>390</v>
       </c>
-      <c r="H144" t="s">
+      <c r="I144" t="s">
         <v>391</v>
-      </c>
-      <c r="I144" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" t="s">
+        <v>392</v>
+      </c>
+      <c r="B145" t="s">
         <v>393</v>
       </c>
-      <c r="B145" t="s">
+      <c r="E145" t="s">
         <v>394</v>
-      </c>
-      <c r="E145" t="s">
-        <v>395</v>
       </c>
       <c r="F145">
         <v>1.0</v>
@@ -5861,18 +5858,18 @@
         <v>276</v>
       </c>
       <c r="I145" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" t="s">
+        <v>396</v>
+      </c>
+      <c r="B146" t="s">
         <v>397</v>
       </c>
-      <c r="B146" t="s">
-        <v>398</v>
-      </c>
       <c r="E146" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F146">
         <v>1.0</v>
@@ -5884,18 +5881,18 @@
         <v>276</v>
       </c>
       <c r="I146" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B147" t="s">
         <v>268</v>
       </c>
       <c r="C147" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E147" t="s">
         <v>270</v>
@@ -5921,7 +5918,7 @@
         <v>381</v>
       </c>
       <c r="C148" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E148" t="s">
         <v>298</v>
@@ -5936,177 +5933,177 @@
         <v>280</v>
       </c>
       <c r="I148" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" t="s">
+        <v>399</v>
+      </c>
+      <c r="B149" t="s">
         <v>400</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" t="s">
+        <v>269</v>
+      </c>
+      <c r="E149" t="s">
+        <v>358</v>
+      </c>
+      <c r="F149">
+        <v>3.0</v>
+      </c>
+      <c r="G149" t="s">
+        <v>359</v>
+      </c>
+      <c r="H149" t="s">
         <v>401</v>
       </c>
-      <c r="C149" t="s">
-        <v>164</v>
-      </c>
-      <c r="E149" t="s">
-        <v>116</v>
-      </c>
-      <c r="F149">
-        <v>1.0</v>
-      </c>
-      <c r="G149" t="s">
-        <v>72</v>
-      </c>
-      <c r="H149" t="s">
-        <v>72</v>
-      </c>
       <c r="I149" t="s">
-        <v>294</v>
+        <v>402</v>
       </c>
     </row>
     <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>295</v>
+        <v>403</v>
       </c>
       <c r="B150" t="s">
-        <v>296</v>
+        <v>404</v>
       </c>
       <c r="C150" t="s">
-        <v>331</v>
+        <v>164</v>
       </c>
       <c r="E150" t="s">
-        <v>298</v>
+        <v>116</v>
       </c>
       <c r="F150">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G150" t="s">
-        <v>276</v>
+        <v>72</v>
       </c>
       <c r="H150" t="s">
-        <v>302</v>
+        <v>72</v>
       </c>
       <c r="I150" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>402</v>
+        <v>295</v>
       </c>
       <c r="B151" t="s">
-        <v>403</v>
+        <v>296</v>
       </c>
       <c r="C151" t="s">
-        <v>269</v>
+        <v>332</v>
       </c>
       <c r="E151" t="s">
-        <v>404</v>
+        <v>298</v>
       </c>
       <c r="F151">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G151" t="s">
-        <v>405</v>
+        <v>276</v>
       </c>
       <c r="H151" t="s">
-        <v>406</v>
+        <v>302</v>
       </c>
       <c r="I151" t="s">
-        <v>407</v>
+        <v>286</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="B152" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="C152" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="E152" t="s">
-        <v>358</v>
+        <v>407</v>
       </c>
       <c r="F152">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G152" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="H152" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="I152" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>247</v>
+        <v>368</v>
       </c>
       <c r="B153" t="s">
-        <v>248</v>
+        <v>369</v>
       </c>
       <c r="C153" t="s">
-        <v>164</v>
+        <v>284</v>
       </c>
       <c r="E153" t="s">
-        <v>238</v>
+        <v>358</v>
       </c>
       <c r="F153">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G153" t="s">
-        <v>409</v>
+        <v>370</v>
       </c>
       <c r="H153" t="s">
         <v>409</v>
       </c>
       <c r="I153" t="s">
-        <v>264</v>
+        <v>411</v>
       </c>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>410</v>
+        <v>247</v>
       </c>
       <c r="B154" t="s">
-        <v>411</v>
+        <v>248</v>
       </c>
       <c r="C154" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="E154" t="s">
+        <v>238</v>
+      </c>
+      <c r="F154">
+        <v>1.0</v>
+      </c>
+      <c r="G154" t="s">
         <v>412</v>
       </c>
-      <c r="F154">
-        <v>1.0</v>
-      </c>
-      <c r="G154" t="s">
-        <v>72</v>
-      </c>
       <c r="H154" t="s">
-        <v>72</v>
+        <v>412</v>
       </c>
       <c r="I154" t="s">
-        <v>187</v>
+        <v>264</v>
       </c>
     </row>
     <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>292</v>
+        <v>413</v>
       </c>
       <c r="B155" t="s">
-        <v>293</v>
+        <v>414</v>
       </c>
       <c r="C155" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="E155" t="s">
-        <v>116</v>
+        <v>415</v>
       </c>
       <c r="F155">
         <v>1.0</v>
@@ -6118,90 +6115,90 @@
         <v>72</v>
       </c>
       <c r="I155" t="s">
-        <v>294</v>
+        <v>187</v>
       </c>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>413</v>
+        <v>292</v>
       </c>
       <c r="B156" t="s">
-        <v>414</v>
+        <v>293</v>
       </c>
       <c r="C156" t="s">
-        <v>269</v>
+        <v>115</v>
       </c>
       <c r="E156" t="s">
-        <v>358</v>
+        <v>116</v>
       </c>
       <c r="F156">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G156" t="s">
-        <v>415</v>
+        <v>72</v>
       </c>
       <c r="H156" t="s">
-        <v>416</v>
+        <v>72</v>
       </c>
       <c r="I156" t="s">
-        <v>417</v>
+        <v>294</v>
       </c>
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
+        <v>416</v>
+      </c>
+      <c r="B157" t="s">
+        <v>417</v>
+      </c>
+      <c r="C157" t="s">
+        <v>269</v>
+      </c>
+      <c r="E157" t="s">
+        <v>358</v>
+      </c>
+      <c r="F157">
+        <v>5.0</v>
+      </c>
+      <c r="G157" t="s">
         <v>418</v>
       </c>
-      <c r="B157" t="s">
+      <c r="H157" t="s">
         <v>419</v>
       </c>
-      <c r="E157" t="s">
+      <c r="I157" t="s">
         <v>420</v>
-      </c>
-      <c r="F157">
-        <v>1.0</v>
-      </c>
-      <c r="G157" t="s">
-        <v>72</v>
-      </c>
-      <c r="H157" t="s">
-        <v>72</v>
-      </c>
-      <c r="I157" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
+        <v>421</v>
+      </c>
+      <c r="B158" t="s">
         <v>422</v>
       </c>
-      <c r="B158" t="s">
+      <c r="E158" t="s">
         <v>423</v>
       </c>
-      <c r="C158" t="s">
-        <v>269</v>
-      </c>
-      <c r="E158" t="s">
-        <v>358</v>
-      </c>
       <c r="F158">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G158" t="s">
-        <v>359</v>
+        <v>72</v>
       </c>
       <c r="H158" t="s">
+        <v>72</v>
+      </c>
+      <c r="I158" t="s">
         <v>424</v>
-      </c>
-      <c r="I158" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:9">
       <c r="A159" t="s">
+        <v>425</v>
+      </c>
+      <c r="B159" t="s">
         <v>426</v>
-      </c>
-      <c r="B159" t="s">
-        <v>427</v>
       </c>
       <c r="C159" t="s">
         <v>269</v>
@@ -6216,18 +6213,18 @@
         <v>359</v>
       </c>
       <c r="H159" t="s">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="I159" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
     </row>
     <row r="160" spans="1:9">
       <c r="A160" t="s">
+        <v>427</v>
+      </c>
+      <c r="B160" t="s">
         <v>428</v>
-      </c>
-      <c r="B160" t="s">
-        <v>429</v>
       </c>
       <c r="C160" t="s">
         <v>269</v>
@@ -6239,91 +6236,91 @@
         <v>6.0</v>
       </c>
       <c r="G160" t="s">
+        <v>429</v>
+      </c>
+      <c r="H160" t="s">
+        <v>401</v>
+      </c>
+      <c r="I160" t="s">
         <v>430</v>
-      </c>
-      <c r="H160" t="s">
-        <v>424</v>
-      </c>
-      <c r="I160" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
+        <v>431</v>
+      </c>
+      <c r="B161" t="s">
         <v>432</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C161" t="s">
+        <v>339</v>
+      </c>
+      <c r="E161" t="s">
         <v>433</v>
-      </c>
-      <c r="C161" t="s">
-        <v>338</v>
-      </c>
-      <c r="E161" t="s">
-        <v>434</v>
       </c>
       <c r="F161">
         <v>8.0</v>
       </c>
       <c r="G161" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H161" t="s">
         <v>371</v>
       </c>
       <c r="I161" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="162" spans="1:9">
       <c r="A162" t="s">
+        <v>435</v>
+      </c>
+      <c r="B162" t="s">
         <v>436</v>
       </c>
-      <c r="B162" t="s">
-        <v>437</v>
-      </c>
       <c r="C162" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E162" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F162">
         <v>3.0</v>
       </c>
       <c r="G162" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H162" t="s">
+        <v>437</v>
+      </c>
+      <c r="I162" t="s">
         <v>438</v>
-      </c>
-      <c r="I162" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" t="s">
+        <v>435</v>
+      </c>
+      <c r="B163" t="s">
         <v>436</v>
-      </c>
-      <c r="B163" t="s">
-        <v>437</v>
       </c>
       <c r="C163" t="s">
         <v>284</v>
       </c>
       <c r="E163" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F163">
         <v>5.0</v>
       </c>
       <c r="G163" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H163" t="s">
         <v>45</v>
       </c>
       <c r="I163" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -6334,7 +6331,7 @@
         <v>369</v>
       </c>
       <c r="C164" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E164" t="s">
         <v>358</v>
@@ -6346,10 +6343,10 @@
         <v>370</v>
       </c>
       <c r="H164" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="I164" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -6360,7 +6357,7 @@
         <v>357</v>
       </c>
       <c r="C165" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E165" t="s">
         <v>358</v>
@@ -6372,18 +6369,18 @@
         <v>359</v>
       </c>
       <c r="H165" t="s">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="I165" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
+        <v>441</v>
+      </c>
+      <c r="B166" t="s">
         <v>442</v>
-      </c>
-      <c r="B166" t="s">
-        <v>443</v>
       </c>
       <c r="C166" t="s">
         <v>269</v>
@@ -6395,24 +6392,24 @@
         <v>5.0</v>
       </c>
       <c r="G166" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="H166" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="I166" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" t="s">
-        <v>368</v>
+        <v>399</v>
       </c>
       <c r="B167" t="s">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="C167" t="s">
-        <v>331</v>
+        <v>284</v>
       </c>
       <c r="E167" t="s">
         <v>358</v>
@@ -6421,226 +6418,226 @@
         <v>2.0</v>
       </c>
       <c r="G167" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="H167" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="I167" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>444</v>
+        <v>368</v>
       </c>
       <c r="B168" t="s">
-        <v>445</v>
+        <v>369</v>
+      </c>
+      <c r="C168" t="s">
+        <v>332</v>
       </c>
       <c r="E168" t="s">
-        <v>420</v>
+        <v>358</v>
       </c>
       <c r="F168">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G168" t="s">
-        <v>72</v>
+        <v>370</v>
       </c>
       <c r="H168" t="s">
-        <v>72</v>
+        <v>409</v>
       </c>
       <c r="I168" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B169" t="s">
-        <v>437</v>
-      </c>
-      <c r="C169" t="s">
-        <v>269</v>
+        <v>445</v>
       </c>
       <c r="E169" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="F169">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G169" t="s">
-        <v>405</v>
+        <v>72</v>
       </c>
       <c r="H169" t="s">
-        <v>370</v>
+        <v>72</v>
       </c>
       <c r="I169" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C170" t="s">
         <v>269</v>
       </c>
       <c r="E170" t="s">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="F170">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G170" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H170" t="s">
-        <v>447</v>
+        <v>370</v>
       </c>
       <c r="I170" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="B171" t="s">
-        <v>403</v>
+        <v>432</v>
       </c>
       <c r="C171" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="E171" t="s">
-        <v>404</v>
+        <v>433</v>
       </c>
       <c r="F171">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
       <c r="G171" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H171" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="I171" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B172" t="s">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="C172" t="s">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="E172" t="s">
-        <v>404</v>
+        <v>358</v>
       </c>
       <c r="F172">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G172" t="s">
-        <v>405</v>
+        <v>359</v>
       </c>
       <c r="H172" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="I172" t="s">
-        <v>451</v>
+        <v>411</v>
       </c>
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>432</v>
+        <v>405</v>
       </c>
       <c r="B173" t="s">
-        <v>433</v>
+        <v>406</v>
       </c>
       <c r="C173" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="E173" t="s">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="F173">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G173" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H173" t="s">
-        <v>370</v>
+        <v>437</v>
       </c>
       <c r="I173" t="s">
-        <v>254</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="B174" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="C174" t="s">
-        <v>338</v>
+        <v>284</v>
       </c>
       <c r="E174" t="s">
-        <v>358</v>
+        <v>407</v>
       </c>
       <c r="F174">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G174" t="s">
-        <v>359</v>
+        <v>408</v>
       </c>
       <c r="H174" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="I174" t="s">
-        <v>408</v>
+        <v>451</v>
       </c>
     </row>
     <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="B175" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C175" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="E175" t="s">
-        <v>358</v>
+        <v>433</v>
       </c>
       <c r="F175">
         <v>2.0</v>
       </c>
       <c r="G175" t="s">
-        <v>359</v>
+        <v>408</v>
       </c>
       <c r="H175" t="s">
-        <v>452</v>
+        <v>370</v>
       </c>
       <c r="I175" t="s">
-        <v>408</v>
+        <v>254</v>
       </c>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
+        <v>425</v>
+      </c>
+      <c r="B176" t="s">
         <v>426</v>
-      </c>
-      <c r="B176" t="s">
-        <v>427</v>
       </c>
       <c r="C176" t="s">
         <v>284</v>
@@ -6655,18 +6652,18 @@
         <v>359</v>
       </c>
       <c r="H176" t="s">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="I176" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
     </row>
     <row r="177" spans="1:9">
       <c r="A177" t="s">
+        <v>427</v>
+      </c>
+      <c r="B177" t="s">
         <v>428</v>
-      </c>
-      <c r="B177" t="s">
-        <v>429</v>
       </c>
       <c r="C177" t="s">
         <v>284</v>
@@ -6678,21 +6675,21 @@
         <v>7.0</v>
       </c>
       <c r="G177" t="s">
+        <v>452</v>
+      </c>
+      <c r="H177" t="s">
+        <v>401</v>
+      </c>
+      <c r="I177" t="s">
         <v>453</v>
-      </c>
-      <c r="H177" t="s">
-        <v>424</v>
-      </c>
-      <c r="I177" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="178" spans="1:9">
       <c r="A178" t="s">
+        <v>441</v>
+      </c>
+      <c r="B178" t="s">
         <v>442</v>
-      </c>
-      <c r="B178" t="s">
-        <v>443</v>
       </c>
       <c r="C178" t="s">
         <v>284</v>
@@ -6710,67 +6707,67 @@
         <v>285</v>
       </c>
       <c r="I178" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="179" spans="1:9">
       <c r="A179" t="s">
+        <v>431</v>
+      </c>
+      <c r="B179" t="s">
         <v>432</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C179" t="s">
+        <v>332</v>
+      </c>
+      <c r="E179" t="s">
         <v>433</v>
-      </c>
-      <c r="C179" t="s">
-        <v>331</v>
-      </c>
-      <c r="E179" t="s">
-        <v>434</v>
       </c>
       <c r="F179">
         <v>4.0</v>
       </c>
       <c r="G179" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H179" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="I179" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="180" spans="1:9">
       <c r="A180" t="s">
+        <v>456</v>
+      </c>
+      <c r="B180" t="s">
         <v>457</v>
-      </c>
-      <c r="B180" t="s">
-        <v>458</v>
       </c>
       <c r="C180" t="s">
         <v>284</v>
       </c>
       <c r="E180" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F180">
         <v>1.0</v>
       </c>
       <c r="G180" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H180" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I180" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="181" spans="1:9">
       <c r="A181" t="s">
+        <v>459</v>
+      </c>
+      <c r="B181" t="s">
         <v>460</v>
-      </c>
-      <c r="B181" t="s">
-        <v>461</v>
       </c>
       <c r="C181" t="s">
         <v>115</v>
@@ -6793,25 +6790,25 @@
     </row>
     <row r="182" spans="1:9">
       <c r="A182" t="s">
+        <v>461</v>
+      </c>
+      <c r="B182" t="s">
         <v>462</v>
       </c>
-      <c r="B182" t="s">
-        <v>463</v>
-      </c>
       <c r="C182" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E182" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F182">
         <v>1.0</v>
       </c>
       <c r="G182" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H182" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I182" t="s">
         <v>250</v>
@@ -6819,22 +6816,22 @@
     </row>
     <row r="183" spans="1:9">
       <c r="A183" t="s">
+        <v>435</v>
+      </c>
+      <c r="B183" t="s">
         <v>436</v>
       </c>
-      <c r="B183" t="s">
-        <v>437</v>
-      </c>
       <c r="C183" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E183" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F183">
         <v>2.0</v>
       </c>
       <c r="G183" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H183" t="s">
         <v>370</v>
@@ -6845,10 +6842,10 @@
     </row>
     <row r="184" spans="1:9">
       <c r="A184" t="s">
+        <v>463</v>
+      </c>
+      <c r="B184" t="s">
         <v>464</v>
-      </c>
-      <c r="B184" t="s">
-        <v>465</v>
       </c>
       <c r="C184" t="s">
         <v>269</v>
@@ -6866,18 +6863,18 @@
         <v>285</v>
       </c>
       <c r="I184" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>466</v>
+        <v>399</v>
       </c>
       <c r="B185" t="s">
-        <v>467</v>
+        <v>400</v>
       </c>
       <c r="C185" t="s">
-        <v>269</v>
+        <v>332</v>
       </c>
       <c r="E185" t="s">
         <v>358</v>
@@ -6886,21 +6883,21 @@
         <v>2.0</v>
       </c>
       <c r="G185" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="H185" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="I185" t="s">
-        <v>468</v>
+        <v>411</v>
       </c>
     </row>
     <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B186" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C186" t="s">
         <v>269</v>
@@ -6915,21 +6912,21 @@
         <v>370</v>
       </c>
       <c r="H186" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="I186" t="s">
-        <v>408</v>
+        <v>467</v>
       </c>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>413</v>
+        <v>468</v>
       </c>
       <c r="B187" t="s">
-        <v>414</v>
+        <v>469</v>
       </c>
       <c r="C187" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="E187" t="s">
         <v>358</v>
@@ -6941,177 +6938,177 @@
         <v>370</v>
       </c>
       <c r="H187" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="I187" t="s">
-        <v>468</v>
+        <v>411</v>
       </c>
     </row>
     <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>471</v>
+        <v>416</v>
       </c>
       <c r="B188" t="s">
-        <v>472</v>
+        <v>417</v>
       </c>
       <c r="C188" t="s">
         <v>284</v>
       </c>
       <c r="E188" t="s">
-        <v>404</v>
+        <v>358</v>
       </c>
       <c r="F188">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G188" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
       <c r="H188" t="s">
-        <v>280</v>
+        <v>409</v>
       </c>
       <c r="I188" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
     </row>
     <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B189" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C189" t="s">
-        <v>115</v>
+        <v>284</v>
       </c>
       <c r="E189" t="s">
-        <v>475</v>
+        <v>407</v>
       </c>
       <c r="F189">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G189" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="H189" t="s">
-        <v>72</v>
+        <v>280</v>
       </c>
       <c r="I189" t="s">
-        <v>321</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>402</v>
+        <v>472</v>
       </c>
       <c r="B190" t="s">
-        <v>403</v>
+        <v>473</v>
       </c>
       <c r="C190" t="s">
-        <v>331</v>
+        <v>115</v>
       </c>
       <c r="E190" t="s">
-        <v>404</v>
+        <v>474</v>
       </c>
       <c r="F190">
         <v>1.0</v>
       </c>
       <c r="G190" t="s">
-        <v>405</v>
+        <v>72</v>
       </c>
       <c r="H190" t="s">
-        <v>405</v>
+        <v>72</v>
       </c>
       <c r="I190" t="s">
-        <v>459</v>
+        <v>322</v>
       </c>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>464</v>
+        <v>405</v>
       </c>
       <c r="B191" t="s">
-        <v>465</v>
+        <v>406</v>
       </c>
       <c r="C191" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="E191" t="s">
-        <v>358</v>
+        <v>407</v>
       </c>
       <c r="F191">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G191" t="s">
-        <v>476</v>
+        <v>408</v>
       </c>
       <c r="H191" t="s">
-        <v>477</v>
+        <v>408</v>
       </c>
       <c r="I191" t="s">
-        <v>478</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="B192" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="C192" t="s">
-        <v>164</v>
+        <v>284</v>
       </c>
       <c r="E192" t="s">
-        <v>481</v>
+        <v>358</v>
       </c>
       <c r="F192">
         <v>2.0</v>
       </c>
       <c r="G192" t="s">
-        <v>72</v>
+        <v>475</v>
       </c>
       <c r="H192" t="s">
-        <v>72</v>
+        <v>476</v>
       </c>
       <c r="I192" t="s">
-        <v>264</v>
+        <v>477</v>
       </c>
     </row>
     <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>422</v>
+        <v>478</v>
       </c>
       <c r="B193" t="s">
-        <v>423</v>
+        <v>479</v>
       </c>
       <c r="C193" t="s">
-        <v>331</v>
+        <v>164</v>
       </c>
       <c r="E193" t="s">
-        <v>358</v>
+        <v>480</v>
       </c>
       <c r="F193">
         <v>2.0</v>
       </c>
       <c r="G193" t="s">
-        <v>359</v>
+        <v>72</v>
       </c>
       <c r="H193" t="s">
-        <v>452</v>
+        <v>72</v>
       </c>
       <c r="I193" t="s">
-        <v>408</v>
+        <v>264</v>
       </c>
     </row>
     <row r="194" spans="1:9">
       <c r="A194" t="s">
+        <v>427</v>
+      </c>
+      <c r="B194" t="s">
         <v>428</v>
       </c>
-      <c r="B194" t="s">
-        <v>429</v>
-      </c>
       <c r="C194" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E194" t="s">
         <v>358</v>
@@ -7131,16 +7128,16 @@
     </row>
     <row r="195" spans="1:9">
       <c r="A195" t="s">
+        <v>470</v>
+      </c>
+      <c r="B195" t="s">
         <v>471</v>
       </c>
-      <c r="B195" t="s">
-        <v>472</v>
-      </c>
       <c r="C195" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E195" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F195">
         <v>3.0</v>
@@ -7152,18 +7149,18 @@
         <v>302</v>
       </c>
       <c r="I195" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="196" spans="1:9">
       <c r="A196" t="s">
+        <v>441</v>
+      </c>
+      <c r="B196" t="s">
         <v>442</v>
       </c>
-      <c r="B196" t="s">
-        <v>443</v>
-      </c>
       <c r="C196" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E196" t="s">
         <v>358</v>
@@ -7175,21 +7172,21 @@
         <v>370</v>
       </c>
       <c r="H196" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="I196" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" t="s">
+        <v>441</v>
+      </c>
+      <c r="B197" t="s">
         <v>442</v>
       </c>
-      <c r="B197" t="s">
-        <v>443</v>
-      </c>
       <c r="C197" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E197" t="s">
         <v>358</v>
@@ -7201,22 +7198,22 @@
         <v>370</v>
       </c>
       <c r="H197" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="I197" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="198" spans="1:9">
       <c r="A198" t="s">
+        <v>482</v>
+      </c>
+      <c r="B198" t="s">
         <v>483</v>
       </c>
-      <c r="B198" t="s">
+      <c r="E198" t="s">
         <v>484</v>
       </c>
-      <c r="E198" t="s">
-        <v>485</v>
-      </c>
       <c r="F198">
         <v>1.0</v>
       </c>
@@ -7227,319 +7224,319 @@
         <v>72</v>
       </c>
       <c r="I198" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="B199" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="C199" t="s">
-        <v>338</v>
+        <v>152</v>
       </c>
       <c r="E199" t="s">
-        <v>434</v>
+        <v>474</v>
       </c>
       <c r="F199">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G199" t="s">
-        <v>405</v>
+        <v>301</v>
       </c>
       <c r="H199" t="s">
-        <v>405</v>
+        <v>302</v>
       </c>
       <c r="I199" t="s">
-        <v>250</v>
+        <v>487</v>
       </c>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="B200" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="C200" t="s">
-        <v>152</v>
+        <v>339</v>
       </c>
       <c r="E200" t="s">
-        <v>475</v>
+        <v>433</v>
       </c>
       <c r="F200">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G200" t="s">
-        <v>72</v>
+        <v>408</v>
       </c>
       <c r="H200" t="s">
-        <v>72</v>
+        <v>408</v>
       </c>
       <c r="I200" t="s">
-        <v>478</v>
+        <v>250</v>
       </c>
     </row>
     <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>368</v>
+        <v>472</v>
       </c>
       <c r="B201" t="s">
-        <v>369</v>
+        <v>473</v>
       </c>
       <c r="C201" t="s">
-        <v>297</v>
+        <v>152</v>
       </c>
       <c r="E201" t="s">
-        <v>358</v>
+        <v>474</v>
       </c>
       <c r="F201">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G201" t="s">
-        <v>370</v>
+        <v>72</v>
       </c>
       <c r="H201" t="s">
-        <v>370</v>
+        <v>72</v>
       </c>
       <c r="I201" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
     </row>
     <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>457</v>
+        <v>368</v>
       </c>
       <c r="B202" t="s">
-        <v>458</v>
+        <v>369</v>
       </c>
       <c r="C202" t="s">
         <v>297</v>
       </c>
       <c r="E202" t="s">
-        <v>404</v>
+        <v>358</v>
       </c>
       <c r="F202">
         <v>1.0</v>
       </c>
       <c r="G202" t="s">
-        <v>405</v>
+        <v>370</v>
       </c>
       <c r="H202" t="s">
-        <v>405</v>
+        <v>370</v>
       </c>
       <c r="I202" t="s">
-        <v>459</v>
+        <v>488</v>
       </c>
     </row>
     <row r="203" spans="1:9">
       <c r="A203" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="B203" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="C203" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="E203" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F203">
         <v>1.0</v>
       </c>
       <c r="G203" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H203" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I203" t="s">
-        <v>321</v>
+        <v>458</v>
       </c>
     </row>
     <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="B204" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="C204" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="E204" t="s">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="F204">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G204" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H204" t="s">
-        <v>487</v>
+        <v>408</v>
       </c>
       <c r="I204" t="s">
-        <v>488</v>
+        <v>322</v>
       </c>
     </row>
     <row r="205" spans="1:9">
       <c r="A205" t="s">
-        <v>469</v>
+        <v>431</v>
       </c>
       <c r="B205" t="s">
-        <v>470</v>
+        <v>432</v>
       </c>
       <c r="C205" t="s">
-        <v>338</v>
+        <v>284</v>
       </c>
       <c r="E205" t="s">
-        <v>358</v>
+        <v>433</v>
       </c>
       <c r="F205">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G205" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="H205" t="s">
-        <v>370</v>
+        <v>489</v>
       </c>
       <c r="I205" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="206" spans="1:9">
       <c r="A206" t="s">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="B206" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
       <c r="C206" t="s">
-        <v>144</v>
+        <v>339</v>
       </c>
       <c r="E206" t="s">
-        <v>238</v>
+        <v>358</v>
       </c>
       <c r="F206">
         <v>1.0</v>
       </c>
       <c r="G206" t="s">
-        <v>72</v>
+        <v>370</v>
       </c>
       <c r="H206" t="s">
-        <v>72</v>
+        <v>370</v>
       </c>
       <c r="I206" t="s">
-        <v>264</v>
+        <v>488</v>
       </c>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="B207" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="C207" t="s">
-        <v>338</v>
+        <v>144</v>
       </c>
       <c r="E207" t="s">
-        <v>404</v>
+        <v>238</v>
       </c>
       <c r="F207">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G207" t="s">
-        <v>276</v>
+        <v>72</v>
       </c>
       <c r="H207" t="s">
-        <v>277</v>
+        <v>72</v>
       </c>
       <c r="I207" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
     </row>
     <row r="208" spans="1:9">
       <c r="A208" t="s">
-        <v>426</v>
+        <v>470</v>
       </c>
       <c r="B208" t="s">
-        <v>427</v>
+        <v>471</v>
       </c>
       <c r="C208" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="E208" t="s">
-        <v>358</v>
+        <v>407</v>
       </c>
       <c r="F208">
         <v>1.0</v>
       </c>
       <c r="G208" t="s">
-        <v>359</v>
+        <v>276</v>
       </c>
       <c r="H208" t="s">
-        <v>359</v>
+        <v>276</v>
       </c>
       <c r="I208" t="s">
-        <v>486</v>
+        <v>250</v>
       </c>
     </row>
     <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B209" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C209" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E209" t="s">
         <v>358</v>
       </c>
       <c r="F209">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G209" t="s">
-        <v>430</v>
+        <v>359</v>
       </c>
       <c r="H209" t="s">
-        <v>452</v>
+        <v>359</v>
       </c>
       <c r="I209" t="s">
-        <v>361</v>
+        <v>488</v>
       </c>
     </row>
     <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>491</v>
+        <v>427</v>
       </c>
       <c r="B210" t="s">
-        <v>492</v>
+        <v>428</v>
       </c>
       <c r="C210" t="s">
-        <v>269</v>
+        <v>332</v>
       </c>
       <c r="E210" t="s">
         <v>358</v>
       </c>
       <c r="F210">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G210" t="s">
-        <v>359</v>
+        <v>429</v>
       </c>
       <c r="H210" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="I210" t="s">
-        <v>468</v>
+        <v>361</v>
       </c>
     </row>
     <row r="211" spans="1:9">
@@ -7550,39 +7547,39 @@
         <v>494</v>
       </c>
       <c r="C211" t="s">
-        <v>152</v>
+        <v>269</v>
       </c>
       <c r="E211" t="s">
-        <v>475</v>
+        <v>358</v>
       </c>
       <c r="F211">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G211" t="s">
-        <v>495</v>
+        <v>359</v>
       </c>
       <c r="H211" t="s">
-        <v>496</v>
+        <v>443</v>
       </c>
       <c r="I211" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
     </row>
     <row r="212" spans="1:9">
       <c r="A212" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B212" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C212" t="s">
-        <v>331</v>
+        <v>152</v>
       </c>
       <c r="E212" t="s">
-        <v>499</v>
+        <v>474</v>
       </c>
       <c r="F212">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G212" t="s">
         <v>72</v>
@@ -7591,212 +7588,212 @@
         <v>72</v>
       </c>
       <c r="I212" t="s">
-        <v>500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B213" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C213" t="s">
         <v>152</v>
       </c>
       <c r="E213" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F213">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G213" t="s">
-        <v>301</v>
+        <v>499</v>
       </c>
       <c r="H213" t="s">
-        <v>302</v>
+        <v>500</v>
       </c>
       <c r="I213" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
     </row>
     <row r="214" spans="1:9">
       <c r="A214" t="s">
+        <v>501</v>
+      </c>
+      <c r="B214" t="s">
+        <v>502</v>
+      </c>
+      <c r="C214" t="s">
+        <v>332</v>
+      </c>
+      <c r="E214" t="s">
+        <v>503</v>
+      </c>
+      <c r="F214">
+        <v>4.0</v>
+      </c>
+      <c r="G214" t="s">
+        <v>72</v>
+      </c>
+      <c r="H214" t="s">
+        <v>72</v>
+      </c>
+      <c r="I214" t="s">
         <v>504</v>
-      </c>
-      <c r="B214" t="s">
-        <v>505</v>
-      </c>
-      <c r="C214" t="s">
-        <v>164</v>
-      </c>
-      <c r="E214" t="s">
-        <v>475</v>
-      </c>
-      <c r="F214">
-        <v>6.0</v>
-      </c>
-      <c r="G214" t="s">
-        <v>506</v>
-      </c>
-      <c r="H214" t="s">
-        <v>302</v>
-      </c>
-      <c r="I214" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="215" spans="1:9">
       <c r="A215" t="s">
+        <v>505</v>
+      </c>
+      <c r="B215" t="s">
+        <v>506</v>
+      </c>
+      <c r="C215" t="s">
+        <v>164</v>
+      </c>
+      <c r="E215" t="s">
+        <v>474</v>
+      </c>
+      <c r="F215">
+        <v>6.0</v>
+      </c>
+      <c r="G215" t="s">
         <v>507</v>
       </c>
-      <c r="B215" t="s">
-        <v>508</v>
-      </c>
-      <c r="C215" t="s">
-        <v>152</v>
-      </c>
-      <c r="E215" t="s">
-        <v>475</v>
-      </c>
-      <c r="F215">
-        <v>4.0</v>
-      </c>
-      <c r="G215" t="s">
-        <v>72</v>
-      </c>
       <c r="H215" t="s">
-        <v>72</v>
+        <v>302</v>
       </c>
       <c r="I215" t="s">
-        <v>478</v>
+        <v>440</v>
       </c>
     </row>
     <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>436</v>
+        <v>508</v>
       </c>
       <c r="B216" t="s">
-        <v>437</v>
+        <v>509</v>
       </c>
       <c r="C216" t="s">
-        <v>297</v>
+        <v>152</v>
       </c>
       <c r="E216" t="s">
-        <v>404</v>
+        <v>474</v>
       </c>
       <c r="F216">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G216" t="s">
-        <v>405</v>
+        <v>72</v>
       </c>
       <c r="H216" t="s">
-        <v>405</v>
+        <v>72</v>
       </c>
       <c r="I216" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
     </row>
     <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>509</v>
+        <v>435</v>
       </c>
       <c r="B217" t="s">
-        <v>510</v>
+        <v>436</v>
       </c>
       <c r="C217" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="E217" t="s">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="F217">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G217" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H217" t="s">
-        <v>438</v>
+        <v>408</v>
       </c>
       <c r="I217" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
     </row>
     <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>426</v>
+        <v>510</v>
       </c>
       <c r="B218" t="s">
-        <v>427</v>
+        <v>511</v>
       </c>
       <c r="C218" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E218" t="s">
-        <v>358</v>
+        <v>433</v>
       </c>
       <c r="F218">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G218" t="s">
-        <v>359</v>
+        <v>408</v>
       </c>
       <c r="H218" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="I218" t="s">
-        <v>408</v>
+        <v>438</v>
       </c>
     </row>
     <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>511</v>
+        <v>425</v>
       </c>
       <c r="B219" t="s">
-        <v>512</v>
+        <v>426</v>
       </c>
       <c r="C219" t="s">
-        <v>269</v>
+        <v>339</v>
       </c>
       <c r="E219" t="s">
         <v>358</v>
       </c>
       <c r="F219">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G219" t="s">
-        <v>513</v>
+        <v>359</v>
       </c>
       <c r="H219" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="I219" t="s">
-        <v>514</v>
+        <v>411</v>
       </c>
     </row>
     <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>413</v>
+        <v>512</v>
       </c>
       <c r="B220" t="s">
-        <v>414</v>
+        <v>513</v>
       </c>
       <c r="C220" t="s">
-        <v>338</v>
+        <v>269</v>
       </c>
       <c r="E220" t="s">
         <v>358</v>
       </c>
       <c r="F220">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G220" t="s">
-        <v>370</v>
+        <v>514</v>
       </c>
       <c r="H220" t="s">
-        <v>370</v>
+        <v>443</v>
       </c>
       <c r="I220" t="s">
         <v>515</v>
@@ -7804,273 +7801,273 @@
     </row>
     <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>347</v>
+        <v>416</v>
       </c>
       <c r="B221" t="s">
-        <v>348</v>
+        <v>417</v>
       </c>
       <c r="C221" t="s">
-        <v>115</v>
+        <v>339</v>
       </c>
       <c r="E221" t="s">
-        <v>244</v>
+        <v>358</v>
       </c>
       <c r="F221">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G221" t="s">
-        <v>72</v>
+        <v>370</v>
       </c>
       <c r="H221" t="s">
-        <v>72</v>
+        <v>370</v>
       </c>
       <c r="I221" t="s">
-        <v>251</v>
+        <v>516</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>509</v>
+        <v>347</v>
       </c>
       <c r="B222" t="s">
-        <v>510</v>
+        <v>348</v>
       </c>
       <c r="C222" t="s">
-        <v>284</v>
+        <v>115</v>
       </c>
       <c r="E222" t="s">
-        <v>434</v>
+        <v>244</v>
       </c>
       <c r="F222">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G222" t="s">
-        <v>405</v>
+        <v>72</v>
       </c>
       <c r="H222" t="s">
-        <v>438</v>
+        <v>72</v>
       </c>
       <c r="I222" t="s">
-        <v>439</v>
+        <v>251</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="A223" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B223" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="C223" t="s">
-        <v>152</v>
+        <v>284</v>
       </c>
       <c r="E223" t="s">
-        <v>475</v>
+        <v>433</v>
       </c>
       <c r="F223">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G223" t="s">
-        <v>495</v>
+        <v>408</v>
       </c>
       <c r="H223" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="I223" t="s">
-        <v>478</v>
+        <v>438</v>
       </c>
     </row>
     <row r="224" spans="1:9">
       <c r="A224" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B224" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C224" t="s">
-        <v>269</v>
+        <v>152</v>
       </c>
       <c r="E224" t="s">
-        <v>434</v>
+        <v>474</v>
       </c>
       <c r="F224">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G224" t="s">
-        <v>405</v>
+        <v>499</v>
       </c>
       <c r="H224" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="I224" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
     </row>
     <row r="225" spans="1:9">
       <c r="A225" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="B225" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="C225" t="s">
-        <v>115</v>
+        <v>269</v>
       </c>
       <c r="E225" t="s">
-        <v>475</v>
+        <v>433</v>
       </c>
       <c r="F225">
         <v>1.0</v>
       </c>
       <c r="G225" t="s">
-        <v>72</v>
+        <v>408</v>
       </c>
       <c r="H225" t="s">
-        <v>72</v>
+        <v>408</v>
       </c>
       <c r="I225" t="s">
-        <v>250</v>
+        <v>458</v>
       </c>
     </row>
     <row r="226" spans="1:9">
       <c r="A226" t="s">
-        <v>356</v>
+        <v>485</v>
       </c>
       <c r="B226" t="s">
-        <v>357</v>
+        <v>486</v>
       </c>
       <c r="C226" t="s">
-        <v>297</v>
+        <v>115</v>
       </c>
       <c r="E226" t="s">
-        <v>358</v>
+        <v>474</v>
       </c>
       <c r="F226">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G226" t="s">
-        <v>359</v>
+        <v>72</v>
       </c>
       <c r="H226" t="s">
-        <v>452</v>
+        <v>72</v>
       </c>
       <c r="I226" t="s">
-        <v>478</v>
+        <v>250</v>
       </c>
     </row>
     <row r="227" spans="1:9">
       <c r="A227" t="s">
-        <v>464</v>
+        <v>356</v>
       </c>
       <c r="B227" t="s">
-        <v>465</v>
+        <v>357</v>
       </c>
       <c r="C227" t="s">
-        <v>331</v>
+        <v>297</v>
       </c>
       <c r="E227" t="s">
         <v>358</v>
       </c>
       <c r="F227">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G227" t="s">
         <v>359</v>
       </c>
       <c r="H227" t="s">
-        <v>359</v>
+        <v>443</v>
       </c>
       <c r="I227" t="s">
-        <v>278</v>
+        <v>477</v>
       </c>
     </row>
     <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>518</v>
+        <v>463</v>
       </c>
       <c r="B228" t="s">
-        <v>519</v>
+        <v>464</v>
       </c>
       <c r="C228" t="s">
-        <v>269</v>
+        <v>332</v>
       </c>
       <c r="E228" t="s">
-        <v>434</v>
+        <v>358</v>
       </c>
       <c r="F228">
         <v>1.0</v>
       </c>
       <c r="G228" t="s">
-        <v>520</v>
+        <v>359</v>
       </c>
       <c r="H228" t="s">
-        <v>520</v>
+        <v>359</v>
       </c>
       <c r="I228" t="s">
-        <v>321</v>
+        <v>278</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="B229" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="C229" t="s">
-        <v>152</v>
+        <v>269</v>
       </c>
       <c r="E229" t="s">
-        <v>475</v>
+        <v>433</v>
       </c>
       <c r="F229">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G229" t="s">
-        <v>72</v>
+        <v>521</v>
       </c>
       <c r="H229" t="s">
-        <v>72</v>
+        <v>521</v>
       </c>
       <c r="I229" t="s">
-        <v>451</v>
+        <v>322</v>
       </c>
     </row>
     <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>413</v>
+        <v>505</v>
       </c>
       <c r="B230" t="s">
-        <v>414</v>
+        <v>506</v>
       </c>
       <c r="C230" t="s">
-        <v>331</v>
+        <v>152</v>
       </c>
       <c r="E230" t="s">
-        <v>358</v>
+        <v>474</v>
       </c>
       <c r="F230">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G230" t="s">
-        <v>370</v>
+        <v>72</v>
       </c>
       <c r="H230" t="s">
-        <v>370</v>
+        <v>72</v>
       </c>
       <c r="I230" t="s">
-        <v>515</v>
+        <v>451</v>
       </c>
     </row>
     <row r="231" spans="1:9">
       <c r="A231" t="s">
-        <v>466</v>
+        <v>416</v>
       </c>
       <c r="B231" t="s">
-        <v>467</v>
+        <v>417</v>
       </c>
       <c r="C231" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="E231" t="s">
         <v>358</v>
@@ -8085,15 +8082,15 @@
         <v>370</v>
       </c>
       <c r="I231" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B232" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C232" t="s">
         <v>284</v>
@@ -8111,134 +8108,134 @@
         <v>370</v>
       </c>
       <c r="I232" t="s">
-        <v>486</v>
+        <v>516</v>
       </c>
     </row>
     <row r="233" spans="1:9">
       <c r="A233" t="s">
-        <v>521</v>
+        <v>468</v>
       </c>
       <c r="B233" t="s">
-        <v>522</v>
+        <v>469</v>
       </c>
       <c r="C233" t="s">
-        <v>128</v>
+        <v>284</v>
       </c>
       <c r="E233" t="s">
-        <v>244</v>
+        <v>358</v>
       </c>
       <c r="F233">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G233" t="s">
-        <v>72</v>
+        <v>370</v>
       </c>
       <c r="H233" t="s">
-        <v>72</v>
+        <v>370</v>
       </c>
       <c r="I233" t="s">
-        <v>389</v>
+        <v>488</v>
       </c>
     </row>
     <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>493</v>
+        <v>522</v>
       </c>
       <c r="B234" t="s">
-        <v>494</v>
+        <v>523</v>
       </c>
       <c r="C234" t="s">
         <v>128</v>
       </c>
       <c r="E234" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="F234">
         <v>3.0</v>
       </c>
       <c r="G234" t="s">
-        <v>523</v>
+        <v>72</v>
       </c>
       <c r="H234" t="s">
-        <v>524</v>
+        <v>72</v>
       </c>
       <c r="I234" t="s">
-        <v>482</v>
+        <v>388</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>464</v>
+        <v>497</v>
       </c>
       <c r="B235" t="s">
-        <v>465</v>
+        <v>498</v>
       </c>
       <c r="C235" t="s">
-        <v>338</v>
+        <v>128</v>
       </c>
       <c r="E235" t="s">
-        <v>358</v>
+        <v>474</v>
       </c>
       <c r="F235">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G235" t="s">
-        <v>359</v>
+        <v>524</v>
       </c>
       <c r="H235" t="s">
-        <v>452</v>
+        <v>525</v>
       </c>
       <c r="I235" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>525</v>
+        <v>463</v>
       </c>
       <c r="B236" t="s">
-        <v>526</v>
+        <v>464</v>
       </c>
       <c r="C236" t="s">
-        <v>269</v>
+        <v>339</v>
       </c>
       <c r="E236" t="s">
         <v>358</v>
       </c>
       <c r="F236">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G236" t="s">
         <v>359</v>
       </c>
       <c r="H236" t="s">
-        <v>359</v>
+        <v>443</v>
       </c>
       <c r="I236" t="s">
-        <v>527</v>
+        <v>477</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="B237" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="C237" t="s">
-        <v>128</v>
+        <v>269</v>
       </c>
       <c r="E237" t="s">
-        <v>475</v>
+        <v>358</v>
       </c>
       <c r="F237">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G237" t="s">
-        <v>72</v>
+        <v>359</v>
       </c>
       <c r="H237" t="s">
-        <v>72</v>
+        <v>359</v>
       </c>
       <c r="I237" t="s">
         <v>528</v>
@@ -8246,19 +8243,19 @@
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="B238" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="C238" t="s">
         <v>128</v>
       </c>
       <c r="E238" t="s">
-        <v>244</v>
+        <v>474</v>
       </c>
       <c r="F238">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G238" t="s">
         <v>72</v>
@@ -8267,24 +8264,24 @@
         <v>72</v>
       </c>
       <c r="I238" t="s">
-        <v>389</v>
+        <v>529</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
+        <v>530</v>
+      </c>
+      <c r="B239" t="s">
         <v>531</v>
       </c>
-      <c r="B239" t="s">
-        <v>532</v>
-      </c>
       <c r="C239" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E239" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="F239">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G239" t="s">
         <v>72</v>
@@ -8293,18 +8290,18 @@
         <v>72</v>
       </c>
       <c r="I239" t="s">
-        <v>250</v>
+        <v>388</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" t="s">
+        <v>465</v>
+      </c>
+      <c r="B240" t="s">
         <v>466</v>
       </c>
-      <c r="B240" t="s">
-        <v>467</v>
-      </c>
       <c r="C240" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E240" t="s">
         <v>358</v>
@@ -8319,18 +8316,18 @@
         <v>370</v>
       </c>
       <c r="I240" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
+        <v>468</v>
+      </c>
+      <c r="B241" t="s">
         <v>469</v>
       </c>
-      <c r="B241" t="s">
-        <v>470</v>
-      </c>
       <c r="C241" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E241" t="s">
         <v>358</v>
@@ -8345,15 +8342,15 @@
         <v>370</v>
       </c>
       <c r="I241" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B242" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C242" t="s">
         <v>284</v>
@@ -8365,30 +8362,30 @@
         <v>4.0</v>
       </c>
       <c r="G242" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H242" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="I242" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="B243" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="C243" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E243" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F243">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G243" t="s">
         <v>72</v>
@@ -8397,24 +8394,24 @@
         <v>72</v>
       </c>
       <c r="I243" t="s">
-        <v>254</v>
+        <v>481</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>428</v>
+        <v>485</v>
       </c>
       <c r="B244" t="s">
-        <v>429</v>
+        <v>486</v>
       </c>
       <c r="C244" t="s">
-        <v>297</v>
+        <v>164</v>
       </c>
       <c r="E244" t="s">
-        <v>358</v>
+        <v>474</v>
       </c>
       <c r="F244">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G244" t="s">
         <v>72</v>
@@ -8423,24 +8420,24 @@
         <v>72</v>
       </c>
       <c r="I244" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>534</v>
+        <v>427</v>
       </c>
       <c r="B245" t="s">
-        <v>535</v>
+        <v>428</v>
       </c>
       <c r="C245" t="s">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="E245" t="s">
         <v>358</v>
       </c>
       <c r="F245">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G245" t="s">
         <v>72</v>
@@ -8449,21 +8446,21 @@
         <v>72</v>
       </c>
       <c r="I245" t="s">
-        <v>81</v>
+        <v>278</v>
       </c>
     </row>
     <row r="246" spans="1:9">
       <c r="A246" t="s">
+        <v>535</v>
+      </c>
+      <c r="B246" t="s">
         <v>536</v>
       </c>
-      <c r="B246" t="s">
-        <v>537</v>
-      </c>
       <c r="C246" t="s">
-        <v>164</v>
+        <v>269</v>
       </c>
       <c r="E246" t="s">
-        <v>244</v>
+        <v>358</v>
       </c>
       <c r="F246">
         <v>2.0</v>
@@ -8475,24 +8472,24 @@
         <v>72</v>
       </c>
       <c r="I246" t="s">
-        <v>251</v>
+        <v>81</v>
       </c>
     </row>
     <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>538</v>
+        <v>472</v>
       </c>
       <c r="B247" t="s">
-        <v>539</v>
+        <v>473</v>
       </c>
       <c r="C247" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="E247" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F247">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G247" t="s">
         <v>72</v>
@@ -8501,67 +8498,67 @@
         <v>72</v>
       </c>
       <c r="I247" t="s">
-        <v>254</v>
+        <v>322</v>
       </c>
     </row>
     <row r="248" spans="1:9">
       <c r="A248" t="s">
-        <v>442</v>
+        <v>537</v>
       </c>
       <c r="B248" t="s">
-        <v>443</v>
+        <v>538</v>
       </c>
       <c r="C248" t="s">
-        <v>297</v>
+        <v>164</v>
       </c>
       <c r="E248" t="s">
-        <v>358</v>
+        <v>244</v>
       </c>
       <c r="F248">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G248" t="s">
-        <v>370</v>
+        <v>72</v>
       </c>
       <c r="H248" t="s">
-        <v>370</v>
+        <v>72</v>
       </c>
       <c r="I248" t="s">
-        <v>515</v>
+        <v>251</v>
       </c>
     </row>
     <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="B249" t="s">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="C249" t="s">
         <v>164</v>
       </c>
       <c r="E249" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F249">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G249" t="s">
-        <v>506</v>
+        <v>72</v>
       </c>
       <c r="H249" t="s">
-        <v>540</v>
+        <v>72</v>
       </c>
       <c r="I249" t="s">
-        <v>451</v>
+        <v>254</v>
       </c>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>469</v>
+        <v>441</v>
       </c>
       <c r="B250" t="s">
-        <v>470</v>
+        <v>442</v>
       </c>
       <c r="C250" t="s">
         <v>297</v>
@@ -8579,73 +8576,73 @@
         <v>370</v>
       </c>
       <c r="I250" t="s">
-        <v>486</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="B251" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="C251" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="E251" t="s">
-        <v>244</v>
+        <v>474</v>
       </c>
       <c r="F251">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G251" t="s">
-        <v>72</v>
+        <v>507</v>
       </c>
       <c r="H251" t="s">
-        <v>72</v>
+        <v>539</v>
       </c>
       <c r="I251" t="s">
-        <v>251</v>
+        <v>451</v>
       </c>
     </row>
     <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>507</v>
+        <v>468</v>
       </c>
       <c r="B252" t="s">
-        <v>508</v>
+        <v>469</v>
       </c>
       <c r="C252" t="s">
-        <v>164</v>
+        <v>297</v>
       </c>
       <c r="E252" t="s">
-        <v>475</v>
+        <v>358</v>
       </c>
       <c r="F252">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G252" t="s">
-        <v>72</v>
+        <v>370</v>
       </c>
       <c r="H252" t="s">
-        <v>72</v>
+        <v>370</v>
       </c>
       <c r="I252" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
     </row>
     <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="B253" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="C253" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
       <c r="E253" t="s">
-        <v>358</v>
+        <v>244</v>
       </c>
       <c r="F253">
         <v>2.0</v>
@@ -8657,76 +8654,76 @@
         <v>72</v>
       </c>
       <c r="I253" t="s">
-        <v>468</v>
+        <v>251</v>
       </c>
     </row>
     <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>543</v>
+        <v>508</v>
       </c>
       <c r="B254" t="s">
-        <v>544</v>
+        <v>509</v>
       </c>
       <c r="C254" t="s">
-        <v>269</v>
+        <v>144</v>
       </c>
       <c r="E254" t="s">
-        <v>358</v>
+        <v>474</v>
       </c>
       <c r="F254">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G254" t="s">
-        <v>359</v>
+        <v>72</v>
       </c>
       <c r="H254" t="s">
-        <v>452</v>
+        <v>72</v>
       </c>
       <c r="I254" t="s">
-        <v>408</v>
+        <v>529</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="B255" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="C255" t="s">
-        <v>331</v>
+        <v>164</v>
       </c>
       <c r="E255" t="s">
-        <v>358</v>
+        <v>474</v>
       </c>
       <c r="F255">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G255" t="s">
-        <v>359</v>
+        <v>72</v>
       </c>
       <c r="H255" t="s">
-        <v>359</v>
+        <v>72</v>
       </c>
       <c r="I255" t="s">
-        <v>527</v>
+        <v>451</v>
       </c>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>545</v>
+        <v>508</v>
       </c>
       <c r="B256" t="s">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="C256" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="E256" t="s">
-        <v>244</v>
+        <v>474</v>
       </c>
       <c r="F256">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="G256" t="s">
         <v>72</v>
@@ -8735,24 +8732,24 @@
         <v>72</v>
       </c>
       <c r="I256" t="s">
-        <v>251</v>
+        <v>361</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B257" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C257" t="s">
-        <v>152</v>
+        <v>269</v>
       </c>
       <c r="E257" t="s">
-        <v>475</v>
+        <v>358</v>
       </c>
       <c r="F257">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G257" t="s">
         <v>72</v>
@@ -8761,76 +8758,76 @@
         <v>72</v>
       </c>
       <c r="I257" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>460</v>
+        <v>542</v>
       </c>
       <c r="B258" t="s">
-        <v>461</v>
+        <v>543</v>
       </c>
       <c r="C258" t="s">
-        <v>152</v>
+        <v>269</v>
       </c>
       <c r="E258" t="s">
-        <v>134</v>
+        <v>358</v>
       </c>
       <c r="F258">
         <v>2.0</v>
       </c>
       <c r="G258" t="s">
-        <v>72</v>
+        <v>359</v>
       </c>
       <c r="H258" t="s">
-        <v>72</v>
+        <v>443</v>
       </c>
       <c r="I258" t="s">
-        <v>218</v>
+        <v>411</v>
       </c>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B259" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C259" t="s">
-        <v>144</v>
+        <v>332</v>
       </c>
       <c r="E259" t="s">
-        <v>244</v>
+        <v>358</v>
       </c>
       <c r="F259">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G259" t="s">
-        <v>72</v>
+        <v>359</v>
       </c>
       <c r="H259" t="s">
-        <v>72</v>
+        <v>359</v>
       </c>
       <c r="I259" t="s">
-        <v>251</v>
+        <v>528</v>
       </c>
     </row>
     <row r="260" spans="1:9">
       <c r="A260" t="s">
-        <v>516</v>
+        <v>544</v>
       </c>
       <c r="B260" t="s">
-        <v>517</v>
+        <v>545</v>
       </c>
       <c r="C260" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="E260" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="F260">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G260" t="s">
         <v>72</v>
@@ -8839,24 +8836,24 @@
         <v>72</v>
       </c>
       <c r="I260" t="s">
-        <v>528</v>
+        <v>251</v>
       </c>
     </row>
     <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>529</v>
+        <v>459</v>
       </c>
       <c r="B261" t="s">
-        <v>530</v>
+        <v>460</v>
       </c>
       <c r="C261" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E261" t="s">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="F261">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G261" t="s">
         <v>72</v>
@@ -8865,47 +8862,47 @@
         <v>72</v>
       </c>
       <c r="I261" t="s">
-        <v>255</v>
+        <v>218</v>
       </c>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>464</v>
+        <v>522</v>
       </c>
       <c r="B262" t="s">
-        <v>465</v>
+        <v>523</v>
       </c>
       <c r="C262" t="s">
-        <v>297</v>
+        <v>144</v>
       </c>
       <c r="E262" t="s">
-        <v>358</v>
+        <v>244</v>
       </c>
       <c r="F262">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G262" t="s">
-        <v>359</v>
+        <v>72</v>
       </c>
       <c r="H262" t="s">
-        <v>359</v>
+        <v>72</v>
       </c>
       <c r="I262" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="B263" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="C263" t="s">
         <v>144</v>
       </c>
       <c r="E263" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F263">
         <v>5.0</v>
@@ -8917,24 +8914,24 @@
         <v>72</v>
       </c>
       <c r="I263" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>507</v>
+        <v>530</v>
       </c>
       <c r="B264" t="s">
-        <v>508</v>
+        <v>531</v>
       </c>
       <c r="C264" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="E264" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="F264">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="G264" t="s">
         <v>72</v>
@@ -8943,44 +8940,44 @@
         <v>72</v>
       </c>
       <c r="I264" t="s">
-        <v>361</v>
+        <v>255</v>
       </c>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>547</v>
+        <v>463</v>
       </c>
       <c r="B265" t="s">
-        <v>548</v>
+        <v>464</v>
       </c>
       <c r="C265" t="s">
-        <v>269</v>
+        <v>297</v>
       </c>
       <c r="E265" t="s">
         <v>358</v>
       </c>
       <c r="F265">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G265" t="s">
-        <v>430</v>
+        <v>359</v>
       </c>
       <c r="H265" t="s">
         <v>359</v>
       </c>
       <c r="I265" t="s">
-        <v>81</v>
+        <v>278</v>
       </c>
     </row>
     <row r="266" spans="1:9">
       <c r="A266" t="s">
-        <v>511</v>
+        <v>546</v>
       </c>
       <c r="B266" t="s">
-        <v>512</v>
+        <v>547</v>
       </c>
       <c r="C266" t="s">
-        <v>338</v>
+        <v>269</v>
       </c>
       <c r="E266" t="s">
         <v>358</v>
@@ -8989,7 +8986,7 @@
         <v>2.0</v>
       </c>
       <c r="G266" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H266" t="s">
         <v>359</v>
@@ -9000,45 +8997,45 @@
     </row>
     <row r="267" spans="1:9">
       <c r="A267" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="B267" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="C267" t="s">
-        <v>152</v>
+        <v>339</v>
       </c>
       <c r="E267" t="s">
-        <v>244</v>
+        <v>358</v>
       </c>
       <c r="F267">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G267" t="s">
-        <v>72</v>
+        <v>429</v>
       </c>
       <c r="H267" t="s">
-        <v>72</v>
+        <v>359</v>
       </c>
       <c r="I267" t="s">
-        <v>255</v>
+        <v>81</v>
       </c>
     </row>
     <row r="268" spans="1:9">
       <c r="A268" t="s">
-        <v>536</v>
+        <v>522</v>
       </c>
       <c r="B268" t="s">
-        <v>537</v>
+        <v>523</v>
       </c>
       <c r="C268" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E268" t="s">
         <v>244</v>
       </c>
       <c r="F268">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G268" t="s">
         <v>72</v>
@@ -9047,24 +9044,24 @@
         <v>72</v>
       </c>
       <c r="I268" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="B269" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="C269" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E269" t="s">
         <v>244</v>
       </c>
       <c r="F269">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G269" t="s">
         <v>72</v>
@@ -9073,24 +9070,24 @@
         <v>72</v>
       </c>
       <c r="I269" t="s">
-        <v>389</v>
+        <v>246</v>
       </c>
     </row>
     <row r="270" spans="1:9">
       <c r="A270" t="s">
+        <v>544</v>
+      </c>
+      <c r="B270" t="s">
         <v>545</v>
       </c>
-      <c r="B270" t="s">
-        <v>546</v>
-      </c>
       <c r="C270" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E270" t="s">
         <v>244</v>
       </c>
       <c r="F270">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G270" t="s">
         <v>72</v>
@@ -9099,24 +9096,24 @@
         <v>72</v>
       </c>
       <c r="I270" t="s">
-        <v>255</v>
+        <v>388</v>
       </c>
     </row>
     <row r="271" spans="1:9">
       <c r="A271" t="s">
-        <v>473</v>
+        <v>544</v>
       </c>
       <c r="B271" t="s">
-        <v>474</v>
+        <v>545</v>
       </c>
       <c r="C271" t="s">
         <v>144</v>
       </c>
       <c r="E271" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="F271">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G271" t="s">
         <v>72</v>
@@ -9125,15 +9122,15 @@
         <v>72</v>
       </c>
       <c r="I271" t="s">
-        <v>321</v>
+        <v>255</v>
       </c>
     </row>
     <row r="272" spans="1:9">
       <c r="A272" t="s">
+        <v>548</v>
+      </c>
+      <c r="B272" t="s">
         <v>549</v>
-      </c>
-      <c r="B272" t="s">
-        <v>550</v>
       </c>
       <c r="C272" t="s">
         <v>144</v>
@@ -9151,21 +9148,21 @@
         <v>72</v>
       </c>
       <c r="I272" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="273" spans="1:9">
       <c r="A273" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B273" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C273" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E273" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F273">
         <v>4.0</v>
@@ -9177,24 +9174,24 @@
         <v>72</v>
       </c>
       <c r="I273" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
     </row>
     <row r="274" spans="1:9">
       <c r="A274" t="s">
-        <v>552</v>
+        <v>485</v>
       </c>
       <c r="B274" t="s">
-        <v>553</v>
+        <v>486</v>
       </c>
       <c r="C274" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="E274" t="s">
-        <v>554</v>
+        <v>474</v>
       </c>
       <c r="F274">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G274" t="s">
         <v>72</v>
@@ -9203,24 +9200,24 @@
         <v>72</v>
       </c>
       <c r="I274" t="s">
-        <v>264</v>
+        <v>455</v>
       </c>
     </row>
     <row r="275" spans="1:9">
       <c r="A275" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B275" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C275" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="E275" t="s">
-        <v>129</v>
+        <v>553</v>
       </c>
       <c r="F275">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G275" t="s">
         <v>72</v>
@@ -9229,24 +9226,24 @@
         <v>72</v>
       </c>
       <c r="I275" t="s">
-        <v>167</v>
+        <v>264</v>
       </c>
     </row>
     <row r="276" spans="1:9">
       <c r="A276" t="s">
+        <v>554</v>
+      </c>
+      <c r="B276" t="s">
         <v>555</v>
       </c>
-      <c r="B276" t="s">
-        <v>556</v>
-      </c>
       <c r="C276" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E276" t="s">
         <v>129</v>
       </c>
       <c r="F276">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="G276" t="s">
         <v>72</v>
@@ -9255,24 +9252,24 @@
         <v>72</v>
       </c>
       <c r="I276" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="277" spans="1:9">
       <c r="A277" t="s">
-        <v>460</v>
+        <v>554</v>
       </c>
       <c r="B277" t="s">
-        <v>461</v>
+        <v>555</v>
       </c>
       <c r="C277" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="E277" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F277">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G277" t="s">
         <v>72</v>
@@ -9281,15 +9278,15 @@
         <v>72</v>
       </c>
       <c r="I277" t="s">
-        <v>551</v>
+        <v>174</v>
       </c>
     </row>
     <row r="278" spans="1:9">
       <c r="A278" t="s">
-        <v>549</v>
+        <v>459</v>
       </c>
       <c r="B278" t="s">
-        <v>550</v>
+        <v>460</v>
       </c>
       <c r="C278" t="s">
         <v>164</v>
@@ -9298,7 +9295,7 @@
         <v>134</v>
       </c>
       <c r="F278">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G278" t="s">
         <v>72</v>
@@ -9307,24 +9304,24 @@
         <v>72</v>
       </c>
       <c r="I278" t="s">
-        <v>179</v>
+        <v>550</v>
       </c>
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
-        <v>521</v>
+        <v>548</v>
       </c>
       <c r="B279" t="s">
-        <v>522</v>
+        <v>549</v>
       </c>
       <c r="C279" t="s">
         <v>164</v>
       </c>
       <c r="E279" t="s">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="F279">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G279" t="s">
         <v>72</v>
@@ -9333,24 +9330,24 @@
         <v>72</v>
       </c>
       <c r="I279" t="s">
-        <v>246</v>
+        <v>179</v>
       </c>
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
-        <v>545</v>
+        <v>522</v>
       </c>
       <c r="B280" t="s">
-        <v>546</v>
+        <v>523</v>
       </c>
       <c r="C280" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="E280" t="s">
         <v>244</v>
       </c>
       <c r="F280">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G280" t="s">
         <v>72</v>
@@ -9359,15 +9356,15 @@
         <v>72</v>
       </c>
       <c r="I280" t="s">
-        <v>389</v>
+        <v>246</v>
       </c>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="B281" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C281" t="s">
         <v>152</v>
@@ -9385,24 +9382,24 @@
         <v>72</v>
       </c>
       <c r="I281" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
-        <v>347</v>
+        <v>537</v>
       </c>
       <c r="B282" t="s">
-        <v>348</v>
+        <v>538</v>
       </c>
       <c r="C282" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="E282" t="s">
         <v>244</v>
       </c>
       <c r="F282">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G282" t="s">
         <v>72</v>
@@ -9411,24 +9408,24 @@
         <v>72</v>
       </c>
       <c r="I282" t="s">
-        <v>557</v>
+        <v>388</v>
       </c>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>529</v>
+        <v>347</v>
       </c>
       <c r="B283" t="s">
-        <v>530</v>
+        <v>348</v>
       </c>
       <c r="C283" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E283" t="s">
         <v>244</v>
       </c>
       <c r="F283">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G283" t="s">
         <v>72</v>
@@ -9437,21 +9434,21 @@
         <v>72</v>
       </c>
       <c r="I283" t="s">
-        <v>255</v>
+        <v>556</v>
       </c>
     </row>
     <row r="284" spans="1:9">
       <c r="A284" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="B284" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="C284" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E284" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="F284">
         <v>4.0</v>
@@ -9463,21 +9460,21 @@
         <v>72</v>
       </c>
       <c r="I284" t="s">
-        <v>478</v>
+        <v>255</v>
       </c>
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B285" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C285" t="s">
         <v>128</v>
       </c>
       <c r="E285" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F285">
         <v>7.0</v>
@@ -9489,21 +9486,21 @@
         <v>72</v>
       </c>
       <c r="I285" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="B286" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="C286" t="s">
         <v>144</v>
       </c>
       <c r="E286" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F286">
         <v>4.0</v>
@@ -9515,21 +9512,21 @@
         <v>72</v>
       </c>
       <c r="I286" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="287" spans="1:9">
       <c r="A287" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B287" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C287" t="s">
         <v>128</v>
       </c>
       <c r="E287" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F287">
         <v>2.0</v>
@@ -9546,13 +9543,13 @@
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
+        <v>558</v>
+      </c>
+      <c r="B288" t="s">
         <v>559</v>
       </c>
-      <c r="B288" t="s">
+      <c r="E288" t="s">
         <v>560</v>
-      </c>
-      <c r="E288" t="s">
-        <v>561</v>
       </c>
       <c r="F288">
         <v>2.0</v>
@@ -9564,18 +9561,18 @@
         <v>72</v>
       </c>
       <c r="I288" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
+        <v>562</v>
+      </c>
+      <c r="B289" t="s">
         <v>563</v>
       </c>
-      <c r="B289" t="s">
-        <v>564</v>
-      </c>
       <c r="E289" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F289">
         <v>1.0</v>
@@ -9592,13 +9589,13 @@
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
+        <v>564</v>
+      </c>
+      <c r="B290" t="s">
         <v>565</v>
       </c>
-      <c r="B290" t="s">
-        <v>566</v>
-      </c>
       <c r="E290" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F290">
         <v>1.0</v>
@@ -9615,13 +9612,13 @@
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
+        <v>566</v>
+      </c>
+      <c r="B291" t="s">
         <v>567</v>
       </c>
-      <c r="B291" t="s">
-        <v>568</v>
-      </c>
       <c r="E291" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F291">
         <v>2.0</v>
@@ -9638,10 +9635,10 @@
     </row>
     <row r="292" spans="1:9">
       <c r="A292" t="s">
+        <v>568</v>
+      </c>
+      <c r="B292" t="s">
         <v>569</v>
-      </c>
-      <c r="B292" t="s">
-        <v>570</v>
       </c>
       <c r="E292" t="s">
         <v>225</v>
@@ -9661,16 +9658,16 @@
     </row>
     <row r="293" spans="1:9">
       <c r="A293" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B293" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C293" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E293" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F293">
         <v>4.0</v>
@@ -9682,21 +9679,21 @@
         <v>72</v>
       </c>
       <c r="I293" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="294" spans="1:9">
       <c r="A294" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B294" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C294" t="s">
         <v>269</v>
       </c>
       <c r="E294" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F294">
         <v>7.0</v>
@@ -9708,21 +9705,21 @@
         <v>72</v>
       </c>
       <c r="I294" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="295" spans="1:9">
       <c r="A295" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B295" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C295" t="s">
         <v>284</v>
       </c>
       <c r="E295" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F295">
         <v>5.0</v>
@@ -9734,21 +9731,21 @@
         <v>72</v>
       </c>
       <c r="I295" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="296" spans="1:9">
       <c r="A296" t="s">
+        <v>572</v>
+      </c>
+      <c r="B296" t="s">
         <v>573</v>
       </c>
-      <c r="B296" t="s">
-        <v>574</v>
-      </c>
       <c r="C296" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E296" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F296">
         <v>4.0</v>
@@ -9760,21 +9757,21 @@
         <v>72</v>
       </c>
       <c r="I296" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="297" spans="1:9">
       <c r="A297" t="s">
+        <v>572</v>
+      </c>
+      <c r="B297" t="s">
         <v>573</v>
-      </c>
-      <c r="B297" t="s">
-        <v>574</v>
       </c>
       <c r="C297" t="s">
         <v>269</v>
       </c>
       <c r="E297" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F297">
         <v>6.0</v>
@@ -9786,21 +9783,21 @@
         <v>72</v>
       </c>
       <c r="I297" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="298" spans="1:9">
       <c r="A298" t="s">
+        <v>572</v>
+      </c>
+      <c r="B298" t="s">
         <v>573</v>
-      </c>
-      <c r="B298" t="s">
-        <v>574</v>
       </c>
       <c r="C298" t="s">
         <v>284</v>
       </c>
       <c r="E298" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F298">
         <v>2.0</v>
@@ -9812,21 +9809,21 @@
         <v>72</v>
       </c>
       <c r="I298" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" t="s">
+        <v>572</v>
+      </c>
+      <c r="B299" t="s">
         <v>573</v>
       </c>
-      <c r="B299" t="s">
-        <v>574</v>
-      </c>
       <c r="C299" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E299" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F299">
         <v>3.0</v>
@@ -9838,21 +9835,21 @@
         <v>72</v>
       </c>
       <c r="I299" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="A300" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B300" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C300" t="s">
         <v>297</v>
       </c>
       <c r="E300" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F300">
         <v>2.0</v>
@@ -9864,21 +9861,21 @@
         <v>72</v>
       </c>
       <c r="I300" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="301" spans="1:9">
       <c r="A301" t="s">
+        <v>578</v>
+      </c>
+      <c r="B301" t="s">
         <v>579</v>
       </c>
-      <c r="B301" t="s">
-        <v>580</v>
-      </c>
       <c r="C301" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E301" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F301">
         <v>2.0</v>
@@ -9890,21 +9887,21 @@
         <v>72</v>
       </c>
       <c r="I301" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="302" spans="1:9">
       <c r="A302" t="s">
+        <v>578</v>
+      </c>
+      <c r="B302" t="s">
         <v>579</v>
-      </c>
-      <c r="B302" t="s">
-        <v>580</v>
       </c>
       <c r="C302" t="s">
         <v>269</v>
       </c>
       <c r="E302" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F302">
         <v>7.0</v>
@@ -9916,21 +9913,21 @@
         <v>72</v>
       </c>
       <c r="I302" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
+        <v>578</v>
+      </c>
+      <c r="B303" t="s">
         <v>579</v>
       </c>
-      <c r="B303" t="s">
-        <v>580</v>
-      </c>
       <c r="C303" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E303" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F303">
         <v>3.0</v>
@@ -9942,21 +9939,21 @@
         <v>72</v>
       </c>
       <c r="I303" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="304" spans="1:9">
       <c r="A304" t="s">
+        <v>578</v>
+      </c>
+      <c r="B304" t="s">
         <v>579</v>
-      </c>
-      <c r="B304" t="s">
-        <v>580</v>
       </c>
       <c r="C304" t="s">
         <v>297</v>
       </c>
       <c r="E304" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F304">
         <v>3.0</v>
@@ -9968,21 +9965,21 @@
         <v>72</v>
       </c>
       <c r="I304" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" t="s">
+        <v>583</v>
+      </c>
+      <c r="B305" t="s">
         <v>584</v>
       </c>
-      <c r="B305" t="s">
-        <v>585</v>
-      </c>
       <c r="C305" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E305" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F305">
         <v>1.0</v>
@@ -9994,21 +9991,21 @@
         <v>72</v>
       </c>
       <c r="I305" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="306" spans="1:9">
       <c r="A306" t="s">
+        <v>583</v>
+      </c>
+      <c r="B306" t="s">
         <v>584</v>
-      </c>
-      <c r="B306" t="s">
-        <v>585</v>
       </c>
       <c r="C306" t="s">
         <v>297</v>
       </c>
       <c r="E306" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F306">
         <v>1.0</v>
@@ -10020,24 +10017,24 @@
         <v>72</v>
       </c>
       <c r="I306" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="307" spans="1:9">
       <c r="A307" t="s">
+        <v>585</v>
+      </c>
+      <c r="B307" t="s">
         <v>586</v>
-      </c>
-      <c r="B307" t="s">
-        <v>587</v>
       </c>
       <c r="C307" t="s">
         <v>269</v>
       </c>
       <c r="E307" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F307">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G307" t="s">
         <v>72</v>
@@ -10046,21 +10043,21 @@
         <v>72</v>
       </c>
       <c r="I307" t="s">
-        <v>440</v>
+        <v>311</v>
       </c>
     </row>
     <row r="308" spans="1:9">
       <c r="A308" t="s">
+        <v>585</v>
+      </c>
+      <c r="B308" t="s">
         <v>586</v>
-      </c>
-      <c r="B308" t="s">
-        <v>587</v>
       </c>
       <c r="C308" t="s">
         <v>284</v>
       </c>
       <c r="E308" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F308">
         <v>2.0</v>
@@ -10072,21 +10069,21 @@
         <v>72</v>
       </c>
       <c r="I308" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="309" spans="1:9">
       <c r="A309" t="s">
+        <v>585</v>
+      </c>
+      <c r="B309" t="s">
         <v>586</v>
       </c>
-      <c r="B309" t="s">
-        <v>587</v>
-      </c>
       <c r="C309" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E309" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F309">
         <v>1.0</v>
@@ -10098,21 +10095,21 @@
         <v>72</v>
       </c>
       <c r="I309" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="310" spans="1:9">
       <c r="A310" t="s">
+        <v>587</v>
+      </c>
+      <c r="B310" t="s">
         <v>588</v>
       </c>
-      <c r="B310" t="s">
-        <v>589</v>
-      </c>
       <c r="C310" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E310" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F310">
         <v>1.0</v>
@@ -10124,21 +10121,21 @@
         <v>72</v>
       </c>
       <c r="I310" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="311" spans="1:9">
       <c r="A311" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B311" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C311" t="s">
         <v>269</v>
       </c>
       <c r="E311" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F311">
         <v>4.0</v>
@@ -10150,21 +10147,21 @@
         <v>72</v>
       </c>
       <c r="I311" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="312" spans="1:9">
       <c r="A312" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B312" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C312" t="s">
         <v>284</v>
       </c>
       <c r="E312" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F312">
         <v>2.0</v>
@@ -10176,21 +10173,21 @@
         <v>72</v>
       </c>
       <c r="I312" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="313" spans="1:9">
       <c r="A313" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B313" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C313" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E313" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F313">
         <v>2.0</v>
@@ -10202,21 +10199,21 @@
         <v>72</v>
       </c>
       <c r="I313" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="314" spans="1:9">
       <c r="A314" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B314" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C314" t="s">
         <v>297</v>
       </c>
       <c r="E314" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F314">
         <v>1.0</v>
@@ -10228,21 +10225,21 @@
         <v>72</v>
       </c>
       <c r="I314" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="315" spans="1:9">
       <c r="A315" t="s">
+        <v>591</v>
+      </c>
+      <c r="B315" t="s">
         <v>592</v>
-      </c>
-      <c r="B315" t="s">
-        <v>593</v>
       </c>
       <c r="C315" t="s">
         <v>284</v>
       </c>
       <c r="E315" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F315">
         <v>1.0</v>
@@ -10254,47 +10251,47 @@
         <v>72</v>
       </c>
       <c r="I315" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" t="s">
+        <v>591</v>
+      </c>
+      <c r="B316" t="s">
         <v>592</v>
       </c>
-      <c r="B316" t="s">
+      <c r="C316" t="s">
+        <v>332</v>
+      </c>
+      <c r="E316" t="s">
+        <v>503</v>
+      </c>
+      <c r="F316">
+        <v>1.0</v>
+      </c>
+      <c r="G316" t="s">
+        <v>72</v>
+      </c>
+      <c r="H316" t="s">
+        <v>72</v>
+      </c>
+      <c r="I316" t="s">
         <v>593</v>
-      </c>
-      <c r="C316" t="s">
-        <v>331</v>
-      </c>
-      <c r="E316" t="s">
-        <v>499</v>
-      </c>
-      <c r="F316">
-        <v>1.0</v>
-      </c>
-      <c r="G316" t="s">
-        <v>72</v>
-      </c>
-      <c r="H316" t="s">
-        <v>72</v>
-      </c>
-      <c r="I316" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" t="s">
+        <v>594</v>
+      </c>
+      <c r="B317" t="s">
         <v>595</v>
-      </c>
-      <c r="B317" t="s">
-        <v>596</v>
       </c>
       <c r="C317" t="s">
         <v>269</v>
       </c>
       <c r="E317" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F317">
         <v>2.0</v>
@@ -10306,21 +10303,21 @@
         <v>72</v>
       </c>
       <c r="I317" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" t="s">
+        <v>594</v>
+      </c>
+      <c r="B318" t="s">
         <v>595</v>
       </c>
-      <c r="B318" t="s">
-        <v>596</v>
-      </c>
       <c r="C318" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E318" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F318">
         <v>1.0</v>
@@ -10332,21 +10329,21 @@
         <v>72</v>
       </c>
       <c r="I318" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="319" spans="1:9">
       <c r="A319" t="s">
+        <v>596</v>
+      </c>
+      <c r="B319" t="s">
         <v>597</v>
-      </c>
-      <c r="B319" t="s">
-        <v>598</v>
       </c>
       <c r="C319" t="s">
         <v>269</v>
       </c>
       <c r="E319" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F319">
         <v>4.0</v>
@@ -10358,24 +10355,24 @@
         <v>72</v>
       </c>
       <c r="I319" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" t="s">
+        <v>596</v>
+      </c>
+      <c r="B320" t="s">
         <v>597</v>
-      </c>
-      <c r="B320" t="s">
-        <v>598</v>
       </c>
       <c r="C320" t="s">
         <v>284</v>
       </c>
       <c r="E320" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F320">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G320" t="s">
         <v>72</v>
@@ -10384,21 +10381,21 @@
         <v>72</v>
       </c>
       <c r="I320" t="s">
-        <v>81</v>
+        <v>528</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" t="s">
+        <v>596</v>
+      </c>
+      <c r="B321" t="s">
         <v>597</v>
       </c>
-      <c r="B321" t="s">
-        <v>598</v>
-      </c>
       <c r="C321" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E321" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F321">
         <v>2.0</v>
@@ -10415,16 +10412,16 @@
     </row>
     <row r="322" spans="1:9">
       <c r="A322" t="s">
+        <v>596</v>
+      </c>
+      <c r="B322" t="s">
         <v>597</v>
-      </c>
-      <c r="B322" t="s">
-        <v>598</v>
       </c>
       <c r="C322" t="s">
         <v>297</v>
       </c>
       <c r="E322" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F322">
         <v>2.0</v>
@@ -10441,10 +10438,10 @@
     </row>
     <row r="323" spans="1:9">
       <c r="A323" t="s">
+        <v>540</v>
+      </c>
+      <c r="B323" t="s">
         <v>541</v>
-      </c>
-      <c r="B323" t="s">
-        <v>542</v>
       </c>
       <c r="C323" t="s">
         <v>284</v>
@@ -10462,18 +10459,18 @@
         <v>72</v>
       </c>
       <c r="I323" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B324" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C324" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E324" t="s">
         <v>358</v>
@@ -10488,15 +10485,15 @@
         <v>72</v>
       </c>
       <c r="I324" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" t="s">
+        <v>598</v>
+      </c>
+      <c r="B325" t="s">
         <v>599</v>
-      </c>
-      <c r="B325" t="s">
-        <v>600</v>
       </c>
       <c r="C325" t="s">
         <v>269</v>
@@ -10514,15 +10511,15 @@
         <v>72</v>
       </c>
       <c r="I325" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="326" spans="1:9">
       <c r="A326" t="s">
+        <v>554</v>
+      </c>
+      <c r="B326" t="s">
         <v>555</v>
-      </c>
-      <c r="B326" t="s">
-        <v>556</v>
       </c>
       <c r="C326" t="s">
         <v>164</v>
@@ -10545,10 +10542,10 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327" t="s">
+        <v>600</v>
+      </c>
+      <c r="B327" t="s">
         <v>601</v>
-      </c>
-      <c r="B327" t="s">
-        <v>602</v>
       </c>
       <c r="C327" t="s">
         <v>144</v>
@@ -10571,10 +10568,10 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328" t="s">
+        <v>600</v>
+      </c>
+      <c r="B328" t="s">
         <v>601</v>
-      </c>
-      <c r="B328" t="s">
-        <v>602</v>
       </c>
       <c r="C328" t="s">
         <v>128</v>
@@ -10597,16 +10594,16 @@
     </row>
     <row r="329" spans="1:9">
       <c r="A329" t="s">
+        <v>602</v>
+      </c>
+      <c r="B329" t="s">
         <v>603</v>
       </c>
-      <c r="B329" t="s">
-        <v>604</v>
-      </c>
       <c r="C329" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E329" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F329">
         <v>1.0</v>
@@ -10618,21 +10615,21 @@
         <v>72</v>
       </c>
       <c r="I329" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="330" spans="1:9">
       <c r="A330" t="s">
+        <v>602</v>
+      </c>
+      <c r="B330" t="s">
         <v>603</v>
       </c>
-      <c r="B330" t="s">
-        <v>604</v>
-      </c>
       <c r="C330" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E330" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F330">
         <v>1.0</v>
@@ -10644,21 +10641,21 @@
         <v>72</v>
       </c>
       <c r="I330" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="331" spans="1:9">
       <c r="A331" t="s">
+        <v>602</v>
+      </c>
+      <c r="B331" t="s">
         <v>603</v>
-      </c>
-      <c r="B331" t="s">
-        <v>604</v>
       </c>
       <c r="C331" t="s">
         <v>269</v>
       </c>
       <c r="E331" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F331">
         <v>3.0</v>
@@ -10670,21 +10667,21 @@
         <v>72</v>
       </c>
       <c r="I331" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="332" spans="1:9">
       <c r="A332" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B332" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C332" t="s">
         <v>297</v>
       </c>
       <c r="E332" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F332">
         <v>2.0</v>
@@ -10696,7 +10693,7 @@
         <v>72</v>
       </c>
       <c r="I332" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>

--- a/src/inventory/War.xlsx
+++ b/src/inventory/War.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="601">
   <si>
     <t>Code/SKU</t>
   </si>
@@ -455,10 +455,10 @@
     <t>৳371.05</t>
   </si>
   <si>
-    <t>৳2,597.37</t>
-  </si>
-  <si>
-    <t>৳6,986.00</t>
+    <t>৳2,226.32</t>
+  </si>
+  <si>
+    <t>৳5,988.00</t>
   </si>
   <si>
     <t>৳714.29</t>
@@ -536,9 +536,6 @@
     <t>৳2,082.86</t>
   </si>
   <si>
-    <t>৳5,988.00</t>
-  </si>
-  <si>
     <t>৳384.38</t>
   </si>
   <si>
@@ -578,7 +575,10 @@
     <t>৳303.57</t>
   </si>
   <si>
-    <t>৳1,821.43</t>
+    <t>৳1,517.86</t>
+  </si>
+  <si>
+    <t>৳4,990.00</t>
   </si>
   <si>
     <t>৳342.86</t>
@@ -647,7 +647,10 @@
     <t>৳344.44</t>
   </si>
   <si>
-    <t>৳1,033.32</t>
+    <t>৳688.88</t>
+  </si>
+  <si>
+    <t>৳1,976.00</t>
   </si>
   <si>
     <t>107-0100-051</t>
@@ -671,9 +674,6 @@
     <t>৳666.66</t>
   </si>
   <si>
-    <t>৳1,976.00</t>
-  </si>
-  <si>
     <t>110-0101-013</t>
   </si>
   <si>
@@ -779,690 +779,687 @@
     <t>৳5,096.00</t>
   </si>
   <si>
+    <t>৳1,600.00</t>
+  </si>
+  <si>
+    <t>৳3,640.00</t>
+  </si>
+  <si>
+    <t>৳1,280.00</t>
+  </si>
+  <si>
+    <t>৳2,912.00</t>
+  </si>
+  <si>
+    <t>109-0103-003</t>
+  </si>
+  <si>
+    <t>৳452.80</t>
+  </si>
+  <si>
+    <t>৳905.60</t>
+  </si>
+  <si>
+    <t>৳1,698.00</t>
+  </si>
+  <si>
+    <t>৳620.00</t>
+  </si>
+  <si>
+    <t>৳3,490.00</t>
+  </si>
+  <si>
+    <t>105-0202-004</t>
+  </si>
+  <si>
+    <t>Light Ash Full Sleeve Turtleneck T-shirt</t>
+  </si>
+  <si>
+    <t>৳698.00</t>
+  </si>
+  <si>
+    <t>৳228.76</t>
+  </si>
+  <si>
+    <t>৳686.27</t>
+  </si>
+  <si>
+    <t>109-0103-001</t>
+  </si>
+  <si>
+    <t>৳271.68</t>
+  </si>
+  <si>
+    <t>৳543.36</t>
+  </si>
+  <si>
+    <t>1105-0301-001</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Men / Drop Shoulder</t>
+  </si>
+  <si>
+    <t>৳550.00</t>
+  </si>
+  <si>
+    <t>৳3,300.00</t>
+  </si>
+  <si>
+    <t>৳5,040.00</t>
+  </si>
+  <si>
+    <t>109-0104-001</t>
+  </si>
+  <si>
+    <t>Card Holder 001</t>
+  </si>
+  <si>
+    <t>৳350.00</t>
+  </si>
+  <si>
+    <t>৳700.00</t>
+  </si>
+  <si>
+    <t>৳1,180.00</t>
+  </si>
+  <si>
+    <t>৳280.00</t>
+  </si>
+  <si>
+    <t>৳1,400.00</t>
+  </si>
+  <si>
+    <t>৳1,745.00</t>
+  </si>
+  <si>
+    <t>105-0301-007</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 07</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>৳1,580.00</t>
+  </si>
+  <si>
+    <t>৳227.28</t>
+  </si>
+  <si>
+    <t>৳1,363.65</t>
+  </si>
+  <si>
+    <t>105-0301-008</t>
+  </si>
+  <si>
+    <t>Crew Graphic Drop Shoulder T-Shirt</t>
+  </si>
+  <si>
+    <t>3XL</t>
+  </si>
+  <si>
+    <t>Men / T-SHIRT</t>
+  </si>
+  <si>
+    <t>৳790.00</t>
+  </si>
+  <si>
+    <t>৳218.18</t>
+  </si>
+  <si>
+    <t>৳210.00</t>
+  </si>
+  <si>
+    <t>৳1,050.00</t>
+  </si>
+  <si>
+    <t>105-0301-005</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 05</t>
+  </si>
+  <si>
+    <t>109-0102-064</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 064</t>
+  </si>
+  <si>
+    <t>109-0402-057</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 57</t>
+  </si>
+  <si>
+    <t>109-0402-058</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 58</t>
+  </si>
+  <si>
+    <t>৳233.33</t>
+  </si>
+  <si>
+    <t>105-0301-003</t>
+  </si>
+  <si>
+    <t>Retro Car Print Drop Shoulder T-Shirt</t>
+  </si>
+  <si>
+    <t>109-0104-002</t>
+  </si>
+  <si>
+    <t>Card Holder 002</t>
+  </si>
+  <si>
+    <t>109-0104-003</t>
+  </si>
+  <si>
+    <t>Card Holder 003</t>
+  </si>
+  <si>
+    <t>৳590.00</t>
+  </si>
+  <si>
+    <t>৳185.94</t>
+  </si>
+  <si>
+    <t>৳371.88</t>
+  </si>
+  <si>
+    <t>109-0104-004</t>
+  </si>
+  <si>
+    <t>Card Holder 004</t>
+  </si>
+  <si>
+    <t>109-0402-051</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 51</t>
+  </si>
+  <si>
+    <t>৳35.87</t>
+  </si>
+  <si>
+    <t>৳143.48</t>
+  </si>
+  <si>
+    <t>৳3,960.00</t>
+  </si>
+  <si>
+    <t>109-0102-073</t>
+  </si>
+  <si>
+    <t>Bifold Leather Wallet 73</t>
+  </si>
+  <si>
+    <t>Men / WALLET,BI-FOLD</t>
+  </si>
+  <si>
+    <t>৳699.00</t>
+  </si>
+  <si>
+    <t>109-0402-048</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 48</t>
+  </si>
+  <si>
+    <t>৳1,980.00</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>৳4,740.00</t>
+  </si>
+  <si>
+    <t>109-0102-074</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 74</t>
+  </si>
+  <si>
+    <t>৳1,350.00</t>
+  </si>
+  <si>
+    <t>৳2,097.00</t>
+  </si>
+  <si>
+    <t>109-0502-001</t>
+  </si>
+  <si>
+    <t>Breathable Face Mask</t>
+  </si>
+  <si>
+    <t>Men / MEN,ACCESSORIES,MASK</t>
+  </si>
+  <si>
+    <t>৳199.51</t>
+  </si>
+  <si>
+    <t>৳1,396.60</t>
+  </si>
+  <si>
+    <t>৳1,960.00</t>
+  </si>
+  <si>
+    <t>105-0201-033</t>
+  </si>
+  <si>
+    <t>Full Sleeve Neon Stripe T-shirt</t>
+  </si>
+  <si>
+    <t>109-0402-050</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 50</t>
+  </si>
+  <si>
+    <t>109-0402-056</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 56</t>
+  </si>
+  <si>
+    <t>৳50.00</t>
+  </si>
+  <si>
+    <t>102-0302-005</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 005</t>
+  </si>
+  <si>
+    <t>Men / SHIRT</t>
+  </si>
+  <si>
+    <t>৳650.00</t>
+  </si>
+  <si>
+    <t>৳2,600.00</t>
+  </si>
+  <si>
+    <t>৳4,720.00</t>
+  </si>
+  <si>
+    <t>2XL</t>
+  </si>
+  <si>
+    <t>৳432.27</t>
+  </si>
+  <si>
+    <t>৳431.25</t>
+  </si>
+  <si>
+    <t>101-0300-140</t>
+  </si>
+  <si>
+    <t>Straight Fit Blue Jeans</t>
+  </si>
+  <si>
+    <t>৳8,450.00</t>
+  </si>
+  <si>
+    <t>102-0302-008</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 008</t>
+  </si>
+  <si>
+    <t>৳500.00</t>
+  </si>
+  <si>
+    <t>৳2,000.00</t>
+  </si>
+  <si>
+    <t>৳5,300.00</t>
+  </si>
+  <si>
+    <t>105-0301-004</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 004</t>
+  </si>
+  <si>
+    <t>Men / T-SHIRT,Drop Shoulder</t>
+  </si>
+  <si>
+    <t>৳840.00</t>
+  </si>
+  <si>
+    <t>109-0402-061</t>
+  </si>
+  <si>
+    <t>Premium Leather Belt 061</t>
+  </si>
+  <si>
+    <t>109-0102-072</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 72</t>
+  </si>
+  <si>
+    <t>105-0301-009</t>
+  </si>
+  <si>
+    <t>Deep Violet Drop Shoulder T-Shirt</t>
+  </si>
+  <si>
+    <t>109-0501-001</t>
+  </si>
+  <si>
+    <t>Durable Aluminum Water Bottle 600 ml.</t>
+  </si>
+  <si>
+    <t>Men / MEN,ACCESSORIES,WATER BOTTLE</t>
+  </si>
+  <si>
+    <t>৳155.51</t>
+  </si>
+  <si>
+    <t>৳1,399.55</t>
+  </si>
+  <si>
+    <t>৳3,591.00</t>
+  </si>
+  <si>
+    <t>৳2,184.00</t>
+  </si>
+  <si>
+    <t>৳332.44</t>
+  </si>
+  <si>
+    <t>৳1,329.77</t>
+  </si>
+  <si>
+    <t>৳3,160.00</t>
+  </si>
+  <si>
+    <t>109-0104-005</t>
+  </si>
+  <si>
+    <t>Card Holder</t>
+  </si>
+  <si>
+    <t>Men / Card Holder</t>
+  </si>
+  <si>
+    <t>৳690.00</t>
+  </si>
+  <si>
+    <t>109-0104-006</t>
+  </si>
+  <si>
+    <t>Card Holder 06</t>
+  </si>
+  <si>
+    <t>105-0301-001</t>
+  </si>
+  <si>
+    <t>105-0401-006</t>
+  </si>
+  <si>
+    <t>Burgundy Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>Men / Tank Top</t>
+  </si>
+  <si>
+    <t>৳250.00</t>
+  </si>
+  <si>
+    <t>৳750.00</t>
+  </si>
+  <si>
+    <t>৳1,620.00</t>
+  </si>
+  <si>
+    <t>৳2,370.00</t>
+  </si>
+  <si>
+    <t>102-0302-006</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 006</t>
+  </si>
+  <si>
+    <t>৳1,950.00</t>
+  </si>
+  <si>
+    <t>৳3,975.00</t>
+  </si>
+  <si>
+    <t>103-0200-098</t>
+  </si>
+  <si>
+    <t>White Polo Shirt in Cotton Pique</t>
+  </si>
+  <si>
+    <t>৳798.00</t>
+  </si>
+  <si>
+    <t>৳1,000.00</t>
+  </si>
+  <si>
+    <t>৳2,650.00</t>
+  </si>
+  <si>
+    <t>৳111.94</t>
+  </si>
+  <si>
+    <t>102-0402-032</t>
+  </si>
+  <si>
+    <t>Dark Blue Denim Shirt</t>
+  </si>
+  <si>
+    <t>Men / NEW IN,NEW,MEN,SHIRT,CASUAL SHIRT,DENIM SHIRT,FULL SLEEVE</t>
+  </si>
+  <si>
+    <t>103-0200-100</t>
+  </si>
+  <si>
+    <t>Malibu Polo Shirt in Cotton Pique</t>
+  </si>
+  <si>
+    <t>102-0302-002</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 002</t>
+  </si>
+  <si>
+    <t>৳560.00</t>
+  </si>
+  <si>
+    <t>৳2,800.00</t>
+  </si>
+  <si>
+    <t>৳7,250.00</t>
+  </si>
+  <si>
+    <t>109-0101-050</t>
+  </si>
+  <si>
+    <t>Leather Long Wallet 50</t>
+  </si>
+  <si>
+    <t>Men / WALLET,LONG</t>
+  </si>
+  <si>
+    <t>৳1,299.00</t>
+  </si>
+  <si>
+    <t>102-0301-002</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 002</t>
+  </si>
+  <si>
+    <t>102-0301-004</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 004</t>
+  </si>
+  <si>
+    <t>৳325.00</t>
+  </si>
+  <si>
+    <t>৳7,080.00</t>
+  </si>
+  <si>
+    <t>105-0401-005</t>
+  </si>
+  <si>
+    <t>Sable Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>105-0401-003</t>
+  </si>
+  <si>
+    <t>Tank Top 003</t>
+  </si>
+  <si>
+    <t>Men / T-SHIRT,Tank Top</t>
+  </si>
+  <si>
+    <t>৳5,120.00</t>
+  </si>
+  <si>
+    <t>৳2,700.00</t>
+  </si>
+  <si>
+    <t>৳3,540.00</t>
+  </si>
+  <si>
+    <t>102-0302-001</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 001</t>
+  </si>
+  <si>
+    <t>৳1,300.00</t>
+  </si>
+  <si>
+    <t>109-0101-049</t>
+  </si>
+  <si>
+    <t>Leather Long Wallet 049</t>
+  </si>
+  <si>
+    <t>৳1,080.00</t>
+  </si>
+  <si>
+    <t>৳3,250.00</t>
+  </si>
+  <si>
+    <t>৳8,320.00</t>
+  </si>
+  <si>
+    <t>105-0401-007</t>
+  </si>
+  <si>
+    <t>Cabbage Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>৳1,770.00</t>
+  </si>
+  <si>
+    <t>৳278.57</t>
+  </si>
+  <si>
+    <t>৳8,260.00</t>
+  </si>
+  <si>
+    <t>৳1,650.00</t>
+  </si>
+  <si>
+    <t>৳4,350.00</t>
+  </si>
+  <si>
+    <t>108-0101-013</t>
+  </si>
+  <si>
+    <t>Brown Sweatshirt in French-Terry</t>
+  </si>
+  <si>
+    <t>105-0401-004</t>
+  </si>
+  <si>
+    <t>Orlando Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>৳2,560.00</t>
+  </si>
+  <si>
+    <t>102-0302-010</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 010</t>
+  </si>
+  <si>
+    <t>৳2,360.00</t>
+  </si>
+  <si>
+    <t>102-0302-004</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 004</t>
+  </si>
+  <si>
+    <t>৳2,900.00</t>
+  </si>
+  <si>
+    <t>102-0302-007</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 007</t>
+  </si>
+  <si>
+    <t>105-0101-377</t>
+  </si>
+  <si>
+    <t>Warm Spice T-shirt</t>
+  </si>
+  <si>
+    <t>Men / NEW IN,NEW,MEN,T-SHIRT,HALF SLEEVE</t>
+  </si>
+  <si>
+    <t>৳540.00</t>
+  </si>
+  <si>
+    <t>105-0401-001</t>
+  </si>
+  <si>
+    <t>Black Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>৳575.00</t>
+  </si>
+  <si>
+    <t>৳1,150.00</t>
+  </si>
+  <si>
+    <t>107-0100-041</t>
+  </si>
+  <si>
+    <t>Black Boxer Brief</t>
+  </si>
+  <si>
+    <t>Men / 30% OFF,MEN,BOXER,BRIEFS,Draft Items</t>
+  </si>
+  <si>
     <t>৳1,920.00</t>
   </si>
   <si>
-    <t>৳4,368.00</t>
-  </si>
-  <si>
-    <t>৳1,280.00</t>
-  </si>
-  <si>
-    <t>৳2,912.00</t>
-  </si>
-  <si>
-    <t>109-0103-003</t>
-  </si>
-  <si>
-    <t>৳452.80</t>
-  </si>
-  <si>
-    <t>৳905.60</t>
-  </si>
-  <si>
-    <t>৳1,698.00</t>
-  </si>
-  <si>
-    <t>৳620.00</t>
-  </si>
-  <si>
-    <t>৳3,490.00</t>
-  </si>
-  <si>
-    <t>105-0202-004</t>
-  </si>
-  <si>
-    <t>Light Ash Full Sleeve Turtleneck T-shirt</t>
-  </si>
-  <si>
-    <t>৳698.00</t>
-  </si>
-  <si>
-    <t>৳228.76</t>
-  </si>
-  <si>
-    <t>৳686.27</t>
-  </si>
-  <si>
-    <t>109-0103-001</t>
-  </si>
-  <si>
-    <t>৳271.68</t>
-  </si>
-  <si>
-    <t>৳543.36</t>
-  </si>
-  <si>
-    <t>1105-0301-001</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Men / Drop Shoulder</t>
-  </si>
-  <si>
-    <t>৳550.00</t>
-  </si>
-  <si>
-    <t>৳3,300.00</t>
-  </si>
-  <si>
-    <t>৳5,040.00</t>
-  </si>
-  <si>
-    <t>109-0104-001</t>
-  </si>
-  <si>
-    <t>Card Holder 001</t>
-  </si>
-  <si>
-    <t>৳350.00</t>
-  </si>
-  <si>
-    <t>৳700.00</t>
-  </si>
-  <si>
-    <t>৳1,180.00</t>
-  </si>
-  <si>
-    <t>৳280.00</t>
-  </si>
-  <si>
-    <t>৳1,400.00</t>
-  </si>
-  <si>
-    <t>৳1,745.00</t>
-  </si>
-  <si>
-    <t>105-0301-007</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 07</t>
-  </si>
-  <si>
-    <t>XL</t>
-  </si>
-  <si>
-    <t>৳1,650.00</t>
-  </si>
-  <si>
-    <t>৳2,370.00</t>
-  </si>
-  <si>
-    <t>৳227.28</t>
-  </si>
-  <si>
-    <t>৳1,363.65</t>
-  </si>
-  <si>
-    <t>105-0301-008</t>
-  </si>
-  <si>
-    <t>Crew Graphic Drop Shoulder T-Shirt</t>
-  </si>
-  <si>
-    <t>3XL</t>
-  </si>
-  <si>
-    <t>Men / T-SHIRT</t>
-  </si>
-  <si>
-    <t>৳790.00</t>
-  </si>
-  <si>
-    <t>৳218.18</t>
-  </si>
-  <si>
-    <t>৳210.00</t>
-  </si>
-  <si>
-    <t>৳1,050.00</t>
-  </si>
-  <si>
-    <t>105-0301-005</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 05</t>
-  </si>
-  <si>
-    <t>৳1,580.00</t>
-  </si>
-  <si>
-    <t>109-0102-064</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 064</t>
-  </si>
-  <si>
-    <t>109-0402-057</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 57</t>
-  </si>
-  <si>
-    <t>109-0402-058</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 58</t>
-  </si>
-  <si>
-    <t>৳233.33</t>
-  </si>
-  <si>
-    <t>105-0301-003</t>
-  </si>
-  <si>
-    <t>Retro Car Print Drop Shoulder T-Shirt</t>
-  </si>
-  <si>
-    <t>109-0104-002</t>
-  </si>
-  <si>
-    <t>Card Holder 002</t>
-  </si>
-  <si>
-    <t>109-0104-003</t>
-  </si>
-  <si>
-    <t>Card Holder 003</t>
-  </si>
-  <si>
-    <t>৳590.00</t>
-  </si>
-  <si>
-    <t>৳185.94</t>
-  </si>
-  <si>
-    <t>৳557.81</t>
-  </si>
-  <si>
-    <t>109-0104-004</t>
-  </si>
-  <si>
-    <t>Card Holder 004</t>
-  </si>
-  <si>
-    <t>109-0402-051</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 51</t>
-  </si>
-  <si>
-    <t>৳35.87</t>
-  </si>
-  <si>
-    <t>৳143.48</t>
-  </si>
-  <si>
-    <t>৳3,960.00</t>
-  </si>
-  <si>
-    <t>109-0102-073</t>
-  </si>
-  <si>
-    <t>Bifold Leather Wallet 73</t>
-  </si>
-  <si>
-    <t>Men / WALLET,BI-FOLD</t>
-  </si>
-  <si>
-    <t>৳699.00</t>
-  </si>
-  <si>
-    <t>109-0402-048</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 48</t>
-  </si>
-  <si>
-    <t>৳1,980.00</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>৳4,740.00</t>
-  </si>
-  <si>
-    <t>109-0102-074</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 74</t>
-  </si>
-  <si>
-    <t>৳1,350.00</t>
-  </si>
-  <si>
-    <t>৳2,097.00</t>
-  </si>
-  <si>
-    <t>109-0502-001</t>
-  </si>
-  <si>
-    <t>Breathable Face Mask</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,MASK</t>
-  </si>
-  <si>
-    <t>৳199.51</t>
-  </si>
-  <si>
-    <t>৳1,396.60</t>
-  </si>
-  <si>
-    <t>৳1,960.00</t>
-  </si>
-  <si>
-    <t>105-0201-033</t>
-  </si>
-  <si>
-    <t>Full Sleeve Neon Stripe T-shirt</t>
-  </si>
-  <si>
-    <t>109-0402-050</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 50</t>
-  </si>
-  <si>
-    <t>109-0402-056</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 56</t>
-  </si>
-  <si>
-    <t>৳50.00</t>
-  </si>
-  <si>
-    <t>102-0302-005</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 005</t>
-  </si>
-  <si>
-    <t>Men / SHIRT</t>
-  </si>
-  <si>
-    <t>৳650.00</t>
-  </si>
-  <si>
-    <t>৳2,600.00</t>
-  </si>
-  <si>
-    <t>৳4,720.00</t>
-  </si>
-  <si>
-    <t>2XL</t>
-  </si>
-  <si>
-    <t>৳432.27</t>
-  </si>
-  <si>
-    <t>৳431.25</t>
-  </si>
-  <si>
-    <t>101-0300-140</t>
-  </si>
-  <si>
-    <t>Straight Fit Blue Jeans</t>
-  </si>
-  <si>
-    <t>৳8,450.00</t>
-  </si>
-  <si>
-    <t>102-0302-008</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 008</t>
-  </si>
-  <si>
-    <t>৳500.00</t>
-  </si>
-  <si>
-    <t>৳2,000.00</t>
-  </si>
-  <si>
-    <t>৳5,300.00</t>
-  </si>
-  <si>
-    <t>105-0301-004</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 004</t>
-  </si>
-  <si>
-    <t>Men / T-SHIRT,Drop Shoulder</t>
-  </si>
-  <si>
-    <t>৳2,520.00</t>
-  </si>
-  <si>
-    <t>৳840.00</t>
-  </si>
-  <si>
-    <t>109-0402-061</t>
-  </si>
-  <si>
-    <t>Premium Leather Belt 061</t>
-  </si>
-  <si>
-    <t>109-0102-072</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 72</t>
-  </si>
-  <si>
-    <t>৳1,398.00</t>
-  </si>
-  <si>
-    <t>105-0301-009</t>
-  </si>
-  <si>
-    <t>Deep Violet Drop Shoulder T-Shirt</t>
-  </si>
-  <si>
-    <t>109-0501-001</t>
-  </si>
-  <si>
-    <t>Durable Aluminum Water Bottle 600 ml.</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,WATER BOTTLE</t>
-  </si>
-  <si>
-    <t>৳155.51</t>
-  </si>
-  <si>
-    <t>৳1,399.55</t>
-  </si>
-  <si>
-    <t>৳3,591.00</t>
-  </si>
-  <si>
-    <t>৳2,184.00</t>
-  </si>
-  <si>
-    <t>৳332.44</t>
-  </si>
-  <si>
-    <t>৳1,329.77</t>
-  </si>
-  <si>
-    <t>৳3,160.00</t>
-  </si>
-  <si>
-    <t>109-0104-005</t>
-  </si>
-  <si>
-    <t>Card Holder</t>
-  </si>
-  <si>
-    <t>Men / Card Holder</t>
-  </si>
-  <si>
-    <t>৳690.00</t>
-  </si>
-  <si>
-    <t>109-0104-006</t>
-  </si>
-  <si>
-    <t>Card Holder 06</t>
-  </si>
-  <si>
-    <t>105-0301-001</t>
-  </si>
-  <si>
-    <t>105-0401-006</t>
-  </si>
-  <si>
-    <t>Burgundy Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>Men / Tank Top</t>
-  </si>
-  <si>
-    <t>৳250.00</t>
-  </si>
-  <si>
-    <t>৳750.00</t>
-  </si>
-  <si>
-    <t>৳1,620.00</t>
-  </si>
-  <si>
-    <t>102-0302-006</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 006</t>
-  </si>
-  <si>
-    <t>৳1,950.00</t>
-  </si>
-  <si>
-    <t>৳3,975.00</t>
-  </si>
-  <si>
-    <t>103-0200-098</t>
-  </si>
-  <si>
-    <t>White Polo Shirt in Cotton Pique</t>
-  </si>
-  <si>
-    <t>৳798.00</t>
-  </si>
-  <si>
-    <t>৳1,000.00</t>
-  </si>
-  <si>
-    <t>৳2,650.00</t>
-  </si>
-  <si>
-    <t>৳111.94</t>
-  </si>
-  <si>
-    <t>102-0402-032</t>
-  </si>
-  <si>
-    <t>Dark Blue Denim Shirt</t>
-  </si>
-  <si>
-    <t>Men / NEW IN,NEW,MEN,SHIRT,CASUAL SHIRT,DENIM SHIRT,FULL SLEEVE</t>
-  </si>
-  <si>
-    <t>103-0200-100</t>
-  </si>
-  <si>
-    <t>Malibu Polo Shirt in Cotton Pique</t>
-  </si>
-  <si>
-    <t>102-0302-002</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 002</t>
-  </si>
-  <si>
-    <t>৳560.00</t>
-  </si>
-  <si>
-    <t>৳2,800.00</t>
-  </si>
-  <si>
-    <t>৳7,250.00</t>
-  </si>
-  <si>
-    <t>109-0101-050</t>
-  </si>
-  <si>
-    <t>Leather Long Wallet 50</t>
-  </si>
-  <si>
-    <t>Men / WALLET,LONG</t>
-  </si>
-  <si>
-    <t>৳1,299.00</t>
-  </si>
-  <si>
-    <t>102-0301-002</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 002</t>
-  </si>
-  <si>
-    <t>102-0301-004</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 004</t>
-  </si>
-  <si>
-    <t>৳325.00</t>
-  </si>
-  <si>
-    <t>৳7,080.00</t>
-  </si>
-  <si>
-    <t>105-0401-005</t>
-  </si>
-  <si>
-    <t>Sable Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>105-0401-003</t>
-  </si>
-  <si>
-    <t>Tank Top 003</t>
-  </si>
-  <si>
-    <t>Men / T-SHIRT,Tank Top</t>
-  </si>
-  <si>
-    <t>৳5,120.00</t>
-  </si>
-  <si>
-    <t>৳2,700.00</t>
-  </si>
-  <si>
-    <t>৳3,540.00</t>
-  </si>
-  <si>
-    <t>102-0302-001</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 001</t>
-  </si>
-  <si>
-    <t>৳1,300.00</t>
-  </si>
-  <si>
-    <t>109-0101-049</t>
-  </si>
-  <si>
-    <t>Leather Long Wallet 049</t>
-  </si>
-  <si>
-    <t>৳1,080.00</t>
-  </si>
-  <si>
-    <t>৳3,250.00</t>
-  </si>
-  <si>
-    <t>৳8,320.00</t>
-  </si>
-  <si>
-    <t>105-0401-007</t>
-  </si>
-  <si>
-    <t>Cabbage Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>৳1,770.00</t>
-  </si>
-  <si>
-    <t>৳278.57</t>
-  </si>
-  <si>
-    <t>৳8,260.00</t>
-  </si>
-  <si>
-    <t>৳4,350.00</t>
-  </si>
-  <si>
-    <t>108-0101-013</t>
-  </si>
-  <si>
-    <t>Brown Sweatshirt in French-Terry</t>
-  </si>
-  <si>
-    <t>105-0401-004</t>
-  </si>
-  <si>
-    <t>Orlando Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>৳2,560.00</t>
-  </si>
-  <si>
-    <t>102-0302-010</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 010</t>
-  </si>
-  <si>
-    <t>102-0302-004</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 004</t>
-  </si>
-  <si>
-    <t>৳2,900.00</t>
-  </si>
-  <si>
-    <t>102-0302-007</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 007</t>
-  </si>
-  <si>
-    <t>105-0101-377</t>
-  </si>
-  <si>
-    <t>Warm Spice T-shirt</t>
-  </si>
-  <si>
-    <t>Men / NEW IN,NEW,MEN,T-SHIRT,HALF SLEEVE</t>
-  </si>
-  <si>
-    <t>৳540.00</t>
-  </si>
-  <si>
-    <t>105-0401-001</t>
-  </si>
-  <si>
-    <t>Black Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>৳575.00</t>
-  </si>
-  <si>
-    <t>৳1,150.00</t>
-  </si>
-  <si>
-    <t>৳2,360.00</t>
-  </si>
-  <si>
-    <t>107-0100-041</t>
-  </si>
-  <si>
-    <t>Black Boxer Brief</t>
-  </si>
-  <si>
-    <t>Men / 30% OFF,MEN,BOXER,BRIEFS,Draft Items</t>
-  </si>
-  <si>
     <t>109-0101-045</t>
   </si>
   <si>
@@ -1520,9 +1517,6 @@
     <t>৳140.00</t>
   </si>
   <si>
-    <t>৳420.00</t>
-  </si>
-  <si>
     <t>102-0501-001</t>
   </si>
   <si>
@@ -1544,6 +1538,12 @@
     <t>৳175.00</t>
   </si>
   <si>
+    <t>৳875.00</t>
+  </si>
+  <si>
+    <t>৳2,950.00</t>
+  </si>
+  <si>
     <t>105-0101-374</t>
   </si>
   <si>
@@ -1619,9 +1619,6 @@
     <t>Essential White T-shirt</t>
   </si>
   <si>
-    <t>৳2,950.00</t>
-  </si>
-  <si>
     <t>102-0301-009</t>
   </si>
   <si>
@@ -1686,9 +1683,6 @@
   </si>
   <si>
     <t>Teal Trousers</t>
-  </si>
-  <si>
-    <t>৳3,640.00</t>
   </si>
   <si>
     <t>109-0102-052</t>
@@ -2163,7 +2157,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I324"/>
+  <dimension ref="A1:I322"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3581,7 +3575,7 @@
         <v>129</v>
       </c>
       <c r="F55">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G55" t="s">
         <v>145</v>
@@ -3795,7 +3789,7 @@
         <v>172</v>
       </c>
       <c r="I63" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -3841,10 +3835,10 @@
         <v>2.0</v>
       </c>
       <c r="G65" t="s">
+        <v>173</v>
+      </c>
+      <c r="H65" t="s">
         <v>174</v>
-      </c>
-      <c r="H65" t="s">
-        <v>175</v>
       </c>
       <c r="I65" t="s">
         <v>117</v>
@@ -3870,10 +3864,10 @@
         <v>135</v>
       </c>
       <c r="H66" t="s">
+        <v>175</v>
+      </c>
+      <c r="I66" t="s">
         <v>176</v>
-      </c>
-      <c r="I66" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -3893,21 +3887,21 @@
         <v>3.0</v>
       </c>
       <c r="G67" t="s">
+        <v>177</v>
+      </c>
+      <c r="H67" t="s">
         <v>178</v>
       </c>
-      <c r="H67" t="s">
+      <c r="I67" t="s">
         <v>179</v>
-      </c>
-      <c r="I67" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
+        <v>180</v>
+      </c>
+      <c r="B68" t="s">
         <v>181</v>
-      </c>
-      <c r="B68" t="s">
-        <v>182</v>
       </c>
       <c r="C68" t="s">
         <v>115</v>
@@ -3919,10 +3913,10 @@
         <v>1.0</v>
       </c>
       <c r="G68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I68" t="s">
         <v>136</v>
@@ -3948,10 +3942,10 @@
         <v>169</v>
       </c>
       <c r="H69" t="s">
+        <v>183</v>
+      </c>
+      <c r="I69" t="s">
         <v>184</v>
-      </c>
-      <c r="I69" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -3968,16 +3962,16 @@
         <v>129</v>
       </c>
       <c r="F70">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G70" t="s">
+        <v>185</v>
+      </c>
+      <c r="H70" t="s">
         <v>186</v>
       </c>
-      <c r="H70" t="s">
+      <c r="I70" t="s">
         <v>187</v>
-      </c>
-      <c r="I70" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -4144,7 +4138,7 @@
         <v>134</v>
       </c>
       <c r="F77">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G77" t="s">
         <v>209</v>
@@ -4153,33 +4147,33 @@
         <v>210</v>
       </c>
       <c r="I77" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B78" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C78" t="s">
         <v>144</v>
       </c>
       <c r="E78" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F78">
         <v>1.0</v>
       </c>
       <c r="G78" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H78" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I78" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -4199,13 +4193,13 @@
         <v>2.0</v>
       </c>
       <c r="G79" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H79" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I79" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -4450,7 +4444,7 @@
         <v>244</v>
       </c>
       <c r="F89">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G89" t="s">
         <v>169</v>
@@ -4638,7 +4632,7 @@
         <v>268</v>
       </c>
       <c r="I96" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -4715,16 +4709,16 @@
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B100" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C100" t="s">
         <v>170</v>
       </c>
       <c r="E100" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F100">
         <v>5.0</v>
@@ -4753,16 +4747,16 @@
         <v>275</v>
       </c>
       <c r="F101">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G101" t="s">
         <v>276</v>
       </c>
       <c r="H101" t="s">
+        <v>199</v>
+      </c>
+      <c r="I101" t="s">
         <v>290</v>
-      </c>
-      <c r="I101" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -4782,27 +4776,27 @@
         <v>6.0</v>
       </c>
       <c r="G102" t="s">
+        <v>291</v>
+      </c>
+      <c r="H102" t="s">
         <v>292</v>
       </c>
-      <c r="H102" t="s">
-        <v>293</v>
-      </c>
       <c r="I102" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
+        <v>293</v>
+      </c>
+      <c r="B103" t="s">
         <v>294</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C103" t="s">
         <v>295</v>
       </c>
-      <c r="C103" t="s">
+      <c r="E103" t="s">
         <v>296</v>
-      </c>
-      <c r="E103" t="s">
-        <v>297</v>
       </c>
       <c r="F103">
         <v>1.0</v>
@@ -4814,7 +4808,7 @@
         <v>281</v>
       </c>
       <c r="I103" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -4834,10 +4828,10 @@
         <v>1.0</v>
       </c>
       <c r="G104" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H104" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I104" t="s">
         <v>136</v>
@@ -4860,10 +4854,10 @@
         <v>5.0</v>
       </c>
       <c r="G105" t="s">
+        <v>299</v>
+      </c>
+      <c r="H105" t="s">
         <v>300</v>
-      </c>
-      <c r="H105" t="s">
-        <v>301</v>
       </c>
       <c r="I105" t="s">
         <v>151</v>
@@ -4871,10 +4865,10 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
+        <v>301</v>
+      </c>
+      <c r="B106" t="s">
         <v>302</v>
-      </c>
-      <c r="B106" t="s">
-        <v>303</v>
       </c>
       <c r="C106" t="s">
         <v>274</v>
@@ -4892,15 +4886,15 @@
         <v>199</v>
       </c>
       <c r="I106" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B107" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E107" t="s">
         <v>226</v>
@@ -4920,10 +4914,10 @@
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B108" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E108" t="s">
         <v>197</v>
@@ -4943,10 +4937,10 @@
     </row>
     <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B109" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E109" t="s">
         <v>197</v>
@@ -4981,10 +4975,10 @@
         <v>1.0</v>
       </c>
       <c r="G110" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H110" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="I110" t="s">
         <v>266</v>
@@ -4992,16 +4986,16 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B111" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C111" t="s">
         <v>274</v>
       </c>
       <c r="E111" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F111">
         <v>1.0</v>
@@ -5013,15 +5007,15 @@
         <v>281</v>
       </c>
       <c r="I111" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B112" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E112" t="s">
         <v>226</v>
@@ -5041,10 +5035,10 @@
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B113" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E113" t="s">
         <v>226</v>
@@ -5059,7 +5053,7 @@
         <v>281</v>
       </c>
       <c r="I113" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -5076,24 +5070,24 @@
         <v>134</v>
       </c>
       <c r="F114">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G114" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H114" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I114" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B115" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E115" t="s">
         <v>226</v>
@@ -5113,10 +5107,10 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B116" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E116" t="s">
         <v>197</v>
@@ -5125,24 +5119,24 @@
         <v>4.0</v>
       </c>
       <c r="G116" t="s">
+        <v>323</v>
+      </c>
+      <c r="H116" t="s">
+        <v>324</v>
+      </c>
+      <c r="I116" t="s">
         <v>325</v>
-      </c>
-      <c r="H116" t="s">
-        <v>326</v>
-      </c>
-      <c r="I116" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
+        <v>326</v>
+      </c>
+      <c r="B117" t="s">
+        <v>327</v>
+      </c>
+      <c r="E117" t="s">
         <v>328</v>
-      </c>
-      <c r="B117" t="s">
-        <v>329</v>
-      </c>
-      <c r="E117" t="s">
-        <v>330</v>
       </c>
       <c r="F117">
         <v>1.0</v>
@@ -5154,15 +5148,15 @@
         <v>227</v>
       </c>
       <c r="I117" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B118" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E118" t="s">
         <v>197</v>
@@ -5177,7 +5171,7 @@
         <v>72</v>
       </c>
       <c r="I118" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -5188,7 +5182,7 @@
         <v>288</v>
       </c>
       <c r="C119" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E119" t="s">
         <v>275</v>
@@ -5203,18 +5197,18 @@
         <v>277</v>
       </c>
       <c r="I119" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B120" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E120" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F120">
         <v>3.0</v>
@@ -5223,41 +5217,41 @@
         <v>227</v>
       </c>
       <c r="H120" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="I120" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
+        <v>339</v>
+      </c>
+      <c r="B121" t="s">
+        <v>340</v>
+      </c>
+      <c r="E121" t="s">
         <v>341</v>
-      </c>
-      <c r="B121" t="s">
-        <v>342</v>
-      </c>
-      <c r="E121" t="s">
-        <v>343</v>
       </c>
       <c r="F121">
         <v>7.0</v>
       </c>
       <c r="G121" t="s">
+        <v>342</v>
+      </c>
+      <c r="H121" t="s">
+        <v>343</v>
+      </c>
+      <c r="I121" t="s">
         <v>344</v>
-      </c>
-      <c r="H121" t="s">
-        <v>345</v>
-      </c>
-      <c r="I121" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B122" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C122" t="s">
         <v>170</v>
@@ -5280,10 +5274,10 @@
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B123" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E123" t="s">
         <v>197</v>
@@ -5298,15 +5292,15 @@
         <v>72</v>
       </c>
       <c r="I123" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B124" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E124" t="s">
         <v>197</v>
@@ -5315,10 +5309,10 @@
         <v>1.0</v>
       </c>
       <c r="G124" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H124" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I124" t="s">
         <v>203</v>
@@ -5326,28 +5320,28 @@
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B125" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C125" t="s">
         <v>274</v>
       </c>
       <c r="E125" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F125">
         <v>4.0</v>
       </c>
       <c r="G125" t="s">
+        <v>355</v>
+      </c>
+      <c r="H125" t="s">
+        <v>356</v>
+      </c>
+      <c r="I125" t="s">
         <v>357</v>
-      </c>
-      <c r="H125" t="s">
-        <v>358</v>
-      </c>
-      <c r="I125" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -5358,7 +5352,7 @@
         <v>288</v>
       </c>
       <c r="C126" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E126" t="s">
         <v>275</v>
@@ -5367,24 +5361,24 @@
         <v>1.0</v>
       </c>
       <c r="G126" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H126" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="I126" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="127" spans="1:9">
       <c r="A127" t="s">
+        <v>301</v>
+      </c>
+      <c r="B127" t="s">
         <v>302</v>
       </c>
-      <c r="B127" t="s">
-        <v>303</v>
-      </c>
       <c r="C127" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E127" t="s">
         <v>275</v>
@@ -5393,21 +5387,21 @@
         <v>1.0</v>
       </c>
       <c r="G127" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H127" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="I127" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B128" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C128">
         <v>28</v>
@@ -5425,73 +5419,73 @@
         <v>72</v>
       </c>
       <c r="I128" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B129" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C129" t="s">
         <v>274</v>
       </c>
       <c r="E129" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F129">
         <v>4.0</v>
       </c>
       <c r="G129" t="s">
+        <v>366</v>
+      </c>
+      <c r="H129" t="s">
+        <v>367</v>
+      </c>
+      <c r="I129" t="s">
         <v>368</v>
-      </c>
-      <c r="H129" t="s">
-        <v>369</v>
-      </c>
-      <c r="I129" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B130" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C130" t="s">
         <v>289</v>
       </c>
       <c r="E130" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F130">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G130" t="s">
         <v>281</v>
       </c>
       <c r="H130" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="I130" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B131" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C131" t="s">
         <v>274</v>
       </c>
       <c r="E131" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F131">
         <v>1.0</v>
@@ -5503,15 +5497,15 @@
         <v>281</v>
       </c>
       <c r="I131" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B132" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E132" t="s">
         <v>197</v>
@@ -5526,44 +5520,44 @@
         <v>228</v>
       </c>
       <c r="I132" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B133" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E133" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F133">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G133" t="s">
         <v>227</v>
       </c>
       <c r="H133" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I133" t="s">
-        <v>380</v>
+        <v>329</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B134" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C134" t="s">
         <v>274</v>
       </c>
       <c r="E134" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F134">
         <v>2.0</v>
@@ -5575,21 +5569,21 @@
         <v>282</v>
       </c>
       <c r="I134" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" t="s">
+        <v>293</v>
+      </c>
+      <c r="B135" t="s">
         <v>294</v>
       </c>
-      <c r="B135" t="s">
-        <v>295</v>
-      </c>
       <c r="C135" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E135" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F135">
         <v>2.0</v>
@@ -5601,21 +5595,21 @@
         <v>282</v>
       </c>
       <c r="I135" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" t="s">
+        <v>293</v>
+      </c>
+      <c r="B136" t="s">
         <v>294</v>
-      </c>
-      <c r="B136" t="s">
-        <v>295</v>
       </c>
       <c r="C136" t="s">
         <v>289</v>
       </c>
       <c r="E136" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F136">
         <v>2.0</v>
@@ -5627,64 +5621,64 @@
         <v>282</v>
       </c>
       <c r="I136" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B137" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E137" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F137">
         <v>9.0</v>
       </c>
       <c r="G137" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="H137" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I137" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B138" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C138" t="s">
         <v>289</v>
       </c>
       <c r="E138" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F138">
         <v>4.0</v>
       </c>
       <c r="G138" t="s">
+        <v>355</v>
+      </c>
+      <c r="H138" t="s">
+        <v>356</v>
+      </c>
+      <c r="I138" t="s">
         <v>357</v>
-      </c>
-      <c r="H138" t="s">
-        <v>358</v>
-      </c>
-      <c r="I138" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B139" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C139" t="s">
         <v>152</v>
@@ -5702,44 +5696,44 @@
         <v>72</v>
       </c>
       <c r="I139" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="140" spans="1:9">
       <c r="A140" t="s">
+        <v>293</v>
+      </c>
+      <c r="B140" t="s">
         <v>294</v>
-      </c>
-      <c r="B140" t="s">
-        <v>295</v>
       </c>
       <c r="C140" t="s">
         <v>274</v>
       </c>
       <c r="E140" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F140">
         <v>4.0</v>
       </c>
       <c r="G140" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="H140" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="I140" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B141" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E141" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F141">
         <v>1.0</v>
@@ -5751,18 +5745,18 @@
         <v>281</v>
       </c>
       <c r="I141" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B142" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E142" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F142">
         <v>1.0</v>
@@ -5774,18 +5768,18 @@
         <v>281</v>
       </c>
       <c r="I142" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B143" t="s">
         <v>273</v>
       </c>
       <c r="C143" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E143" t="s">
         <v>275</v>
@@ -5800,47 +5794,47 @@
         <v>276</v>
       </c>
       <c r="I143" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B144" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C144" t="s">
         <v>274</v>
       </c>
       <c r="E144" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F144">
         <v>3.0</v>
       </c>
       <c r="G144" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H144" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="I144" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B145" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C145" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E145" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F145">
         <v>3.0</v>
@@ -5849,44 +5843,44 @@
         <v>281</v>
       </c>
       <c r="H145" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I145" t="s">
-        <v>291</v>
+        <v>402</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B146" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C146" t="s">
         <v>274</v>
       </c>
       <c r="E146" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F146">
         <v>3.0</v>
       </c>
       <c r="G146" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H146" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I146" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B147" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C147" t="s">
         <v>170</v>
@@ -5904,21 +5898,21 @@
         <v>72</v>
       </c>
       <c r="I147" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" t="s">
+        <v>293</v>
+      </c>
+      <c r="B148" t="s">
         <v>294</v>
       </c>
-      <c r="B148" t="s">
-        <v>295</v>
-      </c>
       <c r="C148" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E148" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F148">
         <v>2.0</v>
@@ -5930,33 +5924,33 @@
         <v>282</v>
       </c>
       <c r="I148" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B149" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C149" t="s">
         <v>289</v>
       </c>
       <c r="E149" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F149">
         <v>2.0</v>
       </c>
       <c r="G149" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H149" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I149" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -5976,10 +5970,10 @@
         <v>1.0</v>
       </c>
       <c r="G150" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="H150" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="I150" t="s">
         <v>266</v>
@@ -5987,16 +5981,16 @@
     </row>
     <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B151" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C151" t="s">
         <v>152</v>
       </c>
       <c r="E151" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="F151">
         <v>1.0</v>
@@ -6013,10 +6007,10 @@
     </row>
     <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B152" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C152" t="s">
         <v>115</v>
@@ -6034,327 +6028,327 @@
         <v>72</v>
       </c>
       <c r="I152" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B153" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C153" t="s">
         <v>274</v>
       </c>
       <c r="E153" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F153">
         <v>5.0</v>
       </c>
       <c r="G153" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="H153" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="I153" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" t="s">
+        <v>423</v>
+      </c>
+      <c r="B154" t="s">
+        <v>424</v>
+      </c>
+      <c r="E154" t="s">
+        <v>425</v>
+      </c>
+      <c r="F154">
+        <v>1.0</v>
+      </c>
+      <c r="G154" t="s">
+        <v>72</v>
+      </c>
+      <c r="H154" t="s">
+        <v>72</v>
+      </c>
+      <c r="I154" t="s">
         <v>426</v>
-      </c>
-      <c r="B154" t="s">
-        <v>427</v>
-      </c>
-      <c r="E154" t="s">
-        <v>428</v>
-      </c>
-      <c r="F154">
-        <v>1.0</v>
-      </c>
-      <c r="G154" t="s">
-        <v>72</v>
-      </c>
-      <c r="H154" t="s">
-        <v>72</v>
-      </c>
-      <c r="I154" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B155" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C155" t="s">
         <v>274</v>
       </c>
       <c r="E155" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F155">
         <v>3.0</v>
       </c>
       <c r="G155" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H155" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I155" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B156" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C156" t="s">
         <v>274</v>
       </c>
       <c r="E156" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F156">
         <v>6.0</v>
       </c>
       <c r="G156" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H156" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I156" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B157" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C157" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E157" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F157">
         <v>3.0</v>
       </c>
       <c r="G157" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H157" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="I157" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B158" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C158" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E158" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F158">
         <v>8.0</v>
       </c>
       <c r="G158" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H158" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I158" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B159" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C159" t="s">
         <v>289</v>
       </c>
       <c r="E159" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F159">
         <v>5.0</v>
       </c>
       <c r="G159" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H159" t="s">
         <v>45</v>
       </c>
       <c r="I159" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="160" spans="1:9">
       <c r="A160" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B160" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C160" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E160" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F160">
         <v>2.0</v>
       </c>
       <c r="G160" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H160" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I160" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
+        <v>352</v>
+      </c>
+      <c r="B161" t="s">
+        <v>353</v>
+      </c>
+      <c r="C161" t="s">
+        <v>358</v>
+      </c>
+      <c r="E161" t="s">
         <v>354</v>
-      </c>
-      <c r="B161" t="s">
-        <v>355</v>
-      </c>
-      <c r="C161" t="s">
-        <v>360</v>
-      </c>
-      <c r="E161" t="s">
-        <v>356</v>
       </c>
       <c r="F161">
         <v>3.0</v>
       </c>
       <c r="G161" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H161" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I161" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B162" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C162" t="s">
         <v>274</v>
       </c>
       <c r="E162" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F162">
         <v>5.0</v>
       </c>
       <c r="G162" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="H162" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="I162" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B163" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C163" t="s">
         <v>289</v>
       </c>
       <c r="E163" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F163">
         <v>2.0</v>
       </c>
       <c r="G163" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H163" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="I163" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B164" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C164" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E164" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F164">
         <v>2.0</v>
       </c>
       <c r="G164" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H164" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I164" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B165" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E165" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F165">
         <v>1.0</v>
@@ -6366,160 +6360,160 @@
         <v>72</v>
       </c>
       <c r="I165" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B166" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C166" t="s">
         <v>274</v>
       </c>
       <c r="E166" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F166">
         <v>2.0</v>
       </c>
       <c r="G166" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H166" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I166" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B167" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C167" t="s">
         <v>274</v>
       </c>
       <c r="E167" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F167">
         <v>13.0</v>
       </c>
       <c r="G167" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H167" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="I167" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B168" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C168" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E168" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F168">
         <v>2.0</v>
       </c>
       <c r="G168" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H168" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="I168" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B169" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C169" t="s">
         <v>289</v>
       </c>
       <c r="E169" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F169">
         <v>2.0</v>
       </c>
       <c r="G169" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H169" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I169" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B170" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C170" t="s">
         <v>289</v>
       </c>
       <c r="E170" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F170">
         <v>3.0</v>
       </c>
       <c r="G170" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H170" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="I170" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B171" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C171" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E171" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F171">
         <v>2.0</v>
       </c>
       <c r="G171" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H171" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I171" t="s">
         <v>256</v>
@@ -6527,68 +6521,68 @@
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B172" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C172" t="s">
         <v>289</v>
       </c>
       <c r="E172" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F172">
         <v>3.0</v>
       </c>
       <c r="G172" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H172" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I172" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B173" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C173" t="s">
         <v>289</v>
       </c>
       <c r="E173" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F173">
         <v>7.0</v>
       </c>
       <c r="G173" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="H173" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="I173" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B174" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C174" t="s">
         <v>289</v>
       </c>
       <c r="E174" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F174">
         <v>3.0</v>
@@ -6597,18 +6591,18 @@
         <v>276</v>
       </c>
       <c r="H174" t="s">
-        <v>290</v>
+        <v>454</v>
       </c>
       <c r="I174" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B175" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C175" t="s">
         <v>115</v>
@@ -6631,25 +6625,25 @@
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B176" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C176" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E176" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F176">
         <v>1.0</v>
       </c>
       <c r="G176" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H176" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="I176" t="s">
         <v>250</v>
@@ -6657,198 +6651,198 @@
     </row>
     <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B177" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C177" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E177" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F177">
         <v>4.0</v>
       </c>
       <c r="G177" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H177" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I177" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B178" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C178" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E178" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F178">
         <v>2.0</v>
       </c>
       <c r="G178" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H178" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I178" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B179" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C179" t="s">
         <v>274</v>
       </c>
       <c r="E179" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F179">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G179" t="s">
         <v>276</v>
       </c>
       <c r="H179" t="s">
-        <v>290</v>
+        <v>199</v>
       </c>
       <c r="I179" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
     </row>
     <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B180" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C180" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E180" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F180">
         <v>2.0</v>
       </c>
       <c r="G180" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H180" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="I180" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="181" spans="1:9">
       <c r="A181" t="s">
+        <v>464</v>
+      </c>
+      <c r="B181" t="s">
         <v>465</v>
-      </c>
-      <c r="B181" t="s">
-        <v>466</v>
       </c>
       <c r="C181" t="s">
         <v>274</v>
       </c>
       <c r="E181" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F181">
         <v>2.0</v>
       </c>
       <c r="G181" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H181" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I181" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="182" spans="1:9">
       <c r="A182" t="s">
+        <v>467</v>
+      </c>
+      <c r="B182" t="s">
         <v>468</v>
-      </c>
-      <c r="B182" t="s">
-        <v>469</v>
       </c>
       <c r="C182" t="s">
         <v>274</v>
       </c>
       <c r="E182" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F182">
         <v>2.0</v>
       </c>
       <c r="G182" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H182" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I182" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B183" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C183" t="s">
         <v>289</v>
       </c>
       <c r="E183" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F183">
         <v>2.0</v>
       </c>
       <c r="G183" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H183" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I183" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="184" spans="1:9">
       <c r="A184" t="s">
+        <v>469</v>
+      </c>
+      <c r="B184" t="s">
         <v>470</v>
-      </c>
-      <c r="B184" t="s">
-        <v>471</v>
       </c>
       <c r="C184" t="s">
         <v>115</v>
       </c>
       <c r="E184" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F184">
         <v>1.0</v>
@@ -6860,47 +6854,47 @@
         <v>72</v>
       </c>
       <c r="I184" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B185" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C185" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E185" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F185">
         <v>1.0</v>
       </c>
       <c r="G185" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H185" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="I185" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="186" spans="1:9">
       <c r="A186" t="s">
+        <v>473</v>
+      </c>
+      <c r="B186" t="s">
         <v>474</v>
-      </c>
-      <c r="B186" t="s">
-        <v>475</v>
       </c>
       <c r="C186" t="s">
         <v>289</v>
       </c>
       <c r="E186" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F186">
         <v>4.0</v>
@@ -6912,47 +6906,47 @@
         <v>285</v>
       </c>
       <c r="I186" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B187" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C187" t="s">
         <v>289</v>
       </c>
       <c r="E187" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F187">
         <v>2.0</v>
       </c>
       <c r="G187" t="s">
+        <v>475</v>
+      </c>
+      <c r="H187" t="s">
         <v>476</v>
       </c>
-      <c r="H187" t="s">
-        <v>477</v>
-      </c>
       <c r="I187" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
     </row>
     <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B188" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C188" t="s">
         <v>170</v>
       </c>
       <c r="E188" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F188">
         <v>2.0</v>
@@ -6969,16 +6963,16 @@
     </row>
     <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B189" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C189" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E189" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F189">
         <v>1.0</v>
@@ -6995,16 +6989,16 @@
     </row>
     <row r="190" spans="1:9">
       <c r="A190" t="s">
+        <v>473</v>
+      </c>
+      <c r="B190" t="s">
         <v>474</v>
       </c>
-      <c r="B190" t="s">
-        <v>475</v>
-      </c>
       <c r="C190" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E190" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F190">
         <v>3.0</v>
@@ -7013,74 +7007,74 @@
         <v>281</v>
       </c>
       <c r="H190" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I190" t="s">
-        <v>254</v>
+        <v>480</v>
       </c>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B191" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C191" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E191" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F191">
         <v>2.0</v>
       </c>
       <c r="G191" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H191" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I191" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B192" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C192" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E192" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F192">
         <v>2.0</v>
       </c>
       <c r="G192" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H192" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I192" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="193" spans="1:9">
       <c r="A193" t="s">
+        <v>481</v>
+      </c>
+      <c r="B193" t="s">
         <v>482</v>
       </c>
-      <c r="B193" t="s">
+      <c r="E193" t="s">
         <v>483</v>
       </c>
-      <c r="E193" t="s">
-        <v>484</v>
-      </c>
       <c r="F193">
         <v>1.0</v>
       </c>
@@ -7091,56 +7085,56 @@
         <v>72</v>
       </c>
       <c r="I193" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="194" spans="1:9">
       <c r="A194" t="s">
+        <v>484</v>
+      </c>
+      <c r="B194" t="s">
         <v>485</v>
-      </c>
-      <c r="B194" t="s">
-        <v>486</v>
       </c>
       <c r="C194" t="s">
         <v>152</v>
       </c>
       <c r="E194" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F194">
         <v>5.0</v>
       </c>
       <c r="G194" t="s">
+        <v>299</v>
+      </c>
+      <c r="H194" t="s">
         <v>300</v>
       </c>
-      <c r="H194" t="s">
-        <v>301</v>
-      </c>
       <c r="I194" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B195" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C195" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E195" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F195">
         <v>1.0</v>
       </c>
       <c r="G195" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H195" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="I195" t="s">
         <v>250</v>
@@ -7148,19 +7142,19 @@
     </row>
     <row r="196" spans="1:9">
       <c r="A196" t="s">
+        <v>469</v>
+      </c>
+      <c r="B196" t="s">
         <v>470</v>
-      </c>
-      <c r="B196" t="s">
-        <v>471</v>
       </c>
       <c r="C196" t="s">
         <v>152</v>
       </c>
       <c r="E196" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F196">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G196" t="s">
         <v>72</v>
@@ -7169,145 +7163,145 @@
         <v>72</v>
       </c>
       <c r="I196" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" t="s">
+        <v>364</v>
+      </c>
+      <c r="B197" t="s">
+        <v>365</v>
+      </c>
+      <c r="C197" t="s">
+        <v>295</v>
+      </c>
+      <c r="E197" t="s">
+        <v>354</v>
+      </c>
+      <c r="F197">
+        <v>1.0</v>
+      </c>
+      <c r="G197" t="s">
         <v>366</v>
       </c>
-      <c r="B197" t="s">
-        <v>367</v>
-      </c>
-      <c r="C197" t="s">
-        <v>296</v>
-      </c>
-      <c r="E197" t="s">
-        <v>356</v>
-      </c>
-      <c r="F197">
-        <v>1.0</v>
-      </c>
-      <c r="G197" t="s">
-        <v>368</v>
-      </c>
       <c r="H197" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I197" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="198" spans="1:9">
       <c r="A198" t="s">
+        <v>488</v>
+      </c>
+      <c r="B198" t="s">
         <v>489</v>
       </c>
-      <c r="B198" t="s">
-        <v>490</v>
-      </c>
       <c r="C198" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E198" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F198">
         <v>1.0</v>
       </c>
       <c r="G198" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H198" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="I198" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B199" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C199" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E199" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F199">
         <v>1.0</v>
       </c>
       <c r="G199" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H199" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="I199" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B200" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C200" t="s">
         <v>289</v>
       </c>
       <c r="E200" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F200">
         <v>7.0</v>
       </c>
       <c r="G200" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H200" t="s">
+        <v>490</v>
+      </c>
+      <c r="I200" t="s">
         <v>491</v>
-      </c>
-      <c r="I200" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="201" spans="1:9">
       <c r="A201" t="s">
+        <v>467</v>
+      </c>
+      <c r="B201" t="s">
         <v>468</v>
       </c>
-      <c r="B201" t="s">
-        <v>469</v>
-      </c>
       <c r="C201" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E201" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F201">
         <v>1.0</v>
       </c>
       <c r="G201" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H201" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I201" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="202" spans="1:9">
       <c r="A202" t="s">
+        <v>492</v>
+      </c>
+      <c r="B202" t="s">
         <v>493</v>
-      </c>
-      <c r="B202" t="s">
-        <v>494</v>
       </c>
       <c r="C202" t="s">
         <v>144</v>
@@ -7330,16 +7324,16 @@
     </row>
     <row r="203" spans="1:9">
       <c r="A203" t="s">
+        <v>473</v>
+      </c>
+      <c r="B203" t="s">
         <v>474</v>
       </c>
-      <c r="B203" t="s">
-        <v>475</v>
-      </c>
       <c r="C203" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E203" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F203">
         <v>1.0</v>
@@ -7356,120 +7350,120 @@
     </row>
     <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B204" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C204" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E204" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F204">
         <v>1.0</v>
       </c>
       <c r="G204" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H204" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I204" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="205" spans="1:9">
       <c r="A205" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B205" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C205" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E205" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F205">
         <v>4.0</v>
       </c>
       <c r="G205" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H205" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="I205" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="206" spans="1:9">
       <c r="A206" t="s">
+        <v>494</v>
+      </c>
+      <c r="B206" t="s">
         <v>495</v>
-      </c>
-      <c r="B206" t="s">
-        <v>496</v>
       </c>
       <c r="C206" t="s">
         <v>274</v>
       </c>
       <c r="E206" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F206">
         <v>1.0</v>
       </c>
       <c r="G206" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H206" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I206" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" t="s">
+        <v>497</v>
+      </c>
+      <c r="B207" t="s">
         <v>498</v>
-      </c>
-      <c r="B207" t="s">
-        <v>499</v>
       </c>
       <c r="C207" t="s">
         <v>152</v>
       </c>
       <c r="E207" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F207">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G207" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H207" t="s">
-        <v>501</v>
+        <v>284</v>
       </c>
       <c r="I207" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="208" spans="1:9">
       <c r="A208" t="s">
+        <v>500</v>
+      </c>
+      <c r="B208" t="s">
+        <v>501</v>
+      </c>
+      <c r="C208" t="s">
+        <v>358</v>
+      </c>
+      <c r="E208" t="s">
         <v>502</v>
-      </c>
-      <c r="B208" t="s">
-        <v>503</v>
-      </c>
-      <c r="C208" t="s">
-        <v>360</v>
-      </c>
-      <c r="E208" t="s">
-        <v>504</v>
       </c>
       <c r="F208">
         <v>4.0</v>
@@ -7481,33 +7475,33 @@
         <v>72</v>
       </c>
       <c r="I208" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B209" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C209" t="s">
         <v>170</v>
       </c>
       <c r="E209" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F209">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G209" t="s">
+        <v>506</v>
+      </c>
+      <c r="H209" t="s">
+        <v>507</v>
+      </c>
+      <c r="I209" t="s">
         <v>508</v>
-      </c>
-      <c r="H209" t="s">
-        <v>301</v>
-      </c>
-      <c r="I209" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="210" spans="1:9">
@@ -7521,7 +7515,7 @@
         <v>152</v>
       </c>
       <c r="E210" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F210">
         <v>4.0</v>
@@ -7533,33 +7527,33 @@
         <v>72</v>
       </c>
       <c r="I210" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
     </row>
     <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B211" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C211" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E211" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F211">
         <v>1.0</v>
       </c>
       <c r="G211" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H211" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="I211" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="212" spans="1:9">
@@ -7570,48 +7564,48 @@
         <v>512</v>
       </c>
       <c r="C212" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E212" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F212">
         <v>3.0</v>
       </c>
       <c r="G212" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H212" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="I212" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B213" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C213" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E213" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F213">
         <v>2.0</v>
       </c>
       <c r="G213" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H213" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="I213" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="214" spans="1:9">
@@ -7625,7 +7619,7 @@
         <v>274</v>
       </c>
       <c r="E214" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F214">
         <v>3.0</v>
@@ -7634,7 +7628,7 @@
         <v>515</v>
       </c>
       <c r="H214" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="I214" t="s">
         <v>516</v>
@@ -7642,36 +7636,36 @@
     </row>
     <row r="215" spans="1:9">
       <c r="A215" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B215" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C215" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E215" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F215">
         <v>1.0</v>
       </c>
       <c r="G215" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H215" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I215" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B216" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C216" t="s">
         <v>115</v>
@@ -7703,19 +7697,19 @@
         <v>152</v>
       </c>
       <c r="E217" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F217">
         <v>4.0</v>
       </c>
       <c r="G217" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H217" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="I217" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
     </row>
     <row r="218" spans="1:9">
@@ -7729,68 +7723,68 @@
         <v>274</v>
       </c>
       <c r="E218" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F218">
         <v>1.0</v>
       </c>
       <c r="G218" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H218" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="I218" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>485</v>
+        <v>352</v>
       </c>
       <c r="B219" t="s">
-        <v>486</v>
+        <v>353</v>
       </c>
       <c r="C219" t="s">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="E219" t="s">
-        <v>472</v>
+        <v>354</v>
       </c>
       <c r="F219">
         <v>1.0</v>
       </c>
       <c r="G219" t="s">
-        <v>72</v>
+        <v>355</v>
       </c>
       <c r="H219" t="s">
-        <v>72</v>
+        <v>355</v>
       </c>
       <c r="I219" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
     </row>
     <row r="220" spans="1:9">
       <c r="A220" t="s">
+        <v>461</v>
+      </c>
+      <c r="B220" t="s">
+        <v>462</v>
+      </c>
+      <c r="C220" t="s">
+        <v>358</v>
+      </c>
+      <c r="E220" t="s">
         <v>354</v>
       </c>
-      <c r="B220" t="s">
+      <c r="F220">
+        <v>1.0</v>
+      </c>
+      <c r="G220" t="s">
         <v>355</v>
       </c>
-      <c r="C220" t="s">
-        <v>296</v>
-      </c>
-      <c r="E220" t="s">
-        <v>356</v>
-      </c>
-      <c r="F220">
-        <v>1.0</v>
-      </c>
-      <c r="G220" t="s">
-        <v>357</v>
-      </c>
       <c r="H220" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I220" t="s">
         <v>283</v>
@@ -7798,279 +7792,279 @@
     </row>
     <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>463</v>
+        <v>511</v>
       </c>
       <c r="B221" t="s">
-        <v>464</v>
+        <v>512</v>
       </c>
       <c r="C221" t="s">
-        <v>360</v>
+        <v>289</v>
       </c>
       <c r="E221" t="s">
-        <v>356</v>
+        <v>437</v>
       </c>
       <c r="F221">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G221" t="s">
-        <v>357</v>
+        <v>399</v>
       </c>
       <c r="H221" t="s">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="I221" t="s">
-        <v>283</v>
+        <v>401</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B222" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="C222" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="E222" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F222">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G222" t="s">
-        <v>403</v>
+        <v>521</v>
       </c>
       <c r="H222" t="s">
-        <v>404</v>
+        <v>521</v>
       </c>
       <c r="I222" t="s">
-        <v>405</v>
+        <v>316</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="A223" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B223" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="C223" t="s">
-        <v>274</v>
+        <v>152</v>
       </c>
       <c r="E223" t="s">
-        <v>440</v>
+        <v>471</v>
       </c>
       <c r="F223">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G223" t="s">
-        <v>521</v>
+        <v>72</v>
       </c>
       <c r="H223" t="s">
-        <v>521</v>
+        <v>72</v>
       </c>
       <c r="I223" t="s">
-        <v>318</v>
+        <v>451</v>
       </c>
     </row>
     <row r="224" spans="1:9">
       <c r="A224" t="s">
-        <v>506</v>
+        <v>464</v>
       </c>
       <c r="B224" t="s">
-        <v>507</v>
+        <v>465</v>
       </c>
       <c r="C224" t="s">
-        <v>152</v>
+        <v>289</v>
       </c>
       <c r="E224" t="s">
-        <v>472</v>
+        <v>354</v>
       </c>
       <c r="F224">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G224" t="s">
-        <v>72</v>
+        <v>366</v>
       </c>
       <c r="H224" t="s">
-        <v>72</v>
+        <v>366</v>
       </c>
       <c r="I224" t="s">
-        <v>454</v>
+        <v>496</v>
       </c>
     </row>
     <row r="225" spans="1:9">
       <c r="A225" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B225" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C225" t="s">
         <v>289</v>
       </c>
       <c r="E225" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F225">
         <v>1.0</v>
       </c>
       <c r="G225" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H225" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I225" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
     </row>
     <row r="226" spans="1:9">
       <c r="A226" t="s">
-        <v>468</v>
+        <v>522</v>
       </c>
       <c r="B226" t="s">
-        <v>469</v>
+        <v>523</v>
       </c>
       <c r="C226" t="s">
-        <v>289</v>
+        <v>128</v>
       </c>
       <c r="E226" t="s">
-        <v>356</v>
+        <v>244</v>
       </c>
       <c r="F226">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G226" t="s">
-        <v>368</v>
+        <v>72</v>
       </c>
       <c r="H226" t="s">
-        <v>368</v>
+        <v>72</v>
       </c>
       <c r="I226" t="s">
-        <v>488</v>
+        <v>385</v>
       </c>
     </row>
     <row r="227" spans="1:9">
       <c r="A227" t="s">
-        <v>522</v>
+        <v>497</v>
       </c>
       <c r="B227" t="s">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="C227" t="s">
         <v>128</v>
       </c>
       <c r="E227" t="s">
-        <v>244</v>
+        <v>471</v>
       </c>
       <c r="F227">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G227" t="s">
-        <v>72</v>
+        <v>524</v>
       </c>
       <c r="H227" t="s">
-        <v>72</v>
+        <v>525</v>
       </c>
       <c r="I227" t="s">
-        <v>389</v>
+        <v>256</v>
       </c>
     </row>
     <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>498</v>
+        <v>461</v>
       </c>
       <c r="B228" t="s">
-        <v>499</v>
+        <v>462</v>
       </c>
       <c r="C228" t="s">
-        <v>128</v>
+        <v>333</v>
       </c>
       <c r="E228" t="s">
-        <v>472</v>
+        <v>354</v>
       </c>
       <c r="F228">
         <v>2.0</v>
       </c>
       <c r="G228" t="s">
-        <v>524</v>
+        <v>355</v>
       </c>
       <c r="H228" t="s">
-        <v>525</v>
+        <v>443</v>
       </c>
       <c r="I228" t="s">
-        <v>256</v>
+        <v>463</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>463</v>
+        <v>526</v>
       </c>
       <c r="B229" t="s">
-        <v>464</v>
+        <v>527</v>
       </c>
       <c r="C229" t="s">
-        <v>335</v>
+        <v>274</v>
       </c>
       <c r="E229" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F229">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G229" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H229" t="s">
-        <v>446</v>
+        <v>355</v>
       </c>
       <c r="I229" t="s">
-        <v>478</v>
+        <v>528</v>
       </c>
     </row>
     <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="B230" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="C230" t="s">
-        <v>274</v>
+        <v>128</v>
       </c>
       <c r="E230" t="s">
-        <v>356</v>
+        <v>471</v>
       </c>
       <c r="F230">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G230" t="s">
-        <v>357</v>
+        <v>72</v>
       </c>
       <c r="H230" t="s">
-        <v>357</v>
+        <v>72</v>
       </c>
       <c r="I230" t="s">
-        <v>528</v>
+        <v>463</v>
       </c>
     </row>
     <row r="231" spans="1:9">
       <c r="A231" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="B231" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="C231" t="s">
         <v>128</v>
       </c>
       <c r="E231" t="s">
-        <v>472</v>
+        <v>244</v>
       </c>
       <c r="F231">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G231" t="s">
         <v>72</v>
@@ -8079,128 +8073,128 @@
         <v>72</v>
       </c>
       <c r="I231" t="s">
-        <v>478</v>
+        <v>385</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>529</v>
+        <v>464</v>
       </c>
       <c r="B232" t="s">
-        <v>530</v>
+        <v>465</v>
       </c>
       <c r="C232" t="s">
-        <v>128</v>
+        <v>333</v>
       </c>
       <c r="E232" t="s">
-        <v>244</v>
+        <v>354</v>
       </c>
       <c r="F232">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G232" t="s">
-        <v>72</v>
+        <v>366</v>
       </c>
       <c r="H232" t="s">
-        <v>72</v>
+        <v>366</v>
       </c>
       <c r="I232" t="s">
-        <v>389</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:9">
       <c r="A233" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B233" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C233" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="E233" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F233">
         <v>1.0</v>
       </c>
       <c r="G233" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H233" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I233" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
     </row>
     <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>468</v>
+        <v>513</v>
       </c>
       <c r="B234" t="s">
-        <v>469</v>
+        <v>514</v>
       </c>
       <c r="C234" t="s">
-        <v>360</v>
+        <v>289</v>
       </c>
       <c r="E234" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F234">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G234" t="s">
-        <v>368</v>
+        <v>431</v>
       </c>
       <c r="H234" t="s">
-        <v>368</v>
+        <v>531</v>
       </c>
       <c r="I234" t="s">
-        <v>488</v>
+        <v>516</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="B235" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="C235" t="s">
-        <v>289</v>
+        <v>152</v>
       </c>
       <c r="E235" t="s">
-        <v>356</v>
+        <v>471</v>
       </c>
       <c r="F235">
         <v>3.0</v>
       </c>
       <c r="G235" t="s">
-        <v>434</v>
+        <v>72</v>
       </c>
       <c r="H235" t="s">
-        <v>531</v>
+        <v>72</v>
       </c>
       <c r="I235" t="s">
-        <v>516</v>
+        <v>480</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>532</v>
+        <v>484</v>
       </c>
       <c r="B236" t="s">
-        <v>533</v>
+        <v>485</v>
       </c>
       <c r="C236" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="E236" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F236">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G236" t="s">
         <v>72</v>
@@ -8209,24 +8203,24 @@
         <v>72</v>
       </c>
       <c r="I236" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>485</v>
+        <v>509</v>
       </c>
       <c r="B237" t="s">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="C237" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="E237" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F237">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G237" t="s">
         <v>72</v>
@@ -8235,24 +8229,24 @@
         <v>72</v>
       </c>
       <c r="I237" t="s">
-        <v>250</v>
+        <v>508</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>509</v>
+        <v>429</v>
       </c>
       <c r="B238" t="s">
-        <v>510</v>
+        <v>430</v>
       </c>
       <c r="C238" t="s">
-        <v>144</v>
+        <v>295</v>
       </c>
       <c r="E238" t="s">
-        <v>472</v>
+        <v>354</v>
       </c>
       <c r="F238">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G238" t="s">
         <v>72</v>
@@ -8261,24 +8255,24 @@
         <v>72</v>
       </c>
       <c r="I238" t="s">
-        <v>534</v>
+        <v>283</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>432</v>
+        <v>534</v>
       </c>
       <c r="B239" t="s">
-        <v>433</v>
+        <v>535</v>
       </c>
       <c r="C239" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="E239" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F239">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G239" t="s">
         <v>72</v>
@@ -8287,24 +8281,24 @@
         <v>72</v>
       </c>
       <c r="I239" t="s">
-        <v>283</v>
+        <v>81</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>535</v>
+        <v>469</v>
       </c>
       <c r="B240" t="s">
-        <v>536</v>
+        <v>470</v>
       </c>
       <c r="C240" t="s">
-        <v>274</v>
+        <v>144</v>
       </c>
       <c r="E240" t="s">
-        <v>356</v>
+        <v>471</v>
       </c>
       <c r="F240">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G240" t="s">
         <v>72</v>
@@ -8313,24 +8307,24 @@
         <v>72</v>
       </c>
       <c r="I240" t="s">
-        <v>81</v>
+        <v>316</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>470</v>
+        <v>536</v>
       </c>
       <c r="B241" t="s">
-        <v>471</v>
+        <v>537</v>
       </c>
       <c r="C241" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="E241" t="s">
-        <v>472</v>
+        <v>244</v>
       </c>
       <c r="F241">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G241" t="s">
         <v>72</v>
@@ -8339,24 +8333,24 @@
         <v>72</v>
       </c>
       <c r="I241" t="s">
-        <v>318</v>
+        <v>251</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B242" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C242" t="s">
         <v>170</v>
       </c>
       <c r="E242" t="s">
-        <v>244</v>
+        <v>471</v>
       </c>
       <c r="F242">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G242" t="s">
         <v>72</v>
@@ -8365,128 +8359,128 @@
         <v>72</v>
       </c>
       <c r="I242" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>532</v>
+        <v>441</v>
       </c>
       <c r="B243" t="s">
-        <v>533</v>
+        <v>442</v>
       </c>
       <c r="C243" t="s">
-        <v>170</v>
+        <v>295</v>
       </c>
       <c r="E243" t="s">
-        <v>472</v>
+        <v>354</v>
       </c>
       <c r="F243">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G243" t="s">
-        <v>72</v>
+        <v>366</v>
       </c>
       <c r="H243" t="s">
-        <v>72</v>
+        <v>366</v>
       </c>
       <c r="I243" t="s">
-        <v>256</v>
+        <v>496</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>444</v>
+        <v>517</v>
       </c>
       <c r="B244" t="s">
-        <v>445</v>
+        <v>518</v>
       </c>
       <c r="C244" t="s">
-        <v>296</v>
+        <v>170</v>
       </c>
       <c r="E244" t="s">
-        <v>356</v>
+        <v>471</v>
       </c>
       <c r="F244">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G244" t="s">
-        <v>368</v>
+        <v>506</v>
       </c>
       <c r="H244" t="s">
-        <v>368</v>
+        <v>538</v>
       </c>
       <c r="I244" t="s">
-        <v>497</v>
+        <v>451</v>
       </c>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>517</v>
+        <v>467</v>
       </c>
       <c r="B245" t="s">
-        <v>518</v>
+        <v>468</v>
       </c>
       <c r="C245" t="s">
-        <v>170</v>
+        <v>295</v>
       </c>
       <c r="E245" t="s">
-        <v>472</v>
+        <v>354</v>
       </c>
       <c r="F245">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G245" t="s">
-        <v>508</v>
+        <v>366</v>
       </c>
       <c r="H245" t="s">
-        <v>539</v>
+        <v>366</v>
       </c>
       <c r="I245" t="s">
-        <v>454</v>
+        <v>487</v>
       </c>
     </row>
     <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>468</v>
+        <v>529</v>
       </c>
       <c r="B246" t="s">
-        <v>469</v>
+        <v>530</v>
       </c>
       <c r="C246" t="s">
-        <v>296</v>
+        <v>144</v>
       </c>
       <c r="E246" t="s">
-        <v>356</v>
+        <v>244</v>
       </c>
       <c r="F246">
         <v>1.0</v>
       </c>
       <c r="G246" t="s">
-        <v>368</v>
+        <v>72</v>
       </c>
       <c r="H246" t="s">
-        <v>368</v>
+        <v>72</v>
       </c>
       <c r="I246" t="s">
-        <v>488</v>
+        <v>246</v>
       </c>
     </row>
     <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="B247" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="C247" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="E247" t="s">
-        <v>244</v>
+        <v>471</v>
       </c>
       <c r="F247">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G247" t="s">
         <v>72</v>
@@ -8495,7 +8489,7 @@
         <v>72</v>
       </c>
       <c r="I247" t="s">
-        <v>251</v>
+        <v>451</v>
       </c>
     </row>
     <row r="248" spans="1:9">
@@ -8506,13 +8500,13 @@
         <v>510</v>
       </c>
       <c r="C248" t="s">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="E248" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F248">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="G248" t="s">
         <v>72</v>
@@ -8521,24 +8515,24 @@
         <v>72</v>
       </c>
       <c r="I248" t="s">
-        <v>454</v>
+        <v>539</v>
       </c>
     </row>
     <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>509</v>
+        <v>540</v>
       </c>
       <c r="B249" t="s">
-        <v>510</v>
+        <v>541</v>
       </c>
       <c r="C249" t="s">
-        <v>128</v>
+        <v>274</v>
       </c>
       <c r="E249" t="s">
-        <v>472</v>
+        <v>354</v>
       </c>
       <c r="F249">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G249" t="s">
         <v>72</v>
@@ -8547,99 +8541,99 @@
         <v>72</v>
       </c>
       <c r="I249" t="s">
-        <v>540</v>
+        <v>466</v>
       </c>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B250" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C250" t="s">
         <v>274</v>
       </c>
       <c r="E250" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F250">
         <v>2.0</v>
       </c>
       <c r="G250" t="s">
-        <v>72</v>
+        <v>355</v>
       </c>
       <c r="H250" t="s">
-        <v>72</v>
+        <v>443</v>
       </c>
       <c r="I250" t="s">
-        <v>467</v>
+        <v>411</v>
       </c>
     </row>
     <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
       <c r="B251" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="C251" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
       <c r="E251" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F251">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G251" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H251" t="s">
-        <v>446</v>
+        <v>355</v>
       </c>
       <c r="I251" t="s">
-        <v>414</v>
+        <v>528</v>
       </c>
     </row>
     <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="B252" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="C252" t="s">
-        <v>360</v>
+        <v>170</v>
       </c>
       <c r="E252" t="s">
-        <v>356</v>
+        <v>244</v>
       </c>
       <c r="F252">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G252" t="s">
-        <v>357</v>
+        <v>72</v>
       </c>
       <c r="H252" t="s">
-        <v>357</v>
+        <v>72</v>
       </c>
       <c r="I252" t="s">
-        <v>528</v>
+        <v>251</v>
       </c>
     </row>
     <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>545</v>
+        <v>456</v>
       </c>
       <c r="B253" t="s">
-        <v>546</v>
+        <v>457</v>
       </c>
       <c r="C253" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="E253" t="s">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="F253">
         <v>2.0</v>
@@ -8651,21 +8645,21 @@
         <v>72</v>
       </c>
       <c r="I253" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
     </row>
     <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>458</v>
+        <v>522</v>
       </c>
       <c r="B254" t="s">
-        <v>459</v>
+        <v>523</v>
       </c>
       <c r="C254" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E254" t="s">
-        <v>134</v>
+        <v>244</v>
       </c>
       <c r="F254">
         <v>2.0</v>
@@ -8677,24 +8671,24 @@
         <v>72</v>
       </c>
       <c r="I254" t="s">
-        <v>218</v>
+        <v>251</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B255" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="C255" t="s">
         <v>144</v>
       </c>
       <c r="E255" t="s">
-        <v>244</v>
+        <v>471</v>
       </c>
       <c r="F255">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G255" t="s">
         <v>72</v>
@@ -8703,24 +8697,24 @@
         <v>72</v>
       </c>
       <c r="I255" t="s">
-        <v>251</v>
+        <v>508</v>
       </c>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="B256" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="C256" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="E256" t="s">
-        <v>472</v>
+        <v>244</v>
       </c>
       <c r="F256">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G256" t="s">
         <v>72</v>
@@ -8729,82 +8723,82 @@
         <v>72</v>
       </c>
       <c r="I256" t="s">
-        <v>534</v>
+        <v>257</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>529</v>
+        <v>461</v>
       </c>
       <c r="B257" t="s">
-        <v>530</v>
+        <v>462</v>
       </c>
       <c r="C257" t="s">
-        <v>170</v>
+        <v>295</v>
       </c>
       <c r="E257" t="s">
-        <v>244</v>
+        <v>354</v>
       </c>
       <c r="F257">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G257" t="s">
-        <v>72</v>
+        <v>355</v>
       </c>
       <c r="H257" t="s">
-        <v>72</v>
+        <v>355</v>
       </c>
       <c r="I257" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>463</v>
+        <v>546</v>
       </c>
       <c r="B258" t="s">
-        <v>464</v>
+        <v>547</v>
       </c>
       <c r="C258" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="E258" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F258">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G258" t="s">
-        <v>357</v>
+        <v>431</v>
       </c>
       <c r="H258" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I258" t="s">
-        <v>283</v>
+        <v>81</v>
       </c>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>547</v>
+        <v>513</v>
       </c>
       <c r="B259" t="s">
-        <v>548</v>
+        <v>514</v>
       </c>
       <c r="C259" t="s">
-        <v>274</v>
+        <v>333</v>
       </c>
       <c r="E259" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F259">
         <v>2.0</v>
       </c>
       <c r="G259" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H259" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I259" t="s">
         <v>81</v>
@@ -8812,45 +8806,45 @@
     </row>
     <row r="260" spans="1:9">
       <c r="A260" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="B260" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="C260" t="s">
-        <v>335</v>
+        <v>152</v>
       </c>
       <c r="E260" t="s">
-        <v>356</v>
+        <v>244</v>
       </c>
       <c r="F260">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G260" t="s">
-        <v>434</v>
+        <v>72</v>
       </c>
       <c r="H260" t="s">
-        <v>357</v>
+        <v>72</v>
       </c>
       <c r="I260" t="s">
-        <v>81</v>
+        <v>257</v>
       </c>
     </row>
     <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>522</v>
+        <v>544</v>
       </c>
       <c r="B261" t="s">
-        <v>523</v>
+        <v>545</v>
       </c>
       <c r="C261" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E261" t="s">
         <v>244</v>
       </c>
       <c r="F261">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G261" t="s">
         <v>72</v>
@@ -8859,15 +8853,15 @@
         <v>72</v>
       </c>
       <c r="I261" t="s">
-        <v>257</v>
+        <v>385</v>
       </c>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="B262" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="C262" t="s">
         <v>144</v>
@@ -8876,7 +8870,7 @@
         <v>244</v>
       </c>
       <c r="F262">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G262" t="s">
         <v>72</v>
@@ -8885,24 +8879,24 @@
         <v>72</v>
       </c>
       <c r="I262" t="s">
-        <v>246</v>
+        <v>385</v>
       </c>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B263" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C263" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E263" t="s">
-        <v>244</v>
+        <v>134</v>
       </c>
       <c r="F263">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G263" t="s">
         <v>72</v>
@@ -8911,21 +8905,21 @@
         <v>72</v>
       </c>
       <c r="I263" t="s">
-        <v>389</v>
+        <v>550</v>
       </c>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>545</v>
+        <v>504</v>
       </c>
       <c r="B264" t="s">
-        <v>546</v>
+        <v>505</v>
       </c>
       <c r="C264" t="s">
         <v>144</v>
       </c>
       <c r="E264" t="s">
-        <v>244</v>
+        <v>471</v>
       </c>
       <c r="F264">
         <v>4.0</v>
@@ -8937,21 +8931,21 @@
         <v>72</v>
       </c>
       <c r="I264" t="s">
-        <v>257</v>
+        <v>463</v>
       </c>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>549</v>
+        <v>484</v>
       </c>
       <c r="B265" t="s">
-        <v>550</v>
+        <v>485</v>
       </c>
       <c r="C265" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E265" t="s">
-        <v>134</v>
+        <v>471</v>
       </c>
       <c r="F265">
         <v>4.0</v>
@@ -8963,24 +8957,24 @@
         <v>72</v>
       </c>
       <c r="I265" t="s">
-        <v>551</v>
+        <v>460</v>
       </c>
     </row>
     <row r="266" spans="1:9">
       <c r="A266" t="s">
-        <v>506</v>
+        <v>551</v>
       </c>
       <c r="B266" t="s">
-        <v>507</v>
+        <v>552</v>
       </c>
       <c r="C266" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="E266" t="s">
-        <v>472</v>
+        <v>553</v>
       </c>
       <c r="F266">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G266" t="s">
         <v>72</v>
@@ -8989,24 +8983,24 @@
         <v>72</v>
       </c>
       <c r="I266" t="s">
-        <v>478</v>
+        <v>266</v>
       </c>
     </row>
     <row r="267" spans="1:9">
       <c r="A267" t="s">
-        <v>485</v>
+        <v>554</v>
       </c>
       <c r="B267" t="s">
-        <v>486</v>
+        <v>555</v>
       </c>
       <c r="C267" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="E267" t="s">
-        <v>472</v>
+        <v>129</v>
       </c>
       <c r="F267">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G267" t="s">
         <v>72</v>
@@ -9015,24 +9009,24 @@
         <v>72</v>
       </c>
       <c r="I267" t="s">
-        <v>462</v>
+        <v>147</v>
       </c>
     </row>
     <row r="268" spans="1:9">
       <c r="A268" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B268" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C268" t="s">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="E268" t="s">
-        <v>554</v>
+        <v>129</v>
       </c>
       <c r="F268">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G268" t="s">
         <v>72</v>
@@ -9041,24 +9035,24 @@
         <v>72</v>
       </c>
       <c r="I268" t="s">
-        <v>266</v>
+        <v>179</v>
       </c>
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>555</v>
+        <v>456</v>
       </c>
       <c r="B269" t="s">
-        <v>556</v>
+        <v>457</v>
       </c>
       <c r="C269" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="E269" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F269">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G269" t="s">
         <v>72</v>
@@ -9067,21 +9061,21 @@
         <v>72</v>
       </c>
       <c r="I269" t="s">
-        <v>173</v>
+        <v>550</v>
       </c>
     </row>
     <row r="270" spans="1:9">
       <c r="A270" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="B270" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="C270" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="E270" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F270">
         <v>3.0</v>
@@ -9093,24 +9087,24 @@
         <v>72</v>
       </c>
       <c r="I270" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="271" spans="1:9">
       <c r="A271" t="s">
-        <v>458</v>
+        <v>522</v>
       </c>
       <c r="B271" t="s">
-        <v>459</v>
+        <v>523</v>
       </c>
       <c r="C271" t="s">
         <v>170</v>
       </c>
       <c r="E271" t="s">
-        <v>134</v>
+        <v>244</v>
       </c>
       <c r="F271">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G271" t="s">
         <v>72</v>
@@ -9119,24 +9113,24 @@
         <v>72</v>
       </c>
       <c r="I271" t="s">
-        <v>551</v>
+        <v>246</v>
       </c>
     </row>
     <row r="272" spans="1:9">
       <c r="A272" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="B272" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="C272" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="E272" t="s">
-        <v>134</v>
+        <v>244</v>
       </c>
       <c r="F272">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G272" t="s">
         <v>72</v>
@@ -9145,24 +9139,24 @@
         <v>72</v>
       </c>
       <c r="I272" t="s">
-        <v>185</v>
+        <v>251</v>
       </c>
     </row>
     <row r="273" spans="1:9">
       <c r="A273" t="s">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="B273" t="s">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="C273" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="E273" t="s">
         <v>244</v>
       </c>
       <c r="F273">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G273" t="s">
         <v>72</v>
@@ -9171,24 +9165,24 @@
         <v>72</v>
       </c>
       <c r="I273" t="s">
-        <v>246</v>
+        <v>385</v>
       </c>
     </row>
     <row r="274" spans="1:9">
       <c r="A274" t="s">
-        <v>545</v>
+        <v>345</v>
       </c>
       <c r="B274" t="s">
-        <v>546</v>
+        <v>346</v>
       </c>
       <c r="C274" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E274" t="s">
         <v>244</v>
       </c>
       <c r="F274">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G274" t="s">
         <v>72</v>
@@ -9197,15 +9191,15 @@
         <v>72</v>
       </c>
       <c r="I274" t="s">
-        <v>389</v>
+        <v>255</v>
       </c>
     </row>
     <row r="275" spans="1:9">
       <c r="A275" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="B275" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="C275" t="s">
         <v>152</v>
@@ -9214,7 +9208,7 @@
         <v>244</v>
       </c>
       <c r="F275">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G275" t="s">
         <v>72</v>
@@ -9223,24 +9217,24 @@
         <v>72</v>
       </c>
       <c r="I275" t="s">
-        <v>389</v>
+        <v>257</v>
       </c>
     </row>
     <row r="276" spans="1:9">
       <c r="A276" t="s">
-        <v>347</v>
+        <v>504</v>
       </c>
       <c r="B276" t="s">
-        <v>348</v>
+        <v>505</v>
       </c>
       <c r="C276" t="s">
         <v>128</v>
       </c>
       <c r="E276" t="s">
-        <v>244</v>
+        <v>471</v>
       </c>
       <c r="F276">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G276" t="s">
         <v>72</v>
@@ -9249,24 +9243,24 @@
         <v>72</v>
       </c>
       <c r="I276" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
     </row>
     <row r="277" spans="1:9">
       <c r="A277" t="s">
-        <v>529</v>
+        <v>484</v>
       </c>
       <c r="B277" t="s">
-        <v>530</v>
+        <v>485</v>
       </c>
       <c r="C277" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E277" t="s">
-        <v>244</v>
+        <v>471</v>
       </c>
       <c r="F277">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G277" t="s">
         <v>72</v>
@@ -9275,24 +9269,24 @@
         <v>72</v>
       </c>
       <c r="I277" t="s">
-        <v>257</v>
+        <v>480</v>
       </c>
     </row>
     <row r="278" spans="1:9">
       <c r="A278" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="B278" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="C278" t="s">
         <v>128</v>
       </c>
       <c r="E278" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F278">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G278" t="s">
         <v>72</v>
@@ -9301,24 +9295,21 @@
         <v>72</v>
       </c>
       <c r="I278" t="s">
-        <v>540</v>
+        <v>256</v>
       </c>
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
-        <v>485</v>
+        <v>556</v>
       </c>
       <c r="B279" t="s">
-        <v>486</v>
-      </c>
-      <c r="C279" t="s">
-        <v>144</v>
+        <v>557</v>
       </c>
       <c r="E279" t="s">
-        <v>472</v>
+        <v>558</v>
       </c>
       <c r="F279">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G279" t="s">
         <v>72</v>
@@ -9327,24 +9318,21 @@
         <v>72</v>
       </c>
       <c r="I279" t="s">
-        <v>254</v>
+        <v>559</v>
       </c>
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
-        <v>532</v>
+        <v>560</v>
       </c>
       <c r="B280" t="s">
-        <v>533</v>
-      </c>
-      <c r="C280" t="s">
-        <v>128</v>
+        <v>561</v>
       </c>
       <c r="E280" t="s">
-        <v>472</v>
+        <v>558</v>
       </c>
       <c r="F280">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G280" t="s">
         <v>72</v>
@@ -9353,18 +9341,18 @@
         <v>72</v>
       </c>
       <c r="I280" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
+        <v>562</v>
+      </c>
+      <c r="B281" t="s">
+        <v>563</v>
+      </c>
+      <c r="E281" t="s">
         <v>558</v>
-      </c>
-      <c r="B281" t="s">
-        <v>559</v>
-      </c>
-      <c r="E281" t="s">
-        <v>560</v>
       </c>
       <c r="F281">
         <v>2.0</v>
@@ -9376,18 +9364,18 @@
         <v>72</v>
       </c>
       <c r="I281" t="s">
-        <v>561</v>
+        <v>285</v>
       </c>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B282" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E282" t="s">
-        <v>560</v>
+        <v>226</v>
       </c>
       <c r="F282">
         <v>1.0</v>
@@ -9399,21 +9387,24 @@
         <v>72</v>
       </c>
       <c r="I282" t="s">
-        <v>228</v>
+        <v>112</v>
       </c>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>564</v>
+        <v>500</v>
       </c>
       <c r="B283" t="s">
-        <v>565</v>
+        <v>501</v>
+      </c>
+      <c r="C283" t="s">
+        <v>333</v>
       </c>
       <c r="E283" t="s">
-        <v>560</v>
+        <v>502</v>
       </c>
       <c r="F283">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G283" t="s">
         <v>72</v>
@@ -9422,47 +9413,50 @@
         <v>72</v>
       </c>
       <c r="I283" t="s">
-        <v>285</v>
+        <v>503</v>
       </c>
     </row>
     <row r="284" spans="1:9">
       <c r="A284" t="s">
+        <v>500</v>
+      </c>
+      <c r="B284" t="s">
+        <v>501</v>
+      </c>
+      <c r="C284" t="s">
+        <v>274</v>
+      </c>
+      <c r="E284" t="s">
+        <v>502</v>
+      </c>
+      <c r="F284">
+        <v>7.0</v>
+      </c>
+      <c r="G284" t="s">
+        <v>72</v>
+      </c>
+      <c r="H284" t="s">
+        <v>72</v>
+      </c>
+      <c r="I284" t="s">
         <v>566</v>
-      </c>
-      <c r="B284" t="s">
-        <v>567</v>
-      </c>
-      <c r="E284" t="s">
-        <v>226</v>
-      </c>
-      <c r="F284">
-        <v>1.0</v>
-      </c>
-      <c r="G284" t="s">
-        <v>72</v>
-      </c>
-      <c r="H284" t="s">
-        <v>72</v>
-      </c>
-      <c r="I284" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
+        <v>500</v>
+      </c>
+      <c r="B285" t="s">
+        <v>501</v>
+      </c>
+      <c r="C285" t="s">
+        <v>289</v>
+      </c>
+      <c r="E285" t="s">
         <v>502</v>
       </c>
-      <c r="B285" t="s">
-        <v>503</v>
-      </c>
-      <c r="C285" t="s">
-        <v>335</v>
-      </c>
-      <c r="E285" t="s">
-        <v>504</v>
-      </c>
       <c r="F285">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G285" t="s">
         <v>72</v>
@@ -9471,50 +9465,50 @@
         <v>72</v>
       </c>
       <c r="I285" t="s">
-        <v>505</v>
+        <v>567</v>
       </c>
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
+        <v>568</v>
+      </c>
+      <c r="B286" t="s">
+        <v>569</v>
+      </c>
+      <c r="C286" t="s">
+        <v>333</v>
+      </c>
+      <c r="E286" t="s">
         <v>502</v>
       </c>
-      <c r="B286" t="s">
+      <c r="F286">
+        <v>4.0</v>
+      </c>
+      <c r="G286" t="s">
+        <v>72</v>
+      </c>
+      <c r="H286" t="s">
+        <v>72</v>
+      </c>
+      <c r="I286" t="s">
         <v>503</v>
-      </c>
-      <c r="C286" t="s">
-        <v>274</v>
-      </c>
-      <c r="E286" t="s">
-        <v>504</v>
-      </c>
-      <c r="F286">
-        <v>7.0</v>
-      </c>
-      <c r="G286" t="s">
-        <v>72</v>
-      </c>
-      <c r="H286" t="s">
-        <v>72</v>
-      </c>
-      <c r="I286" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="287" spans="1:9">
       <c r="A287" t="s">
+        <v>568</v>
+      </c>
+      <c r="B287" t="s">
+        <v>569</v>
+      </c>
+      <c r="C287" t="s">
+        <v>274</v>
+      </c>
+      <c r="E287" t="s">
         <v>502</v>
       </c>
-      <c r="B287" t="s">
-        <v>503</v>
-      </c>
-      <c r="C287" t="s">
-        <v>289</v>
-      </c>
-      <c r="E287" t="s">
-        <v>504</v>
-      </c>
       <c r="F287">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G287" t="s">
         <v>72</v>
@@ -9523,50 +9517,50 @@
         <v>72</v>
       </c>
       <c r="I287" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B288" t="s">
+        <v>569</v>
+      </c>
+      <c r="C288" t="s">
+        <v>289</v>
+      </c>
+      <c r="E288" t="s">
+        <v>502</v>
+      </c>
+      <c r="F288">
+        <v>2.0</v>
+      </c>
+      <c r="G288" t="s">
+        <v>72</v>
+      </c>
+      <c r="H288" t="s">
+        <v>72</v>
+      </c>
+      <c r="I288" t="s">
         <v>571</v>
-      </c>
-      <c r="C288" t="s">
-        <v>335</v>
-      </c>
-      <c r="E288" t="s">
-        <v>504</v>
-      </c>
-      <c r="F288">
-        <v>4.0</v>
-      </c>
-      <c r="G288" t="s">
-        <v>72</v>
-      </c>
-      <c r="H288" t="s">
-        <v>72</v>
-      </c>
-      <c r="I288" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B289" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C289" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
       <c r="E289" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F289">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G289" t="s">
         <v>72</v>
@@ -9580,16 +9574,16 @@
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B290" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C290" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E290" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F290">
         <v>2.0</v>
@@ -9601,24 +9595,24 @@
         <v>72</v>
       </c>
       <c r="I290" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B291" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C291" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="E291" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F291">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G291" t="s">
         <v>72</v>
@@ -9627,24 +9621,24 @@
         <v>72</v>
       </c>
       <c r="I291" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" t="s">
+        <v>574</v>
+      </c>
+      <c r="B292" t="s">
         <v>575</v>
       </c>
-      <c r="B292" t="s">
-        <v>571</v>
-      </c>
       <c r="C292" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="E292" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F292">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G292" t="s">
         <v>72</v>
@@ -9653,24 +9647,24 @@
         <v>72</v>
       </c>
       <c r="I292" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="293" spans="1:9">
       <c r="A293" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B293" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C293" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="E293" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F293">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G293" t="s">
         <v>72</v>
@@ -9684,19 +9678,19 @@
     </row>
     <row r="294" spans="1:9">
       <c r="A294" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B294" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C294" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="E294" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F294">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="G294" t="s">
         <v>72</v>
@@ -9705,24 +9699,24 @@
         <v>72</v>
       </c>
       <c r="I294" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="295" spans="1:9">
       <c r="A295" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B295" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C295" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="E295" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F295">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G295" t="s">
         <v>72</v>
@@ -9731,24 +9725,24 @@
         <v>72</v>
       </c>
       <c r="I295" t="s">
-        <v>580</v>
+        <v>528</v>
       </c>
     </row>
     <row r="296" spans="1:9">
       <c r="A296" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B296" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C296" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E296" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F296">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G296" t="s">
         <v>72</v>
@@ -9757,7 +9751,7 @@
         <v>72</v>
       </c>
       <c r="I296" t="s">
-        <v>580</v>
+        <v>528</v>
       </c>
     </row>
     <row r="297" spans="1:9">
@@ -9768,10 +9762,10 @@
         <v>582</v>
       </c>
       <c r="C297" t="s">
-        <v>335</v>
+        <v>274</v>
       </c>
       <c r="E297" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F297">
         <v>1.0</v>
@@ -9783,7 +9777,7 @@
         <v>72</v>
       </c>
       <c r="I297" t="s">
-        <v>528</v>
+        <v>337</v>
       </c>
     </row>
     <row r="298" spans="1:9">
@@ -9794,13 +9788,13 @@
         <v>582</v>
       </c>
       <c r="C298" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="E298" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F298">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G298" t="s">
         <v>72</v>
@@ -9809,21 +9803,21 @@
         <v>72</v>
       </c>
       <c r="I298" t="s">
-        <v>528</v>
+        <v>439</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B299" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C299" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
       <c r="E299" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F299">
         <v>1.0</v>
@@ -9835,7 +9829,7 @@
         <v>72</v>
       </c>
       <c r="I299" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -9846,13 +9840,13 @@
         <v>584</v>
       </c>
       <c r="C300" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="E300" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F300">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G300" t="s">
         <v>72</v>
@@ -9861,24 +9855,24 @@
         <v>72</v>
       </c>
       <c r="I300" t="s">
-        <v>442</v>
+        <v>337</v>
       </c>
     </row>
     <row r="301" spans="1:9">
       <c r="A301" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B301" t="s">
         <v>584</v>
       </c>
       <c r="C301" t="s">
-        <v>360</v>
+        <v>274</v>
       </c>
       <c r="E301" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F301">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G301" t="s">
         <v>72</v>
@@ -9887,7 +9881,7 @@
         <v>72</v>
       </c>
       <c r="I301" t="s">
-        <v>339</v>
+        <v>586</v>
       </c>
     </row>
     <row r="302" spans="1:9">
@@ -9895,16 +9889,16 @@
         <v>585</v>
       </c>
       <c r="B302" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C302" t="s">
-        <v>335</v>
+        <v>289</v>
       </c>
       <c r="E302" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F302">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G302" t="s">
         <v>72</v>
@@ -9913,24 +9907,24 @@
         <v>72</v>
       </c>
       <c r="I302" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B303" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C303" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
       <c r="E303" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F303">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G303" t="s">
         <v>72</v>
@@ -9939,24 +9933,24 @@
         <v>72</v>
       </c>
       <c r="I303" t="s">
-        <v>588</v>
+        <v>439</v>
       </c>
     </row>
     <row r="304" spans="1:9">
       <c r="A304" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B304" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C304" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E304" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F304">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G304" t="s">
         <v>72</v>
@@ -9965,7 +9959,7 @@
         <v>72</v>
       </c>
       <c r="I304" t="s">
-        <v>442</v>
+        <v>337</v>
       </c>
     </row>
     <row r="305" spans="1:9">
@@ -9973,16 +9967,16 @@
         <v>587</v>
       </c>
       <c r="B305" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C305" t="s">
-        <v>360</v>
+        <v>289</v>
       </c>
       <c r="E305" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F305">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G305" t="s">
         <v>72</v>
@@ -9991,7 +9985,7 @@
         <v>72</v>
       </c>
       <c r="I305" t="s">
-        <v>442</v>
+        <v>589</v>
       </c>
     </row>
     <row r="306" spans="1:9">
@@ -9999,13 +9993,13 @@
         <v>587</v>
       </c>
       <c r="B306" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C306" t="s">
-        <v>296</v>
+        <v>358</v>
       </c>
       <c r="E306" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F306">
         <v>1.0</v>
@@ -10017,24 +10011,24 @@
         <v>72</v>
       </c>
       <c r="I306" t="s">
-        <v>339</v>
+        <v>589</v>
       </c>
     </row>
     <row r="307" spans="1:9">
       <c r="A307" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B307" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C307" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="E307" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F307">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G307" t="s">
         <v>72</v>
@@ -10043,21 +10037,21 @@
         <v>72</v>
       </c>
       <c r="I307" t="s">
-        <v>591</v>
+        <v>439</v>
       </c>
     </row>
     <row r="308" spans="1:9">
       <c r="A308" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B308" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C308" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E308" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F308">
         <v>1.0</v>
@@ -10069,7 +10063,7 @@
         <v>72</v>
       </c>
       <c r="I308" t="s">
-        <v>591</v>
+        <v>337</v>
       </c>
     </row>
     <row r="309" spans="1:9">
@@ -10083,10 +10077,10 @@
         <v>274</v>
       </c>
       <c r="E309" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F309">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G309" t="s">
         <v>72</v>
@@ -10095,7 +10089,7 @@
         <v>72</v>
       </c>
       <c r="I309" t="s">
-        <v>442</v>
+        <v>594</v>
       </c>
     </row>
     <row r="310" spans="1:9">
@@ -10106,10 +10100,10 @@
         <v>593</v>
       </c>
       <c r="C310" t="s">
-        <v>360</v>
+        <v>289</v>
       </c>
       <c r="E310" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F310">
         <v>1.0</v>
@@ -10121,24 +10115,24 @@
         <v>72</v>
       </c>
       <c r="I310" t="s">
-        <v>339</v>
+        <v>528</v>
       </c>
     </row>
     <row r="311" spans="1:9">
       <c r="A311" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B311" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C311" t="s">
-        <v>274</v>
+        <v>358</v>
       </c>
       <c r="E311" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F311">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G311" t="s">
         <v>72</v>
@@ -10147,24 +10141,24 @@
         <v>72</v>
       </c>
       <c r="I311" t="s">
-        <v>596</v>
+        <v>81</v>
       </c>
     </row>
     <row r="312" spans="1:9">
       <c r="A312" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B312" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C312" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E312" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F312">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G312" t="s">
         <v>72</v>
@@ -10173,24 +10167,24 @@
         <v>72</v>
       </c>
       <c r="I312" t="s">
-        <v>528</v>
+        <v>81</v>
       </c>
     </row>
     <row r="313" spans="1:9">
       <c r="A313" t="s">
-        <v>594</v>
+        <v>540</v>
       </c>
       <c r="B313" t="s">
-        <v>595</v>
+        <v>541</v>
       </c>
       <c r="C313" t="s">
-        <v>360</v>
+        <v>289</v>
       </c>
       <c r="E313" t="s">
-        <v>504</v>
+        <v>354</v>
       </c>
       <c r="F313">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G313" t="s">
         <v>72</v>
@@ -10199,24 +10193,24 @@
         <v>72</v>
       </c>
       <c r="I313" t="s">
-        <v>81</v>
+        <v>496</v>
       </c>
     </row>
     <row r="314" spans="1:9">
       <c r="A314" t="s">
-        <v>594</v>
+        <v>534</v>
       </c>
       <c r="B314" t="s">
-        <v>595</v>
+        <v>535</v>
       </c>
       <c r="C314" t="s">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="E314" t="s">
-        <v>504</v>
+        <v>354</v>
       </c>
       <c r="F314">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G314" t="s">
         <v>72</v>
@@ -10225,21 +10219,21 @@
         <v>72</v>
       </c>
       <c r="I314" t="s">
-        <v>81</v>
+        <v>528</v>
       </c>
     </row>
     <row r="315" spans="1:9">
       <c r="A315" t="s">
-        <v>541</v>
+        <v>595</v>
       </c>
       <c r="B315" t="s">
-        <v>542</v>
+        <v>596</v>
       </c>
       <c r="C315" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="E315" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F315">
         <v>1.0</v>
@@ -10251,24 +10245,24 @@
         <v>72</v>
       </c>
       <c r="I315" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" t="s">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="B316" t="s">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="C316" t="s">
-        <v>335</v>
+        <v>170</v>
       </c>
       <c r="E316" t="s">
-        <v>356</v>
+        <v>129</v>
       </c>
       <c r="F316">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G316" t="s">
         <v>72</v>
@@ -10277,7 +10271,7 @@
         <v>72</v>
       </c>
       <c r="I316" t="s">
-        <v>528</v>
+        <v>117</v>
       </c>
     </row>
     <row r="317" spans="1:9">
@@ -10288,10 +10282,10 @@
         <v>598</v>
       </c>
       <c r="C317" t="s">
-        <v>274</v>
+        <v>144</v>
       </c>
       <c r="E317" t="s">
-        <v>356</v>
+        <v>244</v>
       </c>
       <c r="F317">
         <v>1.0</v>
@@ -10303,24 +10297,24 @@
         <v>72</v>
       </c>
       <c r="I317" t="s">
-        <v>497</v>
+        <v>246</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" t="s">
-        <v>555</v>
+        <v>597</v>
       </c>
       <c r="B318" t="s">
-        <v>556</v>
+        <v>598</v>
       </c>
       <c r="C318" t="s">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="E318" t="s">
-        <v>129</v>
+        <v>244</v>
       </c>
       <c r="F318">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G318" t="s">
         <v>72</v>
@@ -10329,7 +10323,7 @@
         <v>72</v>
       </c>
       <c r="I318" t="s">
-        <v>117</v>
+        <v>246</v>
       </c>
     </row>
     <row r="319" spans="1:9">
@@ -10340,13 +10334,13 @@
         <v>600</v>
       </c>
       <c r="C319" t="s">
-        <v>144</v>
+        <v>333</v>
       </c>
       <c r="E319" t="s">
-        <v>244</v>
+        <v>502</v>
       </c>
       <c r="F319">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G319" t="s">
         <v>72</v>
@@ -10355,7 +10349,7 @@
         <v>72</v>
       </c>
       <c r="I319" t="s">
-        <v>251</v>
+        <v>589</v>
       </c>
     </row>
     <row r="320" spans="1:9">
@@ -10366,10 +10360,10 @@
         <v>600</v>
       </c>
       <c r="C320" t="s">
-        <v>128</v>
+        <v>358</v>
       </c>
       <c r="E320" t="s">
-        <v>244</v>
+        <v>502</v>
       </c>
       <c r="F320">
         <v>1.0</v>
@@ -10381,24 +10375,24 @@
         <v>72</v>
       </c>
       <c r="I320" t="s">
-        <v>246</v>
+        <v>589</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B321" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C321" t="s">
-        <v>335</v>
+        <v>274</v>
       </c>
       <c r="E321" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F321">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G321" t="s">
         <v>72</v>
@@ -10407,24 +10401,24 @@
         <v>72</v>
       </c>
       <c r="I321" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" t="s">
-        <v>601</v>
+        <v>500</v>
       </c>
       <c r="B322" t="s">
-        <v>602</v>
+        <v>501</v>
       </c>
       <c r="C322" t="s">
-        <v>360</v>
+        <v>295</v>
       </c>
       <c r="E322" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F322">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G322" t="s">
         <v>72</v>
@@ -10433,59 +10427,7 @@
         <v>72</v>
       </c>
       <c r="I322" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="323" spans="1:9">
-      <c r="A323" t="s">
-        <v>601</v>
-      </c>
-      <c r="B323" t="s">
-        <v>602</v>
-      </c>
-      <c r="C323" t="s">
-        <v>274</v>
-      </c>
-      <c r="E323" t="s">
-        <v>504</v>
-      </c>
-      <c r="F323">
-        <v>3.0</v>
-      </c>
-      <c r="G323" t="s">
-        <v>72</v>
-      </c>
-      <c r="H323" t="s">
-        <v>72</v>
-      </c>
-      <c r="I323" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="324" spans="1:9">
-      <c r="A324" t="s">
-        <v>502</v>
-      </c>
-      <c r="B324" t="s">
-        <v>503</v>
-      </c>
-      <c r="C324" t="s">
-        <v>296</v>
-      </c>
-      <c r="E324" t="s">
-        <v>504</v>
-      </c>
-      <c r="F324">
-        <v>2.0</v>
-      </c>
-      <c r="G324" t="s">
-        <v>72</v>
-      </c>
-      <c r="H324" t="s">
-        <v>72</v>
-      </c>
-      <c r="I324" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>

--- a/src/inventory/War.xlsx
+++ b/src/inventory/War.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="613">
   <si>
     <t>Code/SKU</t>
   </si>
@@ -812,10 +812,10 @@
     <t>৳550.00</t>
   </si>
   <si>
-    <t>৳2,750.00</t>
-  </si>
-  <si>
-    <t>৳4,200.00</t>
+    <t>৳2,200.00</t>
+  </si>
+  <si>
+    <t>৳3,360.00</t>
   </si>
   <si>
     <t>109-0104-001</t>
@@ -896,264 +896,246 @@
     <t>Drop Shoulder T-Shirt 05</t>
   </si>
   <si>
+    <t>109-0102-064</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 064</t>
+  </si>
+  <si>
+    <t>109-0402-057</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 57</t>
+  </si>
+  <si>
+    <t>৳233.33</t>
+  </si>
+  <si>
+    <t>109-0104-002</t>
+  </si>
+  <si>
+    <t>Card Holder 002</t>
+  </si>
+  <si>
+    <t>109-0104-003</t>
+  </si>
+  <si>
+    <t>Card Holder 003</t>
+  </si>
+  <si>
+    <t>৳590.00</t>
+  </si>
+  <si>
+    <t>৳185.94</t>
+  </si>
+  <si>
+    <t>৳371.88</t>
+  </si>
+  <si>
+    <t>109-0104-004</t>
+  </si>
+  <si>
+    <t>Card Holder 004</t>
+  </si>
+  <si>
+    <t>109-0402-051</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 51</t>
+  </si>
+  <si>
+    <t>৳35.87</t>
+  </si>
+  <si>
+    <t>৳107.61</t>
+  </si>
+  <si>
+    <t>109-0102-073</t>
+  </si>
+  <si>
+    <t>Bifold Leather Wallet 73</t>
+  </si>
+  <si>
+    <t>Men / WALLET,BI-FOLD</t>
+  </si>
+  <si>
+    <t>৳699.00</t>
+  </si>
+  <si>
+    <t>109-0402-048</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 48</t>
+  </si>
+  <si>
+    <t>৳1,980.00</t>
+  </si>
+  <si>
+    <t>109-0102-074</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 74</t>
+  </si>
+  <si>
+    <t>৳1,350.00</t>
+  </si>
+  <si>
+    <t>৳2,097.00</t>
+  </si>
+  <si>
+    <t>109-0502-001</t>
+  </si>
+  <si>
+    <t>Breathable Face Mask</t>
+  </si>
+  <si>
+    <t>Men / MEN,ACCESSORIES,MASK</t>
+  </si>
+  <si>
+    <t>৳199.51</t>
+  </si>
+  <si>
+    <t>৳1,197.09</t>
+  </si>
+  <si>
+    <t>৳1,680.00</t>
+  </si>
+  <si>
+    <t>105-0201-033</t>
+  </si>
+  <si>
+    <t>Full Sleeve Neon Stripe T-shirt</t>
+  </si>
+  <si>
+    <t>109-0402-050</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 50</t>
+  </si>
+  <si>
+    <t>109-0402-056</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 56</t>
+  </si>
+  <si>
+    <t>৳50.00</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>৳431.25</t>
+  </si>
+  <si>
+    <t>101-0300-140</t>
+  </si>
+  <si>
+    <t>Straight Fit Blue Jeans</t>
+  </si>
+  <si>
+    <t>Men / MEN,JEANS,STRAIGHT FIT</t>
+  </si>
+  <si>
+    <t>৳6,760.00</t>
+  </si>
+  <si>
+    <t>102-0302-005</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 005</t>
+  </si>
+  <si>
+    <t>Men / SHIRT</t>
+  </si>
+  <si>
+    <t>৳325.00</t>
+  </si>
+  <si>
+    <t>৳2,600.00</t>
+  </si>
+  <si>
+    <t>৳9,440.00</t>
+  </si>
+  <si>
+    <t>105-0301-004</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 004</t>
+  </si>
+  <si>
+    <t>Men / T-SHIRT,Drop Shoulder</t>
+  </si>
+  <si>
+    <t>109-0402-061</t>
+  </si>
+  <si>
+    <t>Premium Leather Belt 061</t>
+  </si>
+  <si>
+    <t>109-0102-072</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 72</t>
+  </si>
+  <si>
+    <t>102-0302-008</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 008</t>
+  </si>
+  <si>
+    <t>৳285.71</t>
+  </si>
+  <si>
+    <t>৳2,000.00</t>
+  </si>
+  <si>
+    <t>৳9,275.00</t>
+  </si>
+  <si>
+    <t>105-0301-009</t>
+  </si>
+  <si>
+    <t>Deep Violet Drop Shoulder T-Shirt</t>
+  </si>
+  <si>
     <t>৳1,580.00</t>
   </si>
   <si>
-    <t>109-0102-064</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 064</t>
-  </si>
-  <si>
-    <t>109-0402-057</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 57</t>
-  </si>
-  <si>
-    <t>৳233.33</t>
-  </si>
-  <si>
-    <t>105-0301-003</t>
-  </si>
-  <si>
-    <t>Retro Car Print Drop Shoulder T-Shirt</t>
-  </si>
-  <si>
-    <t>109-0104-002</t>
-  </si>
-  <si>
-    <t>Card Holder 002</t>
-  </si>
-  <si>
-    <t>109-0104-003</t>
-  </si>
-  <si>
-    <t>Card Holder 003</t>
-  </si>
-  <si>
-    <t>৳590.00</t>
-  </si>
-  <si>
-    <t>৳185.94</t>
-  </si>
-  <si>
-    <t>৳371.88</t>
-  </si>
-  <si>
-    <t>109-0104-004</t>
-  </si>
-  <si>
-    <t>Card Holder 004</t>
-  </si>
-  <si>
-    <t>109-0402-051</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 51</t>
-  </si>
-  <si>
-    <t>৳35.87</t>
-  </si>
-  <si>
-    <t>৳143.48</t>
-  </si>
-  <si>
-    <t>৳3,960.00</t>
-  </si>
-  <si>
-    <t>109-0102-073</t>
-  </si>
-  <si>
-    <t>Bifold Leather Wallet 73</t>
-  </si>
-  <si>
-    <t>Men / WALLET,BI-FOLD</t>
-  </si>
-  <si>
-    <t>৳699.00</t>
-  </si>
-  <si>
-    <t>109-0402-048</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 48</t>
-  </si>
-  <si>
-    <t>৳1,980.00</t>
-  </si>
-  <si>
-    <t>105-0301-007</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 07</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>৳2,200.00</t>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>109-0501-001</t>
+  </si>
+  <si>
+    <t>Durable Aluminum Water Bottle 600 ml.</t>
+  </si>
+  <si>
+    <t>Men / MEN,ACCESSORIES,WATER BOTTLE</t>
+  </si>
+  <si>
+    <t>৳155.51</t>
+  </si>
+  <si>
+    <t>৳1,088.54</t>
+  </si>
+  <si>
+    <t>৳2,793.00</t>
+  </si>
+  <si>
+    <t>৳2,184.00</t>
+  </si>
+  <si>
+    <t>৳332.44</t>
+  </si>
+  <si>
+    <t>৳1,329.77</t>
   </si>
   <si>
     <t>৳3,160.00</t>
   </si>
   <si>
-    <t>109-0102-074</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 74</t>
-  </si>
-  <si>
-    <t>৳1,350.00</t>
-  </si>
-  <si>
-    <t>৳2,097.00</t>
-  </si>
-  <si>
-    <t>109-0502-001</t>
-  </si>
-  <si>
-    <t>Breathable Face Mask</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,MASK</t>
-  </si>
-  <si>
-    <t>৳199.51</t>
-  </si>
-  <si>
-    <t>৳1,197.09</t>
-  </si>
-  <si>
-    <t>৳1,680.00</t>
-  </si>
-  <si>
-    <t>105-0201-033</t>
-  </si>
-  <si>
-    <t>Full Sleeve Neon Stripe T-shirt</t>
-  </si>
-  <si>
-    <t>109-0402-050</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 50</t>
-  </si>
-  <si>
-    <t>109-0402-056</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 56</t>
-  </si>
-  <si>
-    <t>৳50.00</t>
-  </si>
-  <si>
-    <t>৳431.25</t>
-  </si>
-  <si>
-    <t>101-0300-140</t>
-  </si>
-  <si>
-    <t>Straight Fit Blue Jeans</t>
-  </si>
-  <si>
-    <t>Men / MEN,JEANS,STRAIGHT FIT</t>
-  </si>
-  <si>
-    <t>৳6,760.00</t>
-  </si>
-  <si>
-    <t>102-0302-005</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 005</t>
-  </si>
-  <si>
-    <t>Men / SHIRT</t>
-  </si>
-  <si>
-    <t>৳325.00</t>
-  </si>
-  <si>
-    <t>৳2,600.00</t>
-  </si>
-  <si>
-    <t>৳9,440.00</t>
-  </si>
-  <si>
-    <t>105-0301-004</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 004</t>
-  </si>
-  <si>
-    <t>Men / T-SHIRT,Drop Shoulder</t>
-  </si>
-  <si>
-    <t>102-0302-008</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 008</t>
-  </si>
-  <si>
-    <t>৳285.71</t>
-  </si>
-  <si>
-    <t>৳2,000.00</t>
-  </si>
-  <si>
-    <t>৳9,275.00</t>
-  </si>
-  <si>
-    <t>109-0402-061</t>
-  </si>
-  <si>
-    <t>Premium Leather Belt 061</t>
-  </si>
-  <si>
-    <t>109-0102-072</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 72</t>
-  </si>
-  <si>
-    <t>105-0301-009</t>
-  </si>
-  <si>
-    <t>Deep Violet Drop Shoulder T-Shirt</t>
-  </si>
-  <si>
-    <t>XL</t>
-  </si>
-  <si>
-    <t>109-0501-001</t>
-  </si>
-  <si>
-    <t>Durable Aluminum Water Bottle 600 ml.</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,WATER BOTTLE</t>
-  </si>
-  <si>
-    <t>৳155.51</t>
-  </si>
-  <si>
-    <t>৳1,244.05</t>
-  </si>
-  <si>
-    <t>৳3,192.00</t>
-  </si>
-  <si>
-    <t>৳2,184.00</t>
-  </si>
-  <si>
-    <t>৳332.44</t>
-  </si>
-  <si>
-    <t>৳1,329.77</t>
-  </si>
-  <si>
     <t>109-0104-005</t>
   </si>
   <si>
@@ -1172,9 +1154,6 @@
     <t>Card Holder 06</t>
   </si>
   <si>
-    <t>105-0301-001</t>
-  </si>
-  <si>
     <t>105-0401-006</t>
   </si>
   <si>
@@ -1214,6 +1193,87 @@
     <t>৳111.94</t>
   </si>
   <si>
+    <t>102-0402-032</t>
+  </si>
+  <si>
+    <t>Dark Blue Denim Shirt</t>
+  </si>
+  <si>
+    <t>Men / NEW IN,NEW,MEN,SHIRT,CASUAL SHIRT,DENIM SHIRT,FULL SLEEVE</t>
+  </si>
+  <si>
+    <t>103-0200-100</t>
+  </si>
+  <si>
+    <t>Malibu Polo Shirt in Cotton Pique</t>
+  </si>
+  <si>
+    <t>109-0101-050</t>
+  </si>
+  <si>
+    <t>Leather Long Wallet 50</t>
+  </si>
+  <si>
+    <t>Men / WALLET,LONG</t>
+  </si>
+  <si>
+    <t>৳1,299.00</t>
+  </si>
+  <si>
+    <t>102-0302-002</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 002</t>
+  </si>
+  <si>
+    <t>৳466.67</t>
+  </si>
+  <si>
+    <t>৳2,800.00</t>
+  </si>
+  <si>
+    <t>৳8,700.00</t>
+  </si>
+  <si>
+    <t>105-0401-005</t>
+  </si>
+  <si>
+    <t>Sable Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>102-0301-004</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 004</t>
+  </si>
+  <si>
+    <t>৳243.75</t>
+  </si>
+  <si>
+    <t>৳1,950.00</t>
+  </si>
+  <si>
+    <t>105-0401-003</t>
+  </si>
+  <si>
+    <t>Tank Top 003</t>
+  </si>
+  <si>
+    <t>Men / T-SHIRT,Tank Top</t>
+  </si>
+  <si>
+    <t>৳5,120.00</t>
+  </si>
+  <si>
+    <t>৳200.00</t>
+  </si>
+  <si>
+    <t>৳1,000.00</t>
+  </si>
+  <si>
+    <t>৳6,625.00</t>
+  </si>
+  <si>
     <t>102-0302-006</t>
   </si>
   <si>
@@ -1223,595 +1283,514 @@
     <t>৳278.57</t>
   </si>
   <si>
-    <t>৳1,950.00</t>
-  </si>
-  <si>
-    <t>102-0402-032</t>
-  </si>
-  <si>
-    <t>Dark Blue Denim Shirt</t>
-  </si>
-  <si>
-    <t>Men / NEW IN,NEW,MEN,SHIRT,CASUAL SHIRT,DENIM SHIRT,FULL SLEEVE</t>
-  </si>
-  <si>
-    <t>103-0200-100</t>
-  </si>
-  <si>
-    <t>Malibu Polo Shirt in Cotton Pique</t>
-  </si>
-  <si>
-    <t>109-0101-050</t>
-  </si>
-  <si>
-    <t>Leather Long Wallet 50</t>
-  </si>
-  <si>
-    <t>Men / WALLET,LONG</t>
-  </si>
-  <si>
-    <t>৳1,299.00</t>
-  </si>
-  <si>
-    <t>৳200.00</t>
-  </si>
-  <si>
-    <t>৳1,000.00</t>
-  </si>
-  <si>
-    <t>৳6,625.00</t>
-  </si>
-  <si>
-    <t>102-0302-002</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 002</t>
-  </si>
-  <si>
-    <t>৳466.67</t>
-  </si>
-  <si>
-    <t>৳2,800.00</t>
-  </si>
-  <si>
-    <t>৳8,700.00</t>
-  </si>
-  <si>
-    <t>102-0301-004</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 004</t>
-  </si>
-  <si>
-    <t>৳243.75</t>
-  </si>
-  <si>
-    <t>105-0401-005</t>
-  </si>
-  <si>
-    <t>Sable Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>105-0401-003</t>
-  </si>
-  <si>
-    <t>Tank Top 003</t>
-  </si>
-  <si>
-    <t>Men / T-SHIRT,Tank Top</t>
-  </si>
-  <si>
-    <t>৳5,120.00</t>
+    <t>৳487.50</t>
+  </si>
+  <si>
+    <t>৳4,720.00</t>
+  </si>
+  <si>
+    <t>102-0301-002</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 002</t>
+  </si>
+  <si>
+    <t>৳216.67</t>
+  </si>
+  <si>
+    <t>৳11,925.00</t>
+  </si>
+  <si>
+    <t>109-0101-049</t>
+  </si>
+  <si>
+    <t>Leather Long Wallet 049</t>
+  </si>
+  <si>
+    <t>৳5,300.00</t>
+  </si>
+  <si>
+    <t>৳500.00</t>
+  </si>
+  <si>
+    <t>৳1,080.00</t>
+  </si>
+  <si>
+    <t>৳3,250.00</t>
+  </si>
+  <si>
+    <t>৳8,320.00</t>
+  </si>
+  <si>
+    <t>102-0302-001</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 001</t>
+  </si>
+  <si>
+    <t>৳10,150.00</t>
+  </si>
+  <si>
+    <t>105-0401-007</t>
+  </si>
+  <si>
+    <t>Cabbage Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>৳260.00</t>
+  </si>
+  <si>
+    <t>৳1,300.00</t>
+  </si>
+  <si>
+    <t>৳195.00</t>
+  </si>
+  <si>
+    <t>৳11,800.00</t>
+  </si>
+  <si>
+    <t>৳412.50</t>
+  </si>
+  <si>
+    <t>৳1,650.00</t>
+  </si>
+  <si>
+    <t>৳5,800.00</t>
+  </si>
+  <si>
+    <t>৳10,600.00</t>
+  </si>
+  <si>
+    <t>108-0101-013</t>
+  </si>
+  <si>
+    <t>Brown Sweatshirt in French-Terry</t>
+  </si>
+  <si>
+    <t>105-0401-004</t>
+  </si>
+  <si>
+    <t>Orlando Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>৳2,560.00</t>
+  </si>
+  <si>
+    <t>102-0302-004</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 004</t>
+  </si>
+  <si>
+    <t>৳2,900.00</t>
+  </si>
+  <si>
+    <t>105-0101-377</t>
+  </si>
+  <si>
+    <t>Warm Spice T-shirt</t>
+  </si>
+  <si>
+    <t>Men / NEW IN,NEW,MEN,T-SHIRT,HALF SLEEVE</t>
+  </si>
+  <si>
+    <t>102-0302-007</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 007</t>
+  </si>
+  <si>
+    <t>৳3,975.00</t>
+  </si>
+  <si>
+    <t>৳540.00</t>
+  </si>
+  <si>
+    <t>107-0100-041</t>
+  </si>
+  <si>
+    <t>Black Boxer Brief</t>
+  </si>
+  <si>
+    <t>Men / 30% OFF,MEN,BOXER,BRIEFS,Draft Items</t>
+  </si>
+  <si>
+    <t>102-0302-010</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 010</t>
+  </si>
+  <si>
+    <t>৳275.00</t>
+  </si>
+  <si>
+    <t>105-0401-001</t>
+  </si>
+  <si>
+    <t>Black Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>105-0101-372</t>
+  </si>
+  <si>
+    <t>Deep Harbor T-shirt</t>
+  </si>
+  <si>
+    <t>৳287.50</t>
+  </si>
+  <si>
+    <t>৳1,150.00</t>
+  </si>
+  <si>
+    <t>৳2,650.00</t>
+  </si>
+  <si>
+    <t>৳3,200.00</t>
+  </si>
+  <si>
+    <t>৳1,325.00</t>
+  </si>
+  <si>
+    <t>102-0302-003</t>
+  </si>
+  <si>
+    <t>Cuban Shier 003</t>
+  </si>
+  <si>
+    <t>৳1,450.00</t>
+  </si>
+  <si>
+    <t>105-0202-006</t>
+  </si>
+  <si>
+    <t>Lavender Full Sleeve Turtleneck T-shirt</t>
+  </si>
+  <si>
+    <t>109-0101-045</t>
+  </si>
+  <si>
+    <t>Burgendy Leather Long Wallet</t>
+  </si>
+  <si>
+    <t>Men / NEW IN,NEW,MEN,ACCESSORIES,WALLET,LONG</t>
+  </si>
+  <si>
+    <t>105-0101-380</t>
+  </si>
+  <si>
+    <t>Essential Black T-shirt</t>
+  </si>
+  <si>
+    <t>৳140.00</t>
+  </si>
+  <si>
+    <t>102-0501-001</t>
+  </si>
+  <si>
+    <t>Formal Shirt 001</t>
+  </si>
+  <si>
+    <t>Men / SHIRT,FORMAL SHIRT</t>
+  </si>
+  <si>
+    <t>৳4,760.00</t>
+  </si>
+  <si>
+    <t>105-0101-371</t>
+  </si>
+  <si>
+    <t>Green Essence T-shirt</t>
+  </si>
+  <si>
+    <t>৳175.00</t>
+  </si>
+  <si>
+    <t>৳875.00</t>
+  </si>
+  <si>
+    <t>৳2,950.00</t>
+  </si>
+  <si>
+    <t>৳7,080.00</t>
+  </si>
+  <si>
+    <t>105-0101-374</t>
+  </si>
+  <si>
+    <t>Golden Corn T-shirt</t>
+  </si>
+  <si>
+    <t>৳2,360.00</t>
+  </si>
+  <si>
+    <t>105-0401-008</t>
+  </si>
+  <si>
+    <t>White Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>৳650.00</t>
+  </si>
+  <si>
+    <t>৳4,350.00</t>
+  </si>
+  <si>
+    <t>102-0301-008</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 008</t>
+  </si>
+  <si>
+    <t>৳6,360.00</t>
+  </si>
+  <si>
+    <t>105-0101-375</t>
+  </si>
+  <si>
+    <t>Earth Hemp T-shirt</t>
+  </si>
+  <si>
+    <t>৳420.00</t>
+  </si>
+  <si>
+    <t>৳1,770.00</t>
+  </si>
+  <si>
+    <t>৳7,950.00</t>
+  </si>
+  <si>
+    <t>105-0401-009</t>
+  </si>
+  <si>
+    <t>Gravity Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>৳153.30</t>
+  </si>
+  <si>
+    <t>৳3,540.00</t>
+  </si>
+  <si>
+    <t>105-0201-030</t>
+  </si>
+  <si>
+    <t>Full Sleeve Color-Block T-shirt</t>
+  </si>
+  <si>
+    <t>102-0301-010</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 010</t>
+  </si>
+  <si>
+    <t>৳1,590.00</t>
+  </si>
+  <si>
+    <t>৳433.33</t>
+  </si>
+  <si>
+    <t>105-0201-034</t>
+  </si>
+  <si>
+    <t>Full Sleeve Mustard StripeT-shirt</t>
+  </si>
+  <si>
+    <t>৳975.00</t>
+  </si>
+  <si>
+    <t>105-0101-379</t>
+  </si>
+  <si>
+    <t>Essential White T-shirt</t>
+  </si>
+  <si>
+    <t>102-0301-005</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 005</t>
+  </si>
+  <si>
+    <t>102-0301-009</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 009</t>
+  </si>
+  <si>
+    <t>৳4,770.00</t>
+  </si>
+  <si>
+    <t>105-0201-032</t>
+  </si>
+  <si>
+    <t>Full Sleeve White Stripe T-shirt</t>
+  </si>
+  <si>
+    <t>৳525.00</t>
+  </si>
+  <si>
+    <t>102-0301-003</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 003</t>
+  </si>
+  <si>
+    <t>৳5,900.00</t>
+  </si>
+  <si>
+    <t>৳4,130.00</t>
+  </si>
+  <si>
+    <t>105-0201-031</t>
+  </si>
+  <si>
+    <t>Full Sleeve Trio-Tone T-shirt</t>
+  </si>
+  <si>
+    <t>102-0301-001</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 001</t>
+  </si>
+  <si>
+    <t>102-0301-007</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 007</t>
+  </si>
+  <si>
+    <t>102-0301-006</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 006</t>
+  </si>
+  <si>
+    <t>108-0101-014</t>
+  </si>
+  <si>
+    <t>Teal Sweatshirt in French-Terry</t>
+  </si>
+  <si>
+    <t>৳6.37</t>
+  </si>
+  <si>
+    <t>102-0301-014</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 014</t>
+  </si>
+  <si>
+    <t>102-0301-011</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 011</t>
+  </si>
+  <si>
+    <t>107-0100-043</t>
+  </si>
+  <si>
+    <t>Blue Boxer Brief</t>
+  </si>
+  <si>
+    <t>Men / 50% OFF,MEN,BOXER,BRIEFS,Draft Items</t>
+  </si>
+  <si>
+    <t>110-0101-015</t>
+  </si>
+  <si>
+    <t>Teal Trousers</t>
+  </si>
+  <si>
+    <t>109-0102-052</t>
+  </si>
+  <si>
+    <t>Polished Black Bifold Leather Wallet</t>
+  </si>
+  <si>
+    <t>Men / NEW IN,NEW,MEN,ACCESSORIES,WALLET,BI-FOLD</t>
+  </si>
+  <si>
+    <t>৳1,800.00</t>
+  </si>
+  <si>
+    <t>109-0102-053</t>
+  </si>
+  <si>
+    <t>Polished Choco Bifold Leather Wallet</t>
+  </si>
+  <si>
+    <t>109-0102-057</t>
+  </si>
+  <si>
+    <t>Burnt Choco Bifold Leather Wallet</t>
+  </si>
+  <si>
+    <t>DMB114</t>
+  </si>
+  <si>
+    <t>Belt 114</t>
+  </si>
+  <si>
+    <t>৳8,330.00</t>
+  </si>
+  <si>
+    <t>৳5,950.00</t>
+  </si>
+  <si>
+    <t>102-0501-002</t>
+  </si>
+  <si>
+    <t>Formal Shirt  002</t>
+  </si>
+  <si>
+    <t>৳3,570.00</t>
+  </si>
+  <si>
+    <t>102-0501-002-</t>
+  </si>
+  <si>
+    <t>৳2,380.00</t>
+  </si>
+  <si>
+    <t>102-0501-003</t>
+  </si>
+  <si>
+    <t>Formal Shirt 003</t>
+  </si>
+  <si>
+    <t>৳2,980.00</t>
+  </si>
+  <si>
+    <t>৳8,940.00</t>
+  </si>
+  <si>
+    <t>৳4,470.00</t>
+  </si>
+  <si>
+    <t>102-0501-004</t>
+  </si>
+  <si>
+    <t>Formal Shirt 004</t>
+  </si>
+  <si>
+    <t>102-0501-005</t>
+  </si>
+  <si>
+    <t>Formal Shirt 005</t>
+  </si>
+  <si>
+    <t>102-0501-006-</t>
+  </si>
+  <si>
+    <t>Formal Shirt 006</t>
+  </si>
+  <si>
+    <t>102-0501-006</t>
+  </si>
+  <si>
+    <t>৳5,400.00</t>
   </si>
   <si>
     <t>৳2,700.00</t>
-  </si>
-  <si>
-    <t>102-0301-002</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 002</t>
-  </si>
-  <si>
-    <t>৳216.67</t>
-  </si>
-  <si>
-    <t>৳11,925.00</t>
-  </si>
-  <si>
-    <t>৳5,300.00</t>
-  </si>
-  <si>
-    <t>৳487.50</t>
-  </si>
-  <si>
-    <t>৳4,720.00</t>
-  </si>
-  <si>
-    <t>102-0302-001</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 001</t>
-  </si>
-  <si>
-    <t>৳10,150.00</t>
-  </si>
-  <si>
-    <t>109-0101-049</t>
-  </si>
-  <si>
-    <t>Leather Long Wallet 049</t>
-  </si>
-  <si>
-    <t>৳500.00</t>
-  </si>
-  <si>
-    <t>৳1,080.00</t>
-  </si>
-  <si>
-    <t>৳260.00</t>
-  </si>
-  <si>
-    <t>৳1,300.00</t>
-  </si>
-  <si>
-    <t>৳3,250.00</t>
-  </si>
-  <si>
-    <t>৳8,320.00</t>
-  </si>
-  <si>
-    <t>105-0401-007</t>
-  </si>
-  <si>
-    <t>Cabbage Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>৳1,770.00</t>
-  </si>
-  <si>
-    <t>৳195.00</t>
-  </si>
-  <si>
-    <t>৳11,800.00</t>
-  </si>
-  <si>
-    <t>৳10,600.00</t>
-  </si>
-  <si>
-    <t>৳412.50</t>
-  </si>
-  <si>
-    <t>৳1,650.00</t>
-  </si>
-  <si>
-    <t>৳5,800.00</t>
-  </si>
-  <si>
-    <t>108-0101-013</t>
-  </si>
-  <si>
-    <t>Brown Sweatshirt in French-Terry</t>
-  </si>
-  <si>
-    <t>105-0401-004</t>
-  </si>
-  <si>
-    <t>Orlando Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>৳2,560.00</t>
-  </si>
-  <si>
-    <t>102-0302-004</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 004</t>
-  </si>
-  <si>
-    <t>৳2,900.00</t>
-  </si>
-  <si>
-    <t>102-0302-010</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 010</t>
-  </si>
-  <si>
-    <t>৳275.00</t>
-  </si>
-  <si>
-    <t>102-0302-007</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 007</t>
-  </si>
-  <si>
-    <t>৳3,975.00</t>
-  </si>
-  <si>
-    <t>105-0101-377</t>
-  </si>
-  <si>
-    <t>Warm Spice T-shirt</t>
-  </si>
-  <si>
-    <t>Men / NEW IN,NEW,MEN,T-SHIRT,HALF SLEEVE</t>
-  </si>
-  <si>
-    <t>৳540.00</t>
-  </si>
-  <si>
-    <t>105-0401-001</t>
-  </si>
-  <si>
-    <t>Black Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>107-0100-041</t>
-  </si>
-  <si>
-    <t>Black Boxer Brief</t>
-  </si>
-  <si>
-    <t>Men / 30% OFF,MEN,BOXER,BRIEFS,Draft Items</t>
-  </si>
-  <si>
-    <t>৳287.50</t>
-  </si>
-  <si>
-    <t>৳1,150.00</t>
-  </si>
-  <si>
-    <t>105-0101-372</t>
-  </si>
-  <si>
-    <t>Deep Harbor T-shirt</t>
-  </si>
-  <si>
-    <t>৳2,650.00</t>
-  </si>
-  <si>
-    <t>৳3,840.00</t>
-  </si>
-  <si>
-    <t>৳1,325.00</t>
-  </si>
-  <si>
-    <t>102-0302-003</t>
-  </si>
-  <si>
-    <t>Cuban Shier 003</t>
-  </si>
-  <si>
-    <t>৳1,450.00</t>
-  </si>
-  <si>
-    <t>105-0202-006</t>
-  </si>
-  <si>
-    <t>Lavender Full Sleeve Turtleneck T-shirt</t>
-  </si>
-  <si>
-    <t>109-0101-045</t>
-  </si>
-  <si>
-    <t>Burgendy Leather Long Wallet</t>
-  </si>
-  <si>
-    <t>Men / NEW IN,NEW,MEN,ACCESSORIES,WALLET,LONG</t>
-  </si>
-  <si>
-    <t>105-0101-380</t>
-  </si>
-  <si>
-    <t>Essential Black T-shirt</t>
-  </si>
-  <si>
-    <t>৳140.00</t>
-  </si>
-  <si>
-    <t>৳7,080.00</t>
-  </si>
-  <si>
-    <t>৳650.00</t>
-  </si>
-  <si>
-    <t>102-0501-001</t>
-  </si>
-  <si>
-    <t>Formal Shirt 001</t>
-  </si>
-  <si>
-    <t>Men / SHIRT,FORMAL SHIRT</t>
-  </si>
-  <si>
-    <t>৳4,760.00</t>
-  </si>
-  <si>
-    <t>105-0101-371</t>
-  </si>
-  <si>
-    <t>Green Essence T-shirt</t>
-  </si>
-  <si>
-    <t>৳175.00</t>
-  </si>
-  <si>
-    <t>৳875.00</t>
-  </si>
-  <si>
-    <t>৳2,950.00</t>
-  </si>
-  <si>
-    <t>৳4,350.00</t>
-  </si>
-  <si>
-    <t>105-0101-374</t>
-  </si>
-  <si>
-    <t>Golden Corn T-shirt</t>
-  </si>
-  <si>
-    <t>৳2,360.00</t>
-  </si>
-  <si>
-    <t>105-0401-008</t>
-  </si>
-  <si>
-    <t>White Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>102-0301-008</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 008</t>
-  </si>
-  <si>
-    <t>৳6,360.00</t>
-  </si>
-  <si>
-    <t>৳7,950.00</t>
-  </si>
-  <si>
-    <t>105-0101-375</t>
-  </si>
-  <si>
-    <t>Earth Hemp T-shirt</t>
-  </si>
-  <si>
-    <t>৳560.00</t>
-  </si>
-  <si>
-    <t>৳3,540.00</t>
-  </si>
-  <si>
-    <t>105-0401-009</t>
-  </si>
-  <si>
-    <t>Gravity Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>৳153.30</t>
-  </si>
-  <si>
-    <t>105-0201-030</t>
-  </si>
-  <si>
-    <t>Full Sleeve Color-Block T-shirt</t>
-  </si>
-  <si>
-    <t>৳107.69</t>
-  </si>
-  <si>
-    <t>102-0301-010</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 010</t>
-  </si>
-  <si>
-    <t>৳1,590.00</t>
-  </si>
-  <si>
-    <t>৳433.33</t>
-  </si>
-  <si>
-    <t>105-0201-034</t>
-  </si>
-  <si>
-    <t>Full Sleeve Mustard StripeT-shirt</t>
-  </si>
-  <si>
-    <t>৳975.00</t>
-  </si>
-  <si>
-    <t>105-0101-379</t>
-  </si>
-  <si>
-    <t>Essential White T-shirt</t>
-  </si>
-  <si>
-    <t>102-0301-005</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 005</t>
-  </si>
-  <si>
-    <t>102-0301-009</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 009</t>
-  </si>
-  <si>
-    <t>৳4,770.00</t>
-  </si>
-  <si>
-    <t>105-0201-032</t>
-  </si>
-  <si>
-    <t>Full Sleeve White Stripe T-shirt</t>
-  </si>
-  <si>
-    <t>102-0301-003</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 003</t>
-  </si>
-  <si>
-    <t>৳5,900.00</t>
-  </si>
-  <si>
-    <t>৳525.00</t>
-  </si>
-  <si>
-    <t>৳4,130.00</t>
-  </si>
-  <si>
-    <t>102-0301-001</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 001</t>
-  </si>
-  <si>
-    <t>102-0301-007</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 007</t>
-  </si>
-  <si>
-    <t>105-0201-031</t>
-  </si>
-  <si>
-    <t>Full Sleeve Trio-Tone T-shirt</t>
-  </si>
-  <si>
-    <t>102-0301-006</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 006</t>
-  </si>
-  <si>
-    <t>108-0101-014</t>
-  </si>
-  <si>
-    <t>Teal Sweatshirt in French-Terry</t>
-  </si>
-  <si>
-    <t>102-0301-014</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 014</t>
-  </si>
-  <si>
-    <t>102-0301-011</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 011</t>
-  </si>
-  <si>
-    <t>107-0100-043</t>
-  </si>
-  <si>
-    <t>Blue Boxer Brief</t>
-  </si>
-  <si>
-    <t>Men / 50% OFF,MEN,BOXER,BRIEFS,Draft Items</t>
-  </si>
-  <si>
-    <t>110-0101-015</t>
-  </si>
-  <si>
-    <t>Teal Trousers</t>
-  </si>
-  <si>
-    <t>109-0102-052</t>
-  </si>
-  <si>
-    <t>Polished Black Bifold Leather Wallet</t>
-  </si>
-  <si>
-    <t>Men / NEW IN,NEW,MEN,ACCESSORIES,WALLET,BI-FOLD</t>
-  </si>
-  <si>
-    <t>৳1,800.00</t>
-  </si>
-  <si>
-    <t>109-0102-053</t>
-  </si>
-  <si>
-    <t>Polished Choco Bifold Leather Wallet</t>
-  </si>
-  <si>
-    <t>109-0102-057</t>
-  </si>
-  <si>
-    <t>Burnt Choco Bifold Leather Wallet</t>
-  </si>
-  <si>
-    <t>DMB114</t>
-  </si>
-  <si>
-    <t>Belt 114</t>
-  </si>
-  <si>
-    <t>৳8,330.00</t>
-  </si>
-  <si>
-    <t>৳5,950.00</t>
-  </si>
-  <si>
-    <t>102-0501-002</t>
-  </si>
-  <si>
-    <t>Formal Shirt  002</t>
-  </si>
-  <si>
-    <t>৳2,380.00</t>
-  </si>
-  <si>
-    <t>৳3,570.00</t>
-  </si>
-  <si>
-    <t>102-0501-002-</t>
-  </si>
-  <si>
-    <t>102-0501-003</t>
-  </si>
-  <si>
-    <t>Formal Shirt 003</t>
-  </si>
-  <si>
-    <t>৳2,980.00</t>
-  </si>
-  <si>
-    <t>৳8,940.00</t>
-  </si>
-  <si>
-    <t>৳4,470.00</t>
-  </si>
-  <si>
-    <t>102-0501-004</t>
-  </si>
-  <si>
-    <t>Formal Shirt 004</t>
-  </si>
-  <si>
-    <t>102-0501-005</t>
-  </si>
-  <si>
-    <t>Formal Shirt 005</t>
-  </si>
-  <si>
-    <t>102-0501-006-</t>
-  </si>
-  <si>
-    <t>Formal Shirt 006</t>
-  </si>
-  <si>
-    <t>102-0501-006</t>
-  </si>
-  <si>
-    <t>৳5,400.00</t>
   </si>
   <si>
     <t>102-0501-008</t>
@@ -2214,7 +2193,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I352"/>
+  <dimension ref="A1:I339"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -4625,7 +4604,7 @@
         <v>263</v>
       </c>
       <c r="F94">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G94" t="s">
         <v>264</v>
@@ -4827,24 +4806,24 @@
         <v>263</v>
       </c>
       <c r="F102">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G102" t="s">
         <v>264</v>
       </c>
       <c r="H102" t="s">
-        <v>194</v>
+        <v>264</v>
       </c>
       <c r="I102" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
+        <v>293</v>
+      </c>
+      <c r="B103" t="s">
         <v>294</v>
-      </c>
-      <c r="B103" t="s">
-        <v>295</v>
       </c>
       <c r="E103" t="s">
         <v>214</v>
@@ -4864,10 +4843,10 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" t="s">
+        <v>295</v>
+      </c>
+      <c r="B104" t="s">
         <v>296</v>
-      </c>
-      <c r="B104" t="s">
-        <v>297</v>
       </c>
       <c r="E104" t="s">
         <v>192</v>
@@ -4902,10 +4881,10 @@
         <v>1.0</v>
       </c>
       <c r="G105" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H105" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I105" t="s">
         <v>257</v>
@@ -4913,143 +4892,140 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
+        <v>298</v>
+      </c>
+      <c r="B106" t="s">
         <v>299</v>
       </c>
-      <c r="B106" t="s">
-        <v>300</v>
-      </c>
-      <c r="C106" t="s">
-        <v>262</v>
-      </c>
       <c r="E106" t="s">
-        <v>285</v>
+        <v>214</v>
       </c>
       <c r="F106">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G106" t="s">
         <v>269</v>
       </c>
       <c r="H106" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I106" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" t="s">
+        <v>300</v>
+      </c>
+      <c r="B107" t="s">
         <v>301</v>
-      </c>
-      <c r="B107" t="s">
-        <v>302</v>
       </c>
       <c r="E107" t="s">
         <v>214</v>
       </c>
       <c r="F107">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G107" t="s">
         <v>269</v>
       </c>
       <c r="H107" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I107" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
+        <v>202</v>
+      </c>
+      <c r="B108" t="s">
+        <v>203</v>
+      </c>
+      <c r="C108" t="s">
+        <v>164</v>
+      </c>
+      <c r="E108" t="s">
+        <v>130</v>
+      </c>
+      <c r="F108">
+        <v>2.0</v>
+      </c>
+      <c r="G108" t="s">
         <v>303</v>
       </c>
-      <c r="B108" t="s">
+      <c r="H108" t="s">
         <v>304</v>
       </c>
-      <c r="E108" t="s">
-        <v>214</v>
-      </c>
-      <c r="F108">
-        <v>1.0</v>
-      </c>
-      <c r="G108" t="s">
-        <v>269</v>
-      </c>
-      <c r="H108" t="s">
-        <v>269</v>
-      </c>
       <c r="I108" t="s">
-        <v>305</v>
+        <v>206</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>202</v>
+        <v>305</v>
       </c>
       <c r="B109" t="s">
-        <v>203</v>
-      </c>
-      <c r="C109" t="s">
-        <v>164</v>
+        <v>306</v>
       </c>
       <c r="E109" t="s">
-        <v>130</v>
+        <v>214</v>
       </c>
       <c r="F109">
         <v>2.0</v>
       </c>
       <c r="G109" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="H109" t="s">
-        <v>307</v>
+        <v>270</v>
       </c>
       <c r="I109" t="s">
-        <v>206</v>
+        <v>271</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" t="s">
+        <v>307</v>
+      </c>
+      <c r="B110" t="s">
         <v>308</v>
       </c>
-      <c r="B110" t="s">
+      <c r="E110" t="s">
+        <v>192</v>
+      </c>
+      <c r="F110">
+        <v>3.0</v>
+      </c>
+      <c r="G110" t="s">
         <v>309</v>
       </c>
-      <c r="E110" t="s">
-        <v>214</v>
-      </c>
-      <c r="F110">
-        <v>2.0</v>
-      </c>
-      <c r="G110" t="s">
-        <v>269</v>
-      </c>
       <c r="H110" t="s">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="I110" t="s">
-        <v>271</v>
+        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B111" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E111" t="s">
-        <v>192</v>
+        <v>313</v>
       </c>
       <c r="F111">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G111" t="s">
-        <v>312</v>
+        <v>215</v>
       </c>
       <c r="H111" t="s">
-        <v>313</v>
+        <v>215</v>
       </c>
       <c r="I111" t="s">
         <v>314</v>
@@ -5063,39 +5039,39 @@
         <v>316</v>
       </c>
       <c r="E112" t="s">
+        <v>192</v>
+      </c>
+      <c r="F112">
+        <v>2.0</v>
+      </c>
+      <c r="G112" t="s">
+        <v>69</v>
+      </c>
+      <c r="H112" t="s">
+        <v>69</v>
+      </c>
+      <c r="I112" t="s">
         <v>317</v>
-      </c>
-      <c r="F112">
-        <v>1.0</v>
-      </c>
-      <c r="G112" t="s">
-        <v>215</v>
-      </c>
-      <c r="H112" t="s">
-        <v>215</v>
-      </c>
-      <c r="I112" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
+        <v>318</v>
+      </c>
+      <c r="B113" t="s">
         <v>319</v>
       </c>
-      <c r="B113" t="s">
+      <c r="E113" t="s">
+        <v>313</v>
+      </c>
+      <c r="F113">
+        <v>3.0</v>
+      </c>
+      <c r="G113" t="s">
+        <v>215</v>
+      </c>
+      <c r="H113" t="s">
         <v>320</v>
-      </c>
-      <c r="E113" t="s">
-        <v>192</v>
-      </c>
-      <c r="F113">
-        <v>2.0</v>
-      </c>
-      <c r="G113" t="s">
-        <v>69</v>
-      </c>
-      <c r="H113" t="s">
-        <v>69</v>
       </c>
       <c r="I113" t="s">
         <v>321</v>
@@ -5108,328 +5084,331 @@
       <c r="B114" t="s">
         <v>323</v>
       </c>
-      <c r="C114" t="s">
+      <c r="E114" t="s">
         <v>324</v>
       </c>
-      <c r="E114" t="s">
-        <v>263</v>
-      </c>
       <c r="F114">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G114" t="s">
-        <v>264</v>
+        <v>325</v>
       </c>
       <c r="H114" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I114" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B115" t="s">
-        <v>328</v>
+        <v>329</v>
+      </c>
+      <c r="C115" t="s">
+        <v>164</v>
       </c>
       <c r="E115" t="s">
-        <v>317</v>
+        <v>236</v>
       </c>
       <c r="F115">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G115" t="s">
-        <v>215</v>
+        <v>69</v>
       </c>
       <c r="H115" t="s">
-        <v>329</v>
+        <v>69</v>
       </c>
       <c r="I115" t="s">
-        <v>330</v>
+        <v>238</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
+        <v>330</v>
+      </c>
+      <c r="B116" t="s">
         <v>331</v>
       </c>
-      <c r="B116" t="s">
-        <v>332</v>
-      </c>
       <c r="E116" t="s">
-        <v>333</v>
+        <v>192</v>
       </c>
       <c r="F116">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G116" t="s">
-        <v>334</v>
+        <v>69</v>
       </c>
       <c r="H116" t="s">
-        <v>335</v>
+        <v>69</v>
       </c>
       <c r="I116" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B117" t="s">
-        <v>338</v>
-      </c>
-      <c r="C117" t="s">
-        <v>164</v>
+        <v>333</v>
       </c>
       <c r="E117" t="s">
-        <v>236</v>
+        <v>192</v>
       </c>
       <c r="F117">
         <v>1.0</v>
       </c>
       <c r="G117" t="s">
-        <v>69</v>
+        <v>334</v>
       </c>
       <c r="H117" t="s">
-        <v>69</v>
+        <v>334</v>
       </c>
       <c r="I117" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>339</v>
+        <v>291</v>
       </c>
       <c r="B118" t="s">
-        <v>340</v>
+        <v>292</v>
+      </c>
+      <c r="C118" t="s">
+        <v>335</v>
       </c>
       <c r="E118" t="s">
-        <v>192</v>
+        <v>263</v>
       </c>
       <c r="F118">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G118" t="s">
-        <v>69</v>
+        <v>336</v>
       </c>
       <c r="H118" t="s">
-        <v>69</v>
+        <v>336</v>
       </c>
       <c r="I118" t="s">
-        <v>321</v>
+        <v>286</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B119" t="s">
-        <v>342</v>
+        <v>338</v>
+      </c>
+      <c r="C119">
+        <v>28</v>
       </c>
       <c r="E119" t="s">
-        <v>192</v>
+        <v>339</v>
       </c>
       <c r="F119">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G119" t="s">
-        <v>343</v>
+        <v>69</v>
       </c>
       <c r="H119" t="s">
-        <v>343</v>
+        <v>69</v>
       </c>
       <c r="I119" t="s">
-        <v>198</v>
+        <v>340</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="B120" t="s">
-        <v>292</v>
+        <v>342</v>
       </c>
       <c r="C120" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="E120" t="s">
-        <v>263</v>
+        <v>343</v>
       </c>
       <c r="F120">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G120" t="s">
         <v>344</v>
       </c>
       <c r="H120" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I120" t="s">
-        <v>286</v>
+        <v>346</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B121" t="s">
-        <v>346</v>
-      </c>
-      <c r="C121">
-        <v>28</v>
+        <v>348</v>
+      </c>
+      <c r="C121" t="s">
+        <v>262</v>
       </c>
       <c r="E121" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F121">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G121" t="s">
-        <v>69</v>
+        <v>269</v>
       </c>
       <c r="H121" t="s">
-        <v>69</v>
+        <v>269</v>
       </c>
       <c r="I121" t="s">
-        <v>348</v>
+        <v>289</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B122" t="s">
-        <v>350</v>
-      </c>
-      <c r="C122" t="s">
-        <v>262</v>
+        <v>351</v>
       </c>
       <c r="E122" t="s">
-        <v>351</v>
+        <v>192</v>
       </c>
       <c r="F122">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G122" t="s">
-        <v>352</v>
+        <v>215</v>
       </c>
       <c r="H122" t="s">
-        <v>353</v>
+        <v>216</v>
       </c>
       <c r="I122" t="s">
-        <v>354</v>
+        <v>317</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B123" t="s">
-        <v>356</v>
-      </c>
-      <c r="C123" t="s">
-        <v>262</v>
+        <v>353</v>
       </c>
       <c r="E123" t="s">
-        <v>357</v>
+        <v>313</v>
       </c>
       <c r="F123">
         <v>1.0</v>
       </c>
       <c r="G123" t="s">
-        <v>269</v>
+        <v>215</v>
       </c>
       <c r="H123" t="s">
-        <v>269</v>
+        <v>215</v>
       </c>
       <c r="I123" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B124" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C124" t="s">
         <v>262</v>
       </c>
       <c r="E124" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F124">
         <v>7.0</v>
       </c>
       <c r="G124" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H124" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="I124" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B125" t="s">
-        <v>364</v>
+        <v>360</v>
+      </c>
+      <c r="C125" t="s">
+        <v>262</v>
       </c>
       <c r="E125" t="s">
-        <v>192</v>
+        <v>285</v>
       </c>
       <c r="F125">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G125" t="s">
-        <v>215</v>
+        <v>269</v>
       </c>
       <c r="H125" t="s">
-        <v>216</v>
+        <v>269</v>
       </c>
       <c r="I125" t="s">
-        <v>321</v>
+        <v>286</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>365</v>
+        <v>282</v>
       </c>
       <c r="B126" t="s">
-        <v>366</v>
+        <v>283</v>
+      </c>
+      <c r="C126" t="s">
+        <v>335</v>
       </c>
       <c r="E126" t="s">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="F126">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G126" t="s">
-        <v>215</v>
+        <v>269</v>
       </c>
       <c r="H126" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
       <c r="I126" t="s">
-        <v>318</v>
+        <v>361</v>
       </c>
     </row>
     <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="B127" t="s">
-        <v>368</v>
+        <v>283</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>362</v>
       </c>
       <c r="E127" t="s">
         <v>285</v>
@@ -5444,105 +5423,102 @@
         <v>270</v>
       </c>
       <c r="I127" t="s">
-        <v>293</v>
+        <v>361</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>282</v>
+        <v>363</v>
       </c>
       <c r="B128" t="s">
-        <v>283</v>
-      </c>
-      <c r="C128" t="s">
-        <v>324</v>
+        <v>364</v>
       </c>
       <c r="E128" t="s">
-        <v>285</v>
+        <v>365</v>
       </c>
       <c r="F128">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G128" t="s">
-        <v>269</v>
+        <v>366</v>
       </c>
       <c r="H128" t="s">
-        <v>270</v>
+        <v>367</v>
       </c>
       <c r="I128" t="s">
-        <v>293</v>
+        <v>368</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>282</v>
+        <v>328</v>
       </c>
       <c r="B129" t="s">
-        <v>283</v>
+        <v>329</v>
       </c>
       <c r="C129" t="s">
+        <v>148</v>
+      </c>
+      <c r="E129" t="s">
+        <v>236</v>
+      </c>
+      <c r="F129">
+        <v>3.0</v>
+      </c>
+      <c r="G129" t="s">
+        <v>69</v>
+      </c>
+      <c r="H129" t="s">
+        <v>69</v>
+      </c>
+      <c r="I129" t="s">
         <v>369</v>
-      </c>
-      <c r="E129" t="s">
-        <v>285</v>
-      </c>
-      <c r="F129">
-        <v>2.0</v>
-      </c>
-      <c r="G129" t="s">
-        <v>269</v>
-      </c>
-      <c r="H129" t="s">
-        <v>270</v>
-      </c>
-      <c r="I129" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" t="s">
+        <v>282</v>
+      </c>
+      <c r="B130" t="s">
+        <v>283</v>
+      </c>
+      <c r="C130" t="s">
+        <v>262</v>
+      </c>
+      <c r="E130" t="s">
+        <v>285</v>
+      </c>
+      <c r="F130">
+        <v>4.0</v>
+      </c>
+      <c r="G130" t="s">
         <v>370</v>
       </c>
-      <c r="B130" t="s">
+      <c r="H130" t="s">
         <v>371</v>
       </c>
-      <c r="E130" t="s">
+      <c r="I130" t="s">
         <v>372</v>
-      </c>
-      <c r="F130">
-        <v>8.0</v>
-      </c>
-      <c r="G130" t="s">
-        <v>373</v>
-      </c>
-      <c r="H130" t="s">
-        <v>374</v>
-      </c>
-      <c r="I130" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="B131" t="s">
-        <v>338</v>
-      </c>
-      <c r="C131" t="s">
-        <v>148</v>
+        <v>374</v>
       </c>
       <c r="E131" t="s">
-        <v>236</v>
+        <v>375</v>
       </c>
       <c r="F131">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G131" t="s">
-        <v>69</v>
+        <v>269</v>
       </c>
       <c r="H131" t="s">
-        <v>69</v>
+        <v>269</v>
       </c>
       <c r="I131" t="s">
         <v>376</v>
@@ -5550,28 +5526,25 @@
     </row>
     <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>282</v>
+        <v>377</v>
       </c>
       <c r="B132" t="s">
-        <v>283</v>
-      </c>
-      <c r="C132" t="s">
-        <v>262</v>
+        <v>378</v>
       </c>
       <c r="E132" t="s">
-        <v>285</v>
+        <v>375</v>
       </c>
       <c r="F132">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G132" t="s">
-        <v>377</v>
+        <v>269</v>
       </c>
       <c r="H132" t="s">
-        <v>378</v>
+        <v>269</v>
       </c>
       <c r="I132" t="s">
-        <v>326</v>
+        <v>376</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -5581,162 +5554,168 @@
       <c r="B133" t="s">
         <v>380</v>
       </c>
+      <c r="C133" t="s">
+        <v>262</v>
+      </c>
       <c r="E133" t="s">
         <v>381</v>
       </c>
       <c r="F133">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G133" t="s">
-        <v>269</v>
+        <v>382</v>
       </c>
       <c r="H133" t="s">
-        <v>269</v>
+        <v>383</v>
       </c>
       <c r="I133" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="B134" t="s">
-        <v>384</v>
+        <v>360</v>
+      </c>
+      <c r="C134" t="s">
+        <v>335</v>
       </c>
       <c r="E134" t="s">
-        <v>381</v>
+        <v>285</v>
       </c>
       <c r="F134">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G134" t="s">
         <v>269</v>
       </c>
       <c r="H134" t="s">
-        <v>269</v>
+        <v>385</v>
       </c>
       <c r="I134" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B135" t="s">
-        <v>261</v>
+        <v>388</v>
       </c>
       <c r="C135" t="s">
-        <v>324</v>
+        <v>164</v>
       </c>
       <c r="E135" t="s">
-        <v>263</v>
+        <v>112</v>
       </c>
       <c r="F135">
         <v>1.0</v>
       </c>
       <c r="G135" t="s">
-        <v>264</v>
+        <v>69</v>
       </c>
       <c r="H135" t="s">
-        <v>264</v>
+        <v>69</v>
       </c>
       <c r="I135" t="s">
-        <v>289</v>
+        <v>389</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>386</v>
+        <v>282</v>
       </c>
       <c r="B136" t="s">
-        <v>387</v>
+        <v>283</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>390</v>
       </c>
       <c r="E136" t="s">
-        <v>388</v>
+        <v>285</v>
       </c>
       <c r="F136">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G136" t="s">
-        <v>389</v>
+        <v>269</v>
       </c>
       <c r="H136" t="s">
-        <v>390</v>
+        <v>270</v>
       </c>
       <c r="I136" t="s">
-        <v>391</v>
+        <v>361</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="B137" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="C137" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="E137" t="s">
-        <v>285</v>
+        <v>343</v>
       </c>
       <c r="F137">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="G137" t="s">
-        <v>269</v>
+        <v>344</v>
       </c>
       <c r="H137" t="s">
-        <v>392</v>
+        <v>345</v>
       </c>
       <c r="I137" t="s">
-        <v>393</v>
+        <v>346</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>349</v>
+        <v>239</v>
       </c>
       <c r="B138" t="s">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="C138" t="s">
-        <v>369</v>
+        <v>164</v>
       </c>
       <c r="E138" t="s">
-        <v>351</v>
+        <v>226</v>
       </c>
       <c r="F138">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G138" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
       <c r="H138" t="s">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="I138" t="s">
-        <v>354</v>
+        <v>257</v>
       </c>
     </row>
     <row r="139" spans="1:9">
       <c r="A139" t="s">
+        <v>392</v>
+      </c>
+      <c r="B139" t="s">
+        <v>393</v>
+      </c>
+      <c r="C139" t="s">
+        <v>148</v>
+      </c>
+      <c r="E139" t="s">
         <v>394</v>
       </c>
-      <c r="B139" t="s">
-        <v>395</v>
-      </c>
-      <c r="C139" t="s">
-        <v>164</v>
-      </c>
-      <c r="E139" t="s">
-        <v>112</v>
-      </c>
       <c r="F139">
         <v>1.0</v>
       </c>
@@ -5747,408 +5726,405 @@
         <v>69</v>
       </c>
       <c r="I139" t="s">
-        <v>396</v>
+        <v>188</v>
       </c>
     </row>
     <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>282</v>
+        <v>395</v>
       </c>
       <c r="B140" t="s">
-        <v>283</v>
+        <v>396</v>
       </c>
       <c r="C140" t="s">
-        <v>397</v>
+        <v>111</v>
       </c>
       <c r="E140" t="s">
-        <v>285</v>
+        <v>112</v>
       </c>
       <c r="F140">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G140" t="s">
-        <v>269</v>
+        <v>69</v>
       </c>
       <c r="H140" t="s">
-        <v>270</v>
+        <v>69</v>
       </c>
       <c r="I140" t="s">
-        <v>293</v>
+        <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>239</v>
+        <v>397</v>
       </c>
       <c r="B141" t="s">
-        <v>240</v>
-      </c>
-      <c r="C141" t="s">
-        <v>164</v>
+        <v>398</v>
       </c>
       <c r="E141" t="s">
-        <v>226</v>
+        <v>399</v>
       </c>
       <c r="F141">
         <v>1.0</v>
       </c>
       <c r="G141" t="s">
-        <v>398</v>
+        <v>69</v>
       </c>
       <c r="H141" t="s">
-        <v>398</v>
+        <v>69</v>
       </c>
       <c r="I141" t="s">
-        <v>257</v>
+        <v>400</v>
       </c>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B142" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C142" t="s">
         <v>262</v>
       </c>
       <c r="E142" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F142">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G142" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H142" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I142" t="s">
-        <v>362</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B143" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C143" t="s">
-        <v>148</v>
+        <v>390</v>
       </c>
       <c r="E143" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="F143">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G143" t="s">
-        <v>69</v>
+        <v>382</v>
       </c>
       <c r="H143" t="s">
-        <v>69</v>
+        <v>383</v>
       </c>
       <c r="I143" t="s">
-        <v>188</v>
+        <v>384</v>
       </c>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C144" t="s">
-        <v>111</v>
+        <v>262</v>
       </c>
       <c r="E144" t="s">
-        <v>112</v>
+        <v>343</v>
       </c>
       <c r="F144">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G144" t="s">
-        <v>69</v>
+        <v>410</v>
       </c>
       <c r="H144" t="s">
-        <v>69</v>
+        <v>411</v>
       </c>
       <c r="I144" t="s">
-        <v>396</v>
+        <v>346</v>
       </c>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B145" t="s">
-        <v>409</v>
+        <v>413</v>
+      </c>
+      <c r="C145" t="s">
+        <v>335</v>
       </c>
       <c r="E145" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F145">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G145" t="s">
-        <v>69</v>
+        <v>382</v>
       </c>
       <c r="H145" t="s">
-        <v>69</v>
+        <v>357</v>
       </c>
       <c r="I145" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>358</v>
+        <v>406</v>
       </c>
       <c r="B146" t="s">
-        <v>359</v>
+        <v>407</v>
       </c>
       <c r="C146" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E146" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="F146">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G146" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="H146" t="s">
-        <v>413</v>
+        <v>383</v>
       </c>
       <c r="I146" t="s">
-        <v>414</v>
+        <v>384</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>415</v>
+        <v>354</v>
       </c>
       <c r="B147" t="s">
+        <v>355</v>
+      </c>
+      <c r="C147" t="s">
+        <v>362</v>
+      </c>
+      <c r="E147" t="s">
+        <v>343</v>
+      </c>
+      <c r="F147">
+        <v>5.0</v>
+      </c>
+      <c r="G147" t="s">
         <v>416</v>
       </c>
-      <c r="C147" t="s">
-        <v>262</v>
-      </c>
-      <c r="E147" t="s">
-        <v>351</v>
-      </c>
-      <c r="F147">
-        <v>6.0</v>
-      </c>
-      <c r="G147" t="s">
+      <c r="H147" t="s">
         <v>417</v>
       </c>
-      <c r="H147" t="s">
+      <c r="I147" t="s">
         <v>418</v>
-      </c>
-      <c r="I147" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" t="s">
+        <v>419</v>
+      </c>
+      <c r="B148" t="s">
         <v>420</v>
-      </c>
-      <c r="B148" t="s">
-        <v>421</v>
       </c>
       <c r="C148" t="s">
         <v>262</v>
       </c>
       <c r="E148" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F148">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="G148" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H148" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="I148" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" t="s">
+        <v>341</v>
+      </c>
+      <c r="B149" t="s">
+        <v>342</v>
+      </c>
+      <c r="C149" t="s">
+        <v>390</v>
+      </c>
+      <c r="E149" t="s">
+        <v>343</v>
+      </c>
+      <c r="F149">
+        <v>4.0</v>
+      </c>
+      <c r="G149" t="s">
+        <v>422</v>
+      </c>
+      <c r="H149" t="s">
+        <v>411</v>
+      </c>
+      <c r="I149" t="s">
         <v>423</v>
-      </c>
-      <c r="B149" t="s">
-        <v>424</v>
-      </c>
-      <c r="C149" t="s">
-        <v>397</v>
-      </c>
-      <c r="E149" t="s">
-        <v>388</v>
-      </c>
-      <c r="F149">
-        <v>3.0</v>
-      </c>
-      <c r="G149" t="s">
-        <v>389</v>
-      </c>
-      <c r="H149" t="s">
-        <v>390</v>
-      </c>
-      <c r="I149" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="150" spans="1:9">
       <c r="A150" t="s">
+        <v>424</v>
+      </c>
+      <c r="B150" t="s">
         <v>425</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C150" t="s">
+        <v>262</v>
+      </c>
+      <c r="E150" t="s">
+        <v>343</v>
+      </c>
+      <c r="F150">
+        <v>9.0</v>
+      </c>
+      <c r="G150" t="s">
         <v>426</v>
       </c>
-      <c r="C150" t="s">
-        <v>324</v>
-      </c>
-      <c r="E150" t="s">
+      <c r="H150" t="s">
+        <v>411</v>
+      </c>
+      <c r="I150" t="s">
         <v>427</v>
-      </c>
-      <c r="F150">
-        <v>8.0</v>
-      </c>
-      <c r="G150" t="s">
-        <v>389</v>
-      </c>
-      <c r="H150" t="s">
-        <v>361</v>
-      </c>
-      <c r="I150" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B151" t="s">
-        <v>424</v>
-      </c>
-      <c r="C151" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="E151" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="F151">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G151" t="s">
-        <v>389</v>
+        <v>69</v>
       </c>
       <c r="H151" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="I151" t="s">
-        <v>429</v>
+        <v>400</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="A152" t="s">
+        <v>354</v>
+      </c>
+      <c r="B152" t="s">
+        <v>355</v>
+      </c>
+      <c r="C152" t="s">
+        <v>335</v>
+      </c>
+      <c r="E152" t="s">
+        <v>343</v>
+      </c>
+      <c r="F152">
+        <v>4.0</v>
+      </c>
+      <c r="G152" t="s">
+        <v>382</v>
+      </c>
+      <c r="H152" t="s">
+        <v>417</v>
+      </c>
+      <c r="I152" t="s">
         <v>430</v>
-      </c>
-      <c r="B152" t="s">
-        <v>431</v>
-      </c>
-      <c r="C152" t="s">
-        <v>262</v>
-      </c>
-      <c r="E152" t="s">
-        <v>351</v>
-      </c>
-      <c r="F152">
-        <v>9.0</v>
-      </c>
-      <c r="G152" t="s">
-        <v>432</v>
-      </c>
-      <c r="H152" t="s">
-        <v>402</v>
-      </c>
-      <c r="I152" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>358</v>
+        <v>406</v>
       </c>
       <c r="B153" t="s">
-        <v>359</v>
+        <v>407</v>
       </c>
       <c r="C153" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="E153" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="F153">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G153" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="H153" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="I153" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>349</v>
+        <v>412</v>
       </c>
       <c r="B154" t="s">
-        <v>350</v>
+        <v>413</v>
       </c>
       <c r="C154" t="s">
-        <v>397</v>
+        <v>262</v>
       </c>
       <c r="E154" t="s">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="F154">
-        <v>4.0</v>
+        <v>13.0</v>
       </c>
       <c r="G154" t="s">
-        <v>435</v>
+        <v>382</v>
       </c>
       <c r="H154" t="s">
-        <v>402</v>
+        <v>433</v>
       </c>
       <c r="I154" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B155" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C155" t="s">
         <v>262</v>
       </c>
       <c r="E155" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F155">
         <v>7.0</v>
@@ -6157,160 +6133,163 @@
         <v>131</v>
       </c>
       <c r="H155" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="I155" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B156" t="s">
-        <v>441</v>
+        <v>439</v>
+      </c>
+      <c r="C156" t="s">
+        <v>362</v>
       </c>
       <c r="E156" t="s">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="F156">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G156" t="s">
-        <v>69</v>
+        <v>382</v>
       </c>
       <c r="H156" t="s">
-        <v>69</v>
+        <v>431</v>
       </c>
       <c r="I156" t="s">
-        <v>411</v>
+        <v>271</v>
       </c>
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>423</v>
+        <v>354</v>
       </c>
       <c r="B157" t="s">
-        <v>424</v>
+        <v>355</v>
       </c>
       <c r="C157" t="s">
-        <v>262</v>
+        <v>390</v>
       </c>
       <c r="E157" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="F157">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G157" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="H157" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="I157" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="B158" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="C158" t="s">
-        <v>369</v>
+        <v>284</v>
       </c>
       <c r="E158" t="s">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="F158">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G158" t="s">
-        <v>444</v>
+        <v>382</v>
       </c>
       <c r="H158" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="I158" t="s">
-        <v>414</v>
+        <v>248</v>
       </c>
     </row>
     <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B159" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>362</v>
       </c>
       <c r="E159" t="s">
-        <v>427</v>
+        <v>343</v>
       </c>
       <c r="F159">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="G159" t="s">
-        <v>389</v>
+        <v>440</v>
       </c>
       <c r="H159" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="I159" t="s">
-        <v>447</v>
+        <v>418</v>
       </c>
     </row>
     <row r="160" spans="1:9">
       <c r="A160" t="s">
-        <v>358</v>
+        <v>419</v>
       </c>
       <c r="B160" t="s">
-        <v>359</v>
+        <v>420</v>
       </c>
       <c r="C160" t="s">
-        <v>397</v>
+        <v>335</v>
       </c>
       <c r="E160" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F160">
         <v>4.0</v>
       </c>
       <c r="G160" t="s">
-        <v>389</v>
+        <v>344</v>
       </c>
       <c r="H160" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="I160" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="B161" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="C161" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E161" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="F161">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G161" t="s">
-        <v>389</v>
+        <v>442</v>
       </c>
       <c r="H161" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="I161" t="s">
         <v>443</v>
@@ -6318,652 +6297,652 @@
     </row>
     <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="B162" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="C162" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E162" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="F162">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G162" t="s">
-        <v>389</v>
+        <v>444</v>
       </c>
       <c r="H162" t="s">
-        <v>390</v>
+        <v>445</v>
       </c>
       <c r="I162" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="B163" t="s">
-        <v>400</v>
+        <v>425</v>
       </c>
       <c r="C163" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="E163" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F163">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="G163" t="s">
-        <v>352</v>
+        <v>410</v>
       </c>
       <c r="H163" t="s">
-        <v>445</v>
+        <v>411</v>
       </c>
       <c r="I163" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="B164" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="C164" t="s">
-        <v>284</v>
+        <v>111</v>
       </c>
       <c r="E164" t="s">
-        <v>427</v>
+        <v>130</v>
       </c>
       <c r="F164">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G164" t="s">
-        <v>389</v>
+        <v>69</v>
       </c>
       <c r="H164" t="s">
-        <v>442</v>
+        <v>69</v>
       </c>
       <c r="I164" t="s">
-        <v>248</v>
+        <v>132</v>
       </c>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="B165" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
       <c r="C165" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="E165" t="s">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="F165">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G165" t="s">
-        <v>451</v>
+        <v>382</v>
       </c>
       <c r="H165" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="I165" t="s">
-        <v>452</v>
+        <v>242</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="B166" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="C166" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="E166" t="s">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="F166">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="G166" t="s">
-        <v>422</v>
+        <v>382</v>
       </c>
       <c r="H166" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="I166" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" t="s">
-        <v>437</v>
+        <v>406</v>
       </c>
       <c r="B167" t="s">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="C167" t="s">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="E167" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="F167">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G167" t="s">
-        <v>454</v>
+        <v>382</v>
       </c>
       <c r="H167" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="I167" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B168" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C168" t="s">
-        <v>111</v>
+        <v>262</v>
       </c>
       <c r="E168" t="s">
-        <v>130</v>
+        <v>343</v>
       </c>
       <c r="F168">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G168" t="s">
-        <v>69</v>
+        <v>431</v>
       </c>
       <c r="H168" t="s">
-        <v>69</v>
+        <v>417</v>
       </c>
       <c r="I168" t="s">
-        <v>132</v>
+        <v>455</v>
       </c>
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>459</v>
+        <v>401</v>
       </c>
       <c r="B169" t="s">
-        <v>460</v>
+        <v>402</v>
       </c>
       <c r="C169" t="s">
-        <v>397</v>
+        <v>362</v>
       </c>
       <c r="E169" t="s">
-        <v>427</v>
+        <v>343</v>
       </c>
       <c r="F169">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G169" t="s">
-        <v>389</v>
+        <v>431</v>
       </c>
       <c r="H169" t="s">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="I169" t="s">
-        <v>242</v>
+        <v>455</v>
       </c>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>425</v>
+        <v>456</v>
       </c>
       <c r="B170" t="s">
-        <v>426</v>
+        <v>457</v>
       </c>
       <c r="C170" t="s">
-        <v>397</v>
+        <v>111</v>
       </c>
       <c r="E170" t="s">
-        <v>427</v>
+        <v>458</v>
       </c>
       <c r="F170">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G170" t="s">
-        <v>389</v>
+        <v>69</v>
       </c>
       <c r="H170" t="s">
-        <v>413</v>
+        <v>69</v>
       </c>
       <c r="I170" t="s">
-        <v>461</v>
+        <v>302</v>
       </c>
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="B171" t="s">
-        <v>424</v>
+        <v>460</v>
       </c>
       <c r="C171" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="E171" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="F171">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G171" t="s">
-        <v>389</v>
+        <v>204</v>
       </c>
       <c r="H171" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="I171" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
+        <v>379</v>
+      </c>
+      <c r="B172" t="s">
+        <v>380</v>
+      </c>
+      <c r="C172" t="s">
+        <v>390</v>
+      </c>
+      <c r="E172" t="s">
+        <v>381</v>
+      </c>
+      <c r="F172">
+        <v>1.0</v>
+      </c>
+      <c r="G172" t="s">
+        <v>382</v>
+      </c>
+      <c r="H172" t="s">
+        <v>382</v>
+      </c>
+      <c r="I172" t="s">
         <v>462</v>
-      </c>
-      <c r="B172" t="s">
-        <v>463</v>
-      </c>
-      <c r="C172" t="s">
-        <v>262</v>
-      </c>
-      <c r="E172" t="s">
-        <v>351</v>
-      </c>
-      <c r="F172">
-        <v>2.0</v>
-      </c>
-      <c r="G172" t="s">
-        <v>442</v>
-      </c>
-      <c r="H172" t="s">
-        <v>413</v>
-      </c>
-      <c r="I172" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>415</v>
+        <v>463</v>
       </c>
       <c r="B173" t="s">
-        <v>416</v>
+        <v>464</v>
       </c>
       <c r="C173" t="s">
-        <v>369</v>
+        <v>164</v>
       </c>
       <c r="E173" t="s">
-        <v>351</v>
+        <v>465</v>
       </c>
       <c r="F173">
         <v>2.0</v>
       </c>
       <c r="G173" t="s">
-        <v>442</v>
+        <v>69</v>
       </c>
       <c r="H173" t="s">
-        <v>413</v>
+        <v>69</v>
       </c>
       <c r="I173" t="s">
-        <v>464</v>
+        <v>257</v>
       </c>
     </row>
     <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B174" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C174" t="s">
         <v>262</v>
       </c>
       <c r="E174" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F174">
         <v>4.0</v>
       </c>
       <c r="G174" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H174" t="s">
         <v>194</v>
       </c>
       <c r="I174" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
     </row>
     <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B175" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>390</v>
       </c>
       <c r="E175" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="F175">
         <v>3.0</v>
       </c>
       <c r="G175" t="s">
-        <v>204</v>
+        <v>269</v>
       </c>
       <c r="H175" t="s">
-        <v>413</v>
+        <v>385</v>
       </c>
       <c r="I175" t="s">
-        <v>470</v>
+        <v>244</v>
       </c>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>471</v>
+        <v>435</v>
       </c>
       <c r="B176" t="s">
-        <v>472</v>
+        <v>436</v>
       </c>
       <c r="C176" t="s">
-        <v>111</v>
+        <v>335</v>
       </c>
       <c r="E176" t="s">
-        <v>473</v>
+        <v>343</v>
       </c>
       <c r="F176">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G176" t="s">
-        <v>69</v>
+        <v>431</v>
       </c>
       <c r="H176" t="s">
-        <v>69</v>
+        <v>417</v>
       </c>
       <c r="I176" t="s">
-        <v>305</v>
+        <v>455</v>
       </c>
     </row>
     <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>399</v>
+        <v>435</v>
       </c>
       <c r="B177" t="s">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="C177" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E177" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F177">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G177" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="H177" t="s">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="I177" t="s">
-        <v>414</v>
+        <v>455</v>
       </c>
     </row>
     <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>386</v>
+        <v>419</v>
       </c>
       <c r="B178" t="s">
-        <v>387</v>
+        <v>420</v>
       </c>
       <c r="C178" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E178" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="F178">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G178" t="s">
-        <v>389</v>
+        <v>440</v>
       </c>
       <c r="H178" t="s">
-        <v>389</v>
+        <v>441</v>
       </c>
       <c r="I178" t="s">
-        <v>474</v>
+        <v>418</v>
       </c>
     </row>
     <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B179" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C179" t="s">
-        <v>369</v>
+        <v>148</v>
       </c>
       <c r="E179" t="s">
-        <v>388</v>
+        <v>458</v>
       </c>
       <c r="F179">
         <v>4.0</v>
       </c>
       <c r="G179" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="H179" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="I179" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
     </row>
     <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="B180" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="C180" t="s">
-        <v>164</v>
+        <v>335</v>
       </c>
       <c r="E180" t="s">
-        <v>479</v>
+        <v>414</v>
       </c>
       <c r="F180">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G180" t="s">
-        <v>69</v>
+        <v>382</v>
       </c>
       <c r="H180" t="s">
-        <v>69</v>
+        <v>382</v>
       </c>
       <c r="I180" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="181" spans="1:9">
       <c r="A181" t="s">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="B181" t="s">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="C181" t="s">
-        <v>397</v>
+        <v>148</v>
       </c>
       <c r="E181" t="s">
-        <v>388</v>
+        <v>458</v>
       </c>
       <c r="F181">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G181" t="s">
-        <v>269</v>
+        <v>69</v>
       </c>
       <c r="H181" t="s">
-        <v>392</v>
+        <v>69</v>
       </c>
       <c r="I181" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
     </row>
     <row r="182" spans="1:9">
       <c r="A182" t="s">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="B182" t="s">
-        <v>466</v>
+        <v>439</v>
       </c>
       <c r="C182" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="E182" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="F182">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G182" t="s">
-        <v>480</v>
+        <v>382</v>
       </c>
       <c r="H182" t="s">
-        <v>481</v>
+        <v>382</v>
       </c>
       <c r="I182" t="s">
-        <v>436</v>
+        <v>302</v>
       </c>
     </row>
     <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>437</v>
+        <v>408</v>
       </c>
       <c r="B183" t="s">
-        <v>438</v>
+        <v>409</v>
       </c>
       <c r="C183" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E183" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F183">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G183" t="s">
-        <v>442</v>
+        <v>69</v>
       </c>
       <c r="H183" t="s">
-        <v>413</v>
+        <v>69</v>
       </c>
       <c r="I183" t="s">
-        <v>464</v>
+        <v>423</v>
       </c>
     </row>
     <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>437</v>
+        <v>466</v>
       </c>
       <c r="B184" t="s">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="C184" t="s">
-        <v>397</v>
+        <v>362</v>
       </c>
       <c r="E184" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F184">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G184" t="s">
-        <v>442</v>
+        <v>473</v>
       </c>
       <c r="H184" t="s">
-        <v>413</v>
+        <v>474</v>
       </c>
       <c r="I184" t="s">
-        <v>464</v>
+        <v>423</v>
       </c>
     </row>
     <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>420</v>
+        <v>354</v>
       </c>
       <c r="B185" t="s">
-        <v>421</v>
+        <v>355</v>
       </c>
       <c r="C185" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="E185" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F185">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G185" t="s">
-        <v>69</v>
+        <v>382</v>
       </c>
       <c r="H185" t="s">
-        <v>69</v>
+        <v>431</v>
       </c>
       <c r="I185" t="s">
-        <v>436</v>
+        <v>475</v>
       </c>
     </row>
     <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>482</v>
+        <v>412</v>
       </c>
       <c r="B186" t="s">
-        <v>483</v>
+        <v>413</v>
       </c>
       <c r="C186" t="s">
-        <v>148</v>
+        <v>362</v>
       </c>
       <c r="E186" t="s">
-        <v>473</v>
+        <v>414</v>
       </c>
       <c r="F186">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G186" t="s">
-        <v>288</v>
+        <v>382</v>
       </c>
       <c r="H186" t="s">
-        <v>289</v>
+        <v>45</v>
       </c>
       <c r="I186" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -6974,39 +6953,39 @@
         <v>460</v>
       </c>
       <c r="C187" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E187" t="s">
-        <v>427</v>
+        <v>343</v>
       </c>
       <c r="F187">
         <v>1.0</v>
       </c>
       <c r="G187" t="s">
-        <v>389</v>
+        <v>431</v>
       </c>
       <c r="H187" t="s">
-        <v>389</v>
+        <v>431</v>
       </c>
       <c r="I187" t="s">
-        <v>242</v>
+        <v>477</v>
       </c>
     </row>
     <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="B188" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="C188" t="s">
-        <v>148</v>
+        <v>362</v>
       </c>
       <c r="E188" t="s">
-        <v>473</v>
+        <v>343</v>
       </c>
       <c r="F188">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G188" t="s">
         <v>69</v>
@@ -7015,128 +6994,125 @@
         <v>69</v>
       </c>
       <c r="I188" t="s">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>448</v>
+        <v>481</v>
       </c>
       <c r="B189" t="s">
-        <v>449</v>
+        <v>482</v>
       </c>
       <c r="C189" t="s">
-        <v>397</v>
+        <v>140</v>
       </c>
       <c r="E189" t="s">
-        <v>388</v>
+        <v>226</v>
       </c>
       <c r="F189">
         <v>1.0</v>
       </c>
       <c r="G189" t="s">
-        <v>389</v>
+        <v>69</v>
       </c>
       <c r="H189" t="s">
-        <v>389</v>
+        <v>69</v>
       </c>
       <c r="I189" t="s">
-        <v>305</v>
+        <v>257</v>
       </c>
     </row>
     <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>358</v>
+        <v>469</v>
       </c>
       <c r="B190" t="s">
-        <v>359</v>
+        <v>470</v>
       </c>
       <c r="C190" t="s">
-        <v>284</v>
+        <v>335</v>
       </c>
       <c r="E190" t="s">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="F190">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G190" t="s">
-        <v>389</v>
+        <v>269</v>
       </c>
       <c r="H190" t="s">
-        <v>442</v>
+        <v>269</v>
       </c>
       <c r="I190" t="s">
-        <v>484</v>
+        <v>242</v>
       </c>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>425</v>
+        <v>483</v>
       </c>
       <c r="B191" t="s">
-        <v>426</v>
-      </c>
-      <c r="C191" t="s">
-        <v>369</v>
+        <v>484</v>
       </c>
       <c r="E191" t="s">
-        <v>427</v>
+        <v>485</v>
       </c>
       <c r="F191">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G191" t="s">
-        <v>389</v>
+        <v>69</v>
       </c>
       <c r="H191" t="s">
-        <v>220</v>
+        <v>69</v>
       </c>
       <c r="I191" t="s">
-        <v>485</v>
+        <v>400</v>
       </c>
     </row>
     <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="B192" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="C192" t="s">
-        <v>324</v>
+        <v>148</v>
       </c>
       <c r="E192" t="s">
-        <v>351</v>
+        <v>458</v>
       </c>
       <c r="F192">
         <v>1.0</v>
       </c>
       <c r="G192" t="s">
-        <v>442</v>
+        <v>488</v>
       </c>
       <c r="H192" t="s">
-        <v>442</v>
+        <v>488</v>
       </c>
       <c r="I192" t="s">
-        <v>486</v>
+        <v>242</v>
       </c>
     </row>
     <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B193" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C193" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="E193" t="s">
-        <v>351</v>
+        <v>491</v>
       </c>
       <c r="F193">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G193" t="s">
         <v>69</v>
@@ -7145,73 +7121,76 @@
         <v>69</v>
       </c>
       <c r="I193" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B194" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C194" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="E194" t="s">
-        <v>226</v>
+        <v>458</v>
       </c>
       <c r="F194">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G194" t="s">
-        <v>69</v>
+        <v>495</v>
       </c>
       <c r="H194" t="s">
-        <v>69</v>
+        <v>496</v>
       </c>
       <c r="I194" t="s">
-        <v>257</v>
+        <v>497</v>
       </c>
     </row>
     <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>475</v>
+        <v>408</v>
       </c>
       <c r="B195" t="s">
-        <v>476</v>
+        <v>409</v>
       </c>
       <c r="C195" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="E195" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="F195">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G195" t="s">
-        <v>269</v>
+        <v>426</v>
       </c>
       <c r="H195" t="s">
-        <v>269</v>
+        <v>441</v>
       </c>
       <c r="I195" t="s">
-        <v>242</v>
+        <v>498</v>
       </c>
     </row>
     <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="B196" t="s">
-        <v>493</v>
+        <v>500</v>
+      </c>
+      <c r="C196" t="s">
+        <v>148</v>
       </c>
       <c r="E196" t="s">
-        <v>494</v>
+        <v>458</v>
       </c>
       <c r="F196">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G196" t="s">
         <v>69</v>
@@ -7220,134 +7199,134 @@
         <v>69</v>
       </c>
       <c r="I196" t="s">
-        <v>411</v>
+        <v>501</v>
       </c>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>495</v>
+        <v>406</v>
       </c>
       <c r="B197" t="s">
-        <v>496</v>
+        <v>407</v>
       </c>
       <c r="C197" t="s">
-        <v>148</v>
+        <v>284</v>
       </c>
       <c r="E197" t="s">
-        <v>473</v>
+        <v>381</v>
       </c>
       <c r="F197">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G197" t="s">
-        <v>497</v>
+        <v>382</v>
       </c>
       <c r="H197" t="s">
-        <v>275</v>
+        <v>382</v>
       </c>
       <c r="I197" t="s">
-        <v>248</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:9">
       <c r="A198" t="s">
-        <v>420</v>
+        <v>502</v>
       </c>
       <c r="B198" t="s">
-        <v>421</v>
+        <v>503</v>
       </c>
       <c r="C198" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E198" t="s">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="F198">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G198" t="s">
-        <v>432</v>
+        <v>382</v>
       </c>
       <c r="H198" t="s">
-        <v>445</v>
+        <v>383</v>
       </c>
       <c r="I198" t="s">
-        <v>498</v>
+        <v>384</v>
       </c>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B199" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C199" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E199" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F199">
         <v>3.0</v>
       </c>
       <c r="G199" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="H199" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="I199" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="B200" t="s">
-        <v>501</v>
+        <v>479</v>
       </c>
       <c r="C200" t="s">
-        <v>397</v>
+        <v>262</v>
       </c>
       <c r="E200" t="s">
-        <v>502</v>
+        <v>343</v>
       </c>
       <c r="F200">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G200" t="s">
-        <v>69</v>
+        <v>426</v>
       </c>
       <c r="H200" t="s">
-        <v>69</v>
+        <v>504</v>
       </c>
       <c r="I200" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B201" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C201" t="s">
-        <v>164</v>
+        <v>262</v>
       </c>
       <c r="E201" t="s">
-        <v>473</v>
+        <v>343</v>
       </c>
       <c r="F201">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G201" t="s">
-        <v>506</v>
+        <v>344</v>
       </c>
       <c r="H201" t="s">
-        <v>507</v>
+        <v>441</v>
       </c>
       <c r="I201" t="s">
         <v>508</v>
@@ -7355,233 +7334,233 @@
     </row>
     <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>487</v>
+        <v>328</v>
       </c>
       <c r="B202" t="s">
-        <v>488</v>
+        <v>329</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>111</v>
       </c>
       <c r="E202" t="s">
-        <v>351</v>
+        <v>236</v>
       </c>
       <c r="F202">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G202" t="s">
-        <v>432</v>
+        <v>69</v>
       </c>
       <c r="H202" t="s">
-        <v>499</v>
+        <v>69</v>
       </c>
       <c r="I202" t="s">
-        <v>509</v>
+        <v>243</v>
       </c>
     </row>
     <row r="203" spans="1:9">
       <c r="A203" t="s">
-        <v>510</v>
+        <v>401</v>
       </c>
       <c r="B203" t="s">
-        <v>511</v>
+        <v>402</v>
       </c>
       <c r="C203" t="s">
-        <v>148</v>
+        <v>335</v>
       </c>
       <c r="E203" t="s">
-        <v>473</v>
+        <v>343</v>
       </c>
       <c r="F203">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G203" t="s">
-        <v>69</v>
+        <v>382</v>
       </c>
       <c r="H203" t="s">
-        <v>69</v>
+        <v>431</v>
       </c>
       <c r="I203" t="s">
-        <v>512</v>
+        <v>455</v>
       </c>
     </row>
     <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>423</v>
+        <v>509</v>
       </c>
       <c r="B204" t="s">
-        <v>424</v>
+        <v>510</v>
       </c>
       <c r="C204" t="s">
-        <v>284</v>
+        <v>148</v>
       </c>
       <c r="E204" t="s">
-        <v>388</v>
+        <v>458</v>
       </c>
       <c r="F204">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G204" t="s">
-        <v>389</v>
+        <v>488</v>
       </c>
       <c r="H204" t="s">
-        <v>389</v>
+        <v>511</v>
       </c>
       <c r="I204" t="s">
-        <v>474</v>
+        <v>512</v>
       </c>
     </row>
     <row r="205" spans="1:9">
       <c r="A205" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="B205" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="C205" t="s">
-        <v>397</v>
+        <v>262</v>
       </c>
       <c r="E205" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="F205">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G205" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="H205" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="I205" t="s">
-        <v>391</v>
+        <v>462</v>
       </c>
     </row>
     <row r="206" spans="1:9">
       <c r="A206" t="s">
-        <v>515</v>
+        <v>424</v>
       </c>
       <c r="B206" t="s">
-        <v>516</v>
+        <v>425</v>
       </c>
       <c r="C206" t="s">
-        <v>262</v>
+        <v>335</v>
       </c>
       <c r="E206" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F206">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G206" t="s">
-        <v>352</v>
+        <v>426</v>
       </c>
       <c r="H206" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="I206" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>337</v>
+        <v>502</v>
       </c>
       <c r="B207" t="s">
-        <v>338</v>
+        <v>503</v>
       </c>
       <c r="C207" t="s">
-        <v>111</v>
+        <v>362</v>
       </c>
       <c r="E207" t="s">
-        <v>236</v>
+        <v>414</v>
       </c>
       <c r="F207">
         <v>2.0</v>
       </c>
       <c r="G207" t="s">
-        <v>69</v>
+        <v>382</v>
       </c>
       <c r="H207" t="s">
-        <v>69</v>
+        <v>431</v>
       </c>
       <c r="I207" t="s">
-        <v>243</v>
+        <v>432</v>
       </c>
     </row>
     <row r="208" spans="1:9">
       <c r="A208" t="s">
-        <v>415</v>
+        <v>514</v>
       </c>
       <c r="B208" t="s">
-        <v>416</v>
+        <v>515</v>
       </c>
       <c r="C208" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="E208" t="s">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="F208">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G208" t="s">
-        <v>389</v>
+        <v>516</v>
       </c>
       <c r="H208" t="s">
-        <v>442</v>
+        <v>516</v>
       </c>
       <c r="I208" t="s">
-        <v>464</v>
+        <v>302</v>
       </c>
     </row>
     <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>430</v>
+        <v>341</v>
       </c>
       <c r="B209" t="s">
-        <v>431</v>
+        <v>342</v>
       </c>
       <c r="C209" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="E209" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F209">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G209" t="s">
-        <v>432</v>
+        <v>344</v>
       </c>
       <c r="H209" t="s">
-        <v>445</v>
+        <v>344</v>
       </c>
       <c r="I209" t="s">
-        <v>518</v>
+        <v>271</v>
       </c>
     </row>
     <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="B210" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="C210" t="s">
         <v>148</v>
       </c>
       <c r="E210" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="F210">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G210" t="s">
-        <v>497</v>
+        <v>69</v>
       </c>
       <c r="H210" t="s">
-        <v>521</v>
+        <v>69</v>
       </c>
       <c r="I210" t="s">
         <v>512</v>
@@ -7589,227 +7568,227 @@
     </row>
     <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>513</v>
+        <v>466</v>
       </c>
       <c r="B211" t="s">
-        <v>514</v>
+        <v>467</v>
       </c>
       <c r="C211" t="s">
-        <v>262</v>
+        <v>390</v>
       </c>
       <c r="E211" t="s">
-        <v>427</v>
+        <v>343</v>
       </c>
       <c r="F211">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G211" t="s">
-        <v>389</v>
+        <v>426</v>
       </c>
       <c r="H211" t="s">
-        <v>389</v>
+        <v>504</v>
       </c>
       <c r="I211" t="s">
-        <v>474</v>
+        <v>517</v>
       </c>
     </row>
     <row r="212" spans="1:9">
       <c r="A212" t="s">
-        <v>349</v>
+        <v>453</v>
       </c>
       <c r="B212" t="s">
-        <v>350</v>
+        <v>454</v>
       </c>
       <c r="C212" t="s">
-        <v>284</v>
+        <v>362</v>
       </c>
       <c r="E212" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F212">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G212" t="s">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="H212" t="s">
-        <v>352</v>
+        <v>431</v>
       </c>
       <c r="I212" t="s">
-        <v>271</v>
+        <v>455</v>
       </c>
     </row>
     <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>513</v>
+        <v>459</v>
       </c>
       <c r="B213" t="s">
-        <v>514</v>
+        <v>460</v>
       </c>
       <c r="C213" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E213" t="s">
-        <v>427</v>
+        <v>343</v>
       </c>
       <c r="F213">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G213" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="H213" t="s">
-        <v>390</v>
+        <v>431</v>
       </c>
       <c r="I213" t="s">
-        <v>391</v>
+        <v>475</v>
       </c>
     </row>
     <row r="214" spans="1:9">
       <c r="A214" t="s">
-        <v>465</v>
+        <v>401</v>
       </c>
       <c r="B214" t="s">
-        <v>466</v>
+        <v>402</v>
       </c>
       <c r="C214" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E214" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F214">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G214" t="s">
-        <v>432</v>
+        <v>69</v>
       </c>
       <c r="H214" t="s">
-        <v>499</v>
+        <v>69</v>
       </c>
       <c r="I214" t="s">
-        <v>522</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:9">
       <c r="A215" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="B215" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="C215" t="s">
-        <v>262</v>
+        <v>125</v>
       </c>
       <c r="E215" t="s">
-        <v>427</v>
+        <v>236</v>
       </c>
       <c r="F215">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G215" t="s">
-        <v>525</v>
+        <v>69</v>
       </c>
       <c r="H215" t="s">
-        <v>525</v>
+        <v>69</v>
       </c>
       <c r="I215" t="s">
-        <v>305</v>
+        <v>369</v>
       </c>
     </row>
     <row r="216" spans="1:9">
       <c r="A216" t="s">
+        <v>520</v>
+      </c>
+      <c r="B216" t="s">
+        <v>521</v>
+      </c>
+      <c r="C216" t="s">
+        <v>262</v>
+      </c>
+      <c r="E216" t="s">
+        <v>343</v>
+      </c>
+      <c r="F216">
+        <v>1.0</v>
+      </c>
+      <c r="G216" t="s">
         <v>504</v>
       </c>
-      <c r="B216" t="s">
-        <v>505</v>
-      </c>
-      <c r="C216" t="s">
-        <v>148</v>
-      </c>
-      <c r="E216" t="s">
-        <v>473</v>
-      </c>
-      <c r="F216">
-        <v>3.0</v>
-      </c>
-      <c r="G216" t="s">
-        <v>69</v>
-      </c>
       <c r="H216" t="s">
-        <v>69</v>
+        <v>504</v>
       </c>
       <c r="I216" t="s">
-        <v>450</v>
+        <v>522</v>
       </c>
     </row>
     <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>462</v>
+        <v>509</v>
       </c>
       <c r="B217" t="s">
-        <v>463</v>
+        <v>510</v>
       </c>
       <c r="C217" t="s">
-        <v>369</v>
+        <v>125</v>
       </c>
       <c r="E217" t="s">
-        <v>351</v>
+        <v>458</v>
       </c>
       <c r="F217">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G217" t="s">
-        <v>389</v>
+        <v>69</v>
       </c>
       <c r="H217" t="s">
-        <v>442</v>
+        <v>69</v>
       </c>
       <c r="I217" t="s">
-        <v>464</v>
+        <v>501</v>
       </c>
     </row>
     <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B218" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C218" t="s">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="E218" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F218">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G218" t="s">
-        <v>389</v>
+        <v>523</v>
       </c>
       <c r="H218" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I218" t="s">
-        <v>484</v>
+        <v>517</v>
       </c>
     </row>
     <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>415</v>
+        <v>524</v>
       </c>
       <c r="B219" t="s">
-        <v>416</v>
+        <v>525</v>
       </c>
       <c r="C219" t="s">
-        <v>397</v>
+        <v>125</v>
       </c>
       <c r="E219" t="s">
-        <v>351</v>
+        <v>236</v>
       </c>
       <c r="F219">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G219" t="s">
         <v>69</v>
@@ -7818,128 +7797,128 @@
         <v>69</v>
       </c>
       <c r="I219" t="s">
-        <v>489</v>
+        <v>369</v>
       </c>
     </row>
     <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>526</v>
+        <v>453</v>
       </c>
       <c r="B220" t="s">
-        <v>527</v>
+        <v>454</v>
       </c>
       <c r="C220" t="s">
-        <v>125</v>
+        <v>335</v>
       </c>
       <c r="E220" t="s">
-        <v>236</v>
+        <v>343</v>
       </c>
       <c r="F220">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G220" t="s">
-        <v>69</v>
+        <v>431</v>
       </c>
       <c r="H220" t="s">
-        <v>69</v>
+        <v>431</v>
       </c>
       <c r="I220" t="s">
-        <v>376</v>
+        <v>480</v>
       </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="B221" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="C221" t="s">
-        <v>125</v>
+        <v>362</v>
       </c>
       <c r="E221" t="s">
-        <v>473</v>
+        <v>343</v>
       </c>
       <c r="F221">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G221" t="s">
-        <v>528</v>
+        <v>410</v>
       </c>
       <c r="H221" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="I221" t="s">
-        <v>242</v>
+        <v>508</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B222" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>148</v>
       </c>
       <c r="E222" t="s">
-        <v>351</v>
+        <v>458</v>
       </c>
       <c r="F222">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G222" t="s">
-        <v>499</v>
+        <v>69</v>
       </c>
       <c r="H222" t="s">
-        <v>499</v>
+        <v>69</v>
       </c>
       <c r="I222" t="s">
-        <v>531</v>
+        <v>248</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="A223" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="B223" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="C223" t="s">
-        <v>324</v>
+        <v>140</v>
       </c>
       <c r="E223" t="s">
-        <v>351</v>
+        <v>458</v>
       </c>
       <c r="F223">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G223" t="s">
-        <v>532</v>
+        <v>69</v>
       </c>
       <c r="H223" t="s">
-        <v>445</v>
+        <v>69</v>
       </c>
       <c r="I223" t="s">
-        <v>522</v>
+        <v>501</v>
       </c>
     </row>
     <row r="224" spans="1:9">
       <c r="A224" t="s">
-        <v>519</v>
+        <v>408</v>
       </c>
       <c r="B224" t="s">
-        <v>520</v>
+        <v>409</v>
       </c>
       <c r="C224" t="s">
-        <v>125</v>
+        <v>284</v>
       </c>
       <c r="E224" t="s">
-        <v>473</v>
+        <v>343</v>
       </c>
       <c r="F224">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G224" t="s">
         <v>69</v>
@@ -7948,24 +7927,24 @@
         <v>69</v>
       </c>
       <c r="I224" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
     </row>
     <row r="225" spans="1:9">
       <c r="A225" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B225" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C225" t="s">
-        <v>125</v>
+        <v>362</v>
       </c>
       <c r="E225" t="s">
-        <v>236</v>
+        <v>343</v>
       </c>
       <c r="F225">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G225" t="s">
         <v>69</v>
@@ -7974,76 +7953,76 @@
         <v>69</v>
       </c>
       <c r="I225" t="s">
-        <v>376</v>
+        <v>477</v>
       </c>
     </row>
     <row r="226" spans="1:9">
       <c r="A226" t="s">
-        <v>462</v>
+        <v>531</v>
       </c>
       <c r="B226" t="s">
-        <v>463</v>
+        <v>532</v>
       </c>
       <c r="C226" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="E226" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F226">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G226" t="s">
-        <v>442</v>
+        <v>69</v>
       </c>
       <c r="H226" t="s">
-        <v>442</v>
+        <v>69</v>
       </c>
       <c r="I226" t="s">
-        <v>489</v>
+        <v>533</v>
       </c>
     </row>
     <row r="227" spans="1:9">
       <c r="A227" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="B227" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="C227" t="s">
-        <v>369</v>
+        <v>262</v>
       </c>
       <c r="E227" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F227">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G227" t="s">
-        <v>422</v>
+        <v>69</v>
       </c>
       <c r="H227" t="s">
-        <v>535</v>
+        <v>69</v>
       </c>
       <c r="I227" t="s">
-        <v>517</v>
+        <v>477</v>
       </c>
     </row>
     <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B228" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C228" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="E228" t="s">
-        <v>473</v>
+        <v>236</v>
       </c>
       <c r="F228">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G228" t="s">
         <v>69</v>
@@ -8052,24 +8031,24 @@
         <v>69</v>
       </c>
       <c r="I228" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>510</v>
+        <v>527</v>
       </c>
       <c r="B229" t="s">
-        <v>511</v>
+        <v>528</v>
       </c>
       <c r="C229" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="E229" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="F229">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G229" t="s">
         <v>69</v>
@@ -8078,30 +8057,30 @@
         <v>69</v>
       </c>
       <c r="I229" t="s">
-        <v>512</v>
+        <v>242</v>
       </c>
     </row>
     <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>420</v>
+        <v>509</v>
       </c>
       <c r="B230" t="s">
-        <v>421</v>
+        <v>510</v>
       </c>
       <c r="C230" t="s">
-        <v>284</v>
+        <v>164</v>
       </c>
       <c r="E230" t="s">
-        <v>351</v>
+        <v>458</v>
       </c>
       <c r="F230">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G230" t="s">
-        <v>69</v>
+        <v>495</v>
       </c>
       <c r="H230" t="s">
-        <v>69</v>
+        <v>536</v>
       </c>
       <c r="I230" t="s">
         <v>512</v>
@@ -8109,45 +8088,45 @@
     </row>
     <row r="231" spans="1:9">
       <c r="A231" t="s">
-        <v>538</v>
+        <v>459</v>
       </c>
       <c r="B231" t="s">
-        <v>539</v>
+        <v>460</v>
       </c>
       <c r="C231" t="s">
-        <v>369</v>
+        <v>284</v>
       </c>
       <c r="E231" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F231">
         <v>1.0</v>
       </c>
       <c r="G231" t="s">
-        <v>69</v>
+        <v>431</v>
       </c>
       <c r="H231" t="s">
-        <v>69</v>
+        <v>431</v>
       </c>
       <c r="I231" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="B232" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="C232" t="s">
-        <v>262</v>
+        <v>140</v>
       </c>
       <c r="E232" t="s">
-        <v>351</v>
+        <v>236</v>
       </c>
       <c r="F232">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G232" t="s">
         <v>69</v>
@@ -8156,24 +8135,24 @@
         <v>69</v>
       </c>
       <c r="I232" t="s">
-        <v>542</v>
+        <v>238</v>
       </c>
     </row>
     <row r="233" spans="1:9">
       <c r="A233" t="s">
+        <v>537</v>
+      </c>
+      <c r="B233" t="s">
         <v>538</v>
-      </c>
-      <c r="B233" t="s">
-        <v>539</v>
       </c>
       <c r="C233" t="s">
         <v>262</v>
       </c>
       <c r="E233" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F233">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G233" t="s">
         <v>69</v>
@@ -8182,24 +8161,24 @@
         <v>69</v>
       </c>
       <c r="I233" t="s">
-        <v>486</v>
+        <v>539</v>
       </c>
     </row>
     <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>543</v>
+        <v>499</v>
       </c>
       <c r="B234" t="s">
-        <v>544</v>
+        <v>500</v>
       </c>
       <c r="C234" t="s">
         <v>164</v>
       </c>
       <c r="E234" t="s">
-        <v>236</v>
+        <v>458</v>
       </c>
       <c r="F234">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G234" t="s">
         <v>69</v>
@@ -8208,24 +8187,24 @@
         <v>69</v>
       </c>
       <c r="I234" t="s">
-        <v>238</v>
+        <v>512</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>536</v>
+        <v>499</v>
       </c>
       <c r="B235" t="s">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="C235" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="E235" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="F235">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G235" t="s">
         <v>69</v>
@@ -8234,128 +8213,128 @@
         <v>69</v>
       </c>
       <c r="I235" t="s">
-        <v>242</v>
+        <v>540</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>545</v>
+        <v>520</v>
       </c>
       <c r="B236" t="s">
-        <v>546</v>
+        <v>521</v>
       </c>
       <c r="C236" t="s">
-        <v>262</v>
+        <v>390</v>
       </c>
       <c r="E236" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F236">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G236" t="s">
-        <v>69</v>
+        <v>504</v>
       </c>
       <c r="H236" t="s">
-        <v>69</v>
+        <v>504</v>
       </c>
       <c r="I236" t="s">
-        <v>547</v>
+        <v>522</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="B237" t="s">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="C237" t="s">
         <v>164</v>
       </c>
       <c r="E237" t="s">
-        <v>473</v>
+        <v>236</v>
       </c>
       <c r="F237">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G237" t="s">
-        <v>506</v>
+        <v>69</v>
       </c>
       <c r="H237" t="s">
-        <v>548</v>
+        <v>69</v>
       </c>
       <c r="I237" t="s">
-        <v>450</v>
+        <v>243</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>468</v>
+        <v>543</v>
       </c>
       <c r="B238" t="s">
-        <v>469</v>
+        <v>544</v>
       </c>
       <c r="C238" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="E238" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F238">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G238" t="s">
-        <v>442</v>
+        <v>69</v>
       </c>
       <c r="H238" t="s">
-        <v>442</v>
+        <v>69</v>
       </c>
       <c r="I238" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="B239" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="C239" t="s">
-        <v>140</v>
+        <v>262</v>
       </c>
       <c r="E239" t="s">
-        <v>236</v>
+        <v>343</v>
       </c>
       <c r="F239">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G239" t="s">
-        <v>69</v>
+        <v>523</v>
       </c>
       <c r="H239" t="s">
-        <v>69</v>
+        <v>441</v>
       </c>
       <c r="I239" t="s">
-        <v>238</v>
+        <v>461</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>510</v>
+        <v>424</v>
       </c>
       <c r="B240" t="s">
-        <v>511</v>
+        <v>425</v>
       </c>
       <c r="C240" t="s">
-        <v>164</v>
+        <v>284</v>
       </c>
       <c r="E240" t="s">
-        <v>473</v>
+        <v>343</v>
       </c>
       <c r="F240">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G240" t="s">
         <v>69</v>
@@ -8364,24 +8343,24 @@
         <v>69</v>
       </c>
       <c r="I240" t="s">
-        <v>450</v>
+        <v>477</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>510</v>
+        <v>448</v>
       </c>
       <c r="B241" t="s">
-        <v>511</v>
+        <v>449</v>
       </c>
       <c r="C241" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="E241" t="s">
-        <v>473</v>
+        <v>130</v>
       </c>
       <c r="F241">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G241" t="s">
         <v>69</v>
@@ -8390,50 +8369,50 @@
         <v>69</v>
       </c>
       <c r="I241" t="s">
-        <v>549</v>
+        <v>206</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="B242" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="C242" t="s">
-        <v>397</v>
+        <v>140</v>
       </c>
       <c r="E242" t="s">
-        <v>351</v>
+        <v>236</v>
       </c>
       <c r="F242">
         <v>1.0</v>
       </c>
       <c r="G242" t="s">
-        <v>499</v>
+        <v>69</v>
       </c>
       <c r="H242" t="s">
-        <v>499</v>
+        <v>69</v>
       </c>
       <c r="I242" t="s">
-        <v>531</v>
+        <v>238</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>550</v>
+        <v>509</v>
       </c>
       <c r="B243" t="s">
-        <v>551</v>
+        <v>510</v>
       </c>
       <c r="C243" t="s">
-        <v>262</v>
+        <v>140</v>
       </c>
       <c r="E243" t="s">
-        <v>351</v>
+        <v>458</v>
       </c>
       <c r="F243">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G243" t="s">
         <v>69</v>
@@ -8442,102 +8421,102 @@
         <v>69</v>
       </c>
       <c r="I243" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>552</v>
+        <v>524</v>
       </c>
       <c r="B244" t="s">
-        <v>553</v>
+        <v>525</v>
       </c>
       <c r="C244" t="s">
-        <v>262</v>
+        <v>164</v>
       </c>
       <c r="E244" t="s">
-        <v>351</v>
+        <v>236</v>
       </c>
       <c r="F244">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G244" t="s">
-        <v>532</v>
+        <v>69</v>
       </c>
       <c r="H244" t="s">
-        <v>445</v>
+        <v>69</v>
       </c>
       <c r="I244" t="s">
-        <v>470</v>
+        <v>249</v>
       </c>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>430</v>
+        <v>466</v>
       </c>
       <c r="B245" t="s">
-        <v>431</v>
+        <v>467</v>
       </c>
       <c r="C245" t="s">
         <v>284</v>
       </c>
       <c r="E245" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F245">
         <v>1.0</v>
       </c>
       <c r="G245" t="s">
-        <v>69</v>
+        <v>504</v>
       </c>
       <c r="H245" t="s">
-        <v>69</v>
+        <v>504</v>
       </c>
       <c r="I245" t="s">
-        <v>486</v>
+        <v>271</v>
       </c>
     </row>
     <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>554</v>
+        <v>506</v>
       </c>
       <c r="B246" t="s">
-        <v>555</v>
+        <v>507</v>
       </c>
       <c r="C246" t="s">
-        <v>164</v>
+        <v>335</v>
       </c>
       <c r="E246" t="s">
-        <v>236</v>
+        <v>343</v>
       </c>
       <c r="F246">
         <v>2.0</v>
       </c>
       <c r="G246" t="s">
-        <v>69</v>
+        <v>344</v>
       </c>
       <c r="H246" t="s">
-        <v>69</v>
+        <v>504</v>
       </c>
       <c r="I246" t="s">
-        <v>243</v>
+        <v>77</v>
       </c>
     </row>
     <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>457</v>
+        <v>531</v>
       </c>
       <c r="B247" t="s">
-        <v>458</v>
+        <v>532</v>
       </c>
       <c r="C247" t="s">
-        <v>148</v>
+        <v>362</v>
       </c>
       <c r="E247" t="s">
-        <v>130</v>
+        <v>343</v>
       </c>
       <c r="F247">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G247" t="s">
         <v>69</v>
@@ -8546,47 +8525,47 @@
         <v>69</v>
       </c>
       <c r="I247" t="s">
-        <v>206</v>
+        <v>522</v>
       </c>
     </row>
     <row r="248" spans="1:9">
       <c r="A248" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="B248" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="C248" t="s">
-        <v>140</v>
+        <v>262</v>
       </c>
       <c r="E248" t="s">
-        <v>236</v>
+        <v>343</v>
       </c>
       <c r="F248">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G248" t="s">
-        <v>69</v>
+        <v>426</v>
       </c>
       <c r="H248" t="s">
-        <v>69</v>
+        <v>504</v>
       </c>
       <c r="I248" t="s">
-        <v>238</v>
+        <v>533</v>
       </c>
     </row>
     <row r="249" spans="1:9">
       <c r="A249" t="s">
+        <v>518</v>
+      </c>
+      <c r="B249" t="s">
         <v>519</v>
       </c>
-      <c r="B249" t="s">
-        <v>520</v>
-      </c>
       <c r="C249" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E249" t="s">
-        <v>473</v>
+        <v>236</v>
       </c>
       <c r="F249">
         <v>4.0</v>
@@ -8598,24 +8577,24 @@
         <v>69</v>
       </c>
       <c r="I249" t="s">
-        <v>512</v>
+        <v>249</v>
       </c>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B250" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C250" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="E250" t="s">
         <v>236</v>
       </c>
       <c r="F250">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G250" t="s">
         <v>69</v>
@@ -8624,73 +8603,73 @@
         <v>69</v>
       </c>
       <c r="I250" t="s">
-        <v>249</v>
+        <v>369</v>
       </c>
     </row>
     <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>465</v>
+        <v>541</v>
       </c>
       <c r="B251" t="s">
-        <v>466</v>
+        <v>542</v>
       </c>
       <c r="C251" t="s">
-        <v>284</v>
+        <v>140</v>
       </c>
       <c r="E251" t="s">
-        <v>351</v>
+        <v>236</v>
       </c>
       <c r="F251">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G251" t="s">
-        <v>499</v>
+        <v>69</v>
       </c>
       <c r="H251" t="s">
-        <v>499</v>
+        <v>69</v>
       </c>
       <c r="I251" t="s">
-        <v>271</v>
+        <v>369</v>
       </c>
     </row>
     <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="B252" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="C252" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="E252" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F252">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G252" t="s">
-        <v>352</v>
+        <v>69</v>
       </c>
       <c r="H252" t="s">
-        <v>499</v>
+        <v>69</v>
       </c>
       <c r="I252" t="s">
-        <v>77</v>
+        <v>477</v>
       </c>
     </row>
     <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="B253" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="C253" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="E253" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F253">
         <v>1.0</v>
@@ -8702,50 +8681,50 @@
         <v>69</v>
       </c>
       <c r="I253" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
     <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="B254" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="C254" t="s">
-        <v>262</v>
+        <v>140</v>
       </c>
       <c r="E254" t="s">
-        <v>351</v>
+        <v>130</v>
       </c>
       <c r="F254">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G254" t="s">
-        <v>432</v>
+        <v>69</v>
       </c>
       <c r="H254" t="s">
-        <v>499</v>
+        <v>69</v>
       </c>
       <c r="I254" t="s">
-        <v>542</v>
+        <v>290</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="B255" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="C255" t="s">
-        <v>148</v>
+        <v>335</v>
       </c>
       <c r="E255" t="s">
-        <v>236</v>
+        <v>343</v>
       </c>
       <c r="F255">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G255" t="s">
         <v>69</v>
@@ -8754,24 +8733,24 @@
         <v>69</v>
       </c>
       <c r="I255" t="s">
-        <v>249</v>
+        <v>498</v>
       </c>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>554</v>
+        <v>419</v>
       </c>
       <c r="B256" t="s">
-        <v>555</v>
+        <v>420</v>
       </c>
       <c r="C256" t="s">
-        <v>125</v>
+        <v>284</v>
       </c>
       <c r="E256" t="s">
-        <v>236</v>
+        <v>343</v>
       </c>
       <c r="F256">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G256" t="s">
         <v>69</v>
@@ -8780,24 +8759,24 @@
         <v>69</v>
       </c>
       <c r="I256" t="s">
-        <v>376</v>
+        <v>475</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>554</v>
+        <v>520</v>
       </c>
       <c r="B257" t="s">
-        <v>555</v>
+        <v>521</v>
       </c>
       <c r="C257" t="s">
-        <v>140</v>
+        <v>335</v>
       </c>
       <c r="E257" t="s">
-        <v>236</v>
+        <v>343</v>
       </c>
       <c r="F257">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G257" t="s">
         <v>69</v>
@@ -8806,47 +8785,47 @@
         <v>69</v>
       </c>
       <c r="I257" t="s">
-        <v>376</v>
+        <v>522</v>
       </c>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B258" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C258" t="s">
-        <v>397</v>
+        <v>362</v>
       </c>
       <c r="E258" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F258">
         <v>1.0</v>
       </c>
       <c r="G258" t="s">
-        <v>69</v>
+        <v>551</v>
       </c>
       <c r="H258" t="s">
-        <v>69</v>
+        <v>551</v>
       </c>
       <c r="I258" t="s">
-        <v>486</v>
+        <v>522</v>
       </c>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B259" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C259" t="s">
-        <v>397</v>
+        <v>335</v>
       </c>
       <c r="E259" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F259">
         <v>1.0</v>
@@ -8858,7 +8837,7 @@
         <v>69</v>
       </c>
       <c r="I259" t="s">
-        <v>531</v>
+        <v>480</v>
       </c>
     </row>
     <row r="260" spans="1:9">
@@ -8869,13 +8848,13 @@
         <v>546</v>
       </c>
       <c r="C260" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="E260" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F260">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G260" t="s">
         <v>69</v>
@@ -8884,24 +8863,24 @@
         <v>69</v>
       </c>
       <c r="I260" t="s">
-        <v>498</v>
+        <v>477</v>
       </c>
     </row>
     <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B261" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C261" t="s">
-        <v>140</v>
+        <v>262</v>
       </c>
       <c r="E261" t="s">
-        <v>130</v>
+        <v>343</v>
       </c>
       <c r="F261">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G261" t="s">
         <v>69</v>
@@ -8910,24 +8889,24 @@
         <v>69</v>
       </c>
       <c r="I261" t="s">
-        <v>290</v>
+        <v>455</v>
       </c>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>399</v>
+        <v>552</v>
       </c>
       <c r="B262" t="s">
-        <v>400</v>
+        <v>553</v>
       </c>
       <c r="C262" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="E262" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F262">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G262" t="s">
         <v>69</v>
@@ -8936,24 +8915,24 @@
         <v>69</v>
       </c>
       <c r="I262" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>529</v>
+        <v>493</v>
       </c>
       <c r="B263" t="s">
-        <v>530</v>
+        <v>494</v>
       </c>
       <c r="C263" t="s">
-        <v>324</v>
+        <v>140</v>
       </c>
       <c r="E263" t="s">
-        <v>351</v>
+        <v>458</v>
       </c>
       <c r="F263">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G263" t="s">
         <v>69</v>
@@ -8962,24 +8941,24 @@
         <v>69</v>
       </c>
       <c r="I263" t="s">
-        <v>531</v>
+        <v>512</v>
       </c>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B264" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C264" t="s">
-        <v>324</v>
+        <v>164</v>
       </c>
       <c r="E264" t="s">
-        <v>351</v>
+        <v>558</v>
       </c>
       <c r="F264">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G264" t="s">
         <v>69</v>
@@ -8988,24 +8967,24 @@
         <v>69</v>
       </c>
       <c r="I264" t="s">
-        <v>489</v>
+        <v>257</v>
       </c>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="B265" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="C265" t="s">
-        <v>397</v>
+        <v>140</v>
       </c>
       <c r="E265" t="s">
-        <v>351</v>
+        <v>126</v>
       </c>
       <c r="F265">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G265" t="s">
         <v>69</v>
@@ -9014,24 +8993,24 @@
         <v>69</v>
       </c>
       <c r="I265" t="s">
-        <v>486</v>
+        <v>143</v>
       </c>
     </row>
     <row r="266" spans="1:9">
       <c r="A266" t="s">
+        <v>559</v>
+      </c>
+      <c r="B266" t="s">
         <v>560</v>
       </c>
-      <c r="B266" t="s">
-        <v>561</v>
-      </c>
       <c r="C266" t="s">
-        <v>262</v>
+        <v>125</v>
       </c>
       <c r="E266" t="s">
-        <v>351</v>
+        <v>126</v>
       </c>
       <c r="F266">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G266" t="s">
         <v>69</v>
@@ -9040,24 +9019,24 @@
         <v>69</v>
       </c>
       <c r="I266" t="s">
-        <v>489</v>
+        <v>160</v>
       </c>
     </row>
     <row r="267" spans="1:9">
       <c r="A267" t="s">
-        <v>562</v>
+        <v>448</v>
       </c>
       <c r="B267" t="s">
-        <v>563</v>
+        <v>449</v>
       </c>
       <c r="C267" t="s">
-        <v>262</v>
+        <v>164</v>
       </c>
       <c r="E267" t="s">
-        <v>351</v>
+        <v>130</v>
       </c>
       <c r="F267">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G267" t="s">
         <v>69</v>
@@ -9066,21 +9045,21 @@
         <v>69</v>
       </c>
       <c r="I267" t="s">
-        <v>464</v>
+        <v>179</v>
       </c>
     </row>
     <row r="268" spans="1:9">
       <c r="A268" t="s">
-        <v>504</v>
+        <v>549</v>
       </c>
       <c r="B268" t="s">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="C268" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="E268" t="s">
-        <v>473</v>
+        <v>130</v>
       </c>
       <c r="F268">
         <v>3.0</v>
@@ -9092,24 +9071,24 @@
         <v>69</v>
       </c>
       <c r="I268" t="s">
-        <v>450</v>
+        <v>179</v>
       </c>
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>482</v>
+        <v>518</v>
       </c>
       <c r="B269" t="s">
-        <v>483</v>
+        <v>519</v>
       </c>
       <c r="C269" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="E269" t="s">
-        <v>473</v>
+        <v>236</v>
       </c>
       <c r="F269">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G269" t="s">
         <v>69</v>
@@ -9118,21 +9097,21 @@
         <v>69</v>
       </c>
       <c r="I269" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="270" spans="1:9">
       <c r="A270" t="s">
-        <v>564</v>
+        <v>541</v>
       </c>
       <c r="B270" t="s">
-        <v>565</v>
+        <v>542</v>
       </c>
       <c r="C270" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E270" t="s">
-        <v>566</v>
+        <v>236</v>
       </c>
       <c r="F270">
         <v>2.0</v>
@@ -9144,24 +9123,24 @@
         <v>69</v>
       </c>
       <c r="I270" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
     </row>
     <row r="271" spans="1:9">
       <c r="A271" t="s">
-        <v>567</v>
+        <v>534</v>
       </c>
       <c r="B271" t="s">
-        <v>568</v>
+        <v>535</v>
       </c>
       <c r="C271" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E271" t="s">
-        <v>126</v>
+        <v>236</v>
       </c>
       <c r="F271">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G271" t="s">
         <v>69</v>
@@ -9170,24 +9149,24 @@
         <v>69</v>
       </c>
       <c r="I271" t="s">
-        <v>143</v>
+        <v>369</v>
       </c>
     </row>
     <row r="272" spans="1:9">
       <c r="A272" t="s">
-        <v>567</v>
+        <v>328</v>
       </c>
       <c r="B272" t="s">
-        <v>568</v>
+        <v>329</v>
       </c>
       <c r="C272" t="s">
         <v>125</v>
       </c>
       <c r="E272" t="s">
-        <v>126</v>
+        <v>236</v>
       </c>
       <c r="F272">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G272" t="s">
         <v>69</v>
@@ -9196,24 +9175,24 @@
         <v>69</v>
       </c>
       <c r="I272" t="s">
-        <v>160</v>
+        <v>247</v>
       </c>
     </row>
     <row r="273" spans="1:9">
       <c r="A273" t="s">
-        <v>457</v>
+        <v>524</v>
       </c>
       <c r="B273" t="s">
-        <v>458</v>
+        <v>525</v>
       </c>
       <c r="C273" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E273" t="s">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="F273">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G273" t="s">
         <v>69</v>
@@ -9222,24 +9201,24 @@
         <v>69</v>
       </c>
       <c r="I273" t="s">
-        <v>179</v>
+        <v>249</v>
       </c>
     </row>
     <row r="274" spans="1:9">
       <c r="A274" t="s">
-        <v>558</v>
+        <v>493</v>
       </c>
       <c r="B274" t="s">
-        <v>559</v>
+        <v>494</v>
       </c>
       <c r="C274" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="E274" t="s">
-        <v>130</v>
+        <v>458</v>
       </c>
       <c r="F274">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="G274" t="s">
         <v>69</v>
@@ -9248,24 +9227,24 @@
         <v>69</v>
       </c>
       <c r="I274" t="s">
-        <v>179</v>
+        <v>540</v>
       </c>
     </row>
     <row r="275" spans="1:9">
       <c r="A275" t="s">
-        <v>526</v>
+        <v>471</v>
       </c>
       <c r="B275" t="s">
-        <v>527</v>
+        <v>472</v>
       </c>
       <c r="C275" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="E275" t="s">
-        <v>236</v>
+        <v>458</v>
       </c>
       <c r="F275">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G275" t="s">
         <v>69</v>
@@ -9274,24 +9253,24 @@
         <v>69</v>
       </c>
       <c r="I275" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="276" spans="1:9">
       <c r="A276" t="s">
-        <v>554</v>
+        <v>527</v>
       </c>
       <c r="B276" t="s">
-        <v>555</v>
+        <v>528</v>
       </c>
       <c r="C276" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="E276" t="s">
-        <v>236</v>
+        <v>458</v>
       </c>
       <c r="F276">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G276" t="s">
         <v>69</v>
@@ -9300,24 +9279,21 @@
         <v>69</v>
       </c>
       <c r="I276" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="277" spans="1:9">
       <c r="A277" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="B277" t="s">
-        <v>544</v>
-      </c>
-      <c r="C277" t="s">
-        <v>148</v>
+        <v>562</v>
       </c>
       <c r="E277" t="s">
-        <v>236</v>
+        <v>563</v>
       </c>
       <c r="F277">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G277" t="s">
         <v>69</v>
@@ -9326,24 +9302,21 @@
         <v>69</v>
       </c>
       <c r="I277" t="s">
-        <v>376</v>
+        <v>564</v>
       </c>
     </row>
     <row r="278" spans="1:9">
       <c r="A278" t="s">
-        <v>337</v>
+        <v>565</v>
       </c>
       <c r="B278" t="s">
-        <v>338</v>
-      </c>
-      <c r="C278" t="s">
-        <v>125</v>
+        <v>566</v>
       </c>
       <c r="E278" t="s">
-        <v>236</v>
+        <v>563</v>
       </c>
       <c r="F278">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G278" t="s">
         <v>69</v>
@@ -9352,24 +9325,21 @@
         <v>69</v>
       </c>
       <c r="I278" t="s">
-        <v>247</v>
+        <v>216</v>
       </c>
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
-        <v>533</v>
+        <v>567</v>
       </c>
       <c r="B279" t="s">
-        <v>534</v>
-      </c>
-      <c r="C279" t="s">
-        <v>148</v>
+        <v>568</v>
       </c>
       <c r="E279" t="s">
-        <v>236</v>
+        <v>563</v>
       </c>
       <c r="F279">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G279" t="s">
         <v>69</v>
@@ -9378,24 +9348,21 @@
         <v>69</v>
       </c>
       <c r="I279" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="B280" t="s">
-        <v>505</v>
-      </c>
-      <c r="C280" t="s">
-        <v>125</v>
+        <v>570</v>
       </c>
       <c r="E280" t="s">
-        <v>473</v>
+        <v>214</v>
       </c>
       <c r="F280">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G280" t="s">
         <v>69</v>
@@ -9404,24 +9371,24 @@
         <v>69</v>
       </c>
       <c r="I280" t="s">
-        <v>549</v>
+        <v>108</v>
       </c>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="B281" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="C281" t="s">
-        <v>140</v>
+        <v>335</v>
       </c>
       <c r="E281" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="F281">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G281" t="s">
         <v>69</v>
@@ -9430,24 +9397,24 @@
         <v>69</v>
       </c>
       <c r="I281" t="s">
-        <v>244</v>
+        <v>492</v>
       </c>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
-        <v>536</v>
+        <v>489</v>
       </c>
       <c r="B282" t="s">
-        <v>537</v>
+        <v>490</v>
       </c>
       <c r="C282" t="s">
-        <v>125</v>
+        <v>262</v>
       </c>
       <c r="E282" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="F282">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G282" t="s">
         <v>69</v>
@@ -9456,21 +9423,24 @@
         <v>69</v>
       </c>
       <c r="I282" t="s">
-        <v>242</v>
+        <v>571</v>
       </c>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>569</v>
+        <v>489</v>
       </c>
       <c r="B283" t="s">
-        <v>570</v>
+        <v>490</v>
+      </c>
+      <c r="C283" t="s">
+        <v>362</v>
       </c>
       <c r="E283" t="s">
-        <v>571</v>
+        <v>491</v>
       </c>
       <c r="F283">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G283" t="s">
         <v>69</v>
@@ -9489,11 +9459,14 @@
       <c r="B284" t="s">
         <v>574</v>
       </c>
+      <c r="C284" t="s">
+        <v>335</v>
+      </c>
       <c r="E284" t="s">
-        <v>571</v>
+        <v>491</v>
       </c>
       <c r="F284">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G284" t="s">
         <v>69</v>
@@ -9502,21 +9475,24 @@
         <v>69</v>
       </c>
       <c r="I284" t="s">
-        <v>216</v>
+        <v>492</v>
       </c>
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B285" t="s">
-        <v>576</v>
+        <v>574</v>
+      </c>
+      <c r="C285" t="s">
+        <v>262</v>
       </c>
       <c r="E285" t="s">
-        <v>571</v>
+        <v>491</v>
       </c>
       <c r="F285">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G285" t="s">
         <v>69</v>
@@ -9525,21 +9501,24 @@
         <v>69</v>
       </c>
       <c r="I285" t="s">
-        <v>276</v>
+        <v>572</v>
       </c>
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B286" t="s">
-        <v>578</v>
+        <v>574</v>
+      </c>
+      <c r="C286" t="s">
+        <v>390</v>
       </c>
       <c r="E286" t="s">
-        <v>214</v>
+        <v>491</v>
       </c>
       <c r="F286">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G286" t="s">
         <v>69</v>
@@ -9548,24 +9527,24 @@
         <v>69</v>
       </c>
       <c r="I286" t="s">
-        <v>108</v>
+        <v>575</v>
       </c>
     </row>
     <row r="287" spans="1:9">
       <c r="A287" t="s">
-        <v>500</v>
+        <v>576</v>
       </c>
       <c r="B287" t="s">
-        <v>501</v>
+        <v>574</v>
       </c>
       <c r="C287" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="E287" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F287">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G287" t="s">
         <v>69</v>
@@ -9574,24 +9553,24 @@
         <v>69</v>
       </c>
       <c r="I287" t="s">
-        <v>503</v>
+        <v>577</v>
       </c>
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
-        <v>500</v>
+        <v>578</v>
       </c>
       <c r="B288" t="s">
-        <v>501</v>
+        <v>579</v>
       </c>
       <c r="C288" t="s">
-        <v>262</v>
+        <v>335</v>
       </c>
       <c r="E288" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F288">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G288" t="s">
         <v>69</v>
@@ -9600,24 +9579,24 @@
         <v>69</v>
       </c>
       <c r="I288" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
-        <v>500</v>
+        <v>578</v>
       </c>
       <c r="B289" t="s">
-        <v>501</v>
+        <v>579</v>
       </c>
       <c r="C289" t="s">
-        <v>369</v>
+        <v>262</v>
       </c>
       <c r="E289" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F289">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G289" t="s">
         <v>69</v>
@@ -9626,76 +9605,76 @@
         <v>69</v>
       </c>
       <c r="I289" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B290" t="s">
+        <v>579</v>
+      </c>
+      <c r="C290" t="s">
+        <v>390</v>
+      </c>
+      <c r="E290" t="s">
+        <v>491</v>
+      </c>
+      <c r="F290">
+        <v>3.0</v>
+      </c>
+      <c r="G290" t="s">
+        <v>69</v>
+      </c>
+      <c r="H290" t="s">
+        <v>69</v>
+      </c>
+      <c r="I290" t="s">
         <v>582</v>
-      </c>
-      <c r="C290" t="s">
-        <v>324</v>
-      </c>
-      <c r="E290" t="s">
-        <v>502</v>
-      </c>
-      <c r="F290">
-        <v>4.0</v>
-      </c>
-      <c r="G290" t="s">
-        <v>69</v>
-      </c>
-      <c r="H290" t="s">
-        <v>69</v>
-      </c>
-      <c r="I290" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B291" t="s">
+        <v>579</v>
+      </c>
+      <c r="C291" t="s">
+        <v>284</v>
+      </c>
+      <c r="E291" t="s">
+        <v>491</v>
+      </c>
+      <c r="F291">
+        <v>3.0</v>
+      </c>
+      <c r="G291" t="s">
+        <v>69</v>
+      </c>
+      <c r="H291" t="s">
+        <v>69</v>
+      </c>
+      <c r="I291" t="s">
         <v>582</v>
-      </c>
-      <c r="C291" t="s">
-        <v>262</v>
-      </c>
-      <c r="E291" t="s">
-        <v>502</v>
-      </c>
-      <c r="F291">
-        <v>5.0</v>
-      </c>
-      <c r="G291" t="s">
-        <v>69</v>
-      </c>
-      <c r="H291" t="s">
-        <v>69</v>
-      </c>
-      <c r="I291" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B292" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C292" t="s">
-        <v>369</v>
+        <v>284</v>
       </c>
       <c r="E292" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F292">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G292" t="s">
         <v>69</v>
@@ -9704,24 +9683,24 @@
         <v>69</v>
       </c>
       <c r="I292" t="s">
-        <v>583</v>
+        <v>522</v>
       </c>
     </row>
     <row r="293" spans="1:9">
       <c r="A293" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B293" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C293" t="s">
-        <v>397</v>
+        <v>262</v>
       </c>
       <c r="E293" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F293">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G293" t="s">
         <v>69</v>
@@ -9730,24 +9709,24 @@
         <v>69</v>
       </c>
       <c r="I293" t="s">
-        <v>584</v>
+        <v>320</v>
       </c>
     </row>
     <row r="294" spans="1:9">
       <c r="A294" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B294" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="C294" t="s">
-        <v>284</v>
+        <v>335</v>
       </c>
       <c r="E294" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F294">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G294" t="s">
         <v>69</v>
@@ -9756,24 +9735,24 @@
         <v>69</v>
       </c>
       <c r="I294" t="s">
-        <v>583</v>
+        <v>320</v>
       </c>
     </row>
     <row r="295" spans="1:9">
       <c r="A295" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B295" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C295" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="E295" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F295">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G295" t="s">
         <v>69</v>
@@ -9782,24 +9761,24 @@
         <v>69</v>
       </c>
       <c r="I295" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="296" spans="1:9">
       <c r="A296" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B296" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C296" t="s">
-        <v>262</v>
+        <v>362</v>
       </c>
       <c r="E296" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F296">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G296" t="s">
         <v>69</v>
@@ -9808,24 +9787,24 @@
         <v>69</v>
       </c>
       <c r="I296" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="297" spans="1:9">
       <c r="A297" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B297" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C297" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E297" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F297">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G297" t="s">
         <v>69</v>
@@ -9834,24 +9813,24 @@
         <v>69</v>
       </c>
       <c r="I297" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="298" spans="1:9">
       <c r="A298" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B298" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C298" t="s">
         <v>284</v>
       </c>
       <c r="E298" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F298">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G298" t="s">
         <v>69</v>
@@ -9860,21 +9839,21 @@
         <v>69</v>
       </c>
       <c r="I298" t="s">
-        <v>590</v>
+        <v>320</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B299" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C299" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="E299" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F299">
         <v>1.0</v>
@@ -9886,50 +9865,50 @@
         <v>69</v>
       </c>
       <c r="I299" t="s">
-        <v>531</v>
+        <v>594</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="A300" t="s">
+        <v>595</v>
+      </c>
+      <c r="B300" t="s">
+        <v>596</v>
+      </c>
+      <c r="C300" t="s">
+        <v>262</v>
+      </c>
+      <c r="E300" t="s">
+        <v>491</v>
+      </c>
+      <c r="F300">
+        <v>2.0</v>
+      </c>
+      <c r="G300" t="s">
+        <v>69</v>
+      </c>
+      <c r="H300" t="s">
+        <v>69</v>
+      </c>
+      <c r="I300" t="s">
         <v>591</v>
-      </c>
-      <c r="B300" t="s">
-        <v>592</v>
-      </c>
-      <c r="C300" t="s">
-        <v>284</v>
-      </c>
-      <c r="E300" t="s">
-        <v>502</v>
-      </c>
-      <c r="F300">
-        <v>1.0</v>
-      </c>
-      <c r="G300" t="s">
-        <v>69</v>
-      </c>
-      <c r="H300" t="s">
-        <v>69</v>
-      </c>
-      <c r="I300" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="301" spans="1:9">
       <c r="A301" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B301" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C301" t="s">
         <v>262</v>
       </c>
       <c r="E301" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F301">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G301" t="s">
         <v>69</v>
@@ -9938,24 +9917,24 @@
         <v>69</v>
       </c>
       <c r="I301" t="s">
-        <v>329</v>
+        <v>508</v>
       </c>
     </row>
     <row r="302" spans="1:9">
       <c r="A302" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B302" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C302" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E302" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F302">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G302" t="s">
         <v>69</v>
@@ -9964,21 +9943,21 @@
         <v>69</v>
       </c>
       <c r="I302" t="s">
-        <v>429</v>
+        <v>522</v>
       </c>
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B303" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C303" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E303" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F303">
         <v>1.0</v>
@@ -9990,21 +9969,21 @@
         <v>69</v>
       </c>
       <c r="I303" t="s">
-        <v>329</v>
+        <v>522</v>
       </c>
     </row>
     <row r="304" spans="1:9">
       <c r="A304" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B304" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C304" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="E304" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="F304">
         <v>1.0</v>
@@ -10016,24 +9995,24 @@
         <v>69</v>
       </c>
       <c r="I304" t="s">
-        <v>329</v>
+        <v>522</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B305" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C305" t="s">
-        <v>262</v>
+        <v>335</v>
       </c>
       <c r="E305" t="s">
-        <v>502</v>
+        <v>343</v>
       </c>
       <c r="F305">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G305" t="s">
         <v>69</v>
@@ -10042,21 +10021,21 @@
         <v>69</v>
       </c>
       <c r="I305" t="s">
-        <v>598</v>
+        <v>475</v>
       </c>
     </row>
     <row r="306" spans="1:9">
       <c r="A306" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B306" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C306" t="s">
-        <v>369</v>
+        <v>262</v>
       </c>
       <c r="E306" t="s">
-        <v>502</v>
+        <v>343</v>
       </c>
       <c r="F306">
         <v>2.0</v>
@@ -10068,24 +10047,24 @@
         <v>69</v>
       </c>
       <c r="I306" t="s">
-        <v>429</v>
+        <v>475</v>
       </c>
     </row>
     <row r="307" spans="1:9">
       <c r="A307" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B307" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C307" t="s">
-        <v>397</v>
+        <v>362</v>
       </c>
       <c r="E307" t="s">
-        <v>502</v>
+        <v>343</v>
       </c>
       <c r="F307">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G307" t="s">
         <v>69</v>
@@ -10094,24 +10073,24 @@
         <v>69</v>
       </c>
       <c r="I307" t="s">
-        <v>429</v>
+        <v>461</v>
       </c>
     </row>
     <row r="308" spans="1:9">
       <c r="A308" t="s">
-        <v>597</v>
+        <v>543</v>
       </c>
       <c r="B308" t="s">
-        <v>596</v>
+        <v>544</v>
       </c>
       <c r="C308" t="s">
-        <v>284</v>
+        <v>362</v>
       </c>
       <c r="E308" t="s">
-        <v>502</v>
+        <v>343</v>
       </c>
       <c r="F308">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G308" t="s">
         <v>69</v>
@@ -10120,24 +10099,24 @@
         <v>69</v>
       </c>
       <c r="I308" t="s">
-        <v>329</v>
+        <v>455</v>
       </c>
     </row>
     <row r="309" spans="1:9">
       <c r="A309" t="s">
-        <v>599</v>
+        <v>537</v>
       </c>
       <c r="B309" t="s">
-        <v>600</v>
+        <v>538</v>
       </c>
       <c r="C309" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E309" t="s">
-        <v>502</v>
+        <v>343</v>
       </c>
       <c r="F309">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G309" t="s">
         <v>69</v>
@@ -10146,24 +10125,24 @@
         <v>69</v>
       </c>
       <c r="I309" t="s">
-        <v>601</v>
+        <v>539</v>
       </c>
     </row>
     <row r="310" spans="1:9">
       <c r="A310" t="s">
-        <v>599</v>
+        <v>537</v>
       </c>
       <c r="B310" t="s">
-        <v>600</v>
+        <v>538</v>
       </c>
       <c r="C310" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E310" t="s">
-        <v>502</v>
+        <v>343</v>
       </c>
       <c r="F310">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G310" t="s">
         <v>69</v>
@@ -10172,21 +10151,21 @@
         <v>69</v>
       </c>
       <c r="I310" t="s">
-        <v>601</v>
+        <v>517</v>
       </c>
     </row>
     <row r="311" spans="1:9">
       <c r="A311" t="s">
-        <v>602</v>
+        <v>537</v>
       </c>
       <c r="B311" t="s">
-        <v>603</v>
+        <v>538</v>
       </c>
       <c r="C311" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="E311" t="s">
-        <v>502</v>
+        <v>343</v>
       </c>
       <c r="F311">
         <v>2.0</v>
@@ -10198,21 +10177,21 @@
         <v>69</v>
       </c>
       <c r="I311" t="s">
-        <v>429</v>
+        <v>501</v>
       </c>
     </row>
     <row r="312" spans="1:9">
       <c r="A312" t="s">
-        <v>602</v>
+        <v>529</v>
       </c>
       <c r="B312" t="s">
-        <v>603</v>
+        <v>530</v>
       </c>
       <c r="C312" t="s">
-        <v>397</v>
+        <v>335</v>
       </c>
       <c r="E312" t="s">
-        <v>502</v>
+        <v>343</v>
       </c>
       <c r="F312">
         <v>1.0</v>
@@ -10224,24 +10203,24 @@
         <v>69</v>
       </c>
       <c r="I312" t="s">
-        <v>329</v>
+        <v>477</v>
       </c>
     </row>
     <row r="313" spans="1:9">
       <c r="A313" t="s">
-        <v>604</v>
+        <v>547</v>
       </c>
       <c r="B313" t="s">
-        <v>605</v>
+        <v>548</v>
       </c>
       <c r="C313" t="s">
-        <v>262</v>
+        <v>335</v>
       </c>
       <c r="E313" t="s">
-        <v>502</v>
+        <v>343</v>
       </c>
       <c r="F313">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G313" t="s">
         <v>69</v>
@@ -10250,21 +10229,21 @@
         <v>69</v>
       </c>
       <c r="I313" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="314" spans="1:9">
       <c r="A314" t="s">
-        <v>604</v>
+        <v>545</v>
       </c>
       <c r="B314" t="s">
-        <v>605</v>
+        <v>546</v>
       </c>
       <c r="C314" t="s">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="E314" t="s">
-        <v>502</v>
+        <v>343</v>
       </c>
       <c r="F314">
         <v>1.0</v>
@@ -10276,24 +10255,24 @@
         <v>69</v>
       </c>
       <c r="I314" t="s">
-        <v>531</v>
+        <v>477</v>
       </c>
     </row>
     <row r="315" spans="1:9">
       <c r="A315" t="s">
-        <v>604</v>
+        <v>545</v>
       </c>
       <c r="B315" t="s">
-        <v>605</v>
+        <v>546</v>
       </c>
       <c r="C315" t="s">
-        <v>397</v>
+        <v>362</v>
       </c>
       <c r="E315" t="s">
-        <v>502</v>
+        <v>343</v>
       </c>
       <c r="F315">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G315" t="s">
         <v>69</v>
@@ -10302,21 +10281,21 @@
         <v>69</v>
       </c>
       <c r="I315" t="s">
-        <v>77</v>
+        <v>477</v>
       </c>
     </row>
     <row r="316" spans="1:9">
       <c r="A316" t="s">
-        <v>604</v>
+        <v>531</v>
       </c>
       <c r="B316" t="s">
-        <v>605</v>
+        <v>532</v>
       </c>
       <c r="C316" t="s">
-        <v>284</v>
+        <v>335</v>
       </c>
       <c r="E316" t="s">
-        <v>502</v>
+        <v>343</v>
       </c>
       <c r="F316">
         <v>1.0</v>
@@ -10328,24 +10307,24 @@
         <v>69</v>
       </c>
       <c r="I316" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
     <row r="317" spans="1:9">
       <c r="A317" t="s">
-        <v>606</v>
+        <v>554</v>
       </c>
       <c r="B317" t="s">
-        <v>607</v>
+        <v>555</v>
       </c>
       <c r="C317" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E317" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F317">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G317" t="s">
         <v>69</v>
@@ -10354,21 +10333,21 @@
         <v>69</v>
       </c>
       <c r="I317" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" t="s">
-        <v>606</v>
+        <v>554</v>
       </c>
       <c r="B318" t="s">
-        <v>607</v>
+        <v>555</v>
       </c>
       <c r="C318" t="s">
-        <v>262</v>
+        <v>362</v>
       </c>
       <c r="E318" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F318">
         <v>2.0</v>
@@ -10380,24 +10359,24 @@
         <v>69</v>
       </c>
       <c r="I318" t="s">
-        <v>484</v>
+        <v>455</v>
       </c>
     </row>
     <row r="319" spans="1:9">
       <c r="A319" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="B319" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C319" t="s">
-        <v>369</v>
+        <v>262</v>
       </c>
       <c r="E319" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F319">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G319" t="s">
         <v>69</v>
@@ -10406,24 +10385,24 @@
         <v>69</v>
       </c>
       <c r="I319" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
     </row>
     <row r="320" spans="1:9">
       <c r="A320" t="s">
-        <v>550</v>
+        <v>601</v>
       </c>
       <c r="B320" t="s">
-        <v>551</v>
+        <v>602</v>
       </c>
       <c r="C320" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E320" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F320">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G320" t="s">
         <v>69</v>
@@ -10432,24 +10411,24 @@
         <v>69</v>
       </c>
       <c r="I320" t="s">
-        <v>464</v>
+        <v>480</v>
       </c>
     </row>
     <row r="321" spans="1:9">
       <c r="A321" t="s">
-        <v>545</v>
+        <v>603</v>
       </c>
       <c r="B321" t="s">
-        <v>546</v>
+        <v>604</v>
       </c>
       <c r="C321" t="s">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="E321" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F321">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G321" t="s">
         <v>69</v>
@@ -10458,24 +10437,24 @@
         <v>69</v>
       </c>
       <c r="I321" t="s">
-        <v>547</v>
+        <v>477</v>
       </c>
     </row>
     <row r="322" spans="1:9">
       <c r="A322" t="s">
-        <v>545</v>
+        <v>603</v>
       </c>
       <c r="B322" t="s">
-        <v>546</v>
+        <v>604</v>
       </c>
       <c r="C322" t="s">
-        <v>397</v>
+        <v>262</v>
       </c>
       <c r="E322" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F322">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G322" t="s">
         <v>69</v>
@@ -10484,21 +10463,21 @@
         <v>69</v>
       </c>
       <c r="I322" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
     </row>
     <row r="323" spans="1:9">
       <c r="A323" t="s">
-        <v>545</v>
+        <v>603</v>
       </c>
       <c r="B323" t="s">
-        <v>546</v>
+        <v>604</v>
       </c>
       <c r="C323" t="s">
-        <v>284</v>
+        <v>362</v>
       </c>
       <c r="E323" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F323">
         <v>2.0</v>
@@ -10510,21 +10489,21 @@
         <v>69</v>
       </c>
       <c r="I323" t="s">
-        <v>512</v>
+        <v>475</v>
       </c>
     </row>
     <row r="324" spans="1:9">
       <c r="A324" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="B324" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="C324" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="E324" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F324">
         <v>1.0</v>
@@ -10536,21 +10515,21 @@
         <v>69</v>
       </c>
       <c r="I324" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="325" spans="1:9">
       <c r="A325" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B325" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C325" t="s">
-        <v>324</v>
+        <v>390</v>
       </c>
       <c r="E325" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F325">
         <v>1.0</v>
@@ -10562,21 +10541,21 @@
         <v>69</v>
       </c>
       <c r="I325" t="s">
-        <v>531</v>
+        <v>480</v>
       </c>
     </row>
     <row r="326" spans="1:9">
       <c r="A326" t="s">
-        <v>552</v>
+        <v>605</v>
       </c>
       <c r="B326" t="s">
-        <v>553</v>
+        <v>606</v>
       </c>
       <c r="C326" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E326" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F326">
         <v>1.0</v>
@@ -10588,21 +10567,21 @@
         <v>69</v>
       </c>
       <c r="I326" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="327" spans="1:9">
       <c r="A327" t="s">
-        <v>552</v>
+        <v>605</v>
       </c>
       <c r="B327" t="s">
-        <v>553</v>
+        <v>606</v>
       </c>
       <c r="C327" t="s">
-        <v>369</v>
+        <v>262</v>
       </c>
       <c r="E327" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F327">
         <v>1.0</v>
@@ -10614,21 +10593,21 @@
         <v>69</v>
       </c>
       <c r="I327" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="328" spans="1:9">
       <c r="A328" t="s">
-        <v>540</v>
+        <v>605</v>
       </c>
       <c r="B328" t="s">
-        <v>541</v>
+        <v>606</v>
       </c>
       <c r="C328" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="E328" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F328">
         <v>1.0</v>
@@ -10640,24 +10619,24 @@
         <v>69</v>
       </c>
       <c r="I328" t="s">
-        <v>531</v>
+        <v>480</v>
       </c>
     </row>
     <row r="329" spans="1:9">
       <c r="A329" t="s">
-        <v>562</v>
+        <v>607</v>
       </c>
       <c r="B329" t="s">
-        <v>563</v>
+        <v>608</v>
       </c>
       <c r="C329" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E329" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F329">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G329" t="s">
         <v>69</v>
@@ -10666,24 +10645,24 @@
         <v>69</v>
       </c>
       <c r="I329" t="s">
-        <v>489</v>
+        <v>423</v>
       </c>
     </row>
     <row r="330" spans="1:9">
       <c r="A330" t="s">
-        <v>562</v>
+        <v>607</v>
       </c>
       <c r="B330" t="s">
-        <v>563</v>
+        <v>608</v>
       </c>
       <c r="C330" t="s">
-        <v>369</v>
+        <v>262</v>
       </c>
       <c r="E330" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F330">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G330" t="s">
         <v>69</v>
@@ -10692,24 +10671,24 @@
         <v>69</v>
       </c>
       <c r="I330" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
     </row>
     <row r="331" spans="1:9">
       <c r="A331" t="s">
+        <v>607</v>
+      </c>
+      <c r="B331" t="s">
         <v>608</v>
       </c>
-      <c r="B331" t="s">
-        <v>609</v>
-      </c>
       <c r="C331" t="s">
-        <v>262</v>
+        <v>362</v>
       </c>
       <c r="E331" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F331">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G331" t="s">
         <v>69</v>
@@ -10718,24 +10697,24 @@
         <v>69</v>
       </c>
       <c r="I331" t="s">
-        <v>464</v>
+        <v>498</v>
       </c>
     </row>
     <row r="332" spans="1:9">
       <c r="A332" t="s">
+        <v>607</v>
+      </c>
+      <c r="B332" t="s">
         <v>608</v>
       </c>
-      <c r="B332" t="s">
-        <v>609</v>
-      </c>
       <c r="C332" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="E332" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F332">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G332" t="s">
         <v>69</v>
@@ -10744,24 +10723,24 @@
         <v>69</v>
       </c>
       <c r="I332" t="s">
-        <v>489</v>
+        <v>539</v>
       </c>
     </row>
     <row r="333" spans="1:9">
       <c r="A333" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B333" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C333" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="E333" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F333">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G333" t="s">
         <v>69</v>
@@ -10770,24 +10749,24 @@
         <v>69</v>
       </c>
       <c r="I333" t="s">
-        <v>486</v>
+        <v>423</v>
       </c>
     </row>
     <row r="334" spans="1:9">
       <c r="A334" t="s">
-        <v>610</v>
+        <v>559</v>
       </c>
       <c r="B334" t="s">
-        <v>611</v>
+        <v>560</v>
       </c>
       <c r="C334" t="s">
-        <v>262</v>
+        <v>164</v>
       </c>
       <c r="E334" t="s">
-        <v>351</v>
+        <v>126</v>
       </c>
       <c r="F334">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G334" t="s">
         <v>69</v>
@@ -10796,21 +10775,21 @@
         <v>69</v>
       </c>
       <c r="I334" t="s">
-        <v>470</v>
+        <v>160</v>
       </c>
     </row>
     <row r="335" spans="1:9">
       <c r="A335" t="s">
+        <v>609</v>
+      </c>
+      <c r="B335" t="s">
         <v>610</v>
       </c>
-      <c r="B335" t="s">
-        <v>611</v>
-      </c>
       <c r="C335" t="s">
-        <v>369</v>
+        <v>125</v>
       </c>
       <c r="E335" t="s">
-        <v>351</v>
+        <v>236</v>
       </c>
       <c r="F335">
         <v>1.0</v>
@@ -10822,21 +10801,21 @@
         <v>69</v>
       </c>
       <c r="I335" t="s">
-        <v>486</v>
+        <v>238</v>
       </c>
     </row>
     <row r="336" spans="1:9">
       <c r="A336" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B336" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C336" t="s">
-        <v>397</v>
+        <v>335</v>
       </c>
       <c r="E336" t="s">
-        <v>351</v>
+        <v>491</v>
       </c>
       <c r="F336">
         <v>1.0</v>
@@ -10848,21 +10827,21 @@
         <v>69</v>
       </c>
       <c r="I336" t="s">
-        <v>486</v>
+        <v>594</v>
       </c>
     </row>
     <row r="337" spans="1:9">
       <c r="A337" t="s">
-        <v>560</v>
+        <v>611</v>
       </c>
       <c r="B337" t="s">
-        <v>561</v>
+        <v>612</v>
       </c>
       <c r="C337" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="E337" t="s">
-        <v>351</v>
+        <v>491</v>
       </c>
       <c r="F337">
         <v>1.0</v>
@@ -10874,24 +10853,24 @@
         <v>69</v>
       </c>
       <c r="I337" t="s">
-        <v>489</v>
+        <v>594</v>
       </c>
     </row>
     <row r="338" spans="1:9">
       <c r="A338" t="s">
-        <v>560</v>
+        <v>611</v>
       </c>
       <c r="B338" t="s">
-        <v>561</v>
+        <v>612</v>
       </c>
       <c r="C338" t="s">
-        <v>397</v>
+        <v>262</v>
       </c>
       <c r="E338" t="s">
-        <v>351</v>
+        <v>491</v>
       </c>
       <c r="F338">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G338" t="s">
         <v>69</v>
@@ -10900,24 +10879,24 @@
         <v>69</v>
       </c>
       <c r="I338" t="s">
-        <v>489</v>
+        <v>582</v>
       </c>
     </row>
     <row r="339" spans="1:9">
       <c r="A339" t="s">
-        <v>612</v>
+        <v>489</v>
       </c>
       <c r="B339" t="s">
-        <v>613</v>
+        <v>490</v>
       </c>
       <c r="C339" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
       <c r="E339" t="s">
-        <v>351</v>
+        <v>491</v>
       </c>
       <c r="F339">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G339" t="s">
         <v>69</v>
@@ -10926,345 +10905,7 @@
         <v>69</v>
       </c>
       <c r="I339" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="340" spans="1:9">
-      <c r="A340" t="s">
-        <v>612</v>
-      </c>
-      <c r="B340" t="s">
-        <v>613</v>
-      </c>
-      <c r="C340" t="s">
-        <v>262</v>
-      </c>
-      <c r="E340" t="s">
-        <v>351</v>
-      </c>
-      <c r="F340">
-        <v>1.0</v>
-      </c>
-      <c r="G340" t="s">
-        <v>69</v>
-      </c>
-      <c r="H340" t="s">
-        <v>69</v>
-      </c>
-      <c r="I340" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="341" spans="1:9">
-      <c r="A341" t="s">
-        <v>612</v>
-      </c>
-      <c r="B341" t="s">
-        <v>613</v>
-      </c>
-      <c r="C341" t="s">
-        <v>369</v>
-      </c>
-      <c r="E341" t="s">
-        <v>351</v>
-      </c>
-      <c r="F341">
-        <v>1.0</v>
-      </c>
-      <c r="G341" t="s">
-        <v>69</v>
-      </c>
-      <c r="H341" t="s">
-        <v>69</v>
-      </c>
-      <c r="I341" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="342" spans="1:9">
-      <c r="A342" t="s">
-        <v>614</v>
-      </c>
-      <c r="B342" t="s">
-        <v>615</v>
-      </c>
-      <c r="C342" t="s">
-        <v>324</v>
-      </c>
-      <c r="E342" t="s">
-        <v>351</v>
-      </c>
-      <c r="F342">
-        <v>4.0</v>
-      </c>
-      <c r="G342" t="s">
-        <v>69</v>
-      </c>
-      <c r="H342" t="s">
-        <v>69</v>
-      </c>
-      <c r="I342" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="343" spans="1:9">
-      <c r="A343" t="s">
-        <v>614</v>
-      </c>
-      <c r="B343" t="s">
-        <v>615</v>
-      </c>
-      <c r="C343" t="s">
-        <v>262</v>
-      </c>
-      <c r="E343" t="s">
-        <v>351</v>
-      </c>
-      <c r="F343">
-        <v>6.0</v>
-      </c>
-      <c r="G343" t="s">
-        <v>69</v>
-      </c>
-      <c r="H343" t="s">
-        <v>69</v>
-      </c>
-      <c r="I343" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="344" spans="1:9">
-      <c r="A344" t="s">
-        <v>614</v>
-      </c>
-      <c r="B344" t="s">
-        <v>615</v>
-      </c>
-      <c r="C344" t="s">
-        <v>369</v>
-      </c>
-      <c r="E344" t="s">
-        <v>351</v>
-      </c>
-      <c r="F344">
-        <v>6.0</v>
-      </c>
-      <c r="G344" t="s">
-        <v>69</v>
-      </c>
-      <c r="H344" t="s">
-        <v>69</v>
-      </c>
-      <c r="I344" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="345" spans="1:9">
-      <c r="A345" t="s">
-        <v>614</v>
-      </c>
-      <c r="B345" t="s">
-        <v>615</v>
-      </c>
-      <c r="C345" t="s">
-        <v>397</v>
-      </c>
-      <c r="E345" t="s">
-        <v>351</v>
-      </c>
-      <c r="F345">
-        <v>5.0</v>
-      </c>
-      <c r="G345" t="s">
-        <v>69</v>
-      </c>
-      <c r="H345" t="s">
-        <v>69</v>
-      </c>
-      <c r="I345" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="346" spans="1:9">
-      <c r="A346" t="s">
-        <v>614</v>
-      </c>
-      <c r="B346" t="s">
-        <v>615</v>
-      </c>
-      <c r="C346" t="s">
-        <v>284</v>
-      </c>
-      <c r="E346" t="s">
-        <v>351</v>
-      </c>
-      <c r="F346">
-        <v>4.0</v>
-      </c>
-      <c r="G346" t="s">
-        <v>69</v>
-      </c>
-      <c r="H346" t="s">
-        <v>69</v>
-      </c>
-      <c r="I346" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="347" spans="1:9">
-      <c r="A347" t="s">
-        <v>567</v>
-      </c>
-      <c r="B347" t="s">
-        <v>568</v>
-      </c>
-      <c r="C347" t="s">
-        <v>164</v>
-      </c>
-      <c r="E347" t="s">
-        <v>126</v>
-      </c>
-      <c r="F347">
-        <v>2.0</v>
-      </c>
-      <c r="G347" t="s">
-        <v>69</v>
-      </c>
-      <c r="H347" t="s">
-        <v>69</v>
-      </c>
-      <c r="I347" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="348" spans="1:9">
-      <c r="A348" t="s">
-        <v>616</v>
-      </c>
-      <c r="B348" t="s">
-        <v>617</v>
-      </c>
-      <c r="C348" t="s">
-        <v>125</v>
-      </c>
-      <c r="E348" t="s">
-        <v>236</v>
-      </c>
-      <c r="F348">
-        <v>1.0</v>
-      </c>
-      <c r="G348" t="s">
-        <v>69</v>
-      </c>
-      <c r="H348" t="s">
-        <v>69</v>
-      </c>
-      <c r="I348" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="349" spans="1:9">
-      <c r="A349" t="s">
-        <v>618</v>
-      </c>
-      <c r="B349" t="s">
-        <v>619</v>
-      </c>
-      <c r="C349" t="s">
-        <v>324</v>
-      </c>
-      <c r="E349" t="s">
-        <v>502</v>
-      </c>
-      <c r="F349">
-        <v>1.0</v>
-      </c>
-      <c r="G349" t="s">
-        <v>69</v>
-      </c>
-      <c r="H349" t="s">
-        <v>69</v>
-      </c>
-      <c r="I349" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="350" spans="1:9">
-      <c r="A350" t="s">
-        <v>618</v>
-      </c>
-      <c r="B350" t="s">
-        <v>619</v>
-      </c>
-      <c r="C350" t="s">
-        <v>397</v>
-      </c>
-      <c r="E350" t="s">
-        <v>502</v>
-      </c>
-      <c r="F350">
-        <v>1.0</v>
-      </c>
-      <c r="G350" t="s">
-        <v>69</v>
-      </c>
-      <c r="H350" t="s">
-        <v>69</v>
-      </c>
-      <c r="I350" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="351" spans="1:9">
-      <c r="A351" t="s">
-        <v>618</v>
-      </c>
-      <c r="B351" t="s">
-        <v>619</v>
-      </c>
-      <c r="C351" t="s">
-        <v>262</v>
-      </c>
-      <c r="E351" t="s">
-        <v>502</v>
-      </c>
-      <c r="F351">
-        <v>3.0</v>
-      </c>
-      <c r="G351" t="s">
-        <v>69</v>
-      </c>
-      <c r="H351" t="s">
-        <v>69</v>
-      </c>
-      <c r="I351" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="352" spans="1:9">
-      <c r="A352" t="s">
-        <v>500</v>
-      </c>
-      <c r="B352" t="s">
-        <v>501</v>
-      </c>
-      <c r="C352" t="s">
-        <v>284</v>
-      </c>
-      <c r="E352" t="s">
-        <v>502</v>
-      </c>
-      <c r="F352">
-        <v>2.0</v>
-      </c>
-      <c r="G352" t="s">
-        <v>69</v>
-      </c>
-      <c r="H352" t="s">
-        <v>69</v>
-      </c>
-      <c r="I352" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
     </row>
   </sheetData>

--- a/src/inventory/War.xlsx
+++ b/src/inventory/War.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="574">
   <si>
     <t>Code/SKU</t>
   </si>
@@ -623,10 +623,7 @@
     <t>৳286.36</t>
   </si>
   <si>
-    <t>৳2,004.55</t>
-  </si>
-  <si>
-    <t>৳6,986.00</t>
+    <t>৳1,718.18</t>
   </si>
   <si>
     <t>109-0102-063</t>
@@ -893,10 +890,19 @@
     <t>৳2,970.00</t>
   </si>
   <si>
-    <t>109-0102-073</t>
-  </si>
-  <si>
-    <t>Bifold Leather Wallet 73</t>
+    <t>109-0402-048</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 48</t>
+  </si>
+  <si>
+    <t>৳990.00</t>
+  </si>
+  <si>
+    <t>109-0102-074</t>
+  </si>
+  <si>
+    <t>Bifold Wallet 74</t>
   </si>
   <si>
     <t>Men / WALLET,BI-FOLD</t>
@@ -905,102 +911,78 @@
     <t>৳699.00</t>
   </si>
   <si>
-    <t>109-0402-048</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 48</t>
-  </si>
-  <si>
-    <t>109-0102-074</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 74</t>
+    <t>109-0502-001</t>
+  </si>
+  <si>
+    <t>Breathable Face Mask</t>
+  </si>
+  <si>
+    <t>Men / MEN,ACCESSORIES,MASK</t>
+  </si>
+  <si>
+    <t>৳199.51</t>
+  </si>
+  <si>
+    <t>৳1,197.09</t>
+  </si>
+  <si>
+    <t>৳1,680.00</t>
+  </si>
+  <si>
+    <t>105-0201-033</t>
+  </si>
+  <si>
+    <t>Full Sleeve Neon Stripe T-shirt</t>
+  </si>
+  <si>
+    <t>109-0402-050</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 50</t>
+  </si>
+  <si>
+    <t>105-0301-005</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 05</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>৳431.25</t>
+  </si>
+  <si>
+    <t>101-0300-140</t>
+  </si>
+  <si>
+    <t>Straight Fit Blue Jeans</t>
+  </si>
+  <si>
+    <t>Men / MEN,JEANS,STRAIGHT FIT</t>
+  </si>
+  <si>
+    <t>৳6,760.00</t>
+  </si>
+  <si>
+    <t>105-0301-004</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 004</t>
+  </si>
+  <si>
+    <t>Men / T-SHIRT,Drop Shoulder</t>
+  </si>
+  <si>
+    <t>109-0402-061</t>
+  </si>
+  <si>
+    <t>Premium Leather Belt 061</t>
   </si>
   <si>
     <t>৳900.00</t>
   </si>
   <si>
-    <t>৳1,398.00</t>
-  </si>
-  <si>
-    <t>109-0502-001</t>
-  </si>
-  <si>
-    <t>Breathable Face Mask</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,MASK</t>
-  </si>
-  <si>
-    <t>৳199.51</t>
-  </si>
-  <si>
-    <t>৳1,197.09</t>
-  </si>
-  <si>
-    <t>৳1,680.00</t>
-  </si>
-  <si>
-    <t>105-0201-033</t>
-  </si>
-  <si>
-    <t>Full Sleeve Neon Stripe T-shirt</t>
-  </si>
-  <si>
-    <t>109-0402-050</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 50</t>
-  </si>
-  <si>
-    <t>109-0402-056</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 56</t>
-  </si>
-  <si>
-    <t>৳50.00</t>
-  </si>
-  <si>
-    <t>105-0301-005</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 05</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>৳431.25</t>
-  </si>
-  <si>
-    <t>101-0300-140</t>
-  </si>
-  <si>
-    <t>Straight Fit Blue Jeans</t>
-  </si>
-  <si>
-    <t>Men / MEN,JEANS,STRAIGHT FIT</t>
-  </si>
-  <si>
-    <t>৳6,760.00</t>
-  </si>
-  <si>
-    <t>105-0301-004</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 004</t>
-  </si>
-  <si>
-    <t>Men / T-SHIRT,Drop Shoulder</t>
-  </si>
-  <si>
-    <t>109-0402-061</t>
-  </si>
-  <si>
-    <t>Premium Leather Belt 061</t>
-  </si>
-  <si>
     <t>102-0302-005</t>
   </si>
   <si>
@@ -1106,12 +1088,6 @@
     <t>৳1,620.00</t>
   </si>
   <si>
-    <t>105-0301-009</t>
-  </si>
-  <si>
-    <t>Deep Violet Drop Shoulder T-Shirt</t>
-  </si>
-  <si>
     <t>103-0200-098</t>
   </si>
   <si>
@@ -1232,10 +1208,10 @@
     <t>৳278.57</t>
   </si>
   <si>
-    <t>৳2,750.00</t>
-  </si>
-  <si>
-    <t>৳7,040.00</t>
+    <t>৳2,500.00</t>
+  </si>
+  <si>
+    <t>৳6,400.00</t>
   </si>
   <si>
     <t>৳5,300.00</t>
@@ -1661,6 +1637,9 @@
     <t>Belt 114</t>
   </si>
   <si>
+    <t>৳3,570.00</t>
+  </si>
+  <si>
     <t>৳8,330.00</t>
   </si>
   <si>
@@ -1673,9 +1652,6 @@
     <t>Formal Shirt  002</t>
   </si>
   <si>
-    <t>৳3,570.00</t>
-  </si>
-  <si>
     <t>102-0501-002-</t>
   </si>
   <si>
@@ -1713,12 +1689,6 @@
   </si>
   <si>
     <t>৳2,700.00</t>
-  </si>
-  <si>
-    <t>102-0501-009</t>
-  </si>
-  <si>
-    <t>Formal Shirt 009</t>
   </si>
   <si>
     <t>102-0501-011</t>
@@ -2106,7 +2076,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I311"/>
+  <dimension ref="A1:I305"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3934,7 +3904,7 @@
         <v>126</v>
       </c>
       <c r="F71">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G71" t="s">
         <v>201</v>
@@ -3943,30 +3913,30 @@
         <v>202</v>
       </c>
       <c r="I71" t="s">
-        <v>203</v>
+        <v>161</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
+        <v>203</v>
+      </c>
+      <c r="B72" t="s">
         <v>204</v>
       </c>
-      <c r="B72" t="s">
+      <c r="E72" t="s">
         <v>205</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72">
+        <v>1.0</v>
+      </c>
+      <c r="G72" t="s">
         <v>206</v>
       </c>
-      <c r="F72">
-        <v>1.0</v>
-      </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
+        <v>206</v>
+      </c>
+      <c r="I72" t="s">
         <v>207</v>
-      </c>
-      <c r="H72" t="s">
-        <v>207</v>
-      </c>
-      <c r="I72" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3986,44 +3956,44 @@
         <v>8.0</v>
       </c>
       <c r="G73" t="s">
+        <v>208</v>
+      </c>
+      <c r="H73" t="s">
         <v>209</v>
       </c>
-      <c r="H73" t="s">
+      <c r="I73" t="s">
         <v>210</v>
-      </c>
-      <c r="I73" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
+        <v>211</v>
+      </c>
+      <c r="B74" t="s">
         <v>212</v>
-      </c>
-      <c r="B74" t="s">
-        <v>213</v>
       </c>
       <c r="C74" t="s">
         <v>148</v>
       </c>
       <c r="E74" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F74">
         <v>3.0</v>
       </c>
       <c r="G74" t="s">
+        <v>214</v>
+      </c>
+      <c r="H74" t="s">
         <v>215</v>
       </c>
-      <c r="H74" t="s">
+      <c r="I74" t="s">
         <v>216</v>
-      </c>
-      <c r="I74" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B75" t="s">
         <v>150</v>
@@ -4035,79 +4005,79 @@
         <v>2.0</v>
       </c>
       <c r="G75" t="s">
+        <v>218</v>
+      </c>
+      <c r="H75" t="s">
         <v>219</v>
       </c>
-      <c r="H75" t="s">
+      <c r="I75" t="s">
         <v>220</v>
-      </c>
-      <c r="I75" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
+        <v>221</v>
+      </c>
+      <c r="B76" t="s">
         <v>222</v>
-      </c>
-      <c r="B76" t="s">
-        <v>223</v>
       </c>
       <c r="C76" t="s">
         <v>158</v>
       </c>
       <c r="E76" t="s">
+        <v>223</v>
+      </c>
+      <c r="F76">
+        <v>1.0</v>
+      </c>
+      <c r="G76" t="s">
         <v>224</v>
       </c>
-      <c r="F76">
-        <v>1.0</v>
-      </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
+        <v>224</v>
+      </c>
+      <c r="I76" t="s">
         <v>225</v>
-      </c>
-      <c r="H76" t="s">
-        <v>225</v>
-      </c>
-      <c r="I76" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
+        <v>226</v>
+      </c>
+      <c r="B77" t="s">
         <v>227</v>
-      </c>
-      <c r="B77" t="s">
-        <v>228</v>
       </c>
       <c r="C77" t="s">
         <v>125</v>
       </c>
       <c r="E77" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F77">
         <v>2.0</v>
       </c>
       <c r="G77" t="s">
+        <v>228</v>
+      </c>
+      <c r="H77" t="s">
         <v>229</v>
       </c>
-      <c r="H77" t="s">
+      <c r="I77" t="s">
         <v>230</v>
-      </c>
-      <c r="I77" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
+        <v>221</v>
+      </c>
+      <c r="B78" t="s">
         <v>222</v>
-      </c>
-      <c r="B78" t="s">
-        <v>223</v>
       </c>
       <c r="C78" t="s">
         <v>111</v>
       </c>
       <c r="E78" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F78">
         <v>1.0</v>
@@ -4119,21 +4089,21 @@
         <v>172</v>
       </c>
       <c r="I78" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
+        <v>221</v>
+      </c>
+      <c r="B79" t="s">
         <v>222</v>
-      </c>
-      <c r="B79" t="s">
-        <v>223</v>
       </c>
       <c r="C79" t="s">
         <v>140</v>
       </c>
       <c r="E79" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F79">
         <v>6.0</v>
@@ -4142,24 +4112,24 @@
         <v>172</v>
       </c>
       <c r="H79" t="s">
+        <v>231</v>
+      </c>
+      <c r="I79" t="s">
         <v>232</v>
-      </c>
-      <c r="I79" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
+        <v>221</v>
+      </c>
+      <c r="B80" t="s">
         <v>222</v>
-      </c>
-      <c r="B80" t="s">
-        <v>223</v>
       </c>
       <c r="C80" t="s">
         <v>125</v>
       </c>
       <c r="E80" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F80">
         <v>5.0</v>
@@ -4168,24 +4138,24 @@
         <v>172</v>
       </c>
       <c r="H80" t="s">
+        <v>233</v>
+      </c>
+      <c r="I80" t="s">
         <v>234</v>
-      </c>
-      <c r="I80" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
+        <v>221</v>
+      </c>
+      <c r="B81" t="s">
         <v>222</v>
-      </c>
-      <c r="B81" t="s">
-        <v>223</v>
       </c>
       <c r="C81" t="s">
         <v>148</v>
       </c>
       <c r="E81" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F81">
         <v>4.0</v>
@@ -4194,41 +4164,41 @@
         <v>172</v>
       </c>
       <c r="H81" t="s">
+        <v>235</v>
+      </c>
+      <c r="I81" t="s">
         <v>236</v>
-      </c>
-      <c r="I81" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
+        <v>211</v>
+      </c>
+      <c r="B82" t="s">
         <v>212</v>
-      </c>
-      <c r="B82" t="s">
-        <v>213</v>
       </c>
       <c r="C82" t="s">
         <v>125</v>
       </c>
       <c r="E82" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F82">
         <v>3.0</v>
       </c>
       <c r="G82" t="s">
+        <v>214</v>
+      </c>
+      <c r="H82" t="s">
         <v>215</v>
       </c>
-      <c r="H82" t="s">
+      <c r="I82" t="s">
         <v>216</v>
-      </c>
-      <c r="I82" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B83" t="s">
         <v>150</v>
@@ -4240,65 +4210,65 @@
         <v>2.0</v>
       </c>
       <c r="G83" t="s">
+        <v>238</v>
+      </c>
+      <c r="H83" t="s">
         <v>239</v>
       </c>
-      <c r="H83" t="s">
-        <v>240</v>
-      </c>
       <c r="I83" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
+        <v>226</v>
+      </c>
+      <c r="B84" t="s">
         <v>227</v>
-      </c>
-      <c r="B84" t="s">
-        <v>228</v>
       </c>
       <c r="C84" t="s">
         <v>111</v>
       </c>
       <c r="E84" t="s">
+        <v>213</v>
+      </c>
+      <c r="F84">
+        <v>1.0</v>
+      </c>
+      <c r="G84" t="s">
         <v>214</v>
       </c>
-      <c r="F84">
-        <v>1.0</v>
-      </c>
-      <c r="G84" t="s">
-        <v>215</v>
-      </c>
       <c r="H84" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I84" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
+        <v>226</v>
+      </c>
+      <c r="B85" t="s">
         <v>227</v>
-      </c>
-      <c r="B85" t="s">
-        <v>228</v>
       </c>
       <c r="C85" t="s">
         <v>140</v>
       </c>
       <c r="E85" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F85">
         <v>5.0</v>
       </c>
       <c r="G85" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
       </c>
       <c r="I85" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -4318,10 +4288,10 @@
         <v>3.0</v>
       </c>
       <c r="G86" t="s">
+        <v>242</v>
+      </c>
+      <c r="H86" t="s">
         <v>243</v>
-      </c>
-      <c r="H86" t="s">
-        <v>244</v>
       </c>
       <c r="I86" t="s">
         <v>137</v>
@@ -4329,77 +4299,77 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
+        <v>244</v>
+      </c>
+      <c r="B87" t="s">
         <v>245</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>246</v>
       </c>
-      <c r="C87" t="s">
+      <c r="E87" t="s">
         <v>247</v>
-      </c>
-      <c r="E87" t="s">
-        <v>248</v>
       </c>
       <c r="F87">
         <v>3.0</v>
       </c>
       <c r="G87" t="s">
+        <v>248</v>
+      </c>
+      <c r="H87" t="s">
         <v>249</v>
       </c>
-      <c r="H87" t="s">
+      <c r="I87" t="s">
         <v>250</v>
-      </c>
-      <c r="I87" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
+        <v>251</v>
+      </c>
+      <c r="B88" t="s">
         <v>252</v>
       </c>
-      <c r="B88" t="s">
-        <v>253</v>
-      </c>
       <c r="E88" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F88">
         <v>2.0</v>
       </c>
       <c r="G88" t="s">
+        <v>253</v>
+      </c>
+      <c r="H88" t="s">
         <v>254</v>
       </c>
-      <c r="H88" t="s">
+      <c r="I88" t="s">
         <v>255</v>
-      </c>
-      <c r="I88" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
+        <v>256</v>
+      </c>
+      <c r="B89" t="s">
         <v>257</v>
-      </c>
-      <c r="B89" t="s">
-        <v>258</v>
       </c>
       <c r="C89" t="s">
         <v>158</v>
       </c>
       <c r="E89" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F89">
         <v>5.0</v>
       </c>
       <c r="G89" t="s">
+        <v>259</v>
+      </c>
+      <c r="H89" t="s">
         <v>260</v>
       </c>
-      <c r="H89" t="s">
+      <c r="I89" t="s">
         <v>261</v>
-      </c>
-      <c r="I89" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -4419,10 +4389,10 @@
         <v>6.0</v>
       </c>
       <c r="G90" t="s">
+        <v>262</v>
+      </c>
+      <c r="H90" t="s">
         <v>263</v>
-      </c>
-      <c r="H90" t="s">
-        <v>264</v>
       </c>
       <c r="I90" t="s">
         <v>163</v>
@@ -4430,10 +4400,10 @@
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
+        <v>264</v>
+      </c>
+      <c r="B91" t="s">
         <v>265</v>
-      </c>
-      <c r="B91" t="s">
-        <v>266</v>
       </c>
       <c r="E91" t="s">
         <v>188</v>
@@ -4448,33 +4418,33 @@
         <v>67</v>
       </c>
       <c r="I91" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
+        <v>266</v>
+      </c>
+      <c r="B92" t="s">
         <v>267</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>268</v>
       </c>
-      <c r="C92" t="s">
+      <c r="E92" t="s">
         <v>269</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92">
+        <v>1.0</v>
+      </c>
+      <c r="G92" t="s">
+        <v>253</v>
+      </c>
+      <c r="H92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I92" t="s">
         <v>270</v>
-      </c>
-      <c r="F92">
-        <v>1.0</v>
-      </c>
-      <c r="G92" t="s">
-        <v>254</v>
-      </c>
-      <c r="H92" t="s">
-        <v>254</v>
-      </c>
-      <c r="I92" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -4494,10 +4464,10 @@
         <v>1.0</v>
       </c>
       <c r="G93" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H93" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I93" t="s">
         <v>132</v>
@@ -4520,21 +4490,21 @@
         <v>4.0</v>
       </c>
       <c r="G94" t="s">
+        <v>272</v>
+      </c>
+      <c r="H94" t="s">
         <v>273</v>
       </c>
-      <c r="H94" t="s">
+      <c r="I94" t="s">
         <v>274</v>
-      </c>
-      <c r="I94" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
+        <v>275</v>
+      </c>
+      <c r="B95" t="s">
         <v>276</v>
-      </c>
-      <c r="B95" t="s">
-        <v>277</v>
       </c>
       <c r="E95" t="s">
         <v>188</v>
@@ -4549,53 +4519,53 @@
         <v>67</v>
       </c>
       <c r="I95" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
+        <v>277</v>
+      </c>
+      <c r="B96" t="s">
         <v>278</v>
       </c>
-      <c r="B96" t="s">
-        <v>279</v>
-      </c>
       <c r="E96" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F96">
         <v>2.0</v>
       </c>
       <c r="G96" t="s">
+        <v>253</v>
+      </c>
+      <c r="H96" t="s">
         <v>254</v>
       </c>
-      <c r="H96" t="s">
+      <c r="I96" t="s">
         <v>255</v>
-      </c>
-      <c r="I96" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" t="s">
+        <v>279</v>
+      </c>
+      <c r="B97" t="s">
         <v>280</v>
       </c>
-      <c r="B97" t="s">
+      <c r="E97" t="s">
+        <v>205</v>
+      </c>
+      <c r="F97">
+        <v>1.0</v>
+      </c>
+      <c r="G97" t="s">
+        <v>253</v>
+      </c>
+      <c r="H97" t="s">
+        <v>253</v>
+      </c>
+      <c r="I97" t="s">
         <v>281</v>
-      </c>
-      <c r="E97" t="s">
-        <v>206</v>
-      </c>
-      <c r="F97">
-        <v>1.0</v>
-      </c>
-      <c r="G97" t="s">
-        <v>254</v>
-      </c>
-      <c r="H97" t="s">
-        <v>254</v>
-      </c>
-      <c r="I97" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -4615,10 +4585,10 @@
         <v>2.0</v>
       </c>
       <c r="G98" t="s">
+        <v>282</v>
+      </c>
+      <c r="H98" t="s">
         <v>283</v>
-      </c>
-      <c r="H98" t="s">
-        <v>284</v>
       </c>
       <c r="I98" t="s">
         <v>174</v>
@@ -4626,33 +4596,33 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" t="s">
+        <v>284</v>
+      </c>
+      <c r="B99" t="s">
         <v>285</v>
       </c>
-      <c r="B99" t="s">
-        <v>286</v>
-      </c>
       <c r="E99" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F99">
         <v>2.0</v>
       </c>
       <c r="G99" t="s">
+        <v>253</v>
+      </c>
+      <c r="H99" t="s">
         <v>254</v>
       </c>
-      <c r="H99" t="s">
+      <c r="I99" t="s">
         <v>255</v>
-      </c>
-      <c r="I99" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
+        <v>286</v>
+      </c>
+      <c r="B100" t="s">
         <v>287</v>
-      </c>
-      <c r="B100" t="s">
-        <v>288</v>
       </c>
       <c r="E100" t="s">
         <v>188</v>
@@ -4661,59 +4631,59 @@
         <v>3.0</v>
       </c>
       <c r="G100" t="s">
+        <v>288</v>
+      </c>
+      <c r="H100" t="s">
         <v>289</v>
       </c>
-      <c r="H100" t="s">
+      <c r="I100" t="s">
         <v>290</v>
-      </c>
-      <c r="I100" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" t="s">
+        <v>291</v>
+      </c>
+      <c r="B101" t="s">
         <v>292</v>
       </c>
-      <c r="B101" t="s">
+      <c r="E101" t="s">
+        <v>188</v>
+      </c>
+      <c r="F101">
+        <v>1.0</v>
+      </c>
+      <c r="G101" t="s">
+        <v>67</v>
+      </c>
+      <c r="H101" t="s">
+        <v>67</v>
+      </c>
+      <c r="I101" t="s">
         <v>293</v>
-      </c>
-      <c r="E101" t="s">
-        <v>294</v>
-      </c>
-      <c r="F101">
-        <v>1.0</v>
-      </c>
-      <c r="G101" t="s">
-        <v>207</v>
-      </c>
-      <c r="H101" t="s">
-        <v>207</v>
-      </c>
-      <c r="I101" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" t="s">
+        <v>294</v>
+      </c>
+      <c r="B102" t="s">
+        <v>295</v>
+      </c>
+      <c r="E102" t="s">
         <v>296</v>
       </c>
-      <c r="B102" t="s">
+      <c r="F102">
+        <v>1.0</v>
+      </c>
+      <c r="G102" t="s">
+        <v>206</v>
+      </c>
+      <c r="H102" t="s">
+        <v>206</v>
+      </c>
+      <c r="I102" t="s">
         <v>297</v>
-      </c>
-      <c r="E102" t="s">
-        <v>188</v>
-      </c>
-      <c r="F102">
-        <v>2.0</v>
-      </c>
-      <c r="G102" t="s">
-        <v>67</v>
-      </c>
-      <c r="H102" t="s">
-        <v>67</v>
-      </c>
-      <c r="I102" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -4724,59 +4694,59 @@
         <v>299</v>
       </c>
       <c r="E103" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F103">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G103" t="s">
-        <v>207</v>
+        <v>301</v>
       </c>
       <c r="H103" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I103" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B104" t="s">
-        <v>303</v>
+        <v>305</v>
+      </c>
+      <c r="C104" t="s">
+        <v>158</v>
       </c>
       <c r="E104" t="s">
-        <v>304</v>
+        <v>223</v>
       </c>
       <c r="F104">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G104" t="s">
-        <v>305</v>
+        <v>67</v>
       </c>
       <c r="H104" t="s">
-        <v>306</v>
+        <v>67</v>
       </c>
       <c r="I104" t="s">
-        <v>307</v>
+        <v>225</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B105" t="s">
-        <v>309</v>
-      </c>
-      <c r="C105" t="s">
-        <v>158</v>
+        <v>307</v>
       </c>
       <c r="E105" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="F105">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G105" t="s">
         <v>67</v>
@@ -4785,30 +4755,33 @@
         <v>67</v>
       </c>
       <c r="I105" t="s">
-        <v>226</v>
+        <v>191</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
+        <v>308</v>
+      </c>
+      <c r="B106" t="s">
+        <v>309</v>
+      </c>
+      <c r="C106" t="s">
         <v>310</v>
       </c>
-      <c r="B106" t="s">
+      <c r="E106" t="s">
+        <v>247</v>
+      </c>
+      <c r="F106">
+        <v>1.0</v>
+      </c>
+      <c r="G106" t="s">
         <v>311</v>
       </c>
-      <c r="E106" t="s">
-        <v>188</v>
-      </c>
-      <c r="F106">
-        <v>2.0</v>
-      </c>
-      <c r="G106" t="s">
-        <v>67</v>
-      </c>
       <c r="H106" t="s">
-        <v>67</v>
+        <v>311</v>
       </c>
       <c r="I106" t="s">
-        <v>191</v>
+        <v>270</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -4818,46 +4791,49 @@
       <c r="B107" t="s">
         <v>313</v>
       </c>
+      <c r="C107">
+        <v>28</v>
+      </c>
       <c r="E107" t="s">
-        <v>188</v>
+        <v>314</v>
       </c>
       <c r="F107">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G107" t="s">
-        <v>314</v>
+        <v>67</v>
       </c>
       <c r="H107" t="s">
-        <v>314</v>
+        <v>67</v>
       </c>
       <c r="I107" t="s">
-        <v>208</v>
+        <v>315</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B108" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C108" t="s">
-        <v>317</v>
+        <v>246</v>
       </c>
       <c r="E108" t="s">
-        <v>248</v>
+        <v>318</v>
       </c>
       <c r="F108">
         <v>1.0</v>
       </c>
       <c r="G108" t="s">
-        <v>318</v>
+        <v>253</v>
       </c>
       <c r="H108" t="s">
-        <v>318</v>
+        <v>253</v>
       </c>
       <c r="I108" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -4867,225 +4843,219 @@
       <c r="B109" t="s">
         <v>320</v>
       </c>
-      <c r="C109">
-        <v>28</v>
-      </c>
       <c r="E109" t="s">
+        <v>188</v>
+      </c>
+      <c r="F109">
+        <v>2.0</v>
+      </c>
+      <c r="G109" t="s">
+        <v>206</v>
+      </c>
+      <c r="H109" t="s">
         <v>321</v>
       </c>
-      <c r="F109">
-        <v>4.0</v>
-      </c>
-      <c r="G109" t="s">
-        <v>67</v>
-      </c>
-      <c r="H109" t="s">
-        <v>67</v>
-      </c>
       <c r="I109" t="s">
-        <v>322</v>
+        <v>191</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" t="s">
+        <v>322</v>
+      </c>
+      <c r="B110" t="s">
         <v>323</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
+        <v>246</v>
+      </c>
+      <c r="E110" t="s">
         <v>324</v>
       </c>
-      <c r="C110" t="s">
-        <v>247</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="F110">
+        <v>8.0</v>
+      </c>
+      <c r="G110" t="s">
         <v>325</v>
       </c>
-      <c r="F110">
-        <v>1.0</v>
-      </c>
-      <c r="G110" t="s">
-        <v>254</v>
-      </c>
       <c r="H110" t="s">
-        <v>254</v>
+        <v>326</v>
       </c>
       <c r="I110" t="s">
-        <v>274</v>
+        <v>327</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B111" t="s">
-        <v>327</v>
+        <v>329</v>
+      </c>
+      <c r="C111" t="s">
+        <v>246</v>
       </c>
       <c r="E111" t="s">
-        <v>188</v>
+        <v>324</v>
       </c>
       <c r="F111">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G111" t="s">
-        <v>207</v>
+        <v>330</v>
       </c>
       <c r="H111" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="I111" t="s">
-        <v>191</v>
+        <v>332</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>328</v>
+        <v>266</v>
       </c>
       <c r="B112" t="s">
-        <v>329</v>
+        <v>267</v>
       </c>
       <c r="C112" t="s">
-        <v>247</v>
+        <v>333</v>
       </c>
       <c r="E112" t="s">
-        <v>330</v>
+        <v>269</v>
       </c>
       <c r="F112">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G112" t="s">
-        <v>331</v>
+        <v>253</v>
       </c>
       <c r="H112" t="s">
-        <v>332</v>
+        <v>254</v>
       </c>
       <c r="I112" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B113" t="s">
-        <v>335</v>
-      </c>
-      <c r="C113" t="s">
-        <v>247</v>
+        <v>336</v>
       </c>
       <c r="E113" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="F113">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="G113" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H113" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I113" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="B114" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="C114" t="s">
-        <v>339</v>
+        <v>148</v>
       </c>
       <c r="E114" t="s">
-        <v>270</v>
+        <v>223</v>
       </c>
       <c r="F114">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G114" t="s">
-        <v>254</v>
+        <v>67</v>
       </c>
       <c r="H114" t="s">
-        <v>255</v>
+        <v>67</v>
       </c>
       <c r="I114" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>341</v>
+        <v>266</v>
       </c>
       <c r="B115" t="s">
+        <v>267</v>
+      </c>
+      <c r="C115" t="s">
+        <v>246</v>
+      </c>
+      <c r="E115" t="s">
+        <v>269</v>
+      </c>
+      <c r="F115">
+        <v>4.0</v>
+      </c>
+      <c r="G115" t="s">
         <v>342</v>
       </c>
-      <c r="E115" t="s">
+      <c r="H115" t="s">
         <v>343</v>
       </c>
-      <c r="F115">
-        <v>3.0</v>
-      </c>
-      <c r="G115" t="s">
+      <c r="I115" t="s">
         <v>344</v>
-      </c>
-      <c r="H115" t="s">
-        <v>345</v>
-      </c>
-      <c r="I115" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>308</v>
+        <v>345</v>
       </c>
       <c r="B116" t="s">
-        <v>309</v>
-      </c>
-      <c r="C116" t="s">
-        <v>148</v>
+        <v>346</v>
       </c>
       <c r="E116" t="s">
-        <v>224</v>
+        <v>347</v>
       </c>
       <c r="F116">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G116" t="s">
-        <v>67</v>
+        <v>253</v>
       </c>
       <c r="H116" t="s">
-        <v>67</v>
+        <v>253</v>
       </c>
       <c r="I116" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>267</v>
+        <v>349</v>
       </c>
       <c r="B117" t="s">
-        <v>268</v>
-      </c>
-      <c r="C117" t="s">
-        <v>247</v>
+        <v>350</v>
       </c>
       <c r="E117" t="s">
-        <v>270</v>
+        <v>347</v>
       </c>
       <c r="F117">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G117" t="s">
+        <v>253</v>
+      </c>
+      <c r="H117" t="s">
+        <v>253</v>
+      </c>
+      <c r="I117" t="s">
         <v>348</v>
-      </c>
-      <c r="H117" t="s">
-        <v>349</v>
-      </c>
-      <c r="I117" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -5095,225 +5065,228 @@
       <c r="B118" t="s">
         <v>352</v>
       </c>
+      <c r="C118" t="s">
+        <v>246</v>
+      </c>
       <c r="E118" t="s">
         <v>353</v>
       </c>
       <c r="F118">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G118" t="s">
-        <v>254</v>
+        <v>354</v>
       </c>
       <c r="H118" t="s">
-        <v>254</v>
+        <v>355</v>
       </c>
       <c r="I118" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B119" t="s">
-        <v>356</v>
+        <v>358</v>
+      </c>
+      <c r="C119" t="s">
+        <v>158</v>
       </c>
       <c r="E119" t="s">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="F119">
         <v>1.0</v>
       </c>
       <c r="G119" t="s">
-        <v>254</v>
+        <v>67</v>
       </c>
       <c r="H119" t="s">
-        <v>254</v>
+        <v>67</v>
       </c>
       <c r="I119" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>357</v>
+        <v>266</v>
       </c>
       <c r="B120" t="s">
-        <v>358</v>
+        <v>267</v>
       </c>
       <c r="C120" t="s">
-        <v>247</v>
+        <v>360</v>
       </c>
       <c r="E120" t="s">
-        <v>359</v>
+        <v>269</v>
       </c>
       <c r="F120">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G120" t="s">
-        <v>360</v>
+        <v>253</v>
       </c>
       <c r="H120" t="s">
-        <v>361</v>
+        <v>254</v>
       </c>
       <c r="I120" t="s">
-        <v>362</v>
+        <v>334</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="B121" t="s">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="C121" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="E121" t="s">
-        <v>270</v>
+        <v>324</v>
       </c>
       <c r="F121">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="G121" t="s">
-        <v>254</v>
+        <v>325</v>
       </c>
       <c r="H121" t="s">
-        <v>255</v>
+        <v>326</v>
       </c>
       <c r="I121" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>365</v>
+        <v>226</v>
       </c>
       <c r="B122" t="s">
-        <v>366</v>
+        <v>227</v>
       </c>
       <c r="C122" t="s">
         <v>158</v>
       </c>
       <c r="E122" t="s">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="F122">
         <v>1.0</v>
       </c>
       <c r="G122" t="s">
-        <v>67</v>
+        <v>361</v>
       </c>
       <c r="H122" t="s">
-        <v>67</v>
+        <v>361</v>
       </c>
       <c r="I122" t="s">
-        <v>367</v>
+        <v>240</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="B123" t="s">
-        <v>268</v>
+        <v>363</v>
       </c>
       <c r="C123" t="s">
-        <v>368</v>
+        <v>148</v>
       </c>
       <c r="E123" t="s">
-        <v>270</v>
+        <v>364</v>
       </c>
       <c r="F123">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G123" t="s">
-        <v>254</v>
+        <v>67</v>
       </c>
       <c r="H123" t="s">
-        <v>255</v>
+        <v>67</v>
       </c>
       <c r="I123" t="s">
-        <v>340</v>
+        <v>184</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>328</v>
+        <v>365</v>
       </c>
       <c r="B124" t="s">
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="C124" t="s">
-        <v>339</v>
+        <v>111</v>
       </c>
       <c r="E124" t="s">
-        <v>330</v>
+        <v>112</v>
       </c>
       <c r="F124">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G124" t="s">
-        <v>331</v>
+        <v>67</v>
       </c>
       <c r="H124" t="s">
-        <v>332</v>
+        <v>67</v>
       </c>
       <c r="I124" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>227</v>
+        <v>367</v>
       </c>
       <c r="B125" t="s">
-        <v>228</v>
-      </c>
-      <c r="C125" t="s">
-        <v>158</v>
+        <v>368</v>
       </c>
       <c r="E125" t="s">
-        <v>214</v>
+        <v>369</v>
       </c>
       <c r="F125">
         <v>1.0</v>
       </c>
       <c r="G125" t="s">
-        <v>369</v>
+        <v>67</v>
       </c>
       <c r="H125" t="s">
-        <v>369</v>
+        <v>67</v>
       </c>
       <c r="I125" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B126" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C126" t="s">
-        <v>148</v>
+        <v>360</v>
       </c>
       <c r="E126" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="F126">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G126" t="s">
-        <v>67</v>
+        <v>354</v>
       </c>
       <c r="H126" t="s">
-        <v>67</v>
+        <v>355</v>
       </c>
       <c r="I126" t="s">
-        <v>184</v>
+        <v>356</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -5324,299 +5297,302 @@
         <v>374</v>
       </c>
       <c r="C127" t="s">
-        <v>111</v>
+        <v>246</v>
       </c>
       <c r="E127" t="s">
-        <v>112</v>
+        <v>324</v>
       </c>
       <c r="F127">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G127" t="s">
-        <v>67</v>
+        <v>375</v>
       </c>
       <c r="H127" t="s">
-        <v>67</v>
+        <v>376</v>
       </c>
       <c r="I127" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B128" t="s">
-        <v>376</v>
+        <v>379</v>
+      </c>
+      <c r="C128" t="s">
+        <v>310</v>
       </c>
       <c r="E128" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F128">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G128" t="s">
-        <v>67</v>
+        <v>354</v>
       </c>
       <c r="H128" t="s">
-        <v>67</v>
+        <v>381</v>
       </c>
       <c r="I128" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="B129" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="C129" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="E129" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="F129">
         <v>3.0</v>
       </c>
       <c r="G129" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="H129" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="I129" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B130" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C130" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E130" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F130">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G130" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H130" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I130" t="s">
-        <v>385</v>
+        <v>327</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" t="s">
+        <v>322</v>
+      </c>
+      <c r="B131" t="s">
+        <v>323</v>
+      </c>
+      <c r="C131" t="s">
+        <v>360</v>
+      </c>
+      <c r="E131" t="s">
+        <v>324</v>
+      </c>
+      <c r="F131">
+        <v>4.0</v>
+      </c>
+      <c r="G131" t="s">
+        <v>387</v>
+      </c>
+      <c r="H131" t="s">
         <v>386</v>
       </c>
-      <c r="B131" t="s">
-        <v>387</v>
-      </c>
-      <c r="C131" t="s">
-        <v>317</v>
-      </c>
-      <c r="E131" t="s">
+      <c r="I131" t="s">
         <v>388</v>
-      </c>
-      <c r="F131">
-        <v>7.0</v>
-      </c>
-      <c r="G131" t="s">
-        <v>360</v>
-      </c>
-      <c r="H131" t="s">
-        <v>389</v>
-      </c>
-      <c r="I131" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="B132" t="s">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="C132" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="E132" t="s">
-        <v>359</v>
+        <v>324</v>
       </c>
       <c r="F132">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G132" t="s">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="H132" t="s">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="I132" t="s">
-        <v>362</v>
+        <v>391</v>
       </c>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B133" t="s">
-        <v>392</v>
-      </c>
-      <c r="C133" t="s">
-        <v>247</v>
+        <v>393</v>
       </c>
       <c r="E133" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
       <c r="F133">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G133" t="s">
-        <v>393</v>
+        <v>67</v>
       </c>
       <c r="H133" t="s">
-        <v>394</v>
+        <v>67</v>
       </c>
       <c r="I133" t="s">
-        <v>333</v>
+        <v>370</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="B134" t="s">
-        <v>329</v>
+        <v>395</v>
       </c>
       <c r="C134" t="s">
-        <v>368</v>
+        <v>246</v>
       </c>
       <c r="E134" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F134">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G134" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H134" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="I134" t="s">
-        <v>396</v>
+        <v>332</v>
       </c>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" t="s">
-        <v>334</v>
+        <v>378</v>
       </c>
       <c r="B135" t="s">
-        <v>335</v>
+        <v>379</v>
       </c>
       <c r="C135" t="s">
-        <v>339</v>
+        <v>246</v>
       </c>
       <c r="E135" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="F135">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G135" t="s">
+        <v>354</v>
+      </c>
+      <c r="H135" t="s">
         <v>397</v>
       </c>
-      <c r="H135" t="s">
+      <c r="I135" t="s">
         <v>398</v>
-      </c>
-      <c r="I135" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="B136" t="s">
-        <v>401</v>
+        <v>329</v>
+      </c>
+      <c r="C136" t="s">
+        <v>310</v>
       </c>
       <c r="E136" t="s">
-        <v>377</v>
+        <v>324</v>
       </c>
       <c r="F136">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G136" t="s">
-        <v>67</v>
+        <v>354</v>
       </c>
       <c r="H136" t="s">
-        <v>67</v>
+        <v>390</v>
       </c>
       <c r="I136" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" t="s">
+        <v>400</v>
+      </c>
+      <c r="B137" t="s">
+        <v>401</v>
+      </c>
+      <c r="C137" t="s">
+        <v>333</v>
+      </c>
+      <c r="E137" t="s">
+        <v>353</v>
+      </c>
+      <c r="F137">
+        <v>2.0</v>
+      </c>
+      <c r="G137" t="s">
+        <v>354</v>
+      </c>
+      <c r="H137" t="s">
         <v>402</v>
       </c>
-      <c r="B137" t="s">
-        <v>403</v>
-      </c>
-      <c r="C137" t="s">
-        <v>247</v>
-      </c>
-      <c r="E137" t="s">
-        <v>330</v>
-      </c>
-      <c r="F137">
-        <v>7.0</v>
-      </c>
-      <c r="G137" t="s">
-        <v>404</v>
-      </c>
-      <c r="H137" t="s">
-        <v>394</v>
-      </c>
       <c r="I137" t="s">
-        <v>338</v>
+        <v>255</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" t="s">
+        <v>403</v>
+      </c>
+      <c r="B138" t="s">
+        <v>404</v>
+      </c>
+      <c r="C138" t="s">
+        <v>246</v>
+      </c>
+      <c r="E138" t="s">
+        <v>324</v>
+      </c>
+      <c r="F138">
+        <v>9.0</v>
+      </c>
+      <c r="G138" t="s">
+        <v>405</v>
+      </c>
+      <c r="H138" t="s">
         <v>386</v>
-      </c>
-      <c r="B138" t="s">
-        <v>387</v>
-      </c>
-      <c r="C138" t="s">
-        <v>247</v>
-      </c>
-      <c r="E138" t="s">
-        <v>388</v>
-      </c>
-      <c r="F138">
-        <v>11.0</v>
-      </c>
-      <c r="G138" t="s">
-        <v>360</v>
-      </c>
-      <c r="H138" t="s">
-        <v>405</v>
       </c>
       <c r="I138" t="s">
         <v>406</v>
@@ -5624,987 +5600,987 @@
     </row>
     <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>334</v>
+        <v>407</v>
       </c>
       <c r="B139" t="s">
-        <v>335</v>
+        <v>408</v>
       </c>
       <c r="C139" t="s">
-        <v>317</v>
+        <v>246</v>
       </c>
       <c r="E139" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F139">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G139" t="s">
-        <v>360</v>
+        <v>131</v>
       </c>
       <c r="H139" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
       <c r="I139" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>408</v>
+        <v>378</v>
       </c>
       <c r="B140" t="s">
-        <v>409</v>
+        <v>379</v>
       </c>
       <c r="C140" t="s">
-        <v>339</v>
+        <v>268</v>
       </c>
       <c r="E140" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="F140">
         <v>2.0</v>
       </c>
       <c r="G140" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="H140" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="I140" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>411</v>
+        <v>328</v>
       </c>
       <c r="B141" t="s">
-        <v>412</v>
+        <v>329</v>
       </c>
       <c r="C141" t="s">
-        <v>247</v>
+        <v>360</v>
       </c>
       <c r="E141" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F141">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="G141" t="s">
-        <v>413</v>
+        <v>354</v>
       </c>
       <c r="H141" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="I141" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="B142" t="s">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="C142" t="s">
-        <v>247</v>
+        <v>310</v>
       </c>
       <c r="E142" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F142">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G142" t="s">
-        <v>131</v>
+        <v>325</v>
       </c>
       <c r="H142" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="I142" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
     </row>
     <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="B143" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="C143" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="E143" t="s">
-        <v>388</v>
+        <v>324</v>
       </c>
       <c r="F143">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G143" t="s">
-        <v>360</v>
+        <v>411</v>
       </c>
       <c r="H143" t="s">
-        <v>410</v>
+        <v>249</v>
       </c>
       <c r="I143" t="s">
-        <v>236</v>
+        <v>412</v>
       </c>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>334</v>
+        <v>394</v>
       </c>
       <c r="B144" t="s">
-        <v>335</v>
+        <v>395</v>
       </c>
       <c r="C144" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="E144" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F144">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G144" t="s">
-        <v>360</v>
+        <v>413</v>
       </c>
       <c r="H144" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="I144" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="B145" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="C145" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="E145" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F145">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G145" t="s">
-        <v>331</v>
+        <v>414</v>
       </c>
       <c r="H145" t="s">
-        <v>418</v>
+        <v>386</v>
       </c>
       <c r="I145" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="B146" t="s">
+        <v>404</v>
+      </c>
+      <c r="C146" t="s">
+        <v>333</v>
+      </c>
+      <c r="E146" t="s">
+        <v>324</v>
+      </c>
+      <c r="F146">
+        <v>8.0</v>
+      </c>
+      <c r="G146" t="s">
+        <v>385</v>
+      </c>
+      <c r="H146" t="s">
+        <v>386</v>
+      </c>
+      <c r="I146" t="s">
         <v>416</v>
-      </c>
-      <c r="C146" t="s">
-        <v>339</v>
-      </c>
-      <c r="E146" t="s">
-        <v>330</v>
-      </c>
-      <c r="F146">
-        <v>4.0</v>
-      </c>
-      <c r="G146" t="s">
-        <v>419</v>
-      </c>
-      <c r="H146" t="s">
-        <v>250</v>
-      </c>
-      <c r="I146" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="B147" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="C147" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="E147" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="F147">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G147" t="s">
-        <v>421</v>
+        <v>354</v>
       </c>
       <c r="H147" t="s">
-        <v>418</v>
+        <v>354</v>
       </c>
       <c r="I147" t="s">
-        <v>399</v>
+        <v>173</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="B148" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="C148" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="E148" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="F148">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="G148" t="s">
-        <v>422</v>
+        <v>354</v>
       </c>
       <c r="H148" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="I148" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="B149" t="s">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="C149" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="E149" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="F149">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G149" t="s">
-        <v>393</v>
+        <v>354</v>
       </c>
       <c r="H149" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="I149" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>425</v>
+        <v>373</v>
       </c>
       <c r="B150" t="s">
-        <v>426</v>
+        <v>374</v>
       </c>
       <c r="C150" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="E150" t="s">
-        <v>388</v>
+        <v>324</v>
       </c>
       <c r="F150">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G150" t="s">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="H150" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="I150" t="s">
-        <v>173</v>
+        <v>421</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="B151" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="C151" t="s">
-        <v>368</v>
+        <v>246</v>
       </c>
       <c r="E151" t="s">
-        <v>388</v>
+        <v>324</v>
       </c>
       <c r="F151">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G151" t="s">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="H151" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="I151" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
       <c r="B152" t="s">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="C152" t="s">
-        <v>317</v>
+        <v>360</v>
       </c>
       <c r="E152" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="F152">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="H152" t="s">
-        <v>410</v>
+        <v>354</v>
       </c>
       <c r="I152" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>381</v>
+        <v>425</v>
       </c>
       <c r="B153" t="s">
-        <v>382</v>
+        <v>426</v>
       </c>
       <c r="C153" t="s">
-        <v>339</v>
+        <v>246</v>
       </c>
       <c r="E153" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F153">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G153" t="s">
-        <v>410</v>
+        <v>197</v>
       </c>
       <c r="H153" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="I153" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" t="s">
+        <v>428</v>
+      </c>
+      <c r="B154" t="s">
+        <v>429</v>
+      </c>
+      <c r="C154" t="s">
+        <v>158</v>
+      </c>
+      <c r="E154" t="s">
         <v>430</v>
-      </c>
-      <c r="B154" t="s">
-        <v>431</v>
-      </c>
-      <c r="C154" t="s">
-        <v>247</v>
-      </c>
-      <c r="E154" t="s">
-        <v>330</v>
       </c>
       <c r="F154">
         <v>2.0</v>
       </c>
       <c r="G154" t="s">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="H154" t="s">
-        <v>398</v>
+        <v>67</v>
       </c>
       <c r="I154" t="s">
-        <v>429</v>
+        <v>240</v>
       </c>
     </row>
     <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>357</v>
+        <v>431</v>
       </c>
       <c r="B155" t="s">
-        <v>358</v>
+        <v>432</v>
       </c>
       <c r="C155" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="E155" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="F155">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G155" t="s">
-        <v>360</v>
+        <v>253</v>
       </c>
       <c r="H155" t="s">
-        <v>360</v>
+        <v>433</v>
       </c>
       <c r="I155" t="s">
-        <v>432</v>
+        <v>231</v>
       </c>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
       <c r="B156" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="C156" t="s">
-        <v>247</v>
+        <v>310</v>
       </c>
       <c r="E156" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F156">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G156" t="s">
-        <v>197</v>
+        <v>402</v>
       </c>
       <c r="H156" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="I156" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>436</v>
+        <v>407</v>
       </c>
       <c r="B157" t="s">
-        <v>437</v>
+        <v>408</v>
       </c>
       <c r="C157" t="s">
-        <v>158</v>
+        <v>360</v>
       </c>
       <c r="E157" t="s">
-        <v>438</v>
+        <v>324</v>
       </c>
       <c r="F157">
         <v>2.0</v>
       </c>
       <c r="G157" t="s">
-        <v>67</v>
+        <v>402</v>
       </c>
       <c r="H157" t="s">
-        <v>67</v>
+        <v>390</v>
       </c>
       <c r="I157" t="s">
-        <v>241</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B158" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C158" t="s">
-        <v>368</v>
+        <v>148</v>
       </c>
       <c r="E158" t="s">
-        <v>359</v>
+        <v>436</v>
       </c>
       <c r="F158">
         <v>3.0</v>
       </c>
       <c r="G158" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="H158" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="I158" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="B159" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="C159" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="E159" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F159">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G159" t="s">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="H159" t="s">
-        <v>398</v>
+        <v>67</v>
       </c>
       <c r="I159" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
     </row>
     <row r="160" spans="1:9">
       <c r="A160" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B160" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C160" t="s">
-        <v>368</v>
+        <v>310</v>
       </c>
       <c r="E160" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="F160">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G160" t="s">
-        <v>410</v>
+        <v>354</v>
       </c>
       <c r="H160" t="s">
-        <v>398</v>
+        <v>354</v>
       </c>
       <c r="I160" t="s">
-        <v>429</v>
+        <v>173</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
+        <v>441</v>
+      </c>
+      <c r="B161" t="s">
         <v>442</v>
-      </c>
-      <c r="B161" t="s">
-        <v>443</v>
       </c>
       <c r="C161" t="s">
         <v>148</v>
       </c>
       <c r="E161" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="F161">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G161" t="s">
-        <v>273</v>
+        <v>67</v>
       </c>
       <c r="H161" t="s">
-        <v>445</v>
+        <v>67</v>
       </c>
       <c r="I161" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
     </row>
     <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>446</v>
+        <v>400</v>
       </c>
       <c r="B162" t="s">
-        <v>447</v>
+        <v>401</v>
       </c>
       <c r="C162" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="E162" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="F162">
         <v>1.0</v>
       </c>
       <c r="G162" t="s">
-        <v>67</v>
+        <v>354</v>
       </c>
       <c r="H162" t="s">
-        <v>67</v>
+        <v>354</v>
       </c>
       <c r="I162" t="s">
-        <v>448</v>
+        <v>281</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="B163" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="C163" t="s">
-        <v>317</v>
+        <v>246</v>
       </c>
       <c r="E163" t="s">
+        <v>324</v>
+      </c>
+      <c r="F163">
+        <v>4.0</v>
+      </c>
+      <c r="G163" t="s">
+        <v>445</v>
+      </c>
+      <c r="H163" t="s">
+        <v>446</v>
+      </c>
+      <c r="I163" t="s">
         <v>388</v>
-      </c>
-      <c r="F163">
-        <v>1.0</v>
-      </c>
-      <c r="G163" t="s">
-        <v>360</v>
-      </c>
-      <c r="H163" t="s">
-        <v>360</v>
-      </c>
-      <c r="I163" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>449</v>
+        <v>394</v>
       </c>
       <c r="B164" t="s">
-        <v>450</v>
+        <v>395</v>
       </c>
       <c r="C164" t="s">
-        <v>148</v>
+        <v>360</v>
       </c>
       <c r="E164" t="s">
-        <v>444</v>
+        <v>324</v>
       </c>
       <c r="F164">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G164" t="s">
-        <v>67</v>
+        <v>413</v>
       </c>
       <c r="H164" t="s">
-        <v>67</v>
+        <v>410</v>
       </c>
       <c r="I164" t="s">
-        <v>256</v>
+        <v>391</v>
       </c>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="B165" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="C165" t="s">
-        <v>368</v>
+        <v>310</v>
       </c>
       <c r="E165" t="s">
-        <v>359</v>
+        <v>324</v>
       </c>
       <c r="F165">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G165" t="s">
-        <v>360</v>
+        <v>67</v>
       </c>
       <c r="H165" t="s">
-        <v>360</v>
+        <v>67</v>
       </c>
       <c r="I165" t="s">
-        <v>282</v>
+        <v>388</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>451</v>
+        <v>378</v>
       </c>
       <c r="B166" t="s">
-        <v>452</v>
+        <v>379</v>
       </c>
       <c r="C166" t="s">
-        <v>247</v>
+        <v>333</v>
       </c>
       <c r="E166" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="F166">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G166" t="s">
-        <v>453</v>
+        <v>354</v>
       </c>
       <c r="H166" t="s">
-        <v>454</v>
+        <v>45</v>
       </c>
       <c r="I166" t="s">
-        <v>396</v>
+        <v>447</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" t="s">
+        <v>328</v>
+      </c>
+      <c r="B167" t="s">
+        <v>329</v>
+      </c>
+      <c r="C167" t="s">
+        <v>268</v>
+      </c>
+      <c r="E167" t="s">
+        <v>324</v>
+      </c>
+      <c r="F167">
+        <v>2.0</v>
+      </c>
+      <c r="G167" t="s">
+        <v>354</v>
+      </c>
+      <c r="H167" t="s">
         <v>402</v>
       </c>
-      <c r="B167" t="s">
-        <v>403</v>
-      </c>
-      <c r="C167" t="s">
-        <v>368</v>
-      </c>
-      <c r="E167" t="s">
-        <v>330</v>
-      </c>
-      <c r="F167">
-        <v>5.0</v>
-      </c>
-      <c r="G167" t="s">
-        <v>421</v>
-      </c>
-      <c r="H167" t="s">
-        <v>418</v>
-      </c>
       <c r="I167" t="s">
-        <v>399</v>
+        <v>448</v>
       </c>
     </row>
     <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="B168" t="s">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="C168" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="E168" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F168">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G168" t="s">
-        <v>67</v>
+        <v>402</v>
       </c>
       <c r="H168" t="s">
-        <v>67</v>
+        <v>402</v>
       </c>
       <c r="I168" t="s">
-        <v>396</v>
+        <v>449</v>
       </c>
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>386</v>
+        <v>438</v>
       </c>
       <c r="B169" t="s">
-        <v>387</v>
+        <v>439</v>
       </c>
       <c r="C169" t="s">
-        <v>339</v>
+        <v>246</v>
       </c>
       <c r="E169" t="s">
-        <v>388</v>
+        <v>324</v>
       </c>
       <c r="F169">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G169" t="s">
-        <v>360</v>
+        <v>405</v>
       </c>
       <c r="H169" t="s">
-        <v>45</v>
+        <v>450</v>
       </c>
       <c r="I169" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>334</v>
+        <v>443</v>
       </c>
       <c r="B170" t="s">
-        <v>335</v>
+        <v>444</v>
       </c>
       <c r="C170" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="E170" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F170">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G170" t="s">
-        <v>360</v>
+        <v>452</v>
       </c>
       <c r="H170" t="s">
-        <v>410</v>
+        <v>453</v>
       </c>
       <c r="I170" t="s">
-        <v>456</v>
+        <v>388</v>
       </c>
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="B171" t="s">
-        <v>434</v>
-      </c>
-      <c r="C171" t="s">
-        <v>317</v>
+        <v>455</v>
       </c>
       <c r="E171" t="s">
-        <v>330</v>
+        <v>456</v>
       </c>
       <c r="F171">
         <v>1.0</v>
       </c>
       <c r="G171" t="s">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="H171" t="s">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="I171" t="s">
-        <v>457</v>
+        <v>370</v>
       </c>
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="B172" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="C172" t="s">
-        <v>247</v>
+        <v>148</v>
       </c>
       <c r="E172" t="s">
-        <v>330</v>
+        <v>436</v>
       </c>
       <c r="F172">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G172" t="s">
-        <v>413</v>
+        <v>459</v>
       </c>
       <c r="H172" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I172" t="s">
-        <v>459</v>
+        <v>173</v>
       </c>
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="B173" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="C173" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="E173" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="F173">
         <v>4.0</v>
       </c>
       <c r="G173" t="s">
-        <v>460</v>
+        <v>67</v>
       </c>
       <c r="H173" t="s">
-        <v>461</v>
+        <v>67</v>
       </c>
       <c r="I173" t="s">
-        <v>396</v>
+        <v>463</v>
       </c>
     </row>
     <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B174" t="s">
-        <v>463</v>
+        <v>465</v>
+      </c>
+      <c r="C174" t="s">
+        <v>158</v>
       </c>
       <c r="E174" t="s">
-        <v>464</v>
+        <v>436</v>
       </c>
       <c r="F174">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G174" t="s">
-        <v>67</v>
+        <v>466</v>
       </c>
       <c r="H174" t="s">
-        <v>67</v>
+        <v>467</v>
       </c>
       <c r="I174" t="s">
-        <v>378</v>
+        <v>468</v>
       </c>
     </row>
     <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B175" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C175" t="s">
         <v>148</v>
       </c>
       <c r="E175" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="F175">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G175" t="s">
-        <v>467</v>
+        <v>67</v>
       </c>
       <c r="H175" t="s">
-        <v>467</v>
+        <v>67</v>
       </c>
       <c r="I175" t="s">
-        <v>173</v>
+        <v>471</v>
       </c>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>468</v>
+        <v>371</v>
       </c>
       <c r="B176" t="s">
-        <v>469</v>
+        <v>372</v>
       </c>
       <c r="C176" t="s">
-        <v>368</v>
+        <v>268</v>
       </c>
       <c r="E176" t="s">
-        <v>470</v>
+        <v>353</v>
       </c>
       <c r="F176">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G176" t="s">
-        <v>67</v>
+        <v>354</v>
       </c>
       <c r="H176" t="s">
-        <v>67</v>
+        <v>354</v>
       </c>
       <c r="I176" t="s">
-        <v>471</v>
+        <v>424</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -6615,403 +6591,403 @@
         <v>473</v>
       </c>
       <c r="C177" t="s">
-        <v>158</v>
+        <v>360</v>
       </c>
       <c r="E177" t="s">
-        <v>444</v>
+        <v>380</v>
       </c>
       <c r="F177">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G177" t="s">
-        <v>474</v>
+        <v>354</v>
       </c>
       <c r="H177" t="s">
-        <v>475</v>
+        <v>355</v>
       </c>
       <c r="I177" t="s">
-        <v>476</v>
+        <v>356</v>
       </c>
     </row>
     <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>477</v>
+        <v>383</v>
       </c>
       <c r="B178" t="s">
-        <v>478</v>
+        <v>384</v>
       </c>
       <c r="C178" t="s">
-        <v>148</v>
+        <v>360</v>
       </c>
       <c r="E178" t="s">
-        <v>444</v>
+        <v>324</v>
       </c>
       <c r="F178">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G178" t="s">
-        <v>67</v>
+        <v>405</v>
       </c>
       <c r="H178" t="s">
-        <v>67</v>
+        <v>410</v>
       </c>
       <c r="I178" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="B179" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C179" t="s">
-        <v>269</v>
+        <v>360</v>
       </c>
       <c r="E179" t="s">
-        <v>359</v>
+        <v>324</v>
       </c>
       <c r="F179">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G179" t="s">
-        <v>360</v>
+        <v>405</v>
       </c>
       <c r="H179" t="s">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="I179" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>480</v>
+        <v>304</v>
       </c>
       <c r="B180" t="s">
-        <v>481</v>
+        <v>305</v>
       </c>
       <c r="C180" t="s">
-        <v>368</v>
+        <v>111</v>
       </c>
       <c r="E180" t="s">
-        <v>388</v>
+        <v>223</v>
       </c>
       <c r="F180">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G180" t="s">
-        <v>360</v>
+        <v>67</v>
       </c>
       <c r="H180" t="s">
-        <v>361</v>
+        <v>67</v>
       </c>
       <c r="I180" t="s">
-        <v>362</v>
+        <v>475</v>
       </c>
     </row>
     <row r="181" spans="1:9">
       <c r="A181" t="s">
-        <v>391</v>
+        <v>422</v>
       </c>
       <c r="B181" t="s">
-        <v>392</v>
+        <v>423</v>
       </c>
       <c r="C181" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="E181" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F181">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G181" t="s">
-        <v>413</v>
+        <v>354</v>
       </c>
       <c r="H181" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="I181" t="s">
-        <v>482</v>
+        <v>421</v>
       </c>
     </row>
     <row r="182" spans="1:9">
       <c r="A182" t="s">
-        <v>411</v>
+        <v>476</v>
       </c>
       <c r="B182" t="s">
-        <v>412</v>
+        <v>477</v>
       </c>
       <c r="C182" t="s">
-        <v>368</v>
+        <v>246</v>
       </c>
       <c r="E182" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F182">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G182" t="s">
-        <v>413</v>
+        <v>325</v>
       </c>
       <c r="H182" t="s">
-        <v>458</v>
+        <v>410</v>
       </c>
       <c r="I182" t="s">
-        <v>435</v>
+        <v>478</v>
       </c>
     </row>
     <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>308</v>
+        <v>373</v>
       </c>
       <c r="B183" t="s">
-        <v>309</v>
+        <v>374</v>
       </c>
       <c r="C183" t="s">
-        <v>111</v>
+        <v>310</v>
       </c>
       <c r="E183" t="s">
-        <v>224</v>
+        <v>324</v>
       </c>
       <c r="F183">
         <v>2.0</v>
       </c>
       <c r="G183" t="s">
-        <v>67</v>
+        <v>354</v>
       </c>
       <c r="H183" t="s">
-        <v>67</v>
+        <v>402</v>
       </c>
       <c r="I183" t="s">
-        <v>483</v>
+        <v>421</v>
       </c>
     </row>
     <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>430</v>
+        <v>479</v>
       </c>
       <c r="B184" t="s">
-        <v>431</v>
+        <v>480</v>
       </c>
       <c r="C184" t="s">
-        <v>339</v>
+        <v>148</v>
       </c>
       <c r="E184" t="s">
-        <v>330</v>
+        <v>436</v>
       </c>
       <c r="F184">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G184" t="s">
-        <v>360</v>
+        <v>459</v>
       </c>
       <c r="H184" t="s">
-        <v>410</v>
+        <v>481</v>
       </c>
       <c r="I184" t="s">
-        <v>429</v>
+        <v>482</v>
       </c>
     </row>
     <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>484</v>
+        <v>403</v>
       </c>
       <c r="B185" t="s">
-        <v>485</v>
+        <v>404</v>
       </c>
       <c r="C185" t="s">
-        <v>247</v>
+        <v>310</v>
       </c>
       <c r="E185" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F185">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G185" t="s">
-        <v>331</v>
+        <v>405</v>
       </c>
       <c r="H185" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I185" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>381</v>
+        <v>472</v>
       </c>
       <c r="B186" t="s">
-        <v>382</v>
+        <v>473</v>
       </c>
       <c r="C186" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="E186" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="F186">
         <v>2.0</v>
       </c>
       <c r="G186" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="H186" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="I186" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>487</v>
+        <v>464</v>
       </c>
       <c r="B187" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="C187" t="s">
         <v>148</v>
       </c>
       <c r="E187" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="F187">
         <v>3.0</v>
       </c>
       <c r="G187" t="s">
-        <v>467</v>
+        <v>67</v>
       </c>
       <c r="H187" t="s">
-        <v>489</v>
+        <v>67</v>
       </c>
       <c r="I187" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
     </row>
     <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>411</v>
+        <v>322</v>
       </c>
       <c r="B188" t="s">
-        <v>412</v>
+        <v>323</v>
       </c>
       <c r="C188" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="E188" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F188">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G188" t="s">
-        <v>413</v>
+        <v>325</v>
       </c>
       <c r="H188" t="s">
-        <v>418</v>
+        <v>325</v>
       </c>
       <c r="I188" t="s">
-        <v>491</v>
+        <v>255</v>
       </c>
     </row>
     <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B189" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C189" t="s">
-        <v>339</v>
+        <v>125</v>
       </c>
       <c r="E189" t="s">
-        <v>388</v>
+        <v>223</v>
       </c>
       <c r="F189">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G189" t="s">
-        <v>360</v>
+        <v>67</v>
       </c>
       <c r="H189" t="s">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="I189" t="s">
-        <v>428</v>
+        <v>341</v>
       </c>
     </row>
     <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>472</v>
+        <v>425</v>
       </c>
       <c r="B190" t="s">
-        <v>473</v>
+        <v>426</v>
       </c>
       <c r="C190" t="s">
-        <v>148</v>
+        <v>333</v>
       </c>
       <c r="E190" t="s">
-        <v>444</v>
+        <v>324</v>
       </c>
       <c r="F190">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G190" t="s">
-        <v>67</v>
+        <v>354</v>
       </c>
       <c r="H190" t="s">
-        <v>67</v>
+        <v>402</v>
       </c>
       <c r="I190" t="s">
-        <v>490</v>
+        <v>448</v>
       </c>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>328</v>
+        <v>443</v>
       </c>
       <c r="B191" t="s">
-        <v>329</v>
+        <v>444</v>
       </c>
       <c r="C191" t="s">
-        <v>269</v>
+        <v>360</v>
       </c>
       <c r="E191" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F191">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G191" t="s">
-        <v>331</v>
+        <v>405</v>
       </c>
       <c r="H191" t="s">
-        <v>331</v>
+        <v>450</v>
       </c>
       <c r="I191" t="s">
-        <v>256</v>
+        <v>486</v>
       </c>
     </row>
     <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>492</v>
+        <v>373</v>
       </c>
       <c r="B192" t="s">
-        <v>493</v>
+        <v>374</v>
       </c>
       <c r="C192" t="s">
-        <v>125</v>
+        <v>360</v>
       </c>
       <c r="E192" t="s">
-        <v>224</v>
+        <v>324</v>
       </c>
       <c r="F192">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G192" t="s">
         <v>67</v>
@@ -7020,76 +6996,76 @@
         <v>67</v>
       </c>
       <c r="I192" t="s">
-        <v>347</v>
+        <v>440</v>
       </c>
     </row>
     <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>433</v>
+        <v>487</v>
       </c>
       <c r="B193" t="s">
-        <v>434</v>
+        <v>488</v>
       </c>
       <c r="C193" t="s">
-        <v>339</v>
+        <v>246</v>
       </c>
       <c r="E193" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F193">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G193" t="s">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="H193" t="s">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="I193" t="s">
-        <v>456</v>
+        <v>489</v>
       </c>
     </row>
     <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="B194" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="C194" t="s">
-        <v>368</v>
+        <v>125</v>
       </c>
       <c r="E194" t="s">
-        <v>330</v>
+        <v>436</v>
       </c>
       <c r="F194">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G194" t="s">
-        <v>413</v>
+        <v>67</v>
       </c>
       <c r="H194" t="s">
-        <v>458</v>
+        <v>67</v>
       </c>
       <c r="I194" t="s">
-        <v>494</v>
+        <v>471</v>
       </c>
     </row>
     <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>381</v>
+        <v>490</v>
       </c>
       <c r="B195" t="s">
-        <v>382</v>
+        <v>491</v>
       </c>
       <c r="C195" t="s">
-        <v>368</v>
+        <v>125</v>
       </c>
       <c r="E195" t="s">
-        <v>330</v>
+        <v>223</v>
       </c>
       <c r="F195">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G195" t="s">
         <v>67</v>
@@ -7098,180 +7074,180 @@
         <v>67</v>
       </c>
       <c r="I195" t="s">
-        <v>448</v>
+        <v>341</v>
       </c>
     </row>
     <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>495</v>
+        <v>443</v>
       </c>
       <c r="B196" t="s">
-        <v>496</v>
+        <v>444</v>
       </c>
       <c r="C196" t="s">
-        <v>247</v>
+        <v>310</v>
       </c>
       <c r="E196" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F196">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G196" t="s">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="H196" t="s">
-        <v>458</v>
+        <v>410</v>
       </c>
       <c r="I196" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>487</v>
+        <v>422</v>
       </c>
       <c r="B197" t="s">
-        <v>488</v>
+        <v>423</v>
       </c>
       <c r="C197" t="s">
-        <v>125</v>
+        <v>310</v>
       </c>
       <c r="E197" t="s">
-        <v>444</v>
+        <v>324</v>
       </c>
       <c r="F197">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G197" t="s">
-        <v>67</v>
+        <v>402</v>
       </c>
       <c r="H197" t="s">
-        <v>67</v>
+        <v>402</v>
       </c>
       <c r="I197" t="s">
-        <v>479</v>
+        <v>440</v>
       </c>
     </row>
     <row r="198" spans="1:9">
       <c r="A198" t="s">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="B198" t="s">
-        <v>499</v>
+        <v>477</v>
       </c>
       <c r="C198" t="s">
-        <v>125</v>
+        <v>333</v>
       </c>
       <c r="E198" t="s">
-        <v>224</v>
+        <v>324</v>
       </c>
       <c r="F198">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G198" t="s">
-        <v>67</v>
+        <v>385</v>
       </c>
       <c r="H198" t="s">
-        <v>67</v>
+        <v>493</v>
       </c>
       <c r="I198" t="s">
-        <v>347</v>
+        <v>478</v>
       </c>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>451</v>
+        <v>494</v>
       </c>
       <c r="B199" t="s">
-        <v>452</v>
+        <v>495</v>
       </c>
       <c r="C199" t="s">
-        <v>317</v>
+        <v>148</v>
       </c>
       <c r="E199" t="s">
-        <v>330</v>
+        <v>436</v>
       </c>
       <c r="F199">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G199" t="s">
-        <v>500</v>
+        <v>67</v>
       </c>
       <c r="H199" t="s">
-        <v>418</v>
+        <v>67</v>
       </c>
       <c r="I199" t="s">
-        <v>494</v>
+        <v>235</v>
       </c>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>430</v>
+        <v>469</v>
       </c>
       <c r="B200" t="s">
-        <v>431</v>
+        <v>470</v>
       </c>
       <c r="C200" t="s">
-        <v>317</v>
+        <v>140</v>
       </c>
       <c r="E200" t="s">
-        <v>330</v>
+        <v>436</v>
       </c>
       <c r="F200">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G200" t="s">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="H200" t="s">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="I200" t="s">
-        <v>448</v>
+        <v>482</v>
       </c>
     </row>
     <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>484</v>
+        <v>383</v>
       </c>
       <c r="B201" t="s">
-        <v>485</v>
+        <v>384</v>
       </c>
       <c r="C201" t="s">
-        <v>339</v>
+        <v>268</v>
       </c>
       <c r="E201" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F201">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G201" t="s">
-        <v>393</v>
+        <v>67</v>
       </c>
       <c r="H201" t="s">
-        <v>501</v>
+        <v>67</v>
       </c>
       <c r="I201" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B202" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C202" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E202" t="s">
-        <v>444</v>
+        <v>223</v>
       </c>
       <c r="F202">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G202" t="s">
         <v>67</v>
@@ -7280,24 +7256,24 @@
         <v>67</v>
       </c>
       <c r="I202" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
     </row>
     <row r="203" spans="1:9">
       <c r="A203" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="B203" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="C203" t="s">
-        <v>140</v>
+        <v>333</v>
       </c>
       <c r="E203" t="s">
-        <v>444</v>
+        <v>324</v>
       </c>
       <c r="F203">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G203" t="s">
         <v>67</v>
@@ -7306,24 +7282,24 @@
         <v>67</v>
       </c>
       <c r="I203" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
     </row>
     <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>391</v>
+        <v>500</v>
       </c>
       <c r="B204" t="s">
-        <v>392</v>
+        <v>501</v>
       </c>
       <c r="C204" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="E204" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F204">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G204" t="s">
         <v>67</v>
@@ -7332,21 +7308,21 @@
         <v>67</v>
       </c>
       <c r="I204" t="s">
-        <v>479</v>
+        <v>502</v>
       </c>
     </row>
     <row r="205" spans="1:9">
       <c r="A205" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="B205" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C205" t="s">
         <v>158</v>
       </c>
       <c r="E205" t="s">
-        <v>224</v>
+        <v>436</v>
       </c>
       <c r="F205">
         <v>1.0</v>
@@ -7358,21 +7334,21 @@
         <v>67</v>
       </c>
       <c r="I205" t="s">
-        <v>226</v>
+        <v>173</v>
       </c>
     </row>
     <row r="206" spans="1:9">
       <c r="A206" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="B206" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="C206" t="s">
-        <v>339</v>
+        <v>246</v>
       </c>
       <c r="E206" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F206">
         <v>1.0</v>
@@ -7384,73 +7360,73 @@
         <v>67</v>
       </c>
       <c r="I206" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>508</v>
+        <v>479</v>
       </c>
       <c r="B207" t="s">
-        <v>509</v>
+        <v>480</v>
       </c>
       <c r="C207" t="s">
-        <v>247</v>
+        <v>158</v>
       </c>
       <c r="E207" t="s">
-        <v>330</v>
+        <v>436</v>
       </c>
       <c r="F207">
         <v>3.0</v>
       </c>
       <c r="G207" t="s">
-        <v>67</v>
+        <v>466</v>
       </c>
       <c r="H207" t="s">
-        <v>67</v>
+        <v>503</v>
       </c>
       <c r="I207" t="s">
-        <v>510</v>
+        <v>482</v>
       </c>
     </row>
     <row r="208" spans="1:9">
       <c r="A208" t="s">
-        <v>502</v>
+        <v>425</v>
       </c>
       <c r="B208" t="s">
-        <v>503</v>
+        <v>426</v>
       </c>
       <c r="C208" t="s">
-        <v>158</v>
+        <v>268</v>
       </c>
       <c r="E208" t="s">
-        <v>444</v>
+        <v>324</v>
       </c>
       <c r="F208">
         <v>1.0</v>
       </c>
       <c r="G208" t="s">
-        <v>67</v>
+        <v>402</v>
       </c>
       <c r="H208" t="s">
-        <v>67</v>
+        <v>402</v>
       </c>
       <c r="I208" t="s">
-        <v>173</v>
+        <v>449</v>
       </c>
     </row>
     <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="B209" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="C209" t="s">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="E209" t="s">
-        <v>330</v>
+        <v>223</v>
       </c>
       <c r="F209">
         <v>1.0</v>
@@ -7462,76 +7438,76 @@
         <v>67</v>
       </c>
       <c r="I209" t="s">
-        <v>457</v>
+        <v>225</v>
       </c>
     </row>
     <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="B210" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="C210" t="s">
         <v>158</v>
       </c>
       <c r="E210" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="F210">
         <v>3.0</v>
       </c>
       <c r="G210" t="s">
-        <v>474</v>
+        <v>67</v>
       </c>
       <c r="H210" t="s">
-        <v>511</v>
+        <v>67</v>
       </c>
       <c r="I210" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
     </row>
     <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>433</v>
+        <v>469</v>
       </c>
       <c r="B211" t="s">
-        <v>434</v>
+        <v>470</v>
       </c>
       <c r="C211" t="s">
-        <v>269</v>
+        <v>125</v>
       </c>
       <c r="E211" t="s">
-        <v>330</v>
+        <v>436</v>
       </c>
       <c r="F211">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G211" t="s">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="H211" t="s">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="I211" t="s">
-        <v>457</v>
+        <v>486</v>
       </c>
     </row>
     <row r="212" spans="1:9">
       <c r="A212" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B212" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C212" t="s">
-        <v>140</v>
+        <v>246</v>
       </c>
       <c r="E212" t="s">
-        <v>224</v>
+        <v>324</v>
       </c>
       <c r="F212">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G212" t="s">
         <v>67</v>
@@ -7540,24 +7516,24 @@
         <v>67</v>
       </c>
       <c r="I212" t="s">
-        <v>226</v>
+        <v>506</v>
       </c>
     </row>
     <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>477</v>
+        <v>507</v>
       </c>
       <c r="B213" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="C213" t="s">
         <v>158</v>
       </c>
       <c r="E213" t="s">
-        <v>444</v>
+        <v>223</v>
       </c>
       <c r="F213">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G213" t="s">
         <v>67</v>
@@ -7566,24 +7542,24 @@
         <v>67</v>
       </c>
       <c r="I213" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
     </row>
     <row r="214" spans="1:9">
       <c r="A214" t="s">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="B214" t="s">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="C214" t="s">
-        <v>125</v>
+        <v>246</v>
       </c>
       <c r="E214" t="s">
-        <v>444</v>
+        <v>324</v>
       </c>
       <c r="F214">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G214" t="s">
         <v>67</v>
@@ -7592,47 +7568,47 @@
         <v>67</v>
       </c>
       <c r="I214" t="s">
-        <v>494</v>
+        <v>440</v>
       </c>
     </row>
     <row r="215" spans="1:9">
       <c r="A215" t="s">
+        <v>511</v>
+      </c>
+      <c r="B215" t="s">
         <v>512</v>
       </c>
-      <c r="B215" t="s">
-        <v>513</v>
-      </c>
       <c r="C215" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E215" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F215">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G215" t="s">
-        <v>67</v>
+        <v>492</v>
       </c>
       <c r="H215" t="s">
-        <v>67</v>
+        <v>410</v>
       </c>
       <c r="I215" t="s">
-        <v>514</v>
+        <v>427</v>
       </c>
     </row>
     <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B216" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C216" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="E216" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="F216">
         <v>2.0</v>
@@ -7644,21 +7620,21 @@
         <v>67</v>
       </c>
       <c r="I216" t="s">
-        <v>483</v>
+        <v>174</v>
       </c>
     </row>
     <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>517</v>
+        <v>479</v>
       </c>
       <c r="B217" t="s">
-        <v>518</v>
+        <v>480</v>
       </c>
       <c r="C217" t="s">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="E217" t="s">
-        <v>330</v>
+        <v>436</v>
       </c>
       <c r="F217">
         <v>2.0</v>
@@ -7670,102 +7646,102 @@
         <v>67</v>
       </c>
       <c r="I217" t="s">
-        <v>429</v>
+        <v>255</v>
       </c>
     </row>
     <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="B218" t="s">
-        <v>520</v>
+        <v>491</v>
       </c>
       <c r="C218" t="s">
-        <v>247</v>
+        <v>158</v>
       </c>
       <c r="E218" t="s">
-        <v>330</v>
+        <v>223</v>
       </c>
       <c r="F218">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G218" t="s">
-        <v>500</v>
+        <v>67</v>
       </c>
       <c r="H218" t="s">
-        <v>418</v>
+        <v>67</v>
       </c>
       <c r="I218" t="s">
-        <v>435</v>
+        <v>236</v>
       </c>
     </row>
     <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>521</v>
+        <v>443</v>
       </c>
       <c r="B219" t="s">
-        <v>522</v>
+        <v>444</v>
       </c>
       <c r="C219" t="s">
-        <v>148</v>
+        <v>268</v>
       </c>
       <c r="E219" t="s">
-        <v>130</v>
+        <v>324</v>
       </c>
       <c r="F219">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G219" t="s">
-        <v>67</v>
+        <v>450</v>
       </c>
       <c r="H219" t="s">
-        <v>67</v>
+        <v>450</v>
       </c>
       <c r="I219" t="s">
-        <v>174</v>
+        <v>255</v>
       </c>
     </row>
     <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>411</v>
+        <v>476</v>
       </c>
       <c r="B220" t="s">
-        <v>412</v>
+        <v>477</v>
       </c>
       <c r="C220" t="s">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="E220" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F220">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G220" t="s">
-        <v>67</v>
+        <v>325</v>
       </c>
       <c r="H220" t="s">
-        <v>67</v>
+        <v>450</v>
       </c>
       <c r="I220" t="s">
-        <v>457</v>
+        <v>75</v>
       </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="B221" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="C221" t="s">
-        <v>140</v>
+        <v>333</v>
       </c>
       <c r="E221" t="s">
-        <v>444</v>
+        <v>324</v>
       </c>
       <c r="F221">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G221" t="s">
         <v>67</v>
@@ -7774,102 +7750,102 @@
         <v>67</v>
       </c>
       <c r="I221" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="B222" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="C222" t="s">
-        <v>158</v>
+        <v>246</v>
       </c>
       <c r="E222" t="s">
-        <v>224</v>
+        <v>324</v>
       </c>
       <c r="F222">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G222" t="s">
-        <v>67</v>
+        <v>405</v>
       </c>
       <c r="H222" t="s">
-        <v>67</v>
+        <v>450</v>
       </c>
       <c r="I222" t="s">
-        <v>237</v>
+        <v>502</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="A223" t="s">
-        <v>451</v>
+        <v>484</v>
       </c>
       <c r="B223" t="s">
-        <v>452</v>
+        <v>485</v>
       </c>
       <c r="C223" t="s">
-        <v>269</v>
+        <v>148</v>
       </c>
       <c r="E223" t="s">
-        <v>330</v>
+        <v>223</v>
       </c>
       <c r="F223">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G223" t="s">
-        <v>458</v>
+        <v>67</v>
       </c>
       <c r="H223" t="s">
-        <v>458</v>
+        <v>67</v>
       </c>
       <c r="I223" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
     </row>
     <row r="224" spans="1:9">
       <c r="A224" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="B224" t="s">
-        <v>485</v>
+        <v>508</v>
       </c>
       <c r="C224" t="s">
-        <v>317</v>
+        <v>125</v>
       </c>
       <c r="E224" t="s">
-        <v>330</v>
+        <v>223</v>
       </c>
       <c r="F224">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G224" t="s">
-        <v>331</v>
+        <v>67</v>
       </c>
       <c r="H224" t="s">
-        <v>458</v>
+        <v>67</v>
       </c>
       <c r="I224" t="s">
-        <v>75</v>
+        <v>341</v>
       </c>
     </row>
     <row r="225" spans="1:9">
       <c r="A225" t="s">
+        <v>507</v>
+      </c>
+      <c r="B225" t="s">
         <v>508</v>
       </c>
-      <c r="B225" t="s">
-        <v>509</v>
-      </c>
       <c r="C225" t="s">
-        <v>339</v>
+        <v>140</v>
       </c>
       <c r="E225" t="s">
-        <v>330</v>
+        <v>223</v>
       </c>
       <c r="F225">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G225" t="s">
         <v>67</v>
@@ -7878,50 +7854,50 @@
         <v>67</v>
       </c>
       <c r="I225" t="s">
-        <v>497</v>
+        <v>475</v>
       </c>
     </row>
     <row r="226" spans="1:9">
       <c r="A226" t="s">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="B226" t="s">
-        <v>524</v>
+        <v>499</v>
       </c>
       <c r="C226" t="s">
-        <v>247</v>
+        <v>360</v>
       </c>
       <c r="E226" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F226">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G226" t="s">
-        <v>413</v>
+        <v>67</v>
       </c>
       <c r="H226" t="s">
-        <v>458</v>
+        <v>67</v>
       </c>
       <c r="I226" t="s">
-        <v>510</v>
+        <v>449</v>
       </c>
     </row>
     <row r="227" spans="1:9">
       <c r="A227" t="s">
-        <v>492</v>
+        <v>515</v>
       </c>
       <c r="B227" t="s">
-        <v>493</v>
+        <v>516</v>
       </c>
       <c r="C227" t="s">
-        <v>148</v>
+        <v>360</v>
       </c>
       <c r="E227" t="s">
-        <v>224</v>
+        <v>324</v>
       </c>
       <c r="F227">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G227" t="s">
         <v>67</v>
@@ -7930,24 +7906,24 @@
         <v>67</v>
       </c>
       <c r="I227" t="s">
-        <v>237</v>
+        <v>489</v>
       </c>
     </row>
     <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B228" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C228" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="E228" t="s">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="F228">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G228" t="s">
         <v>67</v>
@@ -7956,24 +7932,24 @@
         <v>67</v>
       </c>
       <c r="I228" t="s">
-        <v>347</v>
+        <v>274</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="B229" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="C229" t="s">
-        <v>140</v>
+        <v>310</v>
       </c>
       <c r="E229" t="s">
-        <v>224</v>
+        <v>324</v>
       </c>
       <c r="F229">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G229" t="s">
         <v>67</v>
@@ -7982,24 +7958,24 @@
         <v>67</v>
       </c>
       <c r="I229" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
     </row>
     <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>506</v>
+        <v>394</v>
       </c>
       <c r="B230" t="s">
-        <v>507</v>
+        <v>395</v>
       </c>
       <c r="C230" t="s">
-        <v>368</v>
+        <v>268</v>
       </c>
       <c r="E230" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F230">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G230" t="s">
         <v>67</v>
@@ -8008,21 +7984,21 @@
         <v>67</v>
       </c>
       <c r="I230" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
     </row>
     <row r="231" spans="1:9">
       <c r="A231" t="s">
-        <v>523</v>
+        <v>487</v>
       </c>
       <c r="B231" t="s">
-        <v>524</v>
+        <v>488</v>
       </c>
       <c r="C231" t="s">
-        <v>368</v>
+        <v>310</v>
       </c>
       <c r="E231" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F231">
         <v>1.0</v>
@@ -8034,50 +8010,50 @@
         <v>67</v>
       </c>
       <c r="I231" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="B232" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C232" t="s">
-        <v>140</v>
+        <v>333</v>
       </c>
       <c r="E232" t="s">
-        <v>130</v>
+        <v>324</v>
       </c>
       <c r="F232">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G232" t="s">
-        <v>67</v>
+        <v>519</v>
       </c>
       <c r="H232" t="s">
-        <v>67</v>
+        <v>519</v>
       </c>
       <c r="I232" t="s">
-        <v>275</v>
+        <v>489</v>
       </c>
     </row>
     <row r="233" spans="1:9">
       <c r="A233" t="s">
+        <v>511</v>
+      </c>
+      <c r="B233" t="s">
         <v>512</v>
       </c>
-      <c r="B233" t="s">
-        <v>513</v>
-      </c>
       <c r="C233" t="s">
-        <v>317</v>
+        <v>360</v>
       </c>
       <c r="E233" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F233">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G233" t="s">
         <v>67</v>
@@ -8086,24 +8062,24 @@
         <v>67</v>
       </c>
       <c r="I233" t="s">
-        <v>482</v>
+        <v>449</v>
       </c>
     </row>
     <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>402</v>
+        <v>520</v>
       </c>
       <c r="B234" t="s">
-        <v>403</v>
+        <v>521</v>
       </c>
       <c r="C234" t="s">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="E234" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F234">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G234" t="s">
         <v>67</v>
@@ -8112,21 +8088,21 @@
         <v>67</v>
       </c>
       <c r="I234" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>495</v>
+        <v>522</v>
       </c>
       <c r="B235" t="s">
-        <v>496</v>
+        <v>523</v>
       </c>
       <c r="C235" t="s">
-        <v>317</v>
+        <v>246</v>
       </c>
       <c r="E235" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F235">
         <v>1.0</v>
@@ -8138,50 +8114,50 @@
         <v>67</v>
       </c>
       <c r="I235" t="s">
-        <v>497</v>
+        <v>440</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B236" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C236" t="s">
-        <v>339</v>
+        <v>246</v>
       </c>
       <c r="E236" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F236">
         <v>1.0</v>
       </c>
       <c r="G236" t="s">
-        <v>527</v>
+        <v>67</v>
       </c>
       <c r="H236" t="s">
-        <v>527</v>
+        <v>67</v>
       </c>
       <c r="I236" t="s">
-        <v>497</v>
+        <v>440</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>519</v>
+        <v>464</v>
       </c>
       <c r="B237" t="s">
-        <v>520</v>
+        <v>465</v>
       </c>
       <c r="C237" t="s">
-        <v>368</v>
+        <v>140</v>
       </c>
       <c r="E237" t="s">
-        <v>330</v>
+        <v>436</v>
       </c>
       <c r="F237">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G237" t="s">
         <v>67</v>
@@ -8190,24 +8166,24 @@
         <v>67</v>
       </c>
       <c r="I237" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B238" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C238" t="s">
-        <v>317</v>
+        <v>158</v>
       </c>
       <c r="E238" t="s">
-        <v>330</v>
+        <v>526</v>
       </c>
       <c r="F238">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G238" t="s">
         <v>67</v>
@@ -8216,24 +8192,24 @@
         <v>67</v>
       </c>
       <c r="I238" t="s">
-        <v>448</v>
+        <v>240</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B239" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C239" t="s">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="E239" t="s">
-        <v>330</v>
+        <v>126</v>
       </c>
       <c r="F239">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G239" t="s">
         <v>67</v>
@@ -8242,21 +8218,21 @@
         <v>67</v>
       </c>
       <c r="I239" t="s">
-        <v>448</v>
+        <v>161</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" t="s">
+        <v>527</v>
+      </c>
+      <c r="B240" t="s">
         <v>528</v>
       </c>
-      <c r="B240" t="s">
-        <v>529</v>
-      </c>
       <c r="C240" t="s">
-        <v>247</v>
+        <v>125</v>
       </c>
       <c r="E240" t="s">
-        <v>330</v>
+        <v>126</v>
       </c>
       <c r="F240">
         <v>1.0</v>
@@ -8268,21 +8244,21 @@
         <v>67</v>
       </c>
       <c r="I240" t="s">
-        <v>448</v>
+        <v>113</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>472</v>
+        <v>513</v>
       </c>
       <c r="B241" t="s">
-        <v>473</v>
+        <v>514</v>
       </c>
       <c r="C241" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="E241" t="s">
-        <v>444</v>
+        <v>130</v>
       </c>
       <c r="F241">
         <v>3.0</v>
@@ -8294,24 +8270,24 @@
         <v>67</v>
       </c>
       <c r="I241" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="B242" t="s">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="C242" t="s">
         <v>158</v>
       </c>
       <c r="E242" t="s">
-        <v>534</v>
+        <v>130</v>
       </c>
       <c r="F242">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G242" t="s">
         <v>67</v>
@@ -8320,24 +8296,24 @@
         <v>67</v>
       </c>
       <c r="I242" t="s">
-        <v>241</v>
+        <v>529</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>535</v>
+        <v>484</v>
       </c>
       <c r="B243" t="s">
-        <v>536</v>
+        <v>485</v>
       </c>
       <c r="C243" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="E243" t="s">
-        <v>126</v>
+        <v>223</v>
       </c>
       <c r="F243">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G243" t="s">
         <v>67</v>
@@ -8346,21 +8322,21 @@
         <v>67</v>
       </c>
       <c r="I243" t="s">
-        <v>161</v>
+        <v>225</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>535</v>
+        <v>507</v>
       </c>
       <c r="B244" t="s">
-        <v>536</v>
+        <v>508</v>
       </c>
       <c r="C244" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="E244" t="s">
-        <v>126</v>
+        <v>223</v>
       </c>
       <c r="F244">
         <v>2.0</v>
@@ -8372,24 +8348,24 @@
         <v>67</v>
       </c>
       <c r="I244" t="s">
-        <v>166</v>
+        <v>475</v>
       </c>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>521</v>
+        <v>496</v>
       </c>
       <c r="B245" t="s">
-        <v>522</v>
+        <v>497</v>
       </c>
       <c r="C245" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="E245" t="s">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="F245">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G245" t="s">
         <v>67</v>
@@ -8398,24 +8374,24 @@
         <v>67</v>
       </c>
       <c r="I245" t="s">
-        <v>537</v>
+        <v>475</v>
       </c>
     </row>
     <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>525</v>
+        <v>304</v>
       </c>
       <c r="B246" t="s">
-        <v>526</v>
+        <v>305</v>
       </c>
       <c r="C246" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="E246" t="s">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="F246">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G246" t="s">
         <v>67</v>
@@ -8424,24 +8400,24 @@
         <v>67</v>
       </c>
       <c r="I246" t="s">
-        <v>537</v>
+        <v>234</v>
       </c>
     </row>
     <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B247" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C247" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="E247" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F247">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G247" t="s">
         <v>67</v>
@@ -8450,24 +8426,24 @@
         <v>67</v>
       </c>
       <c r="I247" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
     </row>
     <row r="248" spans="1:9">
       <c r="A248" t="s">
-        <v>515</v>
+        <v>464</v>
       </c>
       <c r="B248" t="s">
-        <v>516</v>
+        <v>465</v>
       </c>
       <c r="C248" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="E248" t="s">
-        <v>224</v>
+        <v>436</v>
       </c>
       <c r="F248">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G248" t="s">
         <v>67</v>
@@ -8476,24 +8452,24 @@
         <v>67</v>
       </c>
       <c r="I248" t="s">
-        <v>483</v>
+        <v>530</v>
       </c>
     </row>
     <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="B249" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C249" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="E249" t="s">
-        <v>224</v>
+        <v>436</v>
       </c>
       <c r="F249">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G249" t="s">
         <v>67</v>
@@ -8502,24 +8478,21 @@
         <v>67</v>
       </c>
       <c r="I249" t="s">
-        <v>483</v>
+        <v>173</v>
       </c>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>308</v>
+        <v>531</v>
       </c>
       <c r="B250" t="s">
-        <v>309</v>
-      </c>
-      <c r="C250" t="s">
-        <v>125</v>
+        <v>532</v>
       </c>
       <c r="E250" t="s">
-        <v>224</v>
+        <v>533</v>
       </c>
       <c r="F250">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G250" t="s">
         <v>67</v>
@@ -8528,24 +8501,21 @@
         <v>67</v>
       </c>
       <c r="I250" t="s">
-        <v>235</v>
+        <v>321</v>
       </c>
     </row>
     <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>498</v>
+        <v>534</v>
       </c>
       <c r="B251" t="s">
-        <v>499</v>
-      </c>
-      <c r="C251" t="s">
-        <v>148</v>
+        <v>535</v>
       </c>
       <c r="E251" t="s">
-        <v>224</v>
+        <v>533</v>
       </c>
       <c r="F251">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G251" t="s">
         <v>67</v>
@@ -8554,24 +8524,21 @@
         <v>67</v>
       </c>
       <c r="I251" t="s">
-        <v>237</v>
+        <v>321</v>
       </c>
     </row>
     <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>472</v>
+        <v>536</v>
       </c>
       <c r="B252" t="s">
-        <v>473</v>
-      </c>
-      <c r="C252" t="s">
-        <v>125</v>
+        <v>537</v>
       </c>
       <c r="E252" t="s">
-        <v>444</v>
+        <v>533</v>
       </c>
       <c r="F252">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G252" t="s">
         <v>67</v>
@@ -8580,21 +8547,18 @@
         <v>67</v>
       </c>
       <c r="I252" t="s">
-        <v>538</v>
+        <v>260</v>
       </c>
     </row>
     <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>502</v>
+        <v>538</v>
       </c>
       <c r="B253" t="s">
-        <v>503</v>
-      </c>
-      <c r="C253" t="s">
-        <v>125</v>
+        <v>539</v>
       </c>
       <c r="E253" t="s">
-        <v>444</v>
+        <v>205</v>
       </c>
       <c r="F253">
         <v>1.0</v>
@@ -8606,67 +8570,76 @@
         <v>67</v>
       </c>
       <c r="I253" t="s">
-        <v>173</v>
+        <v>108</v>
       </c>
     </row>
     <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>539</v>
+        <v>460</v>
       </c>
       <c r="B254" t="s">
+        <v>461</v>
+      </c>
+      <c r="C254" t="s">
+        <v>310</v>
+      </c>
+      <c r="E254" t="s">
+        <v>462</v>
+      </c>
+      <c r="F254">
+        <v>3.0</v>
+      </c>
+      <c r="G254" t="s">
+        <v>67</v>
+      </c>
+      <c r="H254" t="s">
+        <v>67</v>
+      </c>
+      <c r="I254" t="s">
         <v>540</v>
-      </c>
-      <c r="E254" t="s">
-        <v>541</v>
-      </c>
-      <c r="F254">
-        <v>1.0</v>
-      </c>
-      <c r="G254" t="s">
-        <v>67</v>
-      </c>
-      <c r="H254" t="s">
-        <v>67</v>
-      </c>
-      <c r="I254" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>542</v>
+        <v>460</v>
       </c>
       <c r="B255" t="s">
-        <v>543</v>
+        <v>461</v>
+      </c>
+      <c r="C255" t="s">
+        <v>246</v>
       </c>
       <c r="E255" t="s">
+        <v>462</v>
+      </c>
+      <c r="F255">
+        <v>7.0</v>
+      </c>
+      <c r="G255" t="s">
+        <v>67</v>
+      </c>
+      <c r="H255" t="s">
+        <v>67</v>
+      </c>
+      <c r="I255" t="s">
         <v>541</v>
-      </c>
-      <c r="F255">
-        <v>1.0</v>
-      </c>
-      <c r="G255" t="s">
-        <v>67</v>
-      </c>
-      <c r="H255" t="s">
-        <v>67</v>
-      </c>
-      <c r="I255" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>544</v>
+        <v>460</v>
       </c>
       <c r="B256" t="s">
-        <v>545</v>
+        <v>461</v>
+      </c>
+      <c r="C256" t="s">
+        <v>333</v>
       </c>
       <c r="E256" t="s">
-        <v>541</v>
+        <v>462</v>
       </c>
       <c r="F256">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G256" t="s">
         <v>67</v>
@@ -8675,21 +8648,24 @@
         <v>67</v>
       </c>
       <c r="I256" t="s">
-        <v>261</v>
+        <v>542</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B257" t="s">
-        <v>547</v>
+        <v>544</v>
+      </c>
+      <c r="C257" t="s">
+        <v>310</v>
       </c>
       <c r="E257" t="s">
-        <v>206</v>
+        <v>462</v>
       </c>
       <c r="F257">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G257" t="s">
         <v>67</v>
@@ -8698,24 +8674,24 @@
         <v>67</v>
       </c>
       <c r="I257" t="s">
-        <v>108</v>
+        <v>540</v>
       </c>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>468</v>
+        <v>543</v>
       </c>
       <c r="B258" t="s">
-        <v>469</v>
+        <v>544</v>
       </c>
       <c r="C258" t="s">
-        <v>317</v>
+        <v>246</v>
       </c>
       <c r="E258" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F258">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G258" t="s">
         <v>67</v>
@@ -8724,24 +8700,24 @@
         <v>67</v>
       </c>
       <c r="I258" t="s">
-        <v>471</v>
+        <v>540</v>
       </c>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>468</v>
+        <v>543</v>
       </c>
       <c r="B259" t="s">
-        <v>469</v>
+        <v>544</v>
       </c>
       <c r="C259" t="s">
-        <v>247</v>
+        <v>360</v>
       </c>
       <c r="E259" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F259">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="G259" t="s">
         <v>67</v>
@@ -8750,24 +8726,24 @@
         <v>67</v>
       </c>
       <c r="I259" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
     </row>
     <row r="260" spans="1:9">
       <c r="A260" t="s">
-        <v>468</v>
+        <v>545</v>
       </c>
       <c r="B260" t="s">
-        <v>469</v>
+        <v>544</v>
       </c>
       <c r="C260" t="s">
-        <v>339</v>
+        <v>268</v>
       </c>
       <c r="E260" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F260">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G260" t="s">
         <v>67</v>
@@ -8776,24 +8752,24 @@
         <v>67</v>
       </c>
       <c r="I260" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B261" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C261" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="E261" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F261">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G261" t="s">
         <v>67</v>
@@ -8802,21 +8778,21 @@
         <v>67</v>
       </c>
       <c r="I261" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B262" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C262" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E262" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F262">
         <v>4.0</v>
@@ -8828,21 +8804,21 @@
         <v>67</v>
       </c>
       <c r="I262" t="s">
-        <v>471</v>
+        <v>550</v>
       </c>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B263" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C263" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="E263" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F263">
         <v>3.0</v>
@@ -8854,47 +8830,47 @@
         <v>67</v>
       </c>
       <c r="I263" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="B264" t="s">
+        <v>548</v>
+      </c>
+      <c r="C264" t="s">
+        <v>268</v>
+      </c>
+      <c r="E264" t="s">
+        <v>462</v>
+      </c>
+      <c r="F264">
+        <v>3.0</v>
+      </c>
+      <c r="G264" t="s">
+        <v>67</v>
+      </c>
+      <c r="H264" t="s">
+        <v>67</v>
+      </c>
+      <c r="I264" t="s">
         <v>551</v>
-      </c>
-      <c r="C264" t="s">
-        <v>269</v>
-      </c>
-      <c r="E264" t="s">
-        <v>470</v>
-      </c>
-      <c r="F264">
-        <v>2.0</v>
-      </c>
-      <c r="G264" t="s">
-        <v>67</v>
-      </c>
-      <c r="H264" t="s">
-        <v>67</v>
-      </c>
-      <c r="I264" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B265" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C265" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="E265" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F265">
         <v>1.0</v>
@@ -8906,50 +8882,50 @@
         <v>67</v>
       </c>
       <c r="I265" t="s">
-        <v>557</v>
+        <v>489</v>
       </c>
     </row>
     <row r="266" spans="1:9">
       <c r="A266" t="s">
+        <v>554</v>
+      </c>
+      <c r="B266" t="s">
         <v>555</v>
       </c>
-      <c r="B266" t="s">
+      <c r="C266" t="s">
+        <v>333</v>
+      </c>
+      <c r="E266" t="s">
+        <v>462</v>
+      </c>
+      <c r="F266">
+        <v>1.0</v>
+      </c>
+      <c r="G266" t="s">
+        <v>67</v>
+      </c>
+      <c r="H266" t="s">
+        <v>67</v>
+      </c>
+      <c r="I266" t="s">
         <v>556</v>
-      </c>
-      <c r="C266" t="s">
-        <v>247</v>
-      </c>
-      <c r="E266" t="s">
-        <v>470</v>
-      </c>
-      <c r="F266">
-        <v>4.0</v>
-      </c>
-      <c r="G266" t="s">
-        <v>67</v>
-      </c>
-      <c r="H266" t="s">
-        <v>67</v>
-      </c>
-      <c r="I266" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="267" spans="1:9">
       <c r="A267" t="s">
+        <v>554</v>
+      </c>
+      <c r="B267" t="s">
         <v>555</v>
       </c>
-      <c r="B267" t="s">
-        <v>556</v>
-      </c>
       <c r="C267" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="E267" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F267">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G267" t="s">
         <v>67</v>
@@ -8958,50 +8934,50 @@
         <v>67</v>
       </c>
       <c r="I267" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="268" spans="1:9">
       <c r="A268" t="s">
+        <v>554</v>
+      </c>
+      <c r="B268" t="s">
         <v>555</v>
       </c>
-      <c r="B268" t="s">
+      <c r="C268" t="s">
+        <v>268</v>
+      </c>
+      <c r="E268" t="s">
+        <v>462</v>
+      </c>
+      <c r="F268">
+        <v>1.0</v>
+      </c>
+      <c r="G268" t="s">
+        <v>67</v>
+      </c>
+      <c r="H268" t="s">
+        <v>67</v>
+      </c>
+      <c r="I268" t="s">
         <v>556</v>
-      </c>
-      <c r="C268" t="s">
-        <v>269</v>
-      </c>
-      <c r="E268" t="s">
-        <v>470</v>
-      </c>
-      <c r="F268">
-        <v>3.0</v>
-      </c>
-      <c r="G268" t="s">
-        <v>67</v>
-      </c>
-      <c r="H268" t="s">
-        <v>67</v>
-      </c>
-      <c r="I268" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B269" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C269" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="E269" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F269">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G269" t="s">
         <v>67</v>
@@ -9010,21 +8986,21 @@
         <v>67</v>
       </c>
       <c r="I269" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="270" spans="1:9">
       <c r="A270" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B270" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C270" t="s">
-        <v>247</v>
+        <v>360</v>
       </c>
       <c r="E270" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F270">
         <v>1.0</v>
@@ -9036,21 +9012,21 @@
         <v>67</v>
       </c>
       <c r="I270" t="s">
-        <v>564</v>
+        <v>489</v>
       </c>
     </row>
     <row r="271" spans="1:9">
       <c r="A271" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B271" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C271" t="s">
-        <v>339</v>
+        <v>268</v>
       </c>
       <c r="E271" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F271">
         <v>1.0</v>
@@ -9062,21 +9038,21 @@
         <v>67</v>
       </c>
       <c r="I271" t="s">
-        <v>564</v>
+        <v>489</v>
       </c>
     </row>
     <row r="272" spans="1:9">
       <c r="A272" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B272" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C272" t="s">
-        <v>368</v>
+        <v>310</v>
       </c>
       <c r="E272" t="s">
-        <v>470</v>
+        <v>324</v>
       </c>
       <c r="F272">
         <v>2.0</v>
@@ -9088,24 +9064,24 @@
         <v>67</v>
       </c>
       <c r="I272" t="s">
-        <v>565</v>
+        <v>448</v>
       </c>
     </row>
     <row r="273" spans="1:9">
       <c r="A273" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B273" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C273" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="E273" t="s">
-        <v>470</v>
+        <v>324</v>
       </c>
       <c r="F273">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G273" t="s">
         <v>67</v>
@@ -9114,24 +9090,24 @@
         <v>67</v>
       </c>
       <c r="I273" t="s">
-        <v>564</v>
+        <v>448</v>
       </c>
     </row>
     <row r="274" spans="1:9">
       <c r="A274" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B274" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="C274" t="s">
-        <v>247</v>
+        <v>333</v>
       </c>
       <c r="E274" t="s">
-        <v>470</v>
+        <v>324</v>
       </c>
       <c r="F274">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G274" t="s">
         <v>67</v>
@@ -9140,24 +9116,24 @@
         <v>67</v>
       </c>
       <c r="I274" t="s">
-        <v>564</v>
+        <v>427</v>
       </c>
     </row>
     <row r="275" spans="1:9">
       <c r="A275" t="s">
-        <v>568</v>
+        <v>509</v>
       </c>
       <c r="B275" t="s">
-        <v>569</v>
+        <v>510</v>
       </c>
       <c r="C275" t="s">
-        <v>247</v>
+        <v>333</v>
       </c>
       <c r="E275" t="s">
-        <v>470</v>
+        <v>324</v>
       </c>
       <c r="F275">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G275" t="s">
         <v>67</v>
@@ -9166,24 +9142,24 @@
         <v>67</v>
       </c>
       <c r="I275" t="s">
-        <v>510</v>
+        <v>421</v>
       </c>
     </row>
     <row r="276" spans="1:9">
       <c r="A276" t="s">
-        <v>568</v>
+        <v>504</v>
       </c>
       <c r="B276" t="s">
-        <v>569</v>
+        <v>505</v>
       </c>
       <c r="C276" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="E276" t="s">
-        <v>470</v>
+        <v>324</v>
       </c>
       <c r="F276">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G276" t="s">
         <v>67</v>
@@ -9192,24 +9168,24 @@
         <v>67</v>
       </c>
       <c r="I276" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
     </row>
     <row r="277" spans="1:9">
       <c r="A277" t="s">
-        <v>568</v>
+        <v>504</v>
       </c>
       <c r="B277" t="s">
-        <v>569</v>
+        <v>505</v>
       </c>
       <c r="C277" t="s">
-        <v>269</v>
+        <v>360</v>
       </c>
       <c r="E277" t="s">
-        <v>470</v>
+        <v>324</v>
       </c>
       <c r="F277">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G277" t="s">
         <v>67</v>
@@ -9218,21 +9194,21 @@
         <v>67</v>
       </c>
       <c r="I277" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
     </row>
     <row r="278" spans="1:9">
       <c r="A278" t="s">
-        <v>570</v>
+        <v>504</v>
       </c>
       <c r="B278" t="s">
-        <v>571</v>
+        <v>505</v>
       </c>
       <c r="C278" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="E278" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F278">
         <v>2.0</v>
@@ -9244,24 +9220,24 @@
         <v>67</v>
       </c>
       <c r="I278" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
-        <v>570</v>
+        <v>498</v>
       </c>
       <c r="B279" t="s">
-        <v>571</v>
+        <v>499</v>
       </c>
       <c r="C279" t="s">
-        <v>247</v>
+        <v>310</v>
       </c>
       <c r="E279" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F279">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G279" t="s">
         <v>67</v>
@@ -9270,24 +9246,24 @@
         <v>67</v>
       </c>
       <c r="I279" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
-        <v>570</v>
+        <v>515</v>
       </c>
       <c r="B280" t="s">
-        <v>571</v>
+        <v>516</v>
       </c>
       <c r="C280" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="E280" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F280">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G280" t="s">
         <v>67</v>
@@ -9296,24 +9272,24 @@
         <v>67</v>
       </c>
       <c r="I280" t="s">
-        <v>435</v>
+        <v>489</v>
       </c>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B281" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C281" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="E281" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F281">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G281" t="s">
         <v>67</v>
@@ -9322,24 +9298,24 @@
         <v>67</v>
       </c>
       <c r="I281" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
+        <v>511</v>
+      </c>
+      <c r="B282" t="s">
         <v>512</v>
       </c>
-      <c r="B282" t="s">
-        <v>513</v>
-      </c>
       <c r="C282" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="E282" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F282">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G282" t="s">
         <v>67</v>
@@ -9348,24 +9324,24 @@
         <v>67</v>
       </c>
       <c r="I282" t="s">
-        <v>514</v>
+        <v>449</v>
       </c>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="B283" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="C283" t="s">
-        <v>368</v>
+        <v>310</v>
       </c>
       <c r="E283" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F283">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G283" t="s">
         <v>67</v>
@@ -9374,24 +9350,24 @@
         <v>67</v>
       </c>
       <c r="I283" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="284" spans="1:9">
       <c r="A284" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="B284" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="C284" t="s">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="E284" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F284">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G284" t="s">
         <v>67</v>
@@ -9400,24 +9376,24 @@
         <v>67</v>
       </c>
       <c r="I284" t="s">
-        <v>479</v>
+        <v>440</v>
       </c>
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="B285" t="s">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="C285" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="E285" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F285">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G285" t="s">
         <v>67</v>
@@ -9426,24 +9402,24 @@
         <v>67</v>
       </c>
       <c r="I285" t="s">
-        <v>457</v>
+        <v>421</v>
       </c>
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
-        <v>523</v>
+        <v>562</v>
       </c>
       <c r="B286" t="s">
-        <v>524</v>
+        <v>563</v>
       </c>
       <c r="C286" t="s">
-        <v>317</v>
+        <v>246</v>
       </c>
       <c r="E286" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F286">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G286" t="s">
         <v>67</v>
@@ -9452,21 +9428,21 @@
         <v>67</v>
       </c>
       <c r="I286" t="s">
-        <v>497</v>
+        <v>421</v>
       </c>
     </row>
     <row r="287" spans="1:9">
       <c r="A287" t="s">
-        <v>519</v>
+        <v>562</v>
       </c>
       <c r="B287" t="s">
-        <v>520</v>
+        <v>563</v>
       </c>
       <c r="C287" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="E287" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F287">
         <v>1.0</v>
@@ -9478,21 +9454,21 @@
         <v>67</v>
       </c>
       <c r="I287" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
-        <v>519</v>
+        <v>564</v>
       </c>
       <c r="B288" t="s">
-        <v>520</v>
+        <v>565</v>
       </c>
       <c r="C288" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="E288" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F288">
         <v>1.0</v>
@@ -9504,24 +9480,24 @@
         <v>67</v>
       </c>
       <c r="I288" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
-        <v>508</v>
+        <v>564</v>
       </c>
       <c r="B289" t="s">
-        <v>509</v>
+        <v>565</v>
       </c>
       <c r="C289" t="s">
-        <v>317</v>
+        <v>246</v>
       </c>
       <c r="E289" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F289">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G289" t="s">
         <v>67</v>
@@ -9530,24 +9506,24 @@
         <v>67</v>
       </c>
       <c r="I289" t="s">
-        <v>497</v>
+        <v>427</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
-        <v>530</v>
+        <v>564</v>
       </c>
       <c r="B290" t="s">
-        <v>531</v>
+        <v>565</v>
       </c>
       <c r="C290" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="E290" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F290">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G290" t="s">
         <v>67</v>
@@ -9561,19 +9537,19 @@
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="B291" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="C291" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="E291" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F291">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G291" t="s">
         <v>67</v>
@@ -9582,24 +9558,24 @@
         <v>67</v>
       </c>
       <c r="I291" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" t="s">
-        <v>572</v>
+        <v>520</v>
       </c>
       <c r="B292" t="s">
-        <v>573</v>
+        <v>521</v>
       </c>
       <c r="C292" t="s">
-        <v>247</v>
+        <v>360</v>
       </c>
       <c r="E292" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F292">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G292" t="s">
         <v>67</v>
@@ -9608,21 +9584,21 @@
         <v>67</v>
       </c>
       <c r="I292" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
     </row>
     <row r="293" spans="1:9">
       <c r="A293" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="B293" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="C293" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="E293" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F293">
         <v>1.0</v>
@@ -9634,21 +9610,21 @@
         <v>67</v>
       </c>
       <c r="I293" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="294" spans="1:9">
       <c r="A294" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="B294" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="C294" t="s">
-        <v>317</v>
+        <v>246</v>
       </c>
       <c r="E294" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F294">
         <v>1.0</v>
@@ -9660,24 +9636,24 @@
         <v>67</v>
       </c>
       <c r="I294" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
     </row>
     <row r="295" spans="1:9">
       <c r="A295" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="B295" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="C295" t="s">
-        <v>247</v>
+        <v>333</v>
       </c>
       <c r="E295" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F295">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G295" t="s">
         <v>67</v>
@@ -9686,24 +9662,24 @@
         <v>67</v>
       </c>
       <c r="I295" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="296" spans="1:9">
       <c r="A296" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="B296" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="C296" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="E296" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F296">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G296" t="s">
         <v>67</v>
@@ -9712,24 +9688,24 @@
         <v>67</v>
       </c>
       <c r="I296" t="s">
-        <v>456</v>
+        <v>388</v>
       </c>
     </row>
     <row r="297" spans="1:9">
       <c r="A297" t="s">
-        <v>528</v>
+        <v>568</v>
       </c>
       <c r="B297" t="s">
-        <v>529</v>
+        <v>569</v>
       </c>
       <c r="C297" t="s">
-        <v>339</v>
+        <v>246</v>
       </c>
       <c r="E297" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F297">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G297" t="s">
         <v>67</v>
@@ -9738,24 +9714,24 @@
         <v>67</v>
       </c>
       <c r="I297" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
     </row>
     <row r="298" spans="1:9">
       <c r="A298" t="s">
-        <v>528</v>
+        <v>568</v>
       </c>
       <c r="B298" t="s">
-        <v>529</v>
+        <v>569</v>
       </c>
       <c r="C298" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="E298" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F298">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G298" t="s">
         <v>67</v>
@@ -9764,24 +9740,24 @@
         <v>67</v>
       </c>
       <c r="I298" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
     </row>
     <row r="299" spans="1:9">
       <c r="A299" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="B299" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C299" t="s">
-        <v>317</v>
+        <v>360</v>
       </c>
       <c r="E299" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F299">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G299" t="s">
         <v>67</v>
@@ -9790,24 +9766,24 @@
         <v>67</v>
       </c>
       <c r="I299" t="s">
-        <v>448</v>
+        <v>506</v>
       </c>
     </row>
     <row r="300" spans="1:9">
       <c r="A300" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="B300" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C300" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="E300" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F300">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G300" t="s">
         <v>67</v>
@@ -9816,24 +9792,24 @@
         <v>67</v>
       </c>
       <c r="I300" t="s">
-        <v>448</v>
+        <v>388</v>
       </c>
     </row>
     <row r="301" spans="1:9">
       <c r="A301" t="s">
-        <v>576</v>
+        <v>527</v>
       </c>
       <c r="B301" t="s">
-        <v>577</v>
+        <v>528</v>
       </c>
       <c r="C301" t="s">
-        <v>339</v>
+        <v>158</v>
       </c>
       <c r="E301" t="s">
-        <v>330</v>
+        <v>126</v>
       </c>
       <c r="F301">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G301" t="s">
         <v>67</v>
@@ -9842,24 +9818,24 @@
         <v>67</v>
       </c>
       <c r="I301" t="s">
-        <v>448</v>
+        <v>166</v>
       </c>
     </row>
     <row r="302" spans="1:9">
       <c r="A302" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="B302" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="C302" t="s">
-        <v>317</v>
+        <v>125</v>
       </c>
       <c r="E302" t="s">
-        <v>330</v>
+        <v>223</v>
       </c>
       <c r="F302">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G302" t="s">
         <v>67</v>
@@ -9868,24 +9844,24 @@
         <v>67</v>
       </c>
       <c r="I302" t="s">
-        <v>396</v>
+        <v>225</v>
       </c>
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="B303" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="C303" t="s">
-        <v>247</v>
+        <v>360</v>
       </c>
       <c r="E303" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="F303">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G303" t="s">
         <v>67</v>
@@ -9894,24 +9870,24 @@
         <v>67</v>
       </c>
       <c r="I303" t="s">
-        <v>482</v>
+        <v>549</v>
       </c>
     </row>
     <row r="304" spans="1:9">
       <c r="A304" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="B304" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="C304" t="s">
-        <v>339</v>
+        <v>246</v>
       </c>
       <c r="E304" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="F304">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G304" t="s">
         <v>67</v>
@@ -9920,24 +9896,24 @@
         <v>67</v>
       </c>
       <c r="I304" t="s">
-        <v>482</v>
+        <v>549</v>
       </c>
     </row>
     <row r="305" spans="1:9">
       <c r="A305" t="s">
-        <v>578</v>
+        <v>460</v>
       </c>
       <c r="B305" t="s">
-        <v>579</v>
+        <v>461</v>
       </c>
       <c r="C305" t="s">
-        <v>368</v>
+        <v>268</v>
       </c>
       <c r="E305" t="s">
-        <v>330</v>
+        <v>462</v>
       </c>
       <c r="F305">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G305" t="s">
         <v>67</v>
@@ -9946,163 +9922,7 @@
         <v>67</v>
       </c>
       <c r="I305" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="306" spans="1:9">
-      <c r="A306" t="s">
-        <v>578</v>
-      </c>
-      <c r="B306" t="s">
-        <v>579</v>
-      </c>
-      <c r="C306" t="s">
-        <v>269</v>
-      </c>
-      <c r="E306" t="s">
-        <v>330</v>
-      </c>
-      <c r="F306">
-        <v>4.0</v>
-      </c>
-      <c r="G306" t="s">
-        <v>67</v>
-      </c>
-      <c r="H306" t="s">
-        <v>67</v>
-      </c>
-      <c r="I306" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="307" spans="1:9">
-      <c r="A307" t="s">
-        <v>535</v>
-      </c>
-      <c r="B307" t="s">
-        <v>536</v>
-      </c>
-      <c r="C307" t="s">
-        <v>158</v>
-      </c>
-      <c r="E307" t="s">
-        <v>126</v>
-      </c>
-      <c r="F307">
-        <v>2.0</v>
-      </c>
-      <c r="G307" t="s">
-        <v>67</v>
-      </c>
-      <c r="H307" t="s">
-        <v>67</v>
-      </c>
-      <c r="I307" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="308" spans="1:9">
-      <c r="A308" t="s">
-        <v>580</v>
-      </c>
-      <c r="B308" t="s">
-        <v>581</v>
-      </c>
-      <c r="C308" t="s">
-        <v>125</v>
-      </c>
-      <c r="E308" t="s">
-        <v>224</v>
-      </c>
-      <c r="F308">
-        <v>1.0</v>
-      </c>
-      <c r="G308" t="s">
-        <v>67</v>
-      </c>
-      <c r="H308" t="s">
-        <v>67</v>
-      </c>
-      <c r="I308" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="309" spans="1:9">
-      <c r="A309" t="s">
-        <v>582</v>
-      </c>
-      <c r="B309" t="s">
-        <v>583</v>
-      </c>
-      <c r="C309" t="s">
-        <v>368</v>
-      </c>
-      <c r="E309" t="s">
-        <v>470</v>
-      </c>
-      <c r="F309">
-        <v>1.0</v>
-      </c>
-      <c r="G309" t="s">
-        <v>67</v>
-      </c>
-      <c r="H309" t="s">
-        <v>67</v>
-      </c>
-      <c r="I309" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="310" spans="1:9">
-      <c r="A310" t="s">
-        <v>582</v>
-      </c>
-      <c r="B310" t="s">
-        <v>583</v>
-      </c>
-      <c r="C310" t="s">
-        <v>247</v>
-      </c>
-      <c r="E310" t="s">
-        <v>470</v>
-      </c>
-      <c r="F310">
-        <v>1.0</v>
-      </c>
-      <c r="G310" t="s">
-        <v>67</v>
-      </c>
-      <c r="H310" t="s">
-        <v>67</v>
-      </c>
-      <c r="I310" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="311" spans="1:9">
-      <c r="A311" t="s">
-        <v>468</v>
-      </c>
-      <c r="B311" t="s">
-        <v>469</v>
-      </c>
-      <c r="C311" t="s">
-        <v>269</v>
-      </c>
-      <c r="E311" t="s">
-        <v>470</v>
-      </c>
-      <c r="F311">
-        <v>2.0</v>
-      </c>
-      <c r="G311" t="s">
-        <v>67</v>
-      </c>
-      <c r="H311" t="s">
-        <v>67</v>
-      </c>
-      <c r="I311" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>

--- a/src/inventory/War.xlsx
+++ b/src/inventory/War.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="553">
   <si>
     <t>Code/SKU</t>
   </si>
@@ -374,18 +374,6 @@
     <t>৳1,690.00</t>
   </si>
   <si>
-    <t>109-0101-011</t>
-  </si>
-  <si>
-    <t>Rustic Classic Leather Long Wallet</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,WALLET,LONG</t>
-  </si>
-  <si>
-    <t>৳1,149.00</t>
-  </si>
-  <si>
     <t>110-0101-012</t>
   </si>
   <si>
@@ -749,510 +737,468 @@
     <t>৳686.27</t>
   </si>
   <si>
-    <t>1105-0301-001</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt</t>
+    <t>109-0104-001</t>
+  </si>
+  <si>
+    <t>Card Holder 001</t>
+  </si>
+  <si>
+    <t>৳350.00</t>
+  </si>
+  <si>
+    <t>৳700.00</t>
+  </si>
+  <si>
+    <t>৳1,180.00</t>
+  </si>
+  <si>
+    <t>107-0100-051</t>
+  </si>
+  <si>
+    <t>Cool Aqua Boxer Brief</t>
+  </si>
+  <si>
+    <t>Men / 15% OFF,SALE,MEN,BOXER,BRIEFS</t>
+  </si>
+  <si>
+    <t>৳280.00</t>
+  </si>
+  <si>
+    <t>৳1,400.00</t>
+  </si>
+  <si>
+    <t>৳1,745.00</t>
+  </si>
+  <si>
+    <t>৳227.28</t>
+  </si>
+  <si>
+    <t>৳1,363.65</t>
+  </si>
+  <si>
+    <t>109-0402-058</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 58</t>
+  </si>
+  <si>
+    <t>৳218.18</t>
+  </si>
+  <si>
+    <t>৳210.00</t>
+  </si>
+  <si>
+    <t>৳840.00</t>
+  </si>
+  <si>
+    <t>৳3,952.00</t>
+  </si>
+  <si>
+    <t>109-0402-057</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 57</t>
+  </si>
+  <si>
+    <t>109-0104-002</t>
+  </si>
+  <si>
+    <t>Card Holder 002</t>
+  </si>
+  <si>
+    <t>109-0104-003</t>
+  </si>
+  <si>
+    <t>Card Holder 003</t>
+  </si>
+  <si>
+    <t>৳590.00</t>
+  </si>
+  <si>
+    <t>৳185.94</t>
+  </si>
+  <si>
+    <t>৳371.88</t>
+  </si>
+  <si>
+    <t>109-0104-004</t>
+  </si>
+  <si>
+    <t>Card Holder 004</t>
+  </si>
+  <si>
+    <t>109-0402-051</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 51</t>
+  </si>
+  <si>
+    <t>৳35.87</t>
+  </si>
+  <si>
+    <t>৳107.61</t>
+  </si>
+  <si>
+    <t>৳2,970.00</t>
+  </si>
+  <si>
+    <t>109-0402-048</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 48</t>
+  </si>
+  <si>
+    <t>৳990.00</t>
+  </si>
+  <si>
+    <t>109-0502-001</t>
+  </si>
+  <si>
+    <t>Breathable Face Mask</t>
+  </si>
+  <si>
+    <t>Men / MEN,ACCESSORIES,MASK</t>
+  </si>
+  <si>
+    <t>৳199.51</t>
+  </si>
+  <si>
+    <t>৳1,197.09</t>
+  </si>
+  <si>
+    <t>৳1,680.00</t>
+  </si>
+  <si>
+    <t>105-0201-033</t>
+  </si>
+  <si>
+    <t>Full Sleeve Neon Stripe T-shirt</t>
+  </si>
+  <si>
+    <t>109-0402-050</t>
+  </si>
+  <si>
+    <t>Leather Premium Belt 50</t>
+  </si>
+  <si>
+    <t>105-0301-005</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 05</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Men / Drop Shoulder</t>
+  </si>
+  <si>
+    <t>৳431.25</t>
+  </si>
+  <si>
+    <t>৳790.00</t>
+  </si>
+  <si>
+    <t>101-0300-140</t>
+  </si>
+  <si>
+    <t>Straight Fit Blue Jeans</t>
+  </si>
+  <si>
+    <t>Men / MEN,JEANS,STRAIGHT FIT</t>
+  </si>
+  <si>
+    <t>৳6,760.00</t>
+  </si>
+  <si>
+    <t>105-0301-004</t>
+  </si>
+  <si>
+    <t>Drop Shoulder T-Shirt 004</t>
   </si>
   <si>
     <t>L</t>
   </si>
   <si>
-    <t>Men / Drop Shoulder</t>
-  </si>
-  <si>
-    <t>৳550.00</t>
+    <t>Men / T-SHIRT,Drop Shoulder</t>
+  </si>
+  <si>
+    <t>109-0402-061</t>
+  </si>
+  <si>
+    <t>Premium Leather Belt 061</t>
+  </si>
+  <si>
+    <t>৳900.00</t>
+  </si>
+  <si>
+    <t>102-0302-005</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 005</t>
+  </si>
+  <si>
+    <t>Men / SHIRT</t>
+  </si>
+  <si>
+    <t>৳325.00</t>
+  </si>
+  <si>
+    <t>৳2,600.00</t>
+  </si>
+  <si>
+    <t>৳9,440.00</t>
+  </si>
+  <si>
+    <t>102-0302-008</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 008</t>
+  </si>
+  <si>
+    <t>৳285.71</t>
+  </si>
+  <si>
+    <t>৳2,000.00</t>
+  </si>
+  <si>
+    <t>৳9,275.00</t>
+  </si>
+  <si>
+    <t>৳2,184.00</t>
+  </si>
+  <si>
+    <t>105-0301-008</t>
+  </si>
+  <si>
+    <t>Crew Graphic Drop Shoulder T-Shirt</t>
+  </si>
+  <si>
+    <t>Men / T-SHIRT</t>
+  </si>
+  <si>
+    <t>৳332.44</t>
+  </si>
+  <si>
+    <t>৳664.88</t>
+  </si>
+  <si>
+    <t>৳1,580.00</t>
+  </si>
+  <si>
+    <t>109-0104-005</t>
+  </si>
+  <si>
+    <t>Card Holder</t>
+  </si>
+  <si>
+    <t>Men / Card Holder</t>
+  </si>
+  <si>
+    <t>৳690.00</t>
+  </si>
+  <si>
+    <t>109-0104-006</t>
+  </si>
+  <si>
+    <t>Card Holder 06</t>
+  </si>
+  <si>
+    <t>105-0401-006</t>
+  </si>
+  <si>
+    <t>Burgundy Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>Men / Tank Top</t>
+  </si>
+  <si>
+    <t>৳250.00</t>
+  </si>
+  <si>
+    <t>৳500.00</t>
+  </si>
+  <si>
+    <t>৳1,080.00</t>
+  </si>
+  <si>
+    <t>103-0200-098</t>
+  </si>
+  <si>
+    <t>White Polo Shirt in Cotton Pique</t>
+  </si>
+  <si>
+    <t>৳798.00</t>
+  </si>
+  <si>
+    <t>2XL</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>৳111.94</t>
+  </si>
+  <si>
+    <t>102-0402-032</t>
+  </si>
+  <si>
+    <t>Dark Blue Denim Shirt</t>
+  </si>
+  <si>
+    <t>Men / NEW IN,NEW,MEN,SHIRT,CASUAL SHIRT,DENIM SHIRT,FULL SLEEVE</t>
+  </si>
+  <si>
+    <t>103-0200-100</t>
+  </si>
+  <si>
+    <t>Malibu Polo Shirt in Cotton Pique</t>
+  </si>
+  <si>
+    <t>109-0101-050</t>
+  </si>
+  <si>
+    <t>Leather Long Wallet 50</t>
+  </si>
+  <si>
+    <t>Men / WALLET,LONG</t>
+  </si>
+  <si>
+    <t>৳1,299.00</t>
+  </si>
+  <si>
+    <t>105-0401-005</t>
+  </si>
+  <si>
+    <t>Sable Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>102-0302-002</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 002</t>
+  </si>
+  <si>
+    <t>৳466.67</t>
+  </si>
+  <si>
+    <t>৳2,800.00</t>
+  </si>
+  <si>
+    <t>৳8,700.00</t>
+  </si>
+  <si>
+    <t>105-0401-003</t>
+  </si>
+  <si>
+    <t>Tank Top 003</t>
+  </si>
+  <si>
+    <t>Men / T-SHIRT,Tank Top</t>
+  </si>
+  <si>
+    <t>৳1,750.00</t>
+  </si>
+  <si>
+    <t>৳4,480.00</t>
+  </si>
+  <si>
+    <t>৳750.00</t>
+  </si>
+  <si>
+    <t>৳1,620.00</t>
+  </si>
+  <si>
+    <t>102-0301-004</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 004</t>
+  </si>
+  <si>
+    <t>৳243.75</t>
+  </si>
+  <si>
+    <t>৳1,950.00</t>
+  </si>
+  <si>
+    <t>৳487.50</t>
+  </si>
+  <si>
+    <t>৳4,720.00</t>
+  </si>
+  <si>
+    <t>৳200.00</t>
+  </si>
+  <si>
+    <t>৳1,000.00</t>
+  </si>
+  <si>
+    <t>৳6,625.00</t>
+  </si>
+  <si>
+    <t>109-0101-049</t>
+  </si>
+  <si>
+    <t>Leather Long Wallet 049</t>
+  </si>
+  <si>
+    <t>102-0302-006</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 006</t>
+  </si>
+  <si>
+    <t>৳278.57</t>
+  </si>
+  <si>
+    <t>৳2,500.00</t>
+  </si>
+  <si>
+    <t>৳6,400.00</t>
+  </si>
+  <si>
+    <t>৳5,300.00</t>
+  </si>
+  <si>
+    <t>105-0401-007</t>
+  </si>
+  <si>
+    <t>Cabbage Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>102-0301-002</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 002</t>
+  </si>
+  <si>
+    <t>৳216.67</t>
+  </si>
+  <si>
+    <t>৳11,925.00</t>
+  </si>
+  <si>
+    <t>102-0302-001</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 001</t>
+  </si>
+  <si>
+    <t>৳10,150.00</t>
+  </si>
+  <si>
+    <t>3XL</t>
+  </si>
+  <si>
+    <t>৳1,300.00</t>
+  </si>
+  <si>
+    <t>৳412.50</t>
   </si>
   <si>
     <t>৳1,650.00</t>
   </si>
   <si>
-    <t>৳2,520.00</t>
-  </si>
-  <si>
-    <t>109-0104-001</t>
-  </si>
-  <si>
-    <t>Card Holder 001</t>
-  </si>
-  <si>
-    <t>৳350.00</t>
-  </si>
-  <si>
-    <t>৳700.00</t>
-  </si>
-  <si>
-    <t>৳1,180.00</t>
-  </si>
-  <si>
-    <t>107-0100-051</t>
-  </si>
-  <si>
-    <t>Cool Aqua Boxer Brief</t>
-  </si>
-  <si>
-    <t>Men / 15% OFF,SALE,MEN,BOXER,BRIEFS</t>
-  </si>
-  <si>
-    <t>৳280.00</t>
-  </si>
-  <si>
-    <t>৳1,400.00</t>
-  </si>
-  <si>
-    <t>৳1,745.00</t>
-  </si>
-  <si>
-    <t>৳227.28</t>
-  </si>
-  <si>
-    <t>৳1,363.65</t>
-  </si>
-  <si>
-    <t>109-0402-058</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 58</t>
-  </si>
-  <si>
-    <t>105-0301-008</t>
-  </si>
-  <si>
-    <t>Crew Graphic Drop Shoulder T-Shirt</t>
-  </si>
-  <si>
-    <t>3XL</t>
-  </si>
-  <si>
-    <t>Men / T-SHIRT</t>
-  </si>
-  <si>
-    <t>৳790.00</t>
-  </si>
-  <si>
-    <t>৳218.18</t>
-  </si>
-  <si>
-    <t>৳210.00</t>
-  </si>
-  <si>
-    <t>৳840.00</t>
-  </si>
-  <si>
-    <t>৳3,952.00</t>
-  </si>
-  <si>
-    <t>109-0402-057</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 57</t>
-  </si>
-  <si>
-    <t>109-0104-002</t>
-  </si>
-  <si>
-    <t>Card Holder 002</t>
-  </si>
-  <si>
-    <t>109-0104-003</t>
-  </si>
-  <si>
-    <t>Card Holder 003</t>
-  </si>
-  <si>
-    <t>৳590.00</t>
-  </si>
-  <si>
-    <t>৳185.94</t>
-  </si>
-  <si>
-    <t>৳371.88</t>
-  </si>
-  <si>
-    <t>109-0104-004</t>
-  </si>
-  <si>
-    <t>Card Holder 004</t>
-  </si>
-  <si>
-    <t>109-0402-051</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 51</t>
-  </si>
-  <si>
-    <t>৳35.87</t>
-  </si>
-  <si>
-    <t>৳107.61</t>
-  </si>
-  <si>
-    <t>৳2,970.00</t>
-  </si>
-  <si>
-    <t>109-0402-048</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 48</t>
-  </si>
-  <si>
-    <t>৳990.00</t>
-  </si>
-  <si>
-    <t>109-0102-074</t>
-  </si>
-  <si>
-    <t>Bifold Wallet 74</t>
-  </si>
-  <si>
-    <t>Men / WALLET,BI-FOLD</t>
-  </si>
-  <si>
-    <t>৳699.00</t>
-  </si>
-  <si>
-    <t>109-0502-001</t>
-  </si>
-  <si>
-    <t>Breathable Face Mask</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,MASK</t>
-  </si>
-  <si>
-    <t>৳199.51</t>
-  </si>
-  <si>
-    <t>৳1,197.09</t>
-  </si>
-  <si>
-    <t>৳1,680.00</t>
-  </si>
-  <si>
-    <t>105-0201-033</t>
-  </si>
-  <si>
-    <t>Full Sleeve Neon Stripe T-shirt</t>
-  </si>
-  <si>
-    <t>109-0402-050</t>
-  </si>
-  <si>
-    <t>Leather Premium Belt 50</t>
-  </si>
-  <si>
-    <t>105-0301-005</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 05</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>৳431.25</t>
-  </si>
-  <si>
-    <t>101-0300-140</t>
-  </si>
-  <si>
-    <t>Straight Fit Blue Jeans</t>
-  </si>
-  <si>
-    <t>Men / MEN,JEANS,STRAIGHT FIT</t>
-  </si>
-  <si>
-    <t>৳6,760.00</t>
-  </si>
-  <si>
-    <t>105-0301-004</t>
-  </si>
-  <si>
-    <t>Drop Shoulder T-Shirt 004</t>
-  </si>
-  <si>
-    <t>Men / T-SHIRT,Drop Shoulder</t>
-  </si>
-  <si>
-    <t>109-0402-061</t>
-  </si>
-  <si>
-    <t>Premium Leather Belt 061</t>
-  </si>
-  <si>
-    <t>৳900.00</t>
-  </si>
-  <si>
-    <t>102-0302-005</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 005</t>
-  </si>
-  <si>
-    <t>Men / SHIRT</t>
-  </si>
-  <si>
-    <t>৳325.00</t>
-  </si>
-  <si>
-    <t>৳2,600.00</t>
-  </si>
-  <si>
-    <t>৳9,440.00</t>
-  </si>
-  <si>
-    <t>102-0302-008</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 008</t>
-  </si>
-  <si>
-    <t>৳285.71</t>
-  </si>
-  <si>
-    <t>৳2,000.00</t>
-  </si>
-  <si>
-    <t>৳9,275.00</t>
-  </si>
-  <si>
-    <t>XL</t>
-  </si>
-  <si>
-    <t>৳1,580.00</t>
-  </si>
-  <si>
-    <t>109-0501-001</t>
-  </si>
-  <si>
-    <t>Durable Aluminum Water Bottle 600 ml.</t>
-  </si>
-  <si>
-    <t>Men / MEN,ACCESSORIES,WATER BOTTLE</t>
-  </si>
-  <si>
-    <t>৳155.51</t>
-  </si>
-  <si>
-    <t>৳466.52</t>
-  </si>
-  <si>
-    <t>৳1,197.00</t>
-  </si>
-  <si>
-    <t>৳2,184.00</t>
-  </si>
-  <si>
-    <t>৳332.44</t>
-  </si>
-  <si>
-    <t>৳1,329.77</t>
-  </si>
-  <si>
-    <t>৳3,160.00</t>
-  </si>
-  <si>
-    <t>109-0104-005</t>
-  </si>
-  <si>
-    <t>Card Holder</t>
-  </si>
-  <si>
-    <t>Men / Card Holder</t>
-  </si>
-  <si>
-    <t>৳690.00</t>
-  </si>
-  <si>
-    <t>109-0104-006</t>
-  </si>
-  <si>
-    <t>Card Holder 06</t>
-  </si>
-  <si>
-    <t>105-0401-006</t>
-  </si>
-  <si>
-    <t>Burgundy Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>Men / Tank Top</t>
-  </si>
-  <si>
-    <t>৳250.00</t>
-  </si>
-  <si>
-    <t>৳750.00</t>
-  </si>
-  <si>
-    <t>৳1,620.00</t>
-  </si>
-  <si>
-    <t>103-0200-098</t>
-  </si>
-  <si>
-    <t>White Polo Shirt in Cotton Pique</t>
-  </si>
-  <si>
-    <t>৳798.00</t>
-  </si>
-  <si>
-    <t>2XL</t>
-  </si>
-  <si>
-    <t>৳111.94</t>
-  </si>
-  <si>
-    <t>102-0402-032</t>
-  </si>
-  <si>
-    <t>Dark Blue Denim Shirt</t>
-  </si>
-  <si>
-    <t>Men / NEW IN,NEW,MEN,SHIRT,CASUAL SHIRT,DENIM SHIRT,FULL SLEEVE</t>
-  </si>
-  <si>
-    <t>103-0200-100</t>
-  </si>
-  <si>
-    <t>Malibu Polo Shirt in Cotton Pique</t>
-  </si>
-  <si>
-    <t>109-0101-050</t>
-  </si>
-  <si>
-    <t>Leather Long Wallet 50</t>
-  </si>
-  <si>
-    <t>Men / WALLET,LONG</t>
-  </si>
-  <si>
-    <t>৳1,299.00</t>
-  </si>
-  <si>
-    <t>105-0401-005</t>
-  </si>
-  <si>
-    <t>Sable Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>102-0302-002</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 002</t>
-  </si>
-  <si>
-    <t>৳466.67</t>
-  </si>
-  <si>
-    <t>৳2,800.00</t>
-  </si>
-  <si>
-    <t>৳8,700.00</t>
-  </si>
-  <si>
-    <t>105-0401-003</t>
-  </si>
-  <si>
-    <t>Tank Top 003</t>
-  </si>
-  <si>
-    <t>Men / T-SHIRT,Tank Top</t>
-  </si>
-  <si>
-    <t>৳1,750.00</t>
-  </si>
-  <si>
-    <t>৳4,480.00</t>
-  </si>
-  <si>
-    <t>102-0301-004</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 004</t>
-  </si>
-  <si>
-    <t>৳243.75</t>
-  </si>
-  <si>
-    <t>৳1,950.00</t>
-  </si>
-  <si>
-    <t>৳487.50</t>
-  </si>
-  <si>
-    <t>৳4,720.00</t>
-  </si>
-  <si>
-    <t>৳200.00</t>
-  </si>
-  <si>
-    <t>৳1,000.00</t>
-  </si>
-  <si>
-    <t>৳6,625.00</t>
-  </si>
-  <si>
-    <t>109-0101-049</t>
-  </si>
-  <si>
-    <t>Leather Long Wallet 049</t>
-  </si>
-  <si>
-    <t>102-0302-006</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 006</t>
-  </si>
-  <si>
-    <t>৳278.57</t>
-  </si>
-  <si>
-    <t>৳2,500.00</t>
-  </si>
-  <si>
-    <t>৳6,400.00</t>
-  </si>
-  <si>
-    <t>৳5,300.00</t>
-  </si>
-  <si>
-    <t>105-0401-007</t>
-  </si>
-  <si>
-    <t>Cabbage Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>৳500.00</t>
-  </si>
-  <si>
-    <t>102-0301-002</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 002</t>
-  </si>
-  <si>
-    <t>৳216.67</t>
-  </si>
-  <si>
-    <t>৳11,925.00</t>
-  </si>
-  <si>
-    <t>102-0302-001</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 001</t>
-  </si>
-  <si>
-    <t>৳10,150.00</t>
-  </si>
-  <si>
-    <t>৳1,300.00</t>
-  </si>
-  <si>
-    <t>৳412.50</t>
-  </si>
-  <si>
     <t>৳5,800.00</t>
   </si>
   <si>
@@ -1262,175 +1208,199 @@
     <t>৳195.00</t>
   </si>
   <si>
-    <t>৳11,800.00</t>
+    <t>৳1,755.00</t>
+  </si>
+  <si>
+    <t>৳10,620.00</t>
   </si>
   <si>
     <t>৳10,600.00</t>
   </si>
   <si>
+    <t>৳2,560.00</t>
+  </si>
+  <si>
+    <t>৳2,900.00</t>
+  </si>
+  <si>
+    <t>102-0302-004</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 004</t>
+  </si>
+  <si>
+    <t>102-0302-007</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 007</t>
+  </si>
+  <si>
+    <t>৳3,975.00</t>
+  </si>
+  <si>
+    <t>107-0100-041</t>
+  </si>
+  <si>
+    <t>Black Boxer Brief</t>
+  </si>
+  <si>
+    <t>Men / 30% OFF,MEN,BOXER,BRIEFS,Draft Items</t>
+  </si>
+  <si>
+    <t>105-0401-001</t>
+  </si>
+  <si>
+    <t>Black Relaxed Graphic Tank Top</t>
+  </si>
+  <si>
+    <t>৳1,050.00</t>
+  </si>
+  <si>
+    <t>105-0101-372</t>
+  </si>
+  <si>
+    <t>Deep Harbor T-shirt</t>
+  </si>
+  <si>
+    <t>Men / NEW IN,NEW,MEN,T-SHIRT,HALF SLEEVE</t>
+  </si>
+  <si>
+    <t>৳630.00</t>
+  </si>
+  <si>
+    <t>102-0302-003</t>
+  </si>
+  <si>
+    <t>Cuban Shier 003</t>
+  </si>
+  <si>
+    <t>৳1,450.00</t>
+  </si>
+  <si>
     <t>105-0401-004</t>
   </si>
   <si>
     <t>Orlando Relaxed Graphic Tank Top</t>
   </si>
   <si>
-    <t>৳2,560.00</t>
-  </si>
-  <si>
-    <t>৳1,080.00</t>
-  </si>
-  <si>
-    <t>৳2,900.00</t>
-  </si>
-  <si>
-    <t>102-0302-004</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 004</t>
+    <t>105-0101-377</t>
+  </si>
+  <si>
+    <t>Warm Spice T-shirt</t>
+  </si>
+  <si>
+    <t>102-0302-010</t>
+  </si>
+  <si>
+    <t>Cuban Shirt 010</t>
+  </si>
+  <si>
+    <t>৳275.00</t>
+  </si>
+  <si>
+    <t>৳1,100.00</t>
+  </si>
+  <si>
+    <t>৳3,200.00</t>
+  </si>
+  <si>
+    <t>৳2,650.00</t>
+  </si>
+  <si>
+    <t>৳1,325.00</t>
+  </si>
+  <si>
+    <t>৳650.00</t>
+  </si>
+  <si>
+    <t>৳4,350.00</t>
+  </si>
+  <si>
+    <t>৳287.50</t>
+  </si>
+  <si>
+    <t>৳1,150.00</t>
+  </si>
+  <si>
+    <t>109-0101-045</t>
+  </si>
+  <si>
+    <t>Burgendy Leather Long Wallet</t>
+  </si>
+  <si>
+    <t>Men / NEW IN,NEW,MEN,ACCESSORIES,WALLET,LONG</t>
+  </si>
+  <si>
+    <t>102-0501-001</t>
+  </si>
+  <si>
+    <t>Formal Shirt 001</t>
+  </si>
+  <si>
+    <t>Men / SHIRT,FORMAL SHIRT</t>
+  </si>
+  <si>
+    <t>৳4,760.00</t>
+  </si>
+  <si>
+    <t>105-0101-371</t>
+  </si>
+  <si>
+    <t>Green Essence T-shirt</t>
+  </si>
+  <si>
+    <t>৳175.00</t>
+  </si>
+  <si>
+    <t>৳875.00</t>
+  </si>
+  <si>
+    <t>৳2,950.00</t>
+  </si>
+  <si>
+    <t>105-0101-374</t>
+  </si>
+  <si>
+    <t>Golden Corn T-shirt</t>
+  </si>
+  <si>
+    <t>৳2,360.00</t>
   </si>
   <si>
     <t>৳540.00</t>
   </si>
   <si>
-    <t>102-0302-007</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 007</t>
-  </si>
-  <si>
-    <t>৳3,975.00</t>
-  </si>
-  <si>
-    <t>107-0100-041</t>
-  </si>
-  <si>
-    <t>Black Boxer Brief</t>
-  </si>
-  <si>
-    <t>Men / 30% OFF,MEN,BOXER,BRIEFS,Draft Items</t>
-  </si>
-  <si>
-    <t>105-0401-001</t>
-  </si>
-  <si>
-    <t>Black Relaxed Graphic Tank Top</t>
-  </si>
-  <si>
-    <t>৳1,050.00</t>
-  </si>
-  <si>
-    <t>105-0101-372</t>
-  </si>
-  <si>
-    <t>Deep Harbor T-shirt</t>
-  </si>
-  <si>
-    <t>Men / NEW IN,NEW,MEN,T-SHIRT,HALF SLEEVE</t>
-  </si>
-  <si>
-    <t>৳630.00</t>
-  </si>
-  <si>
-    <t>102-0302-003</t>
-  </si>
-  <si>
-    <t>Cuban Shier 003</t>
-  </si>
-  <si>
-    <t>৳1,450.00</t>
-  </si>
-  <si>
-    <t>105-0101-377</t>
-  </si>
-  <si>
-    <t>Warm Spice T-shirt</t>
-  </si>
-  <si>
-    <t>102-0302-010</t>
-  </si>
-  <si>
-    <t>Cuban Shirt 010</t>
-  </si>
-  <si>
-    <t>৳275.00</t>
-  </si>
-  <si>
-    <t>৳1,100.00</t>
-  </si>
-  <si>
-    <t>৳3,200.00</t>
-  </si>
-  <si>
-    <t>৳2,650.00</t>
-  </si>
-  <si>
-    <t>৳1,325.00</t>
-  </si>
-  <si>
-    <t>৳650.00</t>
-  </si>
-  <si>
-    <t>৳4,350.00</t>
-  </si>
-  <si>
-    <t>৳287.50</t>
-  </si>
-  <si>
-    <t>৳1,150.00</t>
-  </si>
-  <si>
-    <t>109-0101-045</t>
-  </si>
-  <si>
-    <t>Burgendy Leather Long Wallet</t>
-  </si>
-  <si>
-    <t>Men / NEW IN,NEW,MEN,ACCESSORIES,WALLET,LONG</t>
-  </si>
-  <si>
-    <t>105-0101-380</t>
-  </si>
-  <si>
-    <t>Essential Black T-shirt</t>
+    <t>৳7,080.00</t>
+  </si>
+  <si>
+    <t>৳1,456.00</t>
+  </si>
+  <si>
+    <t>102-0301-008</t>
+  </si>
+  <si>
+    <t>Half Sleeve shirt 008</t>
+  </si>
+  <si>
+    <t>৳6,360.00</t>
+  </si>
+  <si>
+    <t>105-0101-375</t>
+  </si>
+  <si>
+    <t>Earth Hemp T-shirt</t>
   </si>
   <si>
     <t>৳140.00</t>
   </si>
   <si>
-    <t>102-0501-001</t>
-  </si>
-  <si>
-    <t>Formal Shirt 001</t>
-  </si>
-  <si>
-    <t>Men / SHIRT,FORMAL SHIRT</t>
-  </si>
-  <si>
-    <t>৳4,760.00</t>
-  </si>
-  <si>
-    <t>105-0101-371</t>
-  </si>
-  <si>
-    <t>Green Essence T-shirt</t>
-  </si>
-  <si>
-    <t>৳175.00</t>
-  </si>
-  <si>
-    <t>৳875.00</t>
-  </si>
-  <si>
-    <t>৳2,950.00</t>
-  </si>
-  <si>
-    <t>105-0101-374</t>
-  </si>
-  <si>
-    <t>Golden Corn T-shirt</t>
-  </si>
-  <si>
-    <t>৳2,360.00</t>
+    <t>৳420.00</t>
+  </si>
+  <si>
+    <t>৳1,770.00</t>
+  </si>
+  <si>
+    <t>৳7,950.00</t>
   </si>
   <si>
     <t>105-0401-008</t>
@@ -1439,36 +1409,6 @@
     <t>White Relaxed Graphic Tank Top</t>
   </si>
   <si>
-    <t>৳7,080.00</t>
-  </si>
-  <si>
-    <t>৳1,456.00</t>
-  </si>
-  <si>
-    <t>102-0301-008</t>
-  </si>
-  <si>
-    <t>Half Sleeve shirt 008</t>
-  </si>
-  <si>
-    <t>৳6,360.00</t>
-  </si>
-  <si>
-    <t>105-0101-375</t>
-  </si>
-  <si>
-    <t>Earth Hemp T-shirt</t>
-  </si>
-  <si>
-    <t>৳420.00</t>
-  </si>
-  <si>
-    <t>৳1,770.00</t>
-  </si>
-  <si>
-    <t>৳7,950.00</t>
-  </si>
-  <si>
     <t>105-0201-030</t>
   </si>
   <si>
@@ -1572,9 +1512,6 @@
   </si>
   <si>
     <t>Teal Sweatshirt in French-Terry</t>
-  </si>
-  <si>
-    <t>৳6.37</t>
   </si>
   <si>
     <t>102-0301-014</t>
@@ -2076,7 +2013,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I305"/>
+  <dimension ref="A1:I291"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3308,31 +3245,34 @@
       <c r="B48" t="s">
         <v>120</v>
       </c>
+      <c r="C48" t="s">
+        <v>121</v>
+      </c>
       <c r="E48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F48">
         <v>1.0</v>
       </c>
       <c r="G48" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="H48" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="I48" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C49" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="E49" t="s">
         <v>126</v>
@@ -3347,203 +3287,203 @@
         <v>127</v>
       </c>
       <c r="I49" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E50" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F50">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G50" t="s">
         <v>131</v>
       </c>
       <c r="H50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I50" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B51" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C51" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E51" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F51">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G51" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H51" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I51" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>138</v>
+        <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>139</v>
-      </c>
-      <c r="C52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52">
+        <v>42</v>
+      </c>
+      <c r="E52" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52">
+        <v>1.0</v>
+      </c>
+      <c r="G52" t="s">
         <v>140</v>
       </c>
-      <c r="E52" t="s">
-        <v>126</v>
-      </c>
-      <c r="F52">
-        <v>4.0</v>
-      </c>
-      <c r="G52" t="s">
-        <v>141</v>
-      </c>
       <c r="H52" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I52" t="s">
-        <v>143</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>43</v>
+        <v>124</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
-      </c>
-      <c r="C53">
-        <v>42</v>
+        <v>125</v>
+      </c>
+      <c r="C53" t="s">
+        <v>136</v>
       </c>
       <c r="E53" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="F53">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G53" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H53" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I53" t="s">
-        <v>28</v>
+        <v>143</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
+        <v>124</v>
+      </c>
+      <c r="B54" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" t="s">
+        <v>144</v>
+      </c>
+      <c r="E54" t="s">
+        <v>126</v>
+      </c>
+      <c r="F54">
+        <v>1.0</v>
+      </c>
+      <c r="G54" t="s">
+        <v>67</v>
+      </c>
+      <c r="H54" t="s">
+        <v>67</v>
+      </c>
+      <c r="I54" t="s">
         <v>128</v>
-      </c>
-      <c r="B54" t="s">
-        <v>129</v>
-      </c>
-      <c r="C54" t="s">
-        <v>140</v>
-      </c>
-      <c r="E54" t="s">
-        <v>130</v>
-      </c>
-      <c r="F54">
-        <v>5.0</v>
-      </c>
-      <c r="G54" t="s">
-        <v>145</v>
-      </c>
-      <c r="H54" t="s">
-        <v>146</v>
-      </c>
-      <c r="I54" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="B55" t="s">
-        <v>129</v>
-      </c>
-      <c r="C55" t="s">
+        <v>146</v>
+      </c>
+      <c r="E55" t="s">
+        <v>147</v>
+      </c>
+      <c r="F55">
+        <v>3.0</v>
+      </c>
+      <c r="G55" t="s">
         <v>148</v>
       </c>
-      <c r="E55" t="s">
-        <v>130</v>
-      </c>
-      <c r="F55">
-        <v>1.0</v>
-      </c>
-      <c r="G55" t="s">
-        <v>67</v>
-      </c>
       <c r="H55" t="s">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="I55" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>120</v>
+      </c>
+      <c r="C56" t="s">
+        <v>136</v>
       </c>
       <c r="E56" t="s">
+        <v>122</v>
+      </c>
+      <c r="F56">
+        <v>10.0</v>
+      </c>
+      <c r="G56" t="s">
         <v>151</v>
       </c>
-      <c r="F56">
-        <v>3.0</v>
-      </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>152</v>
       </c>
-      <c r="H56" t="s">
+      <c r="I56" t="s">
         <v>153</v>
-      </c>
-      <c r="I56" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B57" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C57" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E57" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F57">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="G57" t="s">
         <v>155</v>
@@ -3557,88 +3497,88 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s">
-        <v>134</v>
-      </c>
-      <c r="C58" t="s">
-        <v>158</v>
+        <v>22</v>
+      </c>
+      <c r="C58">
+        <v>44</v>
       </c>
       <c r="E58" t="s">
-        <v>126</v>
+        <v>23</v>
       </c>
       <c r="F58">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G58" t="s">
-        <v>159</v>
+        <v>17</v>
       </c>
       <c r="H58" t="s">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="I58" t="s">
-        <v>161</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="B59" t="s">
-        <v>22</v>
-      </c>
-      <c r="C59">
-        <v>44</v>
+        <v>125</v>
+      </c>
+      <c r="C59" t="s">
+        <v>121</v>
       </c>
       <c r="E59" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="F59">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G59" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H59" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="I59" t="s">
-        <v>24</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C60" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="E60" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F60">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G60" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="H60" t="s">
+        <v>161</v>
+      </c>
+      <c r="I60" t="s">
         <v>162</v>
-      </c>
-      <c r="I60" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="B61" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="C61" t="s">
         <v>111</v>
@@ -3647,79 +3587,79 @@
         <v>126</v>
       </c>
       <c r="F61">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G61" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H61" t="s">
         <v>165</v>
       </c>
       <c r="I61" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
+        <v>166</v>
+      </c>
+      <c r="B62" t="s">
         <v>167</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
+        <v>136</v>
+      </c>
+      <c r="E62" t="s">
+        <v>126</v>
+      </c>
+      <c r="F62">
+        <v>2.0</v>
+      </c>
+      <c r="G62" t="s">
         <v>168</v>
-      </c>
-      <c r="C62" t="s">
-        <v>111</v>
-      </c>
-      <c r="E62" t="s">
-        <v>130</v>
-      </c>
-      <c r="F62">
-        <v>1.0</v>
-      </c>
-      <c r="G62" t="s">
-        <v>169</v>
       </c>
       <c r="H62" t="s">
         <v>169</v>
       </c>
       <c r="I62" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="B63" t="s">
+        <v>120</v>
+      </c>
+      <c r="C63" t="s">
+        <v>154</v>
+      </c>
+      <c r="E63" t="s">
+        <v>122</v>
+      </c>
+      <c r="F63">
+        <v>5.0</v>
+      </c>
+      <c r="G63" t="s">
         <v>171</v>
       </c>
-      <c r="C63" t="s">
-        <v>140</v>
-      </c>
-      <c r="E63" t="s">
-        <v>130</v>
-      </c>
-      <c r="F63">
-        <v>2.0</v>
-      </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>172</v>
       </c>
-      <c r="H63" t="s">
+      <c r="I63" t="s">
         <v>173</v>
-      </c>
-      <c r="I63" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="B64" t="s">
-        <v>124</v>
+        <v>167</v>
       </c>
       <c r="C64" t="s">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="E64" t="s">
         <v>126</v>
@@ -3728,140 +3668,140 @@
         <v>5.0</v>
       </c>
       <c r="G64" t="s">
+        <v>174</v>
+      </c>
+      <c r="H64" t="s">
         <v>175</v>
       </c>
-      <c r="H64" t="s">
-        <v>176</v>
-      </c>
       <c r="I64" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B65" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C65" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E65" t="s">
-        <v>130</v>
+        <v>178</v>
       </c>
       <c r="F65">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H65" t="s">
         <v>179</v>
       </c>
       <c r="I65" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
+        <v>176</v>
+      </c>
+      <c r="B66" t="s">
+        <v>177</v>
+      </c>
+      <c r="C66" t="s">
+        <v>144</v>
+      </c>
+      <c r="E66" t="s">
+        <v>178</v>
+      </c>
+      <c r="F66">
+        <v>1.0</v>
+      </c>
+      <c r="G66" t="s">
+        <v>181</v>
+      </c>
+      <c r="H66" t="s">
+        <v>181</v>
+      </c>
+      <c r="I66" t="s">
         <v>180</v>
-      </c>
-      <c r="B66" t="s">
-        <v>181</v>
-      </c>
-      <c r="C66" t="s">
-        <v>140</v>
-      </c>
-      <c r="E66" t="s">
-        <v>182</v>
-      </c>
-      <c r="F66">
-        <v>1.0</v>
-      </c>
-      <c r="G66" t="s">
-        <v>183</v>
-      </c>
-      <c r="H66" t="s">
-        <v>183</v>
-      </c>
-      <c r="I66" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B67" t="s">
-        <v>181</v>
-      </c>
-      <c r="C67" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="E67" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F67">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G67" t="s">
         <v>185</v>
       </c>
       <c r="H67" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I67" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>186</v>
+        <v>129</v>
       </c>
       <c r="B68" t="s">
-        <v>187</v>
+        <v>130</v>
+      </c>
+      <c r="C68" t="s">
+        <v>136</v>
       </c>
       <c r="E68" t="s">
+        <v>122</v>
+      </c>
+      <c r="F68">
+        <v>14.0</v>
+      </c>
+      <c r="G68" t="s">
         <v>188</v>
       </c>
-      <c r="F68">
-        <v>2.0</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>189</v>
       </c>
-      <c r="H68" t="s">
+      <c r="I68" t="s">
         <v>190</v>
-      </c>
-      <c r="I68" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="B69" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E69" t="s">
         <v>126</v>
       </c>
       <c r="F69">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="G69" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H69" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I69" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -3872,13 +3812,13 @@
         <v>196</v>
       </c>
       <c r="C70" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="E70" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F70">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G70" t="s">
         <v>197</v>
@@ -3887,7 +3827,7 @@
         <v>198</v>
       </c>
       <c r="I70" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -3897,89 +3837,86 @@
       <c r="B71" t="s">
         <v>200</v>
       </c>
-      <c r="C71" t="s">
-        <v>125</v>
-      </c>
       <c r="E71" t="s">
-        <v>126</v>
+        <v>201</v>
       </c>
       <c r="F71">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G71" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H71" t="s">
         <v>202</v>
       </c>
       <c r="I71" t="s">
-        <v>161</v>
+        <v>203</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B72" t="s">
+        <v>196</v>
+      </c>
+      <c r="C72" t="s">
+        <v>136</v>
+      </c>
+      <c r="E72" t="s">
+        <v>122</v>
+      </c>
+      <c r="F72">
+        <v>8.0</v>
+      </c>
+      <c r="G72" t="s">
         <v>204</v>
       </c>
-      <c r="E72" t="s">
+      <c r="H72" t="s">
         <v>205</v>
       </c>
-      <c r="F72">
-        <v>1.0</v>
-      </c>
-      <c r="G72" t="s">
+      <c r="I72" t="s">
         <v>206</v>
-      </c>
-      <c r="H72" t="s">
-        <v>206</v>
-      </c>
-      <c r="I72" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B73" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C73" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E73" t="s">
-        <v>126</v>
+        <v>209</v>
       </c>
       <c r="F73">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="G73" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H73" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I73" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B74" t="s">
-        <v>212</v>
-      </c>
-      <c r="C74" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E74" t="s">
-        <v>213</v>
+        <v>147</v>
       </c>
       <c r="F74">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G74" t="s">
         <v>214</v>
@@ -3996,201 +3933,201 @@
         <v>217</v>
       </c>
       <c r="B75" t="s">
-        <v>150</v>
+        <v>218</v>
+      </c>
+      <c r="C75" t="s">
+        <v>154</v>
       </c>
       <c r="E75" t="s">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="F75">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G75" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H75" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I75" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C76" t="s">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="E76" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="F76">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G76" t="s">
         <v>224</v>
       </c>
       <c r="H76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I76" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="B77" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C77" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="E77" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F77">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G77" t="s">
-        <v>228</v>
+        <v>168</v>
       </c>
       <c r="H77" t="s">
-        <v>229</v>
+        <v>168</v>
       </c>
       <c r="I77" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B78" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C78" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="E78" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F78">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G78" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H78" t="s">
-        <v>172</v>
+        <v>227</v>
       </c>
       <c r="I78" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B79" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C79" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="E79" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F79">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G79" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H79" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I79" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B80" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C80" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="E80" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F80">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G80" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H80" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I80" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B81" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="C81" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="E81" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="F81">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G81" t="s">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="H81" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="I81" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="B82" t="s">
-        <v>212</v>
-      </c>
-      <c r="C82" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="E82" t="s">
-        <v>213</v>
+        <v>147</v>
       </c>
       <c r="F82">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G82" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="H82" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="I82" t="s">
         <v>216</v>
@@ -4198,94 +4135,94 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="B83" t="s">
-        <v>150</v>
+        <v>223</v>
+      </c>
+      <c r="C83" t="s">
+        <v>111</v>
       </c>
       <c r="E83" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="F83">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G83" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="H83" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="I83" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B84" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C84" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="E84" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F84">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G84" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H84" t="s">
-        <v>214</v>
+        <v>17</v>
       </c>
       <c r="I84" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="B85" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="C85" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E85" t="s">
-        <v>213</v>
+        <v>122</v>
       </c>
       <c r="F85">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G85" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="H85" t="s">
-        <v>17</v>
+        <v>239</v>
       </c>
       <c r="I85" t="s">
-        <v>241</v>
+        <v>133</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="B86" t="s">
-        <v>200</v>
-      </c>
-      <c r="C86" t="s">
-        <v>158</v>
+        <v>241</v>
       </c>
       <c r="E86" t="s">
-        <v>126</v>
+        <v>201</v>
       </c>
       <c r="F86">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G86" t="s">
         <v>242</v>
@@ -4294,24 +4231,24 @@
         <v>243</v>
       </c>
       <c r="I86" t="s">
-        <v>137</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B87" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C87" t="s">
-        <v>246</v>
+        <v>154</v>
       </c>
       <c r="E87" t="s">
         <v>247</v>
       </c>
       <c r="F87">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G87" t="s">
         <v>248</v>
@@ -4325,333 +4262,330 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
+        <v>124</v>
+      </c>
+      <c r="B88" t="s">
+        <v>125</v>
+      </c>
+      <c r="C88" t="s">
+        <v>154</v>
+      </c>
+      <c r="E88" t="s">
+        <v>126</v>
+      </c>
+      <c r="F88">
+        <v>6.0</v>
+      </c>
+      <c r="G88" t="s">
         <v>251</v>
       </c>
-      <c r="B88" t="s">
+      <c r="H88" t="s">
         <v>252</v>
       </c>
-      <c r="E88" t="s">
-        <v>205</v>
-      </c>
-      <c r="F88">
-        <v>2.0</v>
-      </c>
-      <c r="G88" t="s">
-        <v>253</v>
-      </c>
-      <c r="H88" t="s">
-        <v>254</v>
-      </c>
       <c r="I88" t="s">
-        <v>255</v>
+        <v>159</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B89" t="s">
-        <v>257</v>
-      </c>
-      <c r="C89" t="s">
-        <v>158</v>
+        <v>254</v>
       </c>
       <c r="E89" t="s">
-        <v>258</v>
+        <v>184</v>
       </c>
       <c r="F89">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G89" t="s">
-        <v>259</v>
+        <v>67</v>
       </c>
       <c r="H89" t="s">
-        <v>260</v>
+        <v>67</v>
       </c>
       <c r="I89" t="s">
-        <v>261</v>
+        <v>203</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" t="s">
+        <v>166</v>
+      </c>
+      <c r="B90" t="s">
+        <v>167</v>
+      </c>
+      <c r="C90" t="s">
+        <v>154</v>
+      </c>
+      <c r="E90" t="s">
+        <v>126</v>
+      </c>
+      <c r="F90">
+        <v>1.0</v>
+      </c>
+      <c r="G90" t="s">
+        <v>255</v>
+      </c>
+      <c r="H90" t="s">
+        <v>255</v>
+      </c>
+      <c r="I90" t="s">
         <v>128</v>
-      </c>
-      <c r="B90" t="s">
-        <v>129</v>
-      </c>
-      <c r="C90" t="s">
-        <v>158</v>
-      </c>
-      <c r="E90" t="s">
-        <v>130</v>
-      </c>
-      <c r="F90">
-        <v>6.0</v>
-      </c>
-      <c r="G90" t="s">
-        <v>262</v>
-      </c>
-      <c r="H90" t="s">
-        <v>263</v>
-      </c>
-      <c r="I90" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="B91" t="s">
-        <v>265</v>
+        <v>192</v>
+      </c>
+      <c r="C91" t="s">
+        <v>121</v>
       </c>
       <c r="E91" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="F91">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G91" t="s">
-        <v>67</v>
+        <v>256</v>
       </c>
       <c r="H91" t="s">
-        <v>67</v>
+        <v>257</v>
       </c>
       <c r="I91" t="s">
-        <v>207</v>
+        <v>258</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B92" t="s">
-        <v>267</v>
-      </c>
-      <c r="C92" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="E92" t="s">
-        <v>269</v>
+        <v>184</v>
       </c>
       <c r="F92">
         <v>1.0</v>
       </c>
       <c r="G92" t="s">
-        <v>253</v>
+        <v>67</v>
       </c>
       <c r="H92" t="s">
-        <v>253</v>
+        <v>67</v>
       </c>
       <c r="I92" t="s">
-        <v>270</v>
+        <v>203</v>
       </c>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>170</v>
+        <v>261</v>
       </c>
       <c r="B93" t="s">
-        <v>171</v>
-      </c>
-      <c r="C93" t="s">
-        <v>158</v>
+        <v>262</v>
       </c>
       <c r="E93" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="F93">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G93" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="H93" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="I93" t="s">
-        <v>132</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="B94" t="s">
-        <v>196</v>
-      </c>
-      <c r="C94" t="s">
-        <v>125</v>
+        <v>264</v>
       </c>
       <c r="E94" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="F94">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G94" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="H94" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="I94" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>275</v>
+        <v>191</v>
       </c>
       <c r="B95" t="s">
-        <v>276</v>
+        <v>192</v>
+      </c>
+      <c r="C95" t="s">
+        <v>154</v>
       </c>
       <c r="E95" t="s">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="F95">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G95" t="s">
-        <v>67</v>
+        <v>266</v>
       </c>
       <c r="H95" t="s">
-        <v>67</v>
+        <v>267</v>
       </c>
       <c r="I95" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B96" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="E96" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F96">
         <v>2.0</v>
       </c>
       <c r="G96" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="H96" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="I96" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B97" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="E97" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="F97">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G97" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="H97" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="I97" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>195</v>
+        <v>275</v>
       </c>
       <c r="B98" t="s">
-        <v>196</v>
-      </c>
-      <c r="C98" t="s">
-        <v>158</v>
+        <v>276</v>
       </c>
       <c r="E98" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="F98">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G98" t="s">
-        <v>282</v>
+        <v>67</v>
       </c>
       <c r="H98" t="s">
-        <v>283</v>
+        <v>67</v>
       </c>
       <c r="I98" t="s">
-        <v>174</v>
+        <v>277</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B99" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E99" t="s">
-        <v>205</v>
+        <v>280</v>
       </c>
       <c r="F99">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G99" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="H99" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="I99" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B100" t="s">
-        <v>287</v>
+        <v>285</v>
+      </c>
+      <c r="C100" t="s">
+        <v>154</v>
       </c>
       <c r="E100" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="F100">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G100" t="s">
-        <v>288</v>
+        <v>67</v>
       </c>
       <c r="H100" t="s">
-        <v>289</v>
+        <v>67</v>
       </c>
       <c r="I100" t="s">
-        <v>290</v>
+        <v>221</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B101" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E101" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F101">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G101" t="s">
         <v>67</v>
@@ -4660,151 +4594,157 @@
         <v>67</v>
       </c>
       <c r="I101" t="s">
-        <v>293</v>
+        <v>187</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B102" t="s">
-        <v>295</v>
+        <v>289</v>
+      </c>
+      <c r="C102" t="s">
+        <v>290</v>
       </c>
       <c r="E102" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F102">
         <v>1.0</v>
       </c>
       <c r="G102" t="s">
-        <v>206</v>
+        <v>292</v>
       </c>
       <c r="H102" t="s">
-        <v>206</v>
+        <v>292</v>
       </c>
       <c r="I102" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B103" t="s">
-        <v>299</v>
+        <v>295</v>
+      </c>
+      <c r="C103">
+        <v>28</v>
       </c>
       <c r="E103" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F103">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G103" t="s">
-        <v>301</v>
+        <v>67</v>
       </c>
       <c r="H103" t="s">
-        <v>302</v>
+        <v>67</v>
       </c>
       <c r="I103" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B104" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C104" t="s">
-        <v>158</v>
+        <v>300</v>
       </c>
       <c r="E104" t="s">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="F104">
         <v>1.0</v>
       </c>
       <c r="G104" t="s">
-        <v>67</v>
+        <v>242</v>
       </c>
       <c r="H104" t="s">
-        <v>67</v>
+        <v>242</v>
       </c>
       <c r="I104" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B105" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E105" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F105">
         <v>2.0</v>
       </c>
       <c r="G105" t="s">
-        <v>67</v>
+        <v>202</v>
       </c>
       <c r="H105" t="s">
-        <v>67</v>
+        <v>304</v>
       </c>
       <c r="I105" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
+        <v>305</v>
+      </c>
+      <c r="B106" t="s">
+        <v>306</v>
+      </c>
+      <c r="C106" t="s">
+        <v>300</v>
+      </c>
+      <c r="E106" t="s">
+        <v>307</v>
+      </c>
+      <c r="F106">
+        <v>8.0</v>
+      </c>
+      <c r="G106" t="s">
         <v>308</v>
       </c>
-      <c r="B106" t="s">
+      <c r="H106" t="s">
         <v>309</v>
       </c>
-      <c r="C106" t="s">
+      <c r="I106" t="s">
         <v>310</v>
-      </c>
-      <c r="E106" t="s">
-        <v>247</v>
-      </c>
-      <c r="F106">
-        <v>1.0</v>
-      </c>
-      <c r="G106" t="s">
-        <v>311</v>
-      </c>
-      <c r="H106" t="s">
-        <v>311</v>
-      </c>
-      <c r="I106" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" t="s">
+        <v>311</v>
+      </c>
+      <c r="B107" t="s">
         <v>312</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C107" t="s">
+        <v>300</v>
+      </c>
+      <c r="E107" t="s">
+        <v>307</v>
+      </c>
+      <c r="F107">
+        <v>7.0</v>
+      </c>
+      <c r="G107" t="s">
         <v>313</v>
       </c>
-      <c r="C107">
-        <v>28</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="H107" t="s">
         <v>314</v>
-      </c>
-      <c r="F107">
-        <v>4.0</v>
-      </c>
-      <c r="G107" t="s">
-        <v>67</v>
-      </c>
-      <c r="H107" t="s">
-        <v>67</v>
       </c>
       <c r="I107" t="s">
         <v>315</v>
@@ -4812,126 +4752,123 @@
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
+        <v>284</v>
+      </c>
+      <c r="B108" t="s">
+        <v>285</v>
+      </c>
+      <c r="C108" t="s">
+        <v>144</v>
+      </c>
+      <c r="E108" t="s">
+        <v>219</v>
+      </c>
+      <c r="F108">
+        <v>3.0</v>
+      </c>
+      <c r="G108" t="s">
+        <v>67</v>
+      </c>
+      <c r="H108" t="s">
+        <v>67</v>
+      </c>
+      <c r="I108" t="s">
         <v>316</v>
-      </c>
-      <c r="B108" t="s">
-        <v>317</v>
-      </c>
-      <c r="C108" t="s">
-        <v>246</v>
-      </c>
-      <c r="E108" t="s">
-        <v>318</v>
-      </c>
-      <c r="F108">
-        <v>1.0</v>
-      </c>
-      <c r="G108" t="s">
-        <v>253</v>
-      </c>
-      <c r="H108" t="s">
-        <v>253</v>
-      </c>
-      <c r="I108" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" t="s">
+        <v>317</v>
+      </c>
+      <c r="B109" t="s">
+        <v>318</v>
+      </c>
+      <c r="C109" t="s">
+        <v>300</v>
+      </c>
+      <c r="E109" t="s">
         <v>319</v>
-      </c>
-      <c r="B109" t="s">
-        <v>320</v>
-      </c>
-      <c r="E109" t="s">
-        <v>188</v>
       </c>
       <c r="F109">
         <v>2.0</v>
       </c>
       <c r="G109" t="s">
-        <v>206</v>
+        <v>320</v>
       </c>
       <c r="H109" t="s">
         <v>321</v>
       </c>
       <c r="I109" t="s">
-        <v>191</v>
+        <v>322</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B110" t="s">
-        <v>323</v>
-      </c>
-      <c r="C110" t="s">
-        <v>246</v>
+        <v>324</v>
       </c>
       <c r="E110" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F110">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G110" t="s">
-        <v>325</v>
+        <v>242</v>
       </c>
       <c r="H110" t="s">
+        <v>242</v>
+      </c>
+      <c r="I110" t="s">
         <v>326</v>
-      </c>
-      <c r="I110" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
+        <v>327</v>
+      </c>
+      <c r="B111" t="s">
         <v>328</v>
       </c>
-      <c r="B111" t="s">
-        <v>329</v>
-      </c>
-      <c r="C111" t="s">
-        <v>246</v>
-      </c>
       <c r="E111" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F111">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G111" t="s">
-        <v>330</v>
+        <v>242</v>
       </c>
       <c r="H111" t="s">
-        <v>331</v>
+        <v>242</v>
       </c>
       <c r="I111" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>266</v>
+        <v>329</v>
       </c>
       <c r="B112" t="s">
-        <v>267</v>
+        <v>330</v>
       </c>
       <c r="C112" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="E112" t="s">
-        <v>269</v>
+        <v>331</v>
       </c>
       <c r="F112">
         <v>2.0</v>
       </c>
       <c r="G112" t="s">
-        <v>253</v>
+        <v>332</v>
       </c>
       <c r="H112" t="s">
-        <v>254</v>
+        <v>333</v>
       </c>
       <c r="I112" t="s">
         <v>334</v>
@@ -4944,158 +4881,164 @@
       <c r="B113" t="s">
         <v>336</v>
       </c>
+      <c r="C113" t="s">
+        <v>154</v>
+      </c>
       <c r="E113" t="s">
+        <v>112</v>
+      </c>
+      <c r="F113">
+        <v>1.0</v>
+      </c>
+      <c r="G113" t="s">
+        <v>67</v>
+      </c>
+      <c r="H113" t="s">
+        <v>67</v>
+      </c>
+      <c r="I113" t="s">
         <v>337</v>
-      </c>
-      <c r="F113">
-        <v>3.0</v>
-      </c>
-      <c r="G113" t="s">
-        <v>338</v>
-      </c>
-      <c r="H113" t="s">
-        <v>339</v>
-      </c>
-      <c r="I113" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B114" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="C114" t="s">
-        <v>148</v>
+        <v>338</v>
       </c>
       <c r="E114" t="s">
-        <v>223</v>
+        <v>319</v>
       </c>
       <c r="F114">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G114" t="s">
-        <v>67</v>
+        <v>242</v>
       </c>
       <c r="H114" t="s">
-        <v>67</v>
+        <v>242</v>
       </c>
       <c r="I114" t="s">
-        <v>341</v>
+        <v>293</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>266</v>
+        <v>305</v>
       </c>
       <c r="B115" t="s">
-        <v>267</v>
+        <v>306</v>
       </c>
       <c r="C115" t="s">
-        <v>246</v>
+        <v>339</v>
       </c>
       <c r="E115" t="s">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="F115">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="G115" t="s">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="H115" t="s">
-        <v>343</v>
+        <v>309</v>
       </c>
       <c r="I115" t="s">
-        <v>344</v>
+        <v>310</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>345</v>
+        <v>222</v>
       </c>
       <c r="B116" t="s">
-        <v>346</v>
+        <v>223</v>
+      </c>
+      <c r="C116" t="s">
+        <v>154</v>
       </c>
       <c r="E116" t="s">
-        <v>347</v>
+        <v>209</v>
       </c>
       <c r="F116">
         <v>1.0</v>
       </c>
       <c r="G116" t="s">
-        <v>253</v>
+        <v>340</v>
       </c>
       <c r="H116" t="s">
-        <v>253</v>
+        <v>340</v>
       </c>
       <c r="I116" t="s">
-        <v>348</v>
+        <v>236</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B117" t="s">
-        <v>350</v>
+        <v>342</v>
+      </c>
+      <c r="C117" t="s">
+        <v>144</v>
       </c>
       <c r="E117" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F117">
         <v>1.0</v>
       </c>
       <c r="G117" t="s">
-        <v>253</v>
+        <v>67</v>
       </c>
       <c r="H117" t="s">
-        <v>253</v>
+        <v>67</v>
       </c>
       <c r="I117" t="s">
-        <v>348</v>
+        <v>180</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B118" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C118" t="s">
-        <v>246</v>
+        <v>111</v>
       </c>
       <c r="E118" t="s">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="F118">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G118" t="s">
-        <v>354</v>
+        <v>67</v>
       </c>
       <c r="H118" t="s">
-        <v>355</v>
+        <v>67</v>
       </c>
       <c r="I118" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="B119" t="s">
-        <v>358</v>
-      </c>
-      <c r="C119" t="s">
-        <v>158</v>
+        <v>347</v>
       </c>
       <c r="E119" t="s">
-        <v>112</v>
+        <v>348</v>
       </c>
       <c r="F119">
         <v>1.0</v>
@@ -5107,30 +5050,30 @@
         <v>67</v>
       </c>
       <c r="I119" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>266</v>
+        <v>350</v>
       </c>
       <c r="B120" t="s">
-        <v>267</v>
+        <v>351</v>
       </c>
       <c r="C120" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E120" t="s">
-        <v>269</v>
+        <v>331</v>
       </c>
       <c r="F120">
         <v>2.0</v>
       </c>
       <c r="G120" t="s">
-        <v>253</v>
+        <v>332</v>
       </c>
       <c r="H120" t="s">
-        <v>254</v>
+        <v>333</v>
       </c>
       <c r="I120" t="s">
         <v>334</v>
@@ -5138,155 +5081,158 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="B121" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="C121" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="E121" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F121">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="G121" t="s">
-        <v>325</v>
+        <v>354</v>
       </c>
       <c r="H121" t="s">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="I121" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>226</v>
+        <v>357</v>
       </c>
       <c r="B122" t="s">
-        <v>227</v>
+        <v>358</v>
       </c>
       <c r="C122" t="s">
-        <v>158</v>
+        <v>290</v>
       </c>
       <c r="E122" t="s">
-        <v>213</v>
+        <v>359</v>
       </c>
       <c r="F122">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G122" t="s">
+        <v>332</v>
+      </c>
+      <c r="H122" t="s">
+        <v>360</v>
+      </c>
+      <c r="I122" t="s">
         <v>361</v>
-      </c>
-      <c r="H122" t="s">
-        <v>361</v>
-      </c>
-      <c r="I122" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
+        <v>350</v>
+      </c>
+      <c r="B123" t="s">
+        <v>351</v>
+      </c>
+      <c r="C123" t="s">
+        <v>339</v>
+      </c>
+      <c r="E123" t="s">
+        <v>331</v>
+      </c>
+      <c r="F123">
+        <v>3.0</v>
+      </c>
+      <c r="G123" t="s">
+        <v>332</v>
+      </c>
+      <c r="H123" t="s">
         <v>362</v>
       </c>
-      <c r="B123" t="s">
+      <c r="I123" t="s">
         <v>363</v>
-      </c>
-      <c r="C123" t="s">
-        <v>148</v>
-      </c>
-      <c r="E123" t="s">
-        <v>364</v>
-      </c>
-      <c r="F123">
-        <v>1.0</v>
-      </c>
-      <c r="G123" t="s">
-        <v>67</v>
-      </c>
-      <c r="H123" t="s">
-        <v>67</v>
-      </c>
-      <c r="I123" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
+        <v>364</v>
+      </c>
+      <c r="B124" t="s">
         <v>365</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" t="s">
+        <v>300</v>
+      </c>
+      <c r="E124" t="s">
+        <v>307</v>
+      </c>
+      <c r="F124">
+        <v>8.0</v>
+      </c>
+      <c r="G124" t="s">
         <v>366</v>
       </c>
-      <c r="C124" t="s">
-        <v>111</v>
-      </c>
-      <c r="E124" t="s">
-        <v>112</v>
-      </c>
-      <c r="F124">
-        <v>1.0</v>
-      </c>
-      <c r="G124" t="s">
-        <v>67</v>
-      </c>
       <c r="H124" t="s">
-        <v>67</v>
+        <v>367</v>
       </c>
       <c r="I124" t="s">
-        <v>359</v>
+        <v>310</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
+        <v>305</v>
+      </c>
+      <c r="B125" t="s">
+        <v>306</v>
+      </c>
+      <c r="C125" t="s">
+        <v>338</v>
+      </c>
+      <c r="E125" t="s">
+        <v>307</v>
+      </c>
+      <c r="F125">
+        <v>4.0</v>
+      </c>
+      <c r="G125" t="s">
+        <v>368</v>
+      </c>
+      <c r="H125" t="s">
         <v>367</v>
       </c>
-      <c r="B125" t="s">
-        <v>368</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="I125" t="s">
         <v>369</v>
-      </c>
-      <c r="F125">
-        <v>1.0</v>
-      </c>
-      <c r="G125" t="s">
-        <v>67</v>
-      </c>
-      <c r="H125" t="s">
-        <v>67</v>
-      </c>
-      <c r="I125" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" t="s">
+        <v>311</v>
+      </c>
+      <c r="B126" t="s">
+        <v>312</v>
+      </c>
+      <c r="C126" t="s">
+        <v>339</v>
+      </c>
+      <c r="E126" t="s">
+        <v>307</v>
+      </c>
+      <c r="F126">
+        <v>5.0</v>
+      </c>
+      <c r="G126" t="s">
+        <v>370</v>
+      </c>
+      <c r="H126" t="s">
         <v>371</v>
       </c>
-      <c r="B126" t="s">
+      <c r="I126" t="s">
         <v>372</v>
-      </c>
-      <c r="C126" t="s">
-        <v>360</v>
-      </c>
-      <c r="E126" t="s">
-        <v>353</v>
-      </c>
-      <c r="F126">
-        <v>3.0</v>
-      </c>
-      <c r="G126" t="s">
-        <v>354</v>
-      </c>
-      <c r="H126" t="s">
-        <v>355</v>
-      </c>
-      <c r="I126" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -5296,852 +5242,852 @@
       <c r="B127" t="s">
         <v>374</v>
       </c>
-      <c r="C127" t="s">
-        <v>246</v>
-      </c>
       <c r="E127" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="F127">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G127" t="s">
-        <v>375</v>
+        <v>67</v>
       </c>
       <c r="H127" t="s">
-        <v>376</v>
+        <v>67</v>
       </c>
       <c r="I127" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B128" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C128" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E128" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="F128">
         <v>7.0</v>
       </c>
       <c r="G128" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="H128" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="I128" t="s">
-        <v>382</v>
+        <v>315</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B129" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="C129" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="E129" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F129">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G129" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="H129" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="I129" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>383</v>
+        <v>311</v>
       </c>
       <c r="B130" t="s">
-        <v>384</v>
+        <v>312</v>
       </c>
       <c r="C130" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="E130" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F130">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
       <c r="G130" t="s">
-        <v>385</v>
+        <v>332</v>
       </c>
       <c r="H130" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="I130" t="s">
-        <v>327</v>
+        <v>380</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="B131" t="s">
-        <v>323</v>
+        <v>382</v>
       </c>
       <c r="C131" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="E131" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="F131">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G131" t="s">
-        <v>387</v>
+        <v>332</v>
       </c>
       <c r="H131" t="s">
-        <v>386</v>
+        <v>333</v>
       </c>
       <c r="I131" t="s">
-        <v>388</v>
+        <v>244</v>
       </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>328</v>
+        <v>383</v>
       </c>
       <c r="B132" t="s">
-        <v>329</v>
+        <v>384</v>
       </c>
       <c r="C132" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="E132" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F132">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="G132" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="H132" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="I132" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B133" t="s">
-        <v>393</v>
+        <v>388</v>
+      </c>
+      <c r="C133" t="s">
+        <v>300</v>
       </c>
       <c r="E133" t="s">
-        <v>369</v>
+        <v>307</v>
       </c>
       <c r="F133">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G133" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="H133" t="s">
-        <v>67</v>
+        <v>355</v>
       </c>
       <c r="I133" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>394</v>
+        <v>357</v>
       </c>
       <c r="B134" t="s">
-        <v>395</v>
+        <v>358</v>
       </c>
       <c r="C134" t="s">
-        <v>246</v>
+        <v>390</v>
       </c>
       <c r="E134" t="s">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="F134">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G134" t="s">
-        <v>396</v>
+        <v>332</v>
       </c>
       <c r="H134" t="s">
-        <v>386</v>
+        <v>332</v>
       </c>
       <c r="I134" t="s">
-        <v>332</v>
+        <v>169</v>
       </c>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" t="s">
-        <v>378</v>
+        <v>311</v>
       </c>
       <c r="B135" t="s">
-        <v>379</v>
+        <v>312</v>
       </c>
       <c r="C135" t="s">
-        <v>246</v>
+        <v>338</v>
       </c>
       <c r="E135" t="s">
+        <v>307</v>
+      </c>
+      <c r="F135">
+        <v>4.0</v>
+      </c>
+      <c r="G135" t="s">
+        <v>332</v>
+      </c>
+      <c r="H135" t="s">
+        <v>371</v>
+      </c>
+      <c r="I135" t="s">
         <v>380</v>
-      </c>
-      <c r="F135">
-        <v>10.0</v>
-      </c>
-      <c r="G135" t="s">
-        <v>354</v>
-      </c>
-      <c r="H135" t="s">
-        <v>397</v>
-      </c>
-      <c r="I135" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="B136" t="s">
-        <v>329</v>
+        <v>376</v>
       </c>
       <c r="C136" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="E136" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F136">
         <v>4.0</v>
       </c>
       <c r="G136" t="s">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="H136" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I136" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="B137" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="C137" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E137" t="s">
-        <v>353</v>
+        <v>307</v>
       </c>
       <c r="F137">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G137" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="H137" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="I137" t="s">
-        <v>255</v>
+        <v>394</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>403</v>
+        <v>375</v>
       </c>
       <c r="B138" t="s">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="C138" t="s">
-        <v>246</v>
+        <v>339</v>
       </c>
       <c r="E138" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F138">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="G138" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="H138" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="I138" t="s">
-        <v>406</v>
+        <v>372</v>
       </c>
     </row>
     <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>407</v>
+        <v>364</v>
       </c>
       <c r="B139" t="s">
-        <v>408</v>
+        <v>365</v>
       </c>
       <c r="C139" t="s">
-        <v>246</v>
+        <v>339</v>
       </c>
       <c r="E139" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F139">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="G139" t="s">
-        <v>131</v>
+        <v>396</v>
       </c>
       <c r="H139" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="I139" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
     </row>
     <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B140" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C140" t="s">
-        <v>268</v>
+        <v>339</v>
       </c>
       <c r="E140" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="F140">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="G140" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="H140" t="s">
-        <v>402</v>
+        <v>367</v>
       </c>
       <c r="I140" t="s">
-        <v>235</v>
+        <v>399</v>
       </c>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="B141" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
       <c r="C141" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E141" t="s">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="F141">
         <v>4.0</v>
       </c>
       <c r="G141" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="H141" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="I141" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="B142" t="s">
-        <v>395</v>
+        <v>351</v>
       </c>
       <c r="C142" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="E142" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="F142">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G142" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="H142" t="s">
-        <v>410</v>
+        <v>333</v>
       </c>
       <c r="I142" t="s">
-        <v>399</v>
+        <v>334</v>
       </c>
     </row>
     <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>407</v>
+        <v>352</v>
       </c>
       <c r="B143" t="s">
-        <v>408</v>
+        <v>353</v>
       </c>
       <c r="C143" t="s">
+        <v>339</v>
+      </c>
+      <c r="E143" t="s">
+        <v>307</v>
+      </c>
+      <c r="F143">
+        <v>2.0</v>
+      </c>
+      <c r="G143" t="s">
         <v>333</v>
       </c>
-      <c r="E143" t="s">
-        <v>324</v>
-      </c>
-      <c r="F143">
-        <v>4.0</v>
-      </c>
-      <c r="G143" t="s">
-        <v>411</v>
-      </c>
       <c r="H143" t="s">
-        <v>249</v>
+        <v>371</v>
       </c>
       <c r="I143" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="B144" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C144" t="s">
+        <v>300</v>
+      </c>
+      <c r="E144" t="s">
+        <v>307</v>
+      </c>
+      <c r="F144">
+        <v>2.0</v>
+      </c>
+      <c r="G144" t="s">
         <v>333</v>
       </c>
-      <c r="E144" t="s">
-        <v>324</v>
-      </c>
-      <c r="F144">
-        <v>5.0</v>
-      </c>
-      <c r="G144" t="s">
-        <v>413</v>
-      </c>
       <c r="H144" t="s">
-        <v>410</v>
+        <v>371</v>
       </c>
       <c r="I144" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="B145" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="C145" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="E145" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F145">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G145" t="s">
-        <v>414</v>
+        <v>193</v>
       </c>
       <c r="H145" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="I145" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B146" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C146" t="s">
-        <v>333</v>
+        <v>154</v>
       </c>
       <c r="E146" t="s">
-        <v>324</v>
+        <v>409</v>
       </c>
       <c r="F146">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="G146" t="s">
-        <v>385</v>
+        <v>67</v>
       </c>
       <c r="H146" t="s">
-        <v>386</v>
+        <v>67</v>
       </c>
       <c r="I146" t="s">
-        <v>416</v>
+        <v>236</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="B147" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="C147" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E147" t="s">
-        <v>380</v>
+        <v>331</v>
       </c>
       <c r="F147">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G147" t="s">
-        <v>354</v>
+        <v>242</v>
       </c>
       <c r="H147" t="s">
-        <v>354</v>
+        <v>412</v>
       </c>
       <c r="I147" t="s">
-        <v>173</v>
+        <v>227</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B148" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C148" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="E148" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="F148">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G148" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="H148" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="I148" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="B149" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="C149" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="E149" t="s">
-        <v>353</v>
+        <v>307</v>
       </c>
       <c r="F149">
         <v>2.0</v>
       </c>
       <c r="G149" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="H149" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="I149" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
     </row>
     <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>373</v>
+        <v>413</v>
       </c>
       <c r="B150" t="s">
-        <v>374</v>
+        <v>414</v>
       </c>
       <c r="C150" t="s">
-        <v>333</v>
+        <v>144</v>
       </c>
       <c r="E150" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="F150">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G150" t="s">
-        <v>402</v>
+        <v>256</v>
       </c>
       <c r="H150" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="I150" t="s">
-        <v>421</v>
+        <v>227</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B151" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C151" t="s">
-        <v>246</v>
+        <v>339</v>
       </c>
       <c r="E151" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F151">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G151" t="s">
-        <v>402</v>
+        <v>67</v>
       </c>
       <c r="H151" t="s">
-        <v>390</v>
+        <v>67</v>
       </c>
       <c r="I151" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>351</v>
+        <v>420</v>
       </c>
       <c r="B152" t="s">
-        <v>352</v>
+        <v>421</v>
       </c>
       <c r="C152" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="E152" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F152">
         <v>1.0</v>
       </c>
       <c r="G152" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="H152" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="I152" t="s">
-        <v>424</v>
+        <v>169</v>
       </c>
     </row>
     <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B153" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C153" t="s">
-        <v>246</v>
+        <v>144</v>
       </c>
       <c r="E153" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="F153">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G153" t="s">
-        <v>197</v>
+        <v>67</v>
       </c>
       <c r="H153" t="s">
-        <v>390</v>
+        <v>67</v>
       </c>
       <c r="I153" t="s">
-        <v>427</v>
+        <v>265</v>
       </c>
     </row>
     <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B154" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C154" t="s">
-        <v>158</v>
+        <v>300</v>
       </c>
       <c r="E154" t="s">
-        <v>430</v>
+        <v>307</v>
       </c>
       <c r="F154">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G154" t="s">
-        <v>67</v>
+        <v>426</v>
       </c>
       <c r="H154" t="s">
-        <v>67</v>
+        <v>427</v>
       </c>
       <c r="I154" t="s">
-        <v>240</v>
+        <v>369</v>
       </c>
     </row>
     <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="B155" t="s">
-        <v>432</v>
+        <v>376</v>
       </c>
       <c r="C155" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="E155" t="s">
-        <v>353</v>
+        <v>307</v>
       </c>
       <c r="F155">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G155" t="s">
-        <v>253</v>
+        <v>395</v>
       </c>
       <c r="H155" t="s">
-        <v>433</v>
+        <v>391</v>
       </c>
       <c r="I155" t="s">
-        <v>231</v>
+        <v>372</v>
       </c>
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>407</v>
+        <v>364</v>
       </c>
       <c r="B156" t="s">
-        <v>408</v>
+        <v>365</v>
       </c>
       <c r="C156" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="E156" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F156">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G156" t="s">
-        <v>402</v>
+        <v>67</v>
       </c>
       <c r="H156" t="s">
-        <v>390</v>
+        <v>67</v>
       </c>
       <c r="I156" t="s">
-        <v>421</v>
+        <v>369</v>
       </c>
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>407</v>
+        <v>357</v>
       </c>
       <c r="B157" t="s">
-        <v>408</v>
+        <v>358</v>
       </c>
       <c r="C157" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="E157" t="s">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="F157">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G157" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="H157" t="s">
-        <v>390</v>
+        <v>45</v>
       </c>
       <c r="I157" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>434</v>
+        <v>311</v>
       </c>
       <c r="B158" t="s">
-        <v>435</v>
+        <v>312</v>
       </c>
       <c r="C158" t="s">
-        <v>148</v>
+        <v>390</v>
       </c>
       <c r="E158" t="s">
-        <v>436</v>
+        <v>307</v>
       </c>
       <c r="F158">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G158" t="s">
-        <v>272</v>
+        <v>332</v>
       </c>
       <c r="H158" t="s">
-        <v>437</v>
+        <v>333</v>
       </c>
       <c r="I158" t="s">
-        <v>231</v>
+        <v>429</v>
       </c>
     </row>
     <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
       <c r="B159" t="s">
-        <v>439</v>
+        <v>405</v>
       </c>
       <c r="C159" t="s">
+        <v>290</v>
+      </c>
+      <c r="E159" t="s">
+        <v>307</v>
+      </c>
+      <c r="F159">
+        <v>1.0</v>
+      </c>
+      <c r="G159" t="s">
         <v>333</v>
       </c>
-      <c r="E159" t="s">
-        <v>324</v>
-      </c>
-      <c r="F159">
-        <v>1.0</v>
-      </c>
-      <c r="G159" t="s">
-        <v>67</v>
-      </c>
       <c r="H159" t="s">
-        <v>67</v>
+        <v>333</v>
       </c>
       <c r="I159" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -6152,140 +6098,137 @@
         <v>418</v>
       </c>
       <c r="C160" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E160" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="F160">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G160" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="H160" t="s">
-        <v>354</v>
+        <v>431</v>
       </c>
       <c r="I160" t="s">
-        <v>173</v>
+        <v>432</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="B161" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="C161" t="s">
-        <v>148</v>
+        <v>339</v>
       </c>
       <c r="E161" t="s">
-        <v>436</v>
+        <v>307</v>
       </c>
       <c r="F161">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G161" t="s">
-        <v>67</v>
+        <v>433</v>
       </c>
       <c r="H161" t="s">
-        <v>67</v>
+        <v>434</v>
       </c>
       <c r="I161" t="s">
-        <v>255</v>
+        <v>369</v>
       </c>
     </row>
     <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>400</v>
+        <v>435</v>
       </c>
       <c r="B162" t="s">
-        <v>401</v>
-      </c>
-      <c r="C162" t="s">
-        <v>360</v>
+        <v>436</v>
       </c>
       <c r="E162" t="s">
-        <v>353</v>
+        <v>437</v>
       </c>
       <c r="F162">
         <v>1.0</v>
       </c>
       <c r="G162" t="s">
-        <v>354</v>
+        <v>67</v>
       </c>
       <c r="H162" t="s">
-        <v>354</v>
+        <v>67</v>
       </c>
       <c r="I162" t="s">
-        <v>281</v>
+        <v>349</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B163" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C163" t="s">
-        <v>246</v>
+        <v>338</v>
       </c>
       <c r="E163" t="s">
-        <v>324</v>
+        <v>440</v>
       </c>
       <c r="F163">
         <v>4.0</v>
       </c>
       <c r="G163" t="s">
-        <v>445</v>
+        <v>67</v>
       </c>
       <c r="H163" t="s">
-        <v>446</v>
+        <v>67</v>
       </c>
       <c r="I163" t="s">
-        <v>388</v>
+        <v>441</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>394</v>
+        <v>442</v>
       </c>
       <c r="B164" t="s">
-        <v>395</v>
+        <v>443</v>
       </c>
       <c r="C164" t="s">
-        <v>360</v>
+        <v>154</v>
       </c>
       <c r="E164" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="F164">
         <v>5.0</v>
       </c>
       <c r="G164" t="s">
-        <v>413</v>
+        <v>444</v>
       </c>
       <c r="H164" t="s">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="I164" t="s">
-        <v>391</v>
+        <v>446</v>
       </c>
     </row>
     <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="B165" t="s">
-        <v>384</v>
+        <v>448</v>
       </c>
       <c r="C165" t="s">
-        <v>310</v>
+        <v>144</v>
       </c>
       <c r="E165" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="F165">
         <v>4.0</v>
@@ -6297,616 +6240,619 @@
         <v>67</v>
       </c>
       <c r="I165" t="s">
-        <v>388</v>
+        <v>449</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
       <c r="B166" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
       <c r="C166" t="s">
-        <v>333</v>
+        <v>390</v>
       </c>
       <c r="E166" t="s">
-        <v>380</v>
+        <v>331</v>
       </c>
       <c r="F166">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G166" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
       <c r="H166" t="s">
-        <v>45</v>
+        <v>332</v>
       </c>
       <c r="I166" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="B167" t="s">
-        <v>329</v>
+        <v>365</v>
       </c>
       <c r="C167" t="s">
-        <v>268</v>
+        <v>338</v>
       </c>
       <c r="E167" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F167">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G167" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="H167" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="I167" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="B168" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="C168" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="E168" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F168">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G168" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="H168" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="I168" t="s">
-        <v>449</v>
+        <v>406</v>
       </c>
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>438</v>
+        <v>284</v>
       </c>
       <c r="B169" t="s">
-        <v>439</v>
+        <v>285</v>
       </c>
       <c r="C169" t="s">
-        <v>246</v>
+        <v>111</v>
       </c>
       <c r="E169" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="F169">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G169" t="s">
-        <v>405</v>
+        <v>67</v>
       </c>
       <c r="H169" t="s">
-        <v>450</v>
+        <v>67</v>
       </c>
       <c r="I169" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>443</v>
+        <v>402</v>
       </c>
       <c r="B170" t="s">
-        <v>444</v>
+        <v>403</v>
       </c>
       <c r="C170" t="s">
+        <v>339</v>
+      </c>
+      <c r="E170" t="s">
+        <v>307</v>
+      </c>
+      <c r="F170">
+        <v>2.0</v>
+      </c>
+      <c r="G170" t="s">
+        <v>332</v>
+      </c>
+      <c r="H170" t="s">
         <v>333</v>
       </c>
-      <c r="E170" t="s">
-        <v>324</v>
-      </c>
-      <c r="F170">
-        <v>4.0</v>
-      </c>
-      <c r="G170" t="s">
-        <v>452</v>
-      </c>
-      <c r="H170" t="s">
-        <v>453</v>
-      </c>
       <c r="I170" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
+        <v>453</v>
+      </c>
+      <c r="B171" t="s">
         <v>454</v>
       </c>
-      <c r="B171" t="s">
+      <c r="C171" t="s">
+        <v>300</v>
+      </c>
+      <c r="E171" t="s">
+        <v>307</v>
+      </c>
+      <c r="F171">
+        <v>4.0</v>
+      </c>
+      <c r="G171" t="s">
+        <v>308</v>
+      </c>
+      <c r="H171" t="s">
+        <v>391</v>
+      </c>
+      <c r="I171" t="s">
         <v>455</v>
-      </c>
-      <c r="E171" t="s">
-        <v>456</v>
-      </c>
-      <c r="F171">
-        <v>1.0</v>
-      </c>
-      <c r="G171" t="s">
-        <v>67</v>
-      </c>
-      <c r="H171" t="s">
-        <v>67</v>
-      </c>
-      <c r="I171" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>457</v>
+        <v>352</v>
       </c>
       <c r="B172" t="s">
-        <v>458</v>
+        <v>353</v>
       </c>
       <c r="C172" t="s">
-        <v>148</v>
+        <v>290</v>
       </c>
       <c r="E172" t="s">
-        <v>436</v>
+        <v>307</v>
       </c>
       <c r="F172">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G172" t="s">
-        <v>459</v>
+        <v>332</v>
       </c>
       <c r="H172" t="s">
-        <v>459</v>
+        <v>333</v>
       </c>
       <c r="I172" t="s">
-        <v>173</v>
+        <v>401</v>
       </c>
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
+        <v>456</v>
+      </c>
+      <c r="B173" t="s">
+        <v>457</v>
+      </c>
+      <c r="C173" t="s">
+        <v>144</v>
+      </c>
+      <c r="E173" t="s">
+        <v>415</v>
+      </c>
+      <c r="F173">
+        <v>3.0</v>
+      </c>
+      <c r="G173" t="s">
+        <v>458</v>
+      </c>
+      <c r="H173" t="s">
+        <v>459</v>
+      </c>
+      <c r="I173" t="s">
         <v>460</v>
-      </c>
-      <c r="B173" t="s">
-        <v>461</v>
-      </c>
-      <c r="C173" t="s">
-        <v>360</v>
-      </c>
-      <c r="E173" t="s">
-        <v>462</v>
-      </c>
-      <c r="F173">
-        <v>4.0</v>
-      </c>
-      <c r="G173" t="s">
-        <v>67</v>
-      </c>
-      <c r="H173" t="s">
-        <v>67</v>
-      </c>
-      <c r="I173" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>464</v>
+        <v>383</v>
       </c>
       <c r="B174" t="s">
-        <v>465</v>
+        <v>384</v>
       </c>
       <c r="C174" t="s">
-        <v>158</v>
+        <v>290</v>
       </c>
       <c r="E174" t="s">
-        <v>436</v>
+        <v>307</v>
       </c>
       <c r="F174">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G174" t="s">
-        <v>466</v>
+        <v>385</v>
       </c>
       <c r="H174" t="s">
-        <v>467</v>
+        <v>391</v>
       </c>
       <c r="I174" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
     </row>
     <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="B175" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="C175" t="s">
-        <v>148</v>
+        <v>339</v>
       </c>
       <c r="E175" t="s">
-        <v>436</v>
+        <v>359</v>
       </c>
       <c r="F175">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G175" t="s">
-        <v>67</v>
+        <v>332</v>
       </c>
       <c r="H175" t="s">
-        <v>67</v>
+        <v>333</v>
       </c>
       <c r="I175" t="s">
-        <v>471</v>
+        <v>334</v>
       </c>
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>371</v>
+        <v>442</v>
       </c>
       <c r="B176" t="s">
-        <v>372</v>
+        <v>443</v>
       </c>
       <c r="C176" t="s">
-        <v>268</v>
+        <v>144</v>
       </c>
       <c r="E176" t="s">
-        <v>353</v>
+        <v>415</v>
       </c>
       <c r="F176">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G176" t="s">
-        <v>354</v>
+        <v>67</v>
       </c>
       <c r="H176" t="s">
-        <v>354</v>
+        <v>67</v>
       </c>
       <c r="I176" t="s">
-        <v>424</v>
+        <v>460</v>
       </c>
     </row>
     <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>472</v>
+        <v>305</v>
       </c>
       <c r="B177" t="s">
-        <v>473</v>
+        <v>306</v>
       </c>
       <c r="C177" t="s">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="E177" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="F177">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G177" t="s">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="H177" t="s">
-        <v>355</v>
+        <v>308</v>
       </c>
       <c r="I177" t="s">
-        <v>356</v>
+        <v>244</v>
       </c>
     </row>
     <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>383</v>
+        <v>464</v>
       </c>
       <c r="B178" t="s">
-        <v>384</v>
+        <v>465</v>
       </c>
       <c r="C178" t="s">
-        <v>360</v>
+        <v>121</v>
       </c>
       <c r="E178" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="F178">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G178" t="s">
-        <v>405</v>
+        <v>67</v>
       </c>
       <c r="H178" t="s">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="I178" t="s">
-        <v>474</v>
+        <v>316</v>
       </c>
     </row>
     <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B179" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C179" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="E179" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F179">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G179" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="H179" t="s">
-        <v>450</v>
+        <v>333</v>
       </c>
       <c r="I179" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>304</v>
+        <v>424</v>
       </c>
       <c r="B180" t="s">
-        <v>305</v>
+        <v>425</v>
       </c>
       <c r="C180" t="s">
-        <v>111</v>
+        <v>338</v>
       </c>
       <c r="E180" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="F180">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G180" t="s">
-        <v>67</v>
+        <v>385</v>
       </c>
       <c r="H180" t="s">
-        <v>67</v>
+        <v>431</v>
       </c>
       <c r="I180" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
     </row>
     <row r="181" spans="1:9">
       <c r="A181" t="s">
-        <v>422</v>
+        <v>352</v>
       </c>
       <c r="B181" t="s">
-        <v>423</v>
+        <v>353</v>
       </c>
       <c r="C181" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E181" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F181">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G181" t="s">
-        <v>354</v>
+        <v>67</v>
       </c>
       <c r="H181" t="s">
-        <v>402</v>
+        <v>67</v>
       </c>
       <c r="I181" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="182" spans="1:9">
       <c r="A182" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="B182" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="C182" t="s">
-        <v>246</v>
+        <v>300</v>
       </c>
       <c r="E182" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F182">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G182" t="s">
-        <v>325</v>
+        <v>431</v>
       </c>
       <c r="H182" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="I182" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
     </row>
     <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>373</v>
+        <v>456</v>
       </c>
       <c r="B183" t="s">
-        <v>374</v>
+        <v>457</v>
       </c>
       <c r="C183" t="s">
-        <v>310</v>
+        <v>121</v>
       </c>
       <c r="E183" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="F183">
         <v>2.0</v>
       </c>
       <c r="G183" t="s">
-        <v>354</v>
+        <v>67</v>
       </c>
       <c r="H183" t="s">
-        <v>402</v>
+        <v>67</v>
       </c>
       <c r="I183" t="s">
-        <v>421</v>
+        <v>244</v>
       </c>
     </row>
     <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B184" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="C184" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="E184" t="s">
-        <v>436</v>
+        <v>219</v>
       </c>
       <c r="F184">
         <v>3.0</v>
       </c>
       <c r="G184" t="s">
-        <v>459</v>
+        <v>67</v>
       </c>
       <c r="H184" t="s">
-        <v>481</v>
+        <v>67</v>
       </c>
       <c r="I184" t="s">
-        <v>482</v>
+        <v>316</v>
       </c>
     </row>
     <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="B185" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="C185" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="E185" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F185">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G185" t="s">
-        <v>405</v>
+        <v>472</v>
       </c>
       <c r="H185" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="I185" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
     </row>
     <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>472</v>
+        <v>402</v>
       </c>
       <c r="B186" t="s">
-        <v>473</v>
+        <v>403</v>
       </c>
       <c r="C186" t="s">
+        <v>290</v>
+      </c>
+      <c r="E186" t="s">
+        <v>307</v>
+      </c>
+      <c r="F186">
+        <v>1.0</v>
+      </c>
+      <c r="G186" t="s">
         <v>333</v>
       </c>
-      <c r="E186" t="s">
-        <v>380</v>
-      </c>
-      <c r="F186">
-        <v>2.0</v>
-      </c>
-      <c r="G186" t="s">
-        <v>354</v>
-      </c>
       <c r="H186" t="s">
-        <v>402</v>
+        <v>333</v>
       </c>
       <c r="I186" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="B187" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="C187" t="s">
-        <v>148</v>
+        <v>339</v>
       </c>
       <c r="E187" t="s">
-        <v>436</v>
+        <v>307</v>
       </c>
       <c r="F187">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G187" t="s">
-        <v>67</v>
+        <v>366</v>
       </c>
       <c r="H187" t="s">
-        <v>67</v>
+        <v>473</v>
       </c>
       <c r="I187" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
     </row>
     <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>322</v>
+        <v>474</v>
       </c>
       <c r="B188" t="s">
-        <v>323</v>
+        <v>475</v>
       </c>
       <c r="C188" t="s">
-        <v>268</v>
+        <v>144</v>
       </c>
       <c r="E188" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="F188">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G188" t="s">
-        <v>325</v>
+        <v>67</v>
       </c>
       <c r="H188" t="s">
-        <v>325</v>
+        <v>67</v>
       </c>
       <c r="I188" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
     </row>
     <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>484</v>
+        <v>447</v>
       </c>
       <c r="B189" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
       <c r="C189" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E189" t="s">
-        <v>223</v>
+        <v>415</v>
       </c>
       <c r="F189">
         <v>3.0</v>
@@ -6918,73 +6864,73 @@
         <v>67</v>
       </c>
       <c r="I189" t="s">
-        <v>341</v>
+        <v>460</v>
       </c>
     </row>
     <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>425</v>
+        <v>364</v>
       </c>
       <c r="B190" t="s">
-        <v>426</v>
+        <v>365</v>
       </c>
       <c r="C190" t="s">
-        <v>333</v>
+        <v>390</v>
       </c>
       <c r="E190" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F190">
         <v>2.0</v>
       </c>
       <c r="G190" t="s">
-        <v>354</v>
+        <v>67</v>
       </c>
       <c r="H190" t="s">
-        <v>402</v>
+        <v>67</v>
       </c>
       <c r="I190" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="B191" t="s">
-        <v>444</v>
+        <v>477</v>
       </c>
       <c r="C191" t="s">
-        <v>360</v>
+        <v>154</v>
       </c>
       <c r="E191" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="F191">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G191" t="s">
-        <v>405</v>
+        <v>67</v>
       </c>
       <c r="H191" t="s">
-        <v>450</v>
+        <v>67</v>
       </c>
       <c r="I191" t="s">
-        <v>486</v>
+        <v>221</v>
       </c>
     </row>
     <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>373</v>
+        <v>478</v>
       </c>
       <c r="B192" t="s">
-        <v>374</v>
+        <v>479</v>
       </c>
       <c r="C192" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="E192" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F192">
         <v>1.0</v>
@@ -6996,50 +6942,50 @@
         <v>67</v>
       </c>
       <c r="I192" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B193" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="C193" t="s">
-        <v>246</v>
+        <v>300</v>
       </c>
       <c r="E193" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F193">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G193" t="s">
-        <v>450</v>
+        <v>67</v>
       </c>
       <c r="H193" t="s">
-        <v>450</v>
+        <v>67</v>
       </c>
       <c r="I193" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B194" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C194" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="E194" t="s">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="F194">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G194" t="s">
         <v>67</v>
@@ -7048,24 +6994,24 @@
         <v>67</v>
       </c>
       <c r="I194" t="s">
-        <v>471</v>
+        <v>169</v>
       </c>
     </row>
     <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="B195" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="C195" t="s">
-        <v>125</v>
+        <v>300</v>
       </c>
       <c r="E195" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="F195">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G195" t="s">
         <v>67</v>
@@ -7074,102 +7020,102 @@
         <v>67</v>
       </c>
       <c r="I195" t="s">
-        <v>341</v>
+        <v>430</v>
       </c>
     </row>
     <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="B196" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="C196" t="s">
-        <v>310</v>
+        <v>154</v>
       </c>
       <c r="E196" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="F196">
         <v>3.0</v>
       </c>
       <c r="G196" t="s">
-        <v>492</v>
+        <v>444</v>
       </c>
       <c r="H196" t="s">
-        <v>410</v>
+        <v>483</v>
       </c>
       <c r="I196" t="s">
-        <v>486</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="B197" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="C197" t="s">
-        <v>310</v>
+        <v>390</v>
       </c>
       <c r="E197" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F197">
         <v>1.0</v>
       </c>
       <c r="G197" t="s">
-        <v>402</v>
+        <v>333</v>
       </c>
       <c r="H197" t="s">
-        <v>402</v>
+        <v>333</v>
       </c>
       <c r="I197" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="198" spans="1:9">
       <c r="A198" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B198" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C198" t="s">
-        <v>333</v>
+        <v>136</v>
       </c>
       <c r="E198" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="F198">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G198" t="s">
-        <v>385</v>
+        <v>67</v>
       </c>
       <c r="H198" t="s">
-        <v>493</v>
+        <v>67</v>
       </c>
       <c r="I198" t="s">
-        <v>478</v>
+        <v>221</v>
       </c>
     </row>
     <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>494</v>
+        <v>447</v>
       </c>
       <c r="B199" t="s">
-        <v>495</v>
+        <v>448</v>
       </c>
       <c r="C199" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E199" t="s">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="F199">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G199" t="s">
         <v>67</v>
@@ -7178,24 +7124,24 @@
         <v>67</v>
       </c>
       <c r="I199" t="s">
-        <v>235</v>
+        <v>460</v>
       </c>
     </row>
     <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>469</v>
+        <v>447</v>
       </c>
       <c r="B200" t="s">
-        <v>470</v>
+        <v>448</v>
       </c>
       <c r="C200" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="E200" t="s">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="F200">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G200" t="s">
         <v>67</v>
@@ -7204,24 +7150,24 @@
         <v>67</v>
       </c>
       <c r="I200" t="s">
-        <v>482</v>
+        <v>244</v>
       </c>
     </row>
     <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>383</v>
+        <v>484</v>
       </c>
       <c r="B201" t="s">
-        <v>384</v>
+        <v>485</v>
       </c>
       <c r="C201" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="E201" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F201">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G201" t="s">
         <v>67</v>
@@ -7230,24 +7176,24 @@
         <v>67</v>
       </c>
       <c r="I201" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
     </row>
     <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="B202" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="C202" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E202" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F202">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G202" t="s">
         <v>67</v>
@@ -7256,21 +7202,21 @@
         <v>67</v>
       </c>
       <c r="I202" t="s">
-        <v>225</v>
+        <v>452</v>
       </c>
     </row>
     <row r="203" spans="1:9">
       <c r="A203" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="B203" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="C203" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="E203" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F203">
         <v>1.0</v>
@@ -7282,50 +7228,50 @@
         <v>67</v>
       </c>
       <c r="I203" t="s">
-        <v>449</v>
+        <v>419</v>
       </c>
     </row>
     <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="B204" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="C204" t="s">
-        <v>246</v>
+        <v>300</v>
       </c>
       <c r="E204" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F204">
         <v>3.0</v>
       </c>
       <c r="G204" t="s">
-        <v>67</v>
+        <v>472</v>
       </c>
       <c r="H204" t="s">
-        <v>67</v>
+        <v>391</v>
       </c>
       <c r="I204" t="s">
-        <v>502</v>
+        <v>406</v>
       </c>
     </row>
     <row r="205" spans="1:9">
       <c r="A205" t="s">
+        <v>493</v>
+      </c>
+      <c r="B205" t="s">
         <v>494</v>
       </c>
-      <c r="B205" t="s">
-        <v>495</v>
-      </c>
       <c r="C205" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="E205" t="s">
-        <v>436</v>
+        <v>126</v>
       </c>
       <c r="F205">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G205" t="s">
         <v>67</v>
@@ -7334,24 +7280,24 @@
         <v>67</v>
       </c>
       <c r="I205" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="206" spans="1:9">
       <c r="A206" t="s">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="B206" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
       <c r="C206" t="s">
-        <v>246</v>
+        <v>154</v>
       </c>
       <c r="E206" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="F206">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G206" t="s">
         <v>67</v>
@@ -7360,73 +7306,73 @@
         <v>67</v>
       </c>
       <c r="I206" t="s">
-        <v>449</v>
+        <v>232</v>
       </c>
     </row>
     <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>479</v>
+        <v>424</v>
       </c>
       <c r="B207" t="s">
-        <v>480</v>
+        <v>425</v>
       </c>
       <c r="C207" t="s">
-        <v>158</v>
+        <v>390</v>
       </c>
       <c r="E207" t="s">
-        <v>436</v>
+        <v>307</v>
       </c>
       <c r="F207">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G207" t="s">
-        <v>466</v>
+        <v>431</v>
       </c>
       <c r="H207" t="s">
-        <v>503</v>
+        <v>431</v>
       </c>
       <c r="I207" t="s">
-        <v>482</v>
+        <v>244</v>
       </c>
     </row>
     <row r="208" spans="1:9">
       <c r="A208" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="B208" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="C208" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="E208" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F208">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G208" t="s">
-        <v>402</v>
+        <v>308</v>
       </c>
       <c r="H208" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="I208" t="s">
-        <v>449</v>
+        <v>75</v>
       </c>
     </row>
     <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="B209" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C209" t="s">
-        <v>140</v>
+        <v>339</v>
       </c>
       <c r="E209" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="F209">
         <v>1.0</v>
@@ -7438,30 +7384,30 @@
         <v>67</v>
       </c>
       <c r="I209" t="s">
-        <v>225</v>
+        <v>469</v>
       </c>
     </row>
     <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
       <c r="B210" t="s">
-        <v>470</v>
+        <v>496</v>
       </c>
       <c r="C210" t="s">
-        <v>158</v>
+        <v>300</v>
       </c>
       <c r="E210" t="s">
-        <v>436</v>
+        <v>307</v>
       </c>
       <c r="F210">
         <v>3.0</v>
       </c>
       <c r="G210" t="s">
-        <v>67</v>
+        <v>385</v>
       </c>
       <c r="H210" t="s">
-        <v>67</v>
+        <v>431</v>
       </c>
       <c r="I210" t="s">
         <v>482</v>
@@ -7469,19 +7415,19 @@
     </row>
     <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B211" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C211" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="E211" t="s">
-        <v>436</v>
+        <v>219</v>
       </c>
       <c r="F211">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G211" t="s">
         <v>67</v>
@@ -7490,24 +7436,24 @@
         <v>67</v>
       </c>
       <c r="I211" t="s">
-        <v>486</v>
+        <v>232</v>
       </c>
     </row>
     <row r="212" spans="1:9">
       <c r="A212" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="B212" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="C212" t="s">
-        <v>246</v>
+        <v>121</v>
       </c>
       <c r="E212" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="F212">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G212" t="s">
         <v>67</v>
@@ -7516,21 +7462,21 @@
         <v>67</v>
       </c>
       <c r="I212" t="s">
-        <v>506</v>
+        <v>316</v>
       </c>
     </row>
     <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="B213" t="s">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="C213" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="E213" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F213">
         <v>2.0</v>
@@ -7542,21 +7488,21 @@
         <v>67</v>
       </c>
       <c r="I213" t="s">
-        <v>475</v>
+        <v>452</v>
       </c>
     </row>
     <row r="214" spans="1:9">
       <c r="A214" t="s">
-        <v>509</v>
+        <v>478</v>
       </c>
       <c r="B214" t="s">
-        <v>510</v>
+        <v>479</v>
       </c>
       <c r="C214" t="s">
-        <v>246</v>
+        <v>338</v>
       </c>
       <c r="E214" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F214">
         <v>1.0</v>
@@ -7568,50 +7514,50 @@
         <v>67</v>
       </c>
       <c r="I214" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="215" spans="1:9">
       <c r="A215" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="B215" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="C215" t="s">
-        <v>246</v>
+        <v>338</v>
       </c>
       <c r="E215" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F215">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G215" t="s">
-        <v>492</v>
+        <v>67</v>
       </c>
       <c r="H215" t="s">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="I215" t="s">
-        <v>427</v>
+        <v>469</v>
       </c>
     </row>
     <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="B216" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="C216" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="E216" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F216">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G216" t="s">
         <v>67</v>
@@ -7620,24 +7566,24 @@
         <v>67</v>
       </c>
       <c r="I216" t="s">
-        <v>174</v>
+        <v>258</v>
       </c>
     </row>
     <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B217" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C217" t="s">
-        <v>140</v>
+        <v>290</v>
       </c>
       <c r="E217" t="s">
-        <v>436</v>
+        <v>307</v>
       </c>
       <c r="F217">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G217" t="s">
         <v>67</v>
@@ -7646,24 +7592,24 @@
         <v>67</v>
       </c>
       <c r="I217" t="s">
-        <v>255</v>
+        <v>451</v>
       </c>
     </row>
     <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>490</v>
+        <v>375</v>
       </c>
       <c r="B218" t="s">
-        <v>491</v>
+        <v>376</v>
       </c>
       <c r="C218" t="s">
-        <v>158</v>
+        <v>390</v>
       </c>
       <c r="E218" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="F218">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G218" t="s">
         <v>67</v>
@@ -7672,73 +7618,73 @@
         <v>67</v>
       </c>
       <c r="I218" t="s">
-        <v>236</v>
+        <v>429</v>
       </c>
     </row>
     <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="B219" t="s">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="C219" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="E219" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F219">
         <v>1.0</v>
       </c>
       <c r="G219" t="s">
-        <v>450</v>
+        <v>67</v>
       </c>
       <c r="H219" t="s">
-        <v>450</v>
+        <v>67</v>
       </c>
       <c r="I219" t="s">
-        <v>255</v>
+        <v>469</v>
       </c>
     </row>
     <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="B220" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="C220" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="E220" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F220">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G220" t="s">
-        <v>325</v>
+        <v>67</v>
       </c>
       <c r="H220" t="s">
-        <v>450</v>
+        <v>67</v>
       </c>
       <c r="I220" t="s">
-        <v>75</v>
+        <v>430</v>
       </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221" t="s">
+        <v>499</v>
+      </c>
+      <c r="B221" t="s">
         <v>500</v>
       </c>
-      <c r="B221" t="s">
-        <v>501</v>
-      </c>
       <c r="C221" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="E221" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F221">
         <v>1.0</v>
@@ -7750,50 +7696,50 @@
         <v>67</v>
       </c>
       <c r="I221" t="s">
-        <v>489</v>
+        <v>419</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="B222" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="C222" t="s">
-        <v>246</v>
+        <v>300</v>
       </c>
       <c r="E222" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F222">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G222" t="s">
-        <v>405</v>
+        <v>67</v>
       </c>
       <c r="H222" t="s">
-        <v>450</v>
+        <v>67</v>
       </c>
       <c r="I222" t="s">
-        <v>502</v>
+        <v>419</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="A223" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="B223" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="C223" t="s">
-        <v>148</v>
+        <v>300</v>
       </c>
       <c r="E223" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="F223">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G223" t="s">
         <v>67</v>
@@ -7802,24 +7748,24 @@
         <v>67</v>
       </c>
       <c r="I223" t="s">
-        <v>236</v>
+        <v>419</v>
       </c>
     </row>
     <row r="224" spans="1:9">
       <c r="A224" t="s">
-        <v>507</v>
+        <v>442</v>
       </c>
       <c r="B224" t="s">
-        <v>508</v>
+        <v>443</v>
       </c>
       <c r="C224" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E224" t="s">
-        <v>223</v>
+        <v>415</v>
       </c>
       <c r="F224">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G224" t="s">
         <v>67</v>
@@ -7828,21 +7774,21 @@
         <v>67</v>
       </c>
       <c r="I224" t="s">
-        <v>341</v>
+        <v>244</v>
       </c>
     </row>
     <row r="225" spans="1:9">
       <c r="A225" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B225" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C225" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E225" t="s">
-        <v>223</v>
+        <v>505</v>
       </c>
       <c r="F225">
         <v>2.0</v>
@@ -7854,24 +7800,24 @@
         <v>67</v>
       </c>
       <c r="I225" t="s">
-        <v>475</v>
+        <v>236</v>
       </c>
     </row>
     <row r="226" spans="1:9">
       <c r="A226" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B226" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="C226" t="s">
-        <v>360</v>
+        <v>136</v>
       </c>
       <c r="E226" t="s">
-        <v>324</v>
+        <v>122</v>
       </c>
       <c r="F226">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G226" t="s">
         <v>67</v>
@@ -7880,21 +7826,21 @@
         <v>67</v>
       </c>
       <c r="I226" t="s">
-        <v>449</v>
+        <v>157</v>
       </c>
     </row>
     <row r="227" spans="1:9">
       <c r="A227" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="B227" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="C227" t="s">
-        <v>360</v>
+        <v>121</v>
       </c>
       <c r="E227" t="s">
-        <v>324</v>
+        <v>122</v>
       </c>
       <c r="F227">
         <v>1.0</v>
@@ -7906,24 +7852,24 @@
         <v>67</v>
       </c>
       <c r="I227" t="s">
-        <v>489</v>
+        <v>113</v>
       </c>
     </row>
     <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="B228" t="s">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="C228" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E228" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F228">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G228" t="s">
         <v>67</v>
@@ -7932,24 +7878,24 @@
         <v>67</v>
       </c>
       <c r="I228" t="s">
-        <v>274</v>
+        <v>508</v>
       </c>
     </row>
     <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B229" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C229" t="s">
-        <v>310</v>
+        <v>154</v>
       </c>
       <c r="E229" t="s">
-        <v>324</v>
+        <v>126</v>
       </c>
       <c r="F229">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G229" t="s">
         <v>67</v>
@@ -7958,24 +7904,24 @@
         <v>67</v>
       </c>
       <c r="I229" t="s">
-        <v>474</v>
+        <v>508</v>
       </c>
     </row>
     <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>394</v>
+        <v>464</v>
       </c>
       <c r="B230" t="s">
-        <v>395</v>
+        <v>465</v>
       </c>
       <c r="C230" t="s">
-        <v>268</v>
+        <v>154</v>
       </c>
       <c r="E230" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="F230">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G230" t="s">
         <v>67</v>
@@ -7984,7 +7930,7 @@
         <v>67</v>
       </c>
       <c r="I230" t="s">
-        <v>448</v>
+        <v>221</v>
       </c>
     </row>
     <row r="231" spans="1:9">
@@ -7995,13 +7941,13 @@
         <v>488</v>
       </c>
       <c r="C231" t="s">
-        <v>310</v>
+        <v>144</v>
       </c>
       <c r="E231" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="F231">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G231" t="s">
         <v>67</v>
@@ -8010,50 +7956,50 @@
         <v>67</v>
       </c>
       <c r="I231" t="s">
-        <v>489</v>
+        <v>452</v>
       </c>
     </row>
     <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>515</v>
+        <v>476</v>
       </c>
       <c r="B232" t="s">
-        <v>516</v>
+        <v>477</v>
       </c>
       <c r="C232" t="s">
-        <v>333</v>
+        <v>144</v>
       </c>
       <c r="E232" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="F232">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G232" t="s">
-        <v>519</v>
+        <v>67</v>
       </c>
       <c r="H232" t="s">
-        <v>519</v>
+        <v>67</v>
       </c>
       <c r="I232" t="s">
-        <v>489</v>
+        <v>452</v>
       </c>
     </row>
     <row r="233" spans="1:9">
       <c r="A233" t="s">
-        <v>511</v>
+        <v>284</v>
       </c>
       <c r="B233" t="s">
-        <v>512</v>
+        <v>285</v>
       </c>
       <c r="C233" t="s">
-        <v>360</v>
+        <v>121</v>
       </c>
       <c r="E233" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="F233">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G233" t="s">
         <v>67</v>
@@ -8062,24 +8008,24 @@
         <v>67</v>
       </c>
       <c r="I233" t="s">
-        <v>449</v>
+        <v>230</v>
       </c>
     </row>
     <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>520</v>
+        <v>470</v>
       </c>
       <c r="B234" t="s">
-        <v>521</v>
+        <v>471</v>
       </c>
       <c r="C234" t="s">
-        <v>310</v>
+        <v>144</v>
       </c>
       <c r="E234" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="F234">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G234" t="s">
         <v>67</v>
@@ -8088,24 +8034,24 @@
         <v>67</v>
       </c>
       <c r="I234" t="s">
-        <v>440</v>
+        <v>232</v>
       </c>
     </row>
     <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>522</v>
+        <v>442</v>
       </c>
       <c r="B235" t="s">
-        <v>523</v>
+        <v>443</v>
       </c>
       <c r="C235" t="s">
-        <v>246</v>
+        <v>121</v>
       </c>
       <c r="E235" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="F235">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G235" t="s">
         <v>67</v>
@@ -8114,21 +8060,21 @@
         <v>67</v>
       </c>
       <c r="I235" t="s">
-        <v>440</v>
+        <v>509</v>
       </c>
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>520</v>
+        <v>474</v>
       </c>
       <c r="B236" t="s">
-        <v>521</v>
+        <v>475</v>
       </c>
       <c r="C236" t="s">
-        <v>246</v>
+        <v>121</v>
       </c>
       <c r="E236" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="F236">
         <v>1.0</v>
@@ -8140,24 +8086,21 @@
         <v>67</v>
       </c>
       <c r="I236" t="s">
-        <v>440</v>
+        <v>169</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>464</v>
+        <v>510</v>
       </c>
       <c r="B237" t="s">
-        <v>465</v>
-      </c>
-      <c r="C237" t="s">
-        <v>140</v>
+        <v>511</v>
       </c>
       <c r="E237" t="s">
-        <v>436</v>
+        <v>512</v>
       </c>
       <c r="F237">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G237" t="s">
         <v>67</v>
@@ -8166,24 +8109,21 @@
         <v>67</v>
       </c>
       <c r="I237" t="s">
-        <v>482</v>
+        <v>304</v>
       </c>
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="B238" t="s">
-        <v>525</v>
-      </c>
-      <c r="C238" t="s">
-        <v>158</v>
+        <v>514</v>
       </c>
       <c r="E238" t="s">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="F238">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G238" t="s">
         <v>67</v>
@@ -8192,24 +8132,21 @@
         <v>67</v>
       </c>
       <c r="I238" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="B239" t="s">
-        <v>528</v>
-      </c>
-      <c r="C239" t="s">
-        <v>140</v>
+        <v>516</v>
       </c>
       <c r="E239" t="s">
-        <v>126</v>
+        <v>512</v>
       </c>
       <c r="F239">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G239" t="s">
         <v>67</v>
@@ -8218,21 +8155,18 @@
         <v>67</v>
       </c>
       <c r="I239" t="s">
-        <v>161</v>
+        <v>243</v>
       </c>
     </row>
     <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="B240" t="s">
-        <v>528</v>
-      </c>
-      <c r="C240" t="s">
-        <v>125</v>
+        <v>518</v>
       </c>
       <c r="E240" t="s">
-        <v>126</v>
+        <v>201</v>
       </c>
       <c r="F240">
         <v>1.0</v>
@@ -8244,21 +8178,21 @@
         <v>67</v>
       </c>
       <c r="I240" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>513</v>
+        <v>438</v>
       </c>
       <c r="B241" t="s">
-        <v>514</v>
+        <v>439</v>
       </c>
       <c r="C241" t="s">
-        <v>158</v>
+        <v>290</v>
       </c>
       <c r="E241" t="s">
-        <v>130</v>
+        <v>440</v>
       </c>
       <c r="F241">
         <v>3.0</v>
@@ -8270,24 +8204,24 @@
         <v>67</v>
       </c>
       <c r="I241" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>517</v>
+        <v>438</v>
       </c>
       <c r="B242" t="s">
-        <v>518</v>
+        <v>439</v>
       </c>
       <c r="C242" t="s">
-        <v>158</v>
+        <v>300</v>
       </c>
       <c r="E242" t="s">
-        <v>130</v>
+        <v>440</v>
       </c>
       <c r="F242">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="G242" t="s">
         <v>67</v>
@@ -8296,24 +8230,24 @@
         <v>67</v>
       </c>
       <c r="I242" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
     </row>
     <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>484</v>
+        <v>438</v>
       </c>
       <c r="B243" t="s">
-        <v>485</v>
+        <v>439</v>
       </c>
       <c r="C243" t="s">
-        <v>158</v>
+        <v>339</v>
       </c>
       <c r="E243" t="s">
-        <v>223</v>
+        <v>440</v>
       </c>
       <c r="F243">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G243" t="s">
         <v>67</v>
@@ -8322,24 +8256,24 @@
         <v>67</v>
       </c>
       <c r="I243" t="s">
-        <v>225</v>
+        <v>521</v>
       </c>
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="B244" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="C244" t="s">
-        <v>148</v>
+        <v>290</v>
       </c>
       <c r="E244" t="s">
-        <v>223</v>
+        <v>440</v>
       </c>
       <c r="F244">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G244" t="s">
         <v>67</v>
@@ -8348,24 +8282,24 @@
         <v>67</v>
       </c>
       <c r="I244" t="s">
-        <v>475</v>
+        <v>519</v>
       </c>
     </row>
     <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>496</v>
+        <v>522</v>
       </c>
       <c r="B245" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="C245" t="s">
-        <v>148</v>
+        <v>300</v>
       </c>
       <c r="E245" t="s">
-        <v>223</v>
+        <v>440</v>
       </c>
       <c r="F245">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G245" t="s">
         <v>67</v>
@@ -8374,24 +8308,24 @@
         <v>67</v>
       </c>
       <c r="I245" t="s">
-        <v>475</v>
+        <v>519</v>
       </c>
     </row>
     <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>304</v>
+        <v>522</v>
       </c>
       <c r="B246" t="s">
-        <v>305</v>
+        <v>523</v>
       </c>
       <c r="C246" t="s">
-        <v>125</v>
+        <v>338</v>
       </c>
       <c r="E246" t="s">
-        <v>223</v>
+        <v>440</v>
       </c>
       <c r="F246">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G246" t="s">
         <v>67</v>
@@ -8400,24 +8334,24 @@
         <v>67</v>
       </c>
       <c r="I246" t="s">
-        <v>234</v>
+        <v>519</v>
       </c>
     </row>
     <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>490</v>
+        <v>524</v>
       </c>
       <c r="B247" t="s">
-        <v>491</v>
+        <v>523</v>
       </c>
       <c r="C247" t="s">
-        <v>148</v>
+        <v>390</v>
       </c>
       <c r="E247" t="s">
-        <v>223</v>
+        <v>440</v>
       </c>
       <c r="F247">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G247" t="s">
         <v>67</v>
@@ -8426,24 +8360,24 @@
         <v>67</v>
       </c>
       <c r="I247" t="s">
-        <v>236</v>
+        <v>525</v>
       </c>
     </row>
     <row r="248" spans="1:9">
       <c r="A248" t="s">
-        <v>464</v>
+        <v>526</v>
       </c>
       <c r="B248" t="s">
-        <v>465</v>
+        <v>527</v>
       </c>
       <c r="C248" t="s">
-        <v>125</v>
+        <v>290</v>
       </c>
       <c r="E248" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F248">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G248" t="s">
         <v>67</v>
@@ -8452,24 +8386,24 @@
         <v>67</v>
       </c>
       <c r="I248" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="B249" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="C249" t="s">
-        <v>125</v>
+        <v>300</v>
       </c>
       <c r="E249" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F249">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G249" t="s">
         <v>67</v>
@@ -8478,21 +8412,24 @@
         <v>67</v>
       </c>
       <c r="I249" t="s">
-        <v>173</v>
+        <v>529</v>
       </c>
     </row>
     <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B250" t="s">
-        <v>532</v>
+        <v>527</v>
+      </c>
+      <c r="C250" t="s">
+        <v>338</v>
       </c>
       <c r="E250" t="s">
-        <v>533</v>
+        <v>440</v>
       </c>
       <c r="F250">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G250" t="s">
         <v>67</v>
@@ -8501,21 +8438,24 @@
         <v>67</v>
       </c>
       <c r="I250" t="s">
-        <v>321</v>
+        <v>530</v>
       </c>
     </row>
     <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="B251" t="s">
-        <v>535</v>
+        <v>527</v>
+      </c>
+      <c r="C251" t="s">
+        <v>390</v>
       </c>
       <c r="E251" t="s">
-        <v>533</v>
+        <v>440</v>
       </c>
       <c r="F251">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G251" t="s">
         <v>67</v>
@@ -8524,21 +8464,24 @@
         <v>67</v>
       </c>
       <c r="I251" t="s">
-        <v>321</v>
+        <v>530</v>
       </c>
     </row>
     <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B252" t="s">
-        <v>537</v>
+        <v>532</v>
+      </c>
+      <c r="C252" t="s">
+        <v>390</v>
       </c>
       <c r="E252" t="s">
-        <v>533</v>
+        <v>440</v>
       </c>
       <c r="F252">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G252" t="s">
         <v>67</v>
@@ -8547,18 +8490,21 @@
         <v>67</v>
       </c>
       <c r="I252" t="s">
-        <v>260</v>
+        <v>469</v>
       </c>
     </row>
     <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B253" t="s">
-        <v>539</v>
+        <v>534</v>
+      </c>
+      <c r="C253" t="s">
+        <v>339</v>
       </c>
       <c r="E253" t="s">
-        <v>205</v>
+        <v>440</v>
       </c>
       <c r="F253">
         <v>1.0</v>
@@ -8570,24 +8516,24 @@
         <v>67</v>
       </c>
       <c r="I253" t="s">
-        <v>108</v>
+        <v>535</v>
       </c>
     </row>
     <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>460</v>
+        <v>533</v>
       </c>
       <c r="B254" t="s">
-        <v>461</v>
+        <v>534</v>
       </c>
       <c r="C254" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="E254" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="F254">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G254" t="s">
         <v>67</v>
@@ -8596,24 +8542,24 @@
         <v>67</v>
       </c>
       <c r="I254" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
     <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>460</v>
+        <v>533</v>
       </c>
       <c r="B255" t="s">
-        <v>461</v>
+        <v>534</v>
       </c>
       <c r="C255" t="s">
-        <v>246</v>
+        <v>390</v>
       </c>
       <c r="E255" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="F255">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G255" t="s">
         <v>67</v>
@@ -8622,24 +8568,24 @@
         <v>67</v>
       </c>
       <c r="I255" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
     </row>
     <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>460</v>
+        <v>537</v>
       </c>
       <c r="B256" t="s">
-        <v>461</v>
+        <v>538</v>
       </c>
       <c r="C256" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="E256" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="F256">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G256" t="s">
         <v>67</v>
@@ -8648,24 +8594,24 @@
         <v>67</v>
       </c>
       <c r="I256" t="s">
-        <v>542</v>
+        <v>75</v>
       </c>
     </row>
     <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B257" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C257" t="s">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="E257" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="F257">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G257" t="s">
         <v>67</v>
@@ -8674,24 +8620,24 @@
         <v>67</v>
       </c>
       <c r="I257" t="s">
-        <v>540</v>
+        <v>469</v>
       </c>
     </row>
     <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B258" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C258" t="s">
-        <v>246</v>
+        <v>390</v>
       </c>
       <c r="E258" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="F258">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G258" t="s">
         <v>67</v>
@@ -8700,24 +8646,24 @@
         <v>67</v>
       </c>
       <c r="I258" t="s">
-        <v>540</v>
+        <v>469</v>
       </c>
     </row>
     <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B259" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C259" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="E259" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="F259">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G259" t="s">
         <v>67</v>
@@ -8726,21 +8672,21 @@
         <v>67</v>
       </c>
       <c r="I259" t="s">
-        <v>540</v>
+        <v>429</v>
       </c>
     </row>
     <row r="260" spans="1:9">
       <c r="A260" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B260" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C260" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="E260" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="F260">
         <v>2.0</v>
@@ -8752,24 +8698,24 @@
         <v>67</v>
       </c>
       <c r="I260" t="s">
-        <v>546</v>
+        <v>429</v>
       </c>
     </row>
     <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="B261" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="C261" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="E261" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="F261">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G261" t="s">
         <v>67</v>
@@ -8778,24 +8724,24 @@
         <v>67</v>
       </c>
       <c r="I261" t="s">
-        <v>549</v>
+        <v>406</v>
       </c>
     </row>
     <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>547</v>
+        <v>489</v>
       </c>
       <c r="B262" t="s">
-        <v>548</v>
+        <v>490</v>
       </c>
       <c r="C262" t="s">
-        <v>246</v>
+        <v>339</v>
       </c>
       <c r="E262" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="F262">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G262" t="s">
         <v>67</v>
@@ -8804,24 +8750,24 @@
         <v>67</v>
       </c>
       <c r="I262" t="s">
-        <v>550</v>
+        <v>401</v>
       </c>
     </row>
     <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>547</v>
+        <v>484</v>
       </c>
       <c r="B263" t="s">
-        <v>548</v>
+        <v>485</v>
       </c>
       <c r="C263" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="E263" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="F263">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G263" t="s">
         <v>67</v>
@@ -8830,21 +8776,21 @@
         <v>67</v>
       </c>
       <c r="I263" t="s">
-        <v>551</v>
+        <v>486</v>
       </c>
     </row>
     <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>547</v>
+        <v>484</v>
       </c>
       <c r="B264" t="s">
-        <v>548</v>
+        <v>485</v>
       </c>
       <c r="C264" t="s">
-        <v>268</v>
+        <v>338</v>
       </c>
       <c r="E264" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="F264">
         <v>3.0</v>
@@ -8856,24 +8802,24 @@
         <v>67</v>
       </c>
       <c r="I264" t="s">
-        <v>551</v>
+        <v>466</v>
       </c>
     </row>
     <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>552</v>
+        <v>484</v>
       </c>
       <c r="B265" t="s">
-        <v>553</v>
+        <v>485</v>
       </c>
       <c r="C265" t="s">
-        <v>268</v>
+        <v>390</v>
       </c>
       <c r="E265" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="F265">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G265" t="s">
         <v>67</v>
@@ -8882,21 +8828,21 @@
         <v>67</v>
       </c>
       <c r="I265" t="s">
-        <v>489</v>
+        <v>449</v>
       </c>
     </row>
     <row r="266" spans="1:9">
       <c r="A266" t="s">
-        <v>554</v>
+        <v>478</v>
       </c>
       <c r="B266" t="s">
-        <v>555</v>
+        <v>479</v>
       </c>
       <c r="C266" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="E266" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="F266">
         <v>1.0</v>
@@ -8908,24 +8854,24 @@
         <v>67</v>
       </c>
       <c r="I266" t="s">
-        <v>556</v>
+        <v>430</v>
       </c>
     </row>
     <row r="267" spans="1:9">
       <c r="A267" t="s">
-        <v>554</v>
+        <v>495</v>
       </c>
       <c r="B267" t="s">
-        <v>555</v>
+        <v>496</v>
       </c>
       <c r="C267" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="E267" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="F267">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G267" t="s">
         <v>67</v>
@@ -8934,21 +8880,21 @@
         <v>67</v>
       </c>
       <c r="I267" t="s">
-        <v>557</v>
+        <v>469</v>
       </c>
     </row>
     <row r="268" spans="1:9">
       <c r="A268" t="s">
-        <v>554</v>
+        <v>491</v>
       </c>
       <c r="B268" t="s">
-        <v>555</v>
+        <v>492</v>
       </c>
       <c r="C268" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="E268" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="F268">
         <v>1.0</v>
@@ -8960,24 +8906,24 @@
         <v>67</v>
       </c>
       <c r="I268" t="s">
-        <v>556</v>
+        <v>430</v>
       </c>
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>558</v>
+        <v>491</v>
       </c>
       <c r="B269" t="s">
-        <v>559</v>
+        <v>492</v>
       </c>
       <c r="C269" t="s">
-        <v>246</v>
+        <v>339</v>
       </c>
       <c r="E269" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="F269">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G269" t="s">
         <v>67</v>
@@ -8986,21 +8932,21 @@
         <v>67</v>
       </c>
       <c r="I269" t="s">
-        <v>502</v>
+        <v>430</v>
       </c>
     </row>
     <row r="270" spans="1:9">
       <c r="A270" t="s">
-        <v>558</v>
+        <v>480</v>
       </c>
       <c r="B270" t="s">
-        <v>559</v>
+        <v>481</v>
       </c>
       <c r="C270" t="s">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="E270" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="F270">
         <v>1.0</v>
@@ -9012,21 +8958,21 @@
         <v>67</v>
       </c>
       <c r="I270" t="s">
-        <v>489</v>
+        <v>469</v>
       </c>
     </row>
     <row r="271" spans="1:9">
       <c r="A271" t="s">
-        <v>558</v>
+        <v>501</v>
       </c>
       <c r="B271" t="s">
-        <v>559</v>
+        <v>502</v>
       </c>
       <c r="C271" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="E271" t="s">
-        <v>462</v>
+        <v>307</v>
       </c>
       <c r="F271">
         <v>1.0</v>
@@ -9038,24 +8984,24 @@
         <v>67</v>
       </c>
       <c r="I271" t="s">
-        <v>489</v>
+        <v>419</v>
       </c>
     </row>
     <row r="272" spans="1:9">
       <c r="A272" t="s">
-        <v>560</v>
+        <v>501</v>
       </c>
       <c r="B272" t="s">
-        <v>561</v>
+        <v>502</v>
       </c>
       <c r="C272" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="E272" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F272">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G272" t="s">
         <v>67</v>
@@ -9064,21 +9010,21 @@
         <v>67</v>
       </c>
       <c r="I272" t="s">
-        <v>448</v>
+        <v>419</v>
       </c>
     </row>
     <row r="273" spans="1:9">
       <c r="A273" t="s">
-        <v>560</v>
+        <v>541</v>
       </c>
       <c r="B273" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
       <c r="C273" t="s">
-        <v>246</v>
+        <v>300</v>
       </c>
       <c r="E273" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F273">
         <v>2.0</v>
@@ -9090,24 +9036,24 @@
         <v>67</v>
       </c>
       <c r="I273" t="s">
-        <v>448</v>
+        <v>401</v>
       </c>
     </row>
     <row r="274" spans="1:9">
       <c r="A274" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="B274" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="C274" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="E274" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F274">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G274" t="s">
         <v>67</v>
@@ -9116,24 +9062,24 @@
         <v>67</v>
       </c>
       <c r="I274" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="275" spans="1:9">
       <c r="A275" t="s">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="B275" t="s">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="C275" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="E275" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F275">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G275" t="s">
         <v>67</v>
@@ -9142,24 +9088,24 @@
         <v>67</v>
       </c>
       <c r="I275" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
     </row>
     <row r="276" spans="1:9">
       <c r="A276" t="s">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="B276" t="s">
-        <v>505</v>
+        <v>544</v>
       </c>
       <c r="C276" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E276" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F276">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G276" t="s">
         <v>67</v>
@@ -9168,24 +9114,24 @@
         <v>67</v>
       </c>
       <c r="I276" t="s">
-        <v>506</v>
+        <v>429</v>
       </c>
     </row>
     <row r="277" spans="1:9">
       <c r="A277" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B277" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C277" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="E277" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F277">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G277" t="s">
         <v>67</v>
@@ -9194,24 +9140,24 @@
         <v>67</v>
       </c>
       <c r="I277" t="s">
-        <v>486</v>
+        <v>419</v>
       </c>
     </row>
     <row r="278" spans="1:9">
       <c r="A278" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B278" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C278" t="s">
-        <v>268</v>
+        <v>338</v>
       </c>
       <c r="E278" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F278">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G278" t="s">
         <v>67</v>
@@ -9220,21 +9166,21 @@
         <v>67</v>
       </c>
       <c r="I278" t="s">
-        <v>471</v>
+        <v>419</v>
       </c>
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
-        <v>498</v>
+        <v>545</v>
       </c>
       <c r="B279" t="s">
-        <v>499</v>
+        <v>546</v>
       </c>
       <c r="C279" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="E279" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F279">
         <v>1.0</v>
@@ -9246,21 +9192,21 @@
         <v>67</v>
       </c>
       <c r="I279" t="s">
-        <v>449</v>
+        <v>419</v>
       </c>
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
       <c r="B280" t="s">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="C280" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E280" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F280">
         <v>1.0</v>
@@ -9272,21 +9218,21 @@
         <v>67</v>
       </c>
       <c r="I280" t="s">
-        <v>489</v>
+        <v>419</v>
       </c>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
-        <v>511</v>
+        <v>545</v>
       </c>
       <c r="B281" t="s">
-        <v>512</v>
+        <v>546</v>
       </c>
       <c r="C281" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="E281" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F281">
         <v>1.0</v>
@@ -9298,24 +9244,24 @@
         <v>67</v>
       </c>
       <c r="I281" t="s">
-        <v>449</v>
+        <v>419</v>
       </c>
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
-        <v>511</v>
+        <v>547</v>
       </c>
       <c r="B282" t="s">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="C282" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="E282" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F282">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G282" t="s">
         <v>67</v>
@@ -9324,24 +9270,24 @@
         <v>67</v>
       </c>
       <c r="I282" t="s">
-        <v>449</v>
+        <v>369</v>
       </c>
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>500</v>
+        <v>547</v>
       </c>
       <c r="B283" t="s">
-        <v>501</v>
+        <v>548</v>
       </c>
       <c r="C283" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="E283" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F283">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G283" t="s">
         <v>67</v>
@@ -9350,24 +9296,24 @@
         <v>67</v>
       </c>
       <c r="I283" t="s">
-        <v>489</v>
+        <v>451</v>
       </c>
     </row>
     <row r="284" spans="1:9">
       <c r="A284" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="B284" t="s">
-        <v>523</v>
+        <v>548</v>
       </c>
       <c r="C284" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="E284" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F284">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G284" t="s">
         <v>67</v>
@@ -9376,24 +9322,24 @@
         <v>67</v>
       </c>
       <c r="I284" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="B285" t="s">
-        <v>523</v>
+        <v>548</v>
       </c>
       <c r="C285" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="E285" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F285">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G285" t="s">
         <v>67</v>
@@ -9402,24 +9348,24 @@
         <v>67</v>
       </c>
       <c r="I285" t="s">
-        <v>421</v>
+        <v>486</v>
       </c>
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="B286" t="s">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="C286" t="s">
-        <v>246</v>
+        <v>390</v>
       </c>
       <c r="E286" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F286">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G286" t="s">
         <v>67</v>
@@ -9428,24 +9374,24 @@
         <v>67</v>
       </c>
       <c r="I286" t="s">
-        <v>421</v>
+        <v>369</v>
       </c>
     </row>
     <row r="287" spans="1:9">
       <c r="A287" t="s">
-        <v>562</v>
+        <v>506</v>
       </c>
       <c r="B287" t="s">
-        <v>563</v>
+        <v>507</v>
       </c>
       <c r="C287" t="s">
-        <v>333</v>
+        <v>154</v>
       </c>
       <c r="E287" t="s">
-        <v>324</v>
+        <v>122</v>
       </c>
       <c r="F287">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G287" t="s">
         <v>67</v>
@@ -9454,21 +9400,21 @@
         <v>67</v>
       </c>
       <c r="I287" t="s">
-        <v>440</v>
+        <v>162</v>
       </c>
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="B288" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="C288" t="s">
-        <v>310</v>
+        <v>121</v>
       </c>
       <c r="E288" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="F288">
         <v>1.0</v>
@@ -9480,24 +9426,24 @@
         <v>67</v>
       </c>
       <c r="I288" t="s">
-        <v>449</v>
+        <v>221</v>
       </c>
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="B289" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="C289" t="s">
-        <v>246</v>
+        <v>338</v>
       </c>
       <c r="E289" t="s">
-        <v>324</v>
+        <v>440</v>
       </c>
       <c r="F289">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G289" t="s">
         <v>67</v>
@@ -9506,24 +9452,24 @@
         <v>67</v>
       </c>
       <c r="I289" t="s">
-        <v>427</v>
+        <v>528</v>
       </c>
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="B290" t="s">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="C290" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="E290" t="s">
-        <v>324</v>
+        <v>440</v>
       </c>
       <c r="F290">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G290" t="s">
         <v>67</v>
@@ -9532,24 +9478,24 @@
         <v>67</v>
       </c>
       <c r="I290" t="s">
-        <v>448</v>
+        <v>528</v>
       </c>
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
-        <v>520</v>
+        <v>438</v>
       </c>
       <c r="B291" t="s">
-        <v>521</v>
+        <v>439</v>
       </c>
       <c r="C291" t="s">
-        <v>333</v>
+        <v>390</v>
       </c>
       <c r="E291" t="s">
-        <v>324</v>
+        <v>440</v>
       </c>
       <c r="F291">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G291" t="s">
         <v>67</v>
@@ -9558,371 +9504,7 @@
         <v>67</v>
       </c>
       <c r="I291" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9">
-      <c r="A292" t="s">
-        <v>520</v>
-      </c>
-      <c r="B292" t="s">
-        <v>521</v>
-      </c>
-      <c r="C292" t="s">
-        <v>360</v>
-      </c>
-      <c r="E292" t="s">
-        <v>324</v>
-      </c>
-      <c r="F292">
-        <v>1.0</v>
-      </c>
-      <c r="G292" t="s">
-        <v>67</v>
-      </c>
-      <c r="H292" t="s">
-        <v>67</v>
-      </c>
-      <c r="I292" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="293" spans="1:9">
-      <c r="A293" t="s">
-        <v>566</v>
-      </c>
-      <c r="B293" t="s">
-        <v>567</v>
-      </c>
-      <c r="C293" t="s">
-        <v>310</v>
-      </c>
-      <c r="E293" t="s">
-        <v>324</v>
-      </c>
-      <c r="F293">
-        <v>1.0</v>
-      </c>
-      <c r="G293" t="s">
-        <v>67</v>
-      </c>
-      <c r="H293" t="s">
-        <v>67</v>
-      </c>
-      <c r="I293" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="294" spans="1:9">
-      <c r="A294" t="s">
-        <v>566</v>
-      </c>
-      <c r="B294" t="s">
-        <v>567</v>
-      </c>
-      <c r="C294" t="s">
-        <v>246</v>
-      </c>
-      <c r="E294" t="s">
-        <v>324</v>
-      </c>
-      <c r="F294">
-        <v>1.0</v>
-      </c>
-      <c r="G294" t="s">
-        <v>67</v>
-      </c>
-      <c r="H294" t="s">
-        <v>67</v>
-      </c>
-      <c r="I294" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="295" spans="1:9">
-      <c r="A295" t="s">
-        <v>566</v>
-      </c>
-      <c r="B295" t="s">
-        <v>567</v>
-      </c>
-      <c r="C295" t="s">
-        <v>333</v>
-      </c>
-      <c r="E295" t="s">
-        <v>324</v>
-      </c>
-      <c r="F295">
-        <v>1.0</v>
-      </c>
-      <c r="G295" t="s">
-        <v>67</v>
-      </c>
-      <c r="H295" t="s">
-        <v>67</v>
-      </c>
-      <c r="I295" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9">
-      <c r="A296" t="s">
-        <v>568</v>
-      </c>
-      <c r="B296" t="s">
-        <v>569</v>
-      </c>
-      <c r="C296" t="s">
-        <v>310</v>
-      </c>
-      <c r="E296" t="s">
-        <v>324</v>
-      </c>
-      <c r="F296">
-        <v>4.0</v>
-      </c>
-      <c r="G296" t="s">
-        <v>67</v>
-      </c>
-      <c r="H296" t="s">
-        <v>67</v>
-      </c>
-      <c r="I296" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9">
-      <c r="A297" t="s">
-        <v>568</v>
-      </c>
-      <c r="B297" t="s">
-        <v>569</v>
-      </c>
-      <c r="C297" t="s">
-        <v>246</v>
-      </c>
-      <c r="E297" t="s">
-        <v>324</v>
-      </c>
-      <c r="F297">
-        <v>6.0</v>
-      </c>
-      <c r="G297" t="s">
-        <v>67</v>
-      </c>
-      <c r="H297" t="s">
-        <v>67</v>
-      </c>
-      <c r="I297" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9">
-      <c r="A298" t="s">
-        <v>568</v>
-      </c>
-      <c r="B298" t="s">
-        <v>569</v>
-      </c>
-      <c r="C298" t="s">
-        <v>333</v>
-      </c>
-      <c r="E298" t="s">
-        <v>324</v>
-      </c>
-      <c r="F298">
-        <v>6.0</v>
-      </c>
-      <c r="G298" t="s">
-        <v>67</v>
-      </c>
-      <c r="H298" t="s">
-        <v>67</v>
-      </c>
-      <c r="I298" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9">
-      <c r="A299" t="s">
-        <v>568</v>
-      </c>
-      <c r="B299" t="s">
-        <v>569</v>
-      </c>
-      <c r="C299" t="s">
-        <v>360</v>
-      </c>
-      <c r="E299" t="s">
-        <v>324</v>
-      </c>
-      <c r="F299">
-        <v>5.0</v>
-      </c>
-      <c r="G299" t="s">
-        <v>67</v>
-      </c>
-      <c r="H299" t="s">
-        <v>67</v>
-      </c>
-      <c r="I299" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9">
-      <c r="A300" t="s">
-        <v>568</v>
-      </c>
-      <c r="B300" t="s">
-        <v>569</v>
-      </c>
-      <c r="C300" t="s">
-        <v>268</v>
-      </c>
-      <c r="E300" t="s">
-        <v>324</v>
-      </c>
-      <c r="F300">
-        <v>4.0</v>
-      </c>
-      <c r="G300" t="s">
-        <v>67</v>
-      </c>
-      <c r="H300" t="s">
-        <v>67</v>
-      </c>
-      <c r="I300" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="301" spans="1:9">
-      <c r="A301" t="s">
-        <v>527</v>
-      </c>
-      <c r="B301" t="s">
-        <v>528</v>
-      </c>
-      <c r="C301" t="s">
-        <v>158</v>
-      </c>
-      <c r="E301" t="s">
-        <v>126</v>
-      </c>
-      <c r="F301">
-        <v>2.0</v>
-      </c>
-      <c r="G301" t="s">
-        <v>67</v>
-      </c>
-      <c r="H301" t="s">
-        <v>67</v>
-      </c>
-      <c r="I301" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="302" spans="1:9">
-      <c r="A302" t="s">
-        <v>570</v>
-      </c>
-      <c r="B302" t="s">
-        <v>571</v>
-      </c>
-      <c r="C302" t="s">
-        <v>125</v>
-      </c>
-      <c r="E302" t="s">
-        <v>223</v>
-      </c>
-      <c r="F302">
-        <v>1.0</v>
-      </c>
-      <c r="G302" t="s">
-        <v>67</v>
-      </c>
-      <c r="H302" t="s">
-        <v>67</v>
-      </c>
-      <c r="I302" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9">
-      <c r="A303" t="s">
-        <v>572</v>
-      </c>
-      <c r="B303" t="s">
-        <v>573</v>
-      </c>
-      <c r="C303" t="s">
-        <v>360</v>
-      </c>
-      <c r="E303" t="s">
-        <v>462</v>
-      </c>
-      <c r="F303">
-        <v>1.0</v>
-      </c>
-      <c r="G303" t="s">
-        <v>67</v>
-      </c>
-      <c r="H303" t="s">
-        <v>67</v>
-      </c>
-      <c r="I303" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="304" spans="1:9">
-      <c r="A304" t="s">
-        <v>572</v>
-      </c>
-      <c r="B304" t="s">
-        <v>573</v>
-      </c>
-      <c r="C304" t="s">
-        <v>246</v>
-      </c>
-      <c r="E304" t="s">
-        <v>462</v>
-      </c>
-      <c r="F304">
-        <v>1.0</v>
-      </c>
-      <c r="G304" t="s">
-        <v>67</v>
-      </c>
-      <c r="H304" t="s">
-        <v>67</v>
-      </c>
-      <c r="I304" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="305" spans="1:9">
-      <c r="A305" t="s">
-        <v>460</v>
-      </c>
-      <c r="B305" t="s">
-        <v>461</v>
-      </c>
-      <c r="C305" t="s">
-        <v>268</v>
-      </c>
-      <c r="E305" t="s">
-        <v>462</v>
-      </c>
-      <c r="F305">
-        <v>2.0</v>
-      </c>
-      <c r="G305" t="s">
-        <v>67</v>
-      </c>
-      <c r="H305" t="s">
-        <v>67</v>
-      </c>
-      <c r="I305" t="s">
-        <v>546</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
